--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="618">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1421,6 +1421,18 @@
     <t>BEBEDOURO INDUSTRIAL</t>
   </si>
   <si>
+    <t>E.02.0211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILME DE POLIETILENO  ADESIVADO SEM COLA REMOVIVEL  PROTEÇÃO DE CAIXILHO  PROCAIXILHO 200MM/100M =20M² PROMAFLEX</t>
+  </si>
+  <si>
+    <t>00000000006868</t>
+  </si>
+  <si>
+    <t>PROMAFLEX FILME PVC</t>
+  </si>
+  <si>
     <t>E.02.0015</t>
   </si>
   <si>
@@ -1575,12 +1587,6 @@
   </si>
   <si>
     <t>LIXEIRA DE PLÁSTICO 20 LTS</t>
-  </si>
-  <si>
-    <t>E.02.0211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILME DE POLIETILENO  ADESIVADO SEM COLA REMOVIVEL  PROTEÇÃO DE CAIXILHO  PROCAIXILHO 200MM/100M =20M² PROMAFLEX</t>
   </si>
   <si>
     <t>E.02.0106</t>
@@ -12381,37 +12387,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F205" s="2">
-        <v>82311</v>
+        <v>82385</v>
       </c>
       <c r="G205" s="3">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="H205" s="1" t="s">
-        <v>262</v>
+        <v>469</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>263</v>
+        <v>470</v>
       </c>
       <c r="J205" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L205" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M205" s="4">
-        <v>23.43</v>
+        <v>100</v>
       </c>
       <c r="N205" s="4">
-        <v>234.3</v>
+        <v>200</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>62</v>
+        <v>471</v>
       </c>
       <c r="P205" s="1" t="s">
-        <v>63</v>
+        <v>472</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="206">
@@ -12431,37 +12437,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F206" s="2">
-        <v>82313</v>
+        <v>82311</v>
       </c>
       <c r="G206" s="3">
         <v>46078</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>218</v>
+        <v>262</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K206" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L206" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M206" s="4">
-        <v>158</v>
+        <v>23.43</v>
       </c>
       <c r="N206" s="4">
-        <v>158</v>
+        <v>234.3</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="P206" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="207">
@@ -12487,25 +12493,25 @@
         <v>46078</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>469</v>
+        <v>218</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>470</v>
+        <v>219</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K207" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L207" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M207" s="4">
-        <v>8.5</v>
+        <v>158</v>
       </c>
       <c r="N207" s="4">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="O207" s="1" t="s">
         <v>49</v>
@@ -12537,25 +12543,25 @@
         <v>46078</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>170</v>
+        <v>473</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>171</v>
+        <v>474</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L208" s="4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M208" s="4">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="N208" s="4">
-        <v>52.5</v>
+        <v>17</v>
       </c>
       <c r="O208" s="1" t="s">
         <v>49</v>
@@ -12581,37 +12587,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F209" s="2">
-        <v>82361</v>
+        <v>82313</v>
       </c>
       <c r="G209" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>471</v>
+        <v>170</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>472</v>
+        <v>171</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L209" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M209" s="4">
-        <v>54.68</v>
+        <v>3.5</v>
       </c>
       <c r="N209" s="4">
-        <v>54.68</v>
+        <v>52.5</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>453</v>
+        <v>49</v>
       </c>
       <c r="P209" s="1" t="s">
-        <v>454</v>
+        <v>50</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="210">
@@ -12631,16 +12637,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F210" s="2">
-        <v>82313</v>
+        <v>82361</v>
       </c>
       <c r="G210" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>20</v>
@@ -12649,19 +12655,19 @@
         <v>28</v>
       </c>
       <c r="L210" s="4">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="M210" s="4">
-        <v>1.5</v>
+        <v>54.68</v>
       </c>
       <c r="N210" s="4">
-        <v>112.5</v>
+        <v>54.68</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>49</v>
+        <v>453</v>
       </c>
       <c r="P210" s="1" t="s">
-        <v>50</v>
+        <v>454</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="211">
@@ -12681,16 +12687,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F211" s="2">
-        <v>82361</v>
+        <v>82313</v>
       </c>
       <c r="G211" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>20</v>
@@ -12699,19 +12705,19 @@
         <v>28</v>
       </c>
       <c r="L211" s="4">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="M211" s="4">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="N211" s="4">
-        <v>18.45</v>
+        <v>112.5</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>453</v>
+        <v>49</v>
       </c>
       <c r="P211" s="1" t="s">
-        <v>454</v>
+        <v>50</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="212">
@@ -12737,10 +12743,10 @@
         <v>46080</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>298</v>
+        <v>479</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>299</v>
+        <v>480</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>20</v>
@@ -12749,13 +12755,13 @@
         <v>28</v>
       </c>
       <c r="L212" s="4">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M212" s="4">
-        <v>31.46</v>
+        <v>1.23</v>
       </c>
       <c r="N212" s="4">
-        <v>94.38</v>
+        <v>18.45</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>453</v>
@@ -12781,16 +12787,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F213" s="2">
-        <v>82313</v>
+        <v>82361</v>
       </c>
       <c r="G213" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>477</v>
+        <v>298</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>478</v>
+        <v>299</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>20</v>
@@ -12799,19 +12805,19 @@
         <v>28</v>
       </c>
       <c r="L213" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M213" s="4">
-        <v>92.5</v>
+        <v>31.46</v>
       </c>
       <c r="N213" s="4">
-        <v>555</v>
+        <v>94.38</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>49</v>
+        <v>453</v>
       </c>
       <c r="P213" s="1" t="s">
-        <v>50</v>
+        <v>454</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="214">
@@ -12831,16 +12837,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F214" s="2">
-        <v>82311</v>
+        <v>82313</v>
       </c>
       <c r="G214" s="3">
         <v>46078</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>20</v>
@@ -12849,19 +12855,19 @@
         <v>28</v>
       </c>
       <c r="L214" s="4">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M214" s="4">
-        <v>11.39</v>
+        <v>92.5</v>
       </c>
       <c r="N214" s="4">
-        <v>170.85</v>
+        <v>555</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="P214" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="215">
@@ -12881,16 +12887,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F215" s="2">
-        <v>82313</v>
+        <v>82311</v>
       </c>
       <c r="G215" s="3">
         <v>46078</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>20</v>
@@ -12899,19 +12905,19 @@
         <v>28</v>
       </c>
       <c r="L215" s="4">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M215" s="4">
-        <v>165</v>
+        <v>11.39</v>
       </c>
       <c r="N215" s="4">
-        <v>495</v>
+        <v>170.85</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="216">
@@ -12937,25 +12943,25 @@
         <v>46078</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L216" s="4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M216" s="4">
-        <v>11.5</v>
+        <v>165</v>
       </c>
       <c r="N216" s="4">
-        <v>172.5</v>
+        <v>495</v>
       </c>
       <c r="O216" s="1" t="s">
         <v>49</v>
@@ -12981,37 +12987,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F217" s="2">
-        <v>82361</v>
+        <v>82313</v>
       </c>
       <c r="G217" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L217" s="4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M217" s="4">
-        <v>170.09</v>
+        <v>11.5</v>
       </c>
       <c r="N217" s="4">
-        <v>340.18</v>
+        <v>172.5</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>453</v>
+        <v>49</v>
       </c>
       <c r="P217" s="1" t="s">
-        <v>454</v>
+        <v>50</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="218">
@@ -13031,37 +13037,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F218" s="2">
-        <v>82314</v>
+        <v>82361</v>
       </c>
       <c r="G218" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K218" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L218" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="M218" s="4">
-        <v>8</v>
+        <v>170.09</v>
       </c>
       <c r="N218" s="4">
-        <v>800</v>
+        <v>340.18</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="P218" s="1" t="s">
-        <v>490</v>
+        <v>454</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="219">
@@ -13096,22 +13102,22 @@
         <v>20</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="L219" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M219" s="4">
-        <v>3.65</v>
+        <v>8</v>
       </c>
       <c r="N219" s="4">
-        <v>73</v>
+        <v>800</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="P219" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="220">
@@ -13137,31 +13143,31 @@
         <v>46078</v>
       </c>
       <c r="H220" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K220" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L220" s="4">
+        <v>20</v>
+      </c>
+      <c r="M220" s="4">
+        <v>3.65</v>
+      </c>
+      <c r="N220" s="4">
+        <v>73</v>
+      </c>
+      <c r="O220" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="I220" s="1" t="s">
+      <c r="P220" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="J220" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K220" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L220" s="4">
-        <v>20</v>
-      </c>
-      <c r="M220" s="4">
-        <v>4.05</v>
-      </c>
-      <c r="N220" s="4">
-        <v>81</v>
-      </c>
-      <c r="O220" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="P220" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="221">
@@ -13187,10 +13193,10 @@
         <v>46078</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>20</v>
@@ -13202,16 +13208,16 @@
         <v>20</v>
       </c>
       <c r="M221" s="4">
-        <v>4.8</v>
+        <v>4.05</v>
       </c>
       <c r="N221" s="4">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="P221" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="222">
@@ -13237,10 +13243,10 @@
         <v>46078</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>20</v>
@@ -13252,16 +13258,16 @@
         <v>20</v>
       </c>
       <c r="M222" s="4">
-        <v>4.54</v>
+        <v>4.8</v>
       </c>
       <c r="N222" s="4">
-        <v>90.8</v>
+        <v>96</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="P222" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="223">
@@ -13281,37 +13287,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F223" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="G223" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K223" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L223" s="4">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="M223" s="4">
-        <v>8.4</v>
+        <v>4.54</v>
       </c>
       <c r="N223" s="4">
-        <v>630</v>
+        <v>90.8</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="P223" s="1" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="224">
@@ -13346,22 +13352,22 @@
         <v>20</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="L224" s="4">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="M224" s="4">
-        <v>112</v>
+        <v>8.4</v>
       </c>
       <c r="N224" s="4">
-        <v>224</v>
+        <v>630</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="P224" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="225">
@@ -13387,31 +13393,31 @@
         <v>46080</v>
       </c>
       <c r="H225" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K225" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L225" s="4">
+        <v>2</v>
+      </c>
+      <c r="M225" s="4">
+        <v>112</v>
+      </c>
+      <c r="N225" s="4">
+        <v>224</v>
+      </c>
+      <c r="O225" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="I225" s="1" t="s">
+      <c r="P225" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="J225" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K225" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="L225" s="4">
-        <v>60</v>
-      </c>
-      <c r="M225" s="4">
-        <v>9</v>
-      </c>
-      <c r="N225" s="4">
-        <v>540</v>
-      </c>
-      <c r="O225" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="P225" s="1" t="s">
-        <v>502</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="226">
@@ -13431,37 +13437,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F226" s="2">
-        <v>82311</v>
+        <v>82346</v>
       </c>
       <c r="G226" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H226" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K226" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L226" s="4">
         <v>60</v>
       </c>
-      <c r="I226" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J226" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K226" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L226" s="4">
-        <v>3</v>
-      </c>
       <c r="M226" s="4">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="N226" s="4">
-        <v>40.5</v>
+        <v>540</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>62</v>
+        <v>505</v>
       </c>
       <c r="P226" s="1" t="s">
-        <v>63</v>
+        <v>506</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="227">
@@ -13587,10 +13593,10 @@
         <v>46078</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>507</v>
+        <v>60</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>508</v>
+        <v>61</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>20</v>
@@ -13599,13 +13605,13 @@
         <v>28</v>
       </c>
       <c r="L229" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M229" s="4">
-        <v>87.92</v>
+        <v>13.5</v>
       </c>
       <c r="N229" s="4">
-        <v>87.92</v>
+        <v>40.5</v>
       </c>
       <c r="O229" s="1" t="s">
         <v>62</v>
@@ -13631,16 +13637,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F230" s="2">
-        <v>82312</v>
+        <v>82311</v>
       </c>
       <c r="G230" s="3">
         <v>46078</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>20</v>
@@ -13649,19 +13655,19 @@
         <v>28</v>
       </c>
       <c r="L230" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M230" s="4">
-        <v>47.5</v>
+        <v>87.92</v>
       </c>
       <c r="N230" s="4">
-        <v>95</v>
+        <v>87.92</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="P230" s="1" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="231">
@@ -13687,10 +13693,10 @@
         <v>46078</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>20</v>
@@ -13731,37 +13737,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F232" s="2">
-        <v>82311</v>
+        <v>82312</v>
       </c>
       <c r="G232" s="3">
         <v>46078</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K232" s="1" t="s">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="L232" s="4">
         <v>2</v>
       </c>
       <c r="M232" s="4">
-        <v>18.95</v>
+        <v>47.5</v>
       </c>
       <c r="N232" s="4">
-        <v>37.9</v>
+        <v>95</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="P232" s="1" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="233">
@@ -13787,10 +13793,10 @@
         <v>46078</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>20</v>
@@ -13802,10 +13808,10 @@
         <v>2</v>
       </c>
       <c r="M233" s="4">
-        <v>10.83</v>
+        <v>18.95</v>
       </c>
       <c r="N233" s="4">
-        <v>21.66</v>
+        <v>37.9</v>
       </c>
       <c r="O233" s="1" t="s">
         <v>62</v>
@@ -13837,25 +13843,25 @@
         <v>46078</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="L234" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M234" s="4">
-        <v>169.4</v>
+        <v>10.83</v>
       </c>
       <c r="N234" s="4">
-        <v>169.4</v>
+        <v>21.66</v>
       </c>
       <c r="O234" s="1" t="s">
         <v>62</v>
@@ -13880,13 +13886,17 @@
       <c r="E235" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F235" s="1"/>
-      <c r="G235" s="1"/>
+      <c r="F235" s="2">
+        <v>82311</v>
+      </c>
+      <c r="G235" s="3">
+        <v>46078</v>
+      </c>
       <c r="H235" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>20</v>
@@ -13895,16 +13905,20 @@
         <v>28</v>
       </c>
       <c r="L235" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M235" s="4">
-        <v>0</v>
+        <v>169.4</v>
       </c>
       <c r="N235" s="4">
-        <v>0</v>
-      </c>
-      <c r="O235" s="1"/>
-      <c r="P235" s="1"/>
+        <v>169.4</v>
+      </c>
+      <c r="O235" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P235" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="236">
       <c r="A236" s="2">
@@ -13925,25 +13939,25 @@
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
       <c r="H236" s="1" t="s">
-        <v>315</v>
+        <v>523</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>316</v>
+        <v>524</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L236" s="4">
         <v>2</v>
       </c>
       <c r="M236" s="4">
-        <v>305</v>
+        <v>0</v>
       </c>
       <c r="N236" s="4">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="O236" s="1"/>
       <c r="P236" s="1"/>
@@ -13967,10 +13981,10 @@
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
-        <v>521</v>
+        <v>315</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>522</v>
+        <v>316</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>20</v>
@@ -13982,10 +13996,10 @@
         <v>2</v>
       </c>
       <c r="M237" s="4">
-        <v>162.4</v>
+        <v>305</v>
       </c>
       <c r="N237" s="4">
-        <v>324.8</v>
+        <v>610</v>
       </c>
       <c r="O237" s="1"/>
       <c r="P237" s="1"/>
@@ -14051,10 +14065,10 @@
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
       <c r="H239" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J239" s="1" t="s">
         <v>20</v>
@@ -14093,10 +14107,10 @@
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
       <c r="H240" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>20</v>
@@ -14135,10 +14149,10 @@
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
       <c r="H241" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>20</v>
@@ -14177,10 +14191,10 @@
       <c r="F242" s="1"/>
       <c r="G242" s="1"/>
       <c r="H242" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>20</v>
@@ -14261,10 +14275,10 @@
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
       <c r="H244" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>20</v>
@@ -14307,10 +14321,10 @@
         <v>46078</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>20</v>
@@ -14357,10 +14371,10 @@
         <v>46078</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>20</v>
@@ -14407,10 +14421,10 @@
         <v>46078</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J247" s="1" t="s">
         <v>20</v>
@@ -14457,10 +14471,10 @@
         <v>46078</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J248" s="1" t="s">
         <v>20</v>
@@ -14507,10 +14521,10 @@
         <v>46078</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>20</v>
@@ -14557,10 +14571,10 @@
         <v>46078</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J250" s="1" t="s">
         <v>20</v>
@@ -14607,10 +14621,10 @@
         <v>46078</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>20</v>
@@ -14657,10 +14671,10 @@
         <v>46078</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>20</v>
@@ -14707,10 +14721,10 @@
         <v>46078</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>20</v>
@@ -14739,7 +14753,7 @@
         <v>2409</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>17</v>
@@ -14789,7 +14803,7 @@
         <v>2409</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>17</v>
@@ -14807,10 +14821,10 @@
         <v>46078</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>20</v>
@@ -14839,7 +14853,7 @@
         <v>2409</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>17</v>
@@ -14889,7 +14903,7 @@
         <v>2409</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>17</v>
@@ -14939,7 +14953,7 @@
         <v>2409</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>17</v>
@@ -14989,7 +15003,7 @@
         <v>2409</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>17</v>
@@ -15028,10 +15042,10 @@
         <v>300</v>
       </c>
       <c r="O259" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="P259" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="260">
@@ -15039,7 +15053,7 @@
         <v>2409</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>17</v>
@@ -15107,10 +15121,10 @@
         <v>46079</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>20</v>
@@ -15128,10 +15142,10 @@
         <v>102000.01</v>
       </c>
       <c r="O261" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="P261" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="262">
@@ -15295,10 +15309,10 @@
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
       <c r="H265" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>20</v>
@@ -15337,10 +15351,10 @@
       <c r="F266" s="1"/>
       <c r="G266" s="1"/>
       <c r="H266" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>20</v>
@@ -15421,10 +15435,10 @@
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
       <c r="H268" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>20</v>
@@ -15505,10 +15519,10 @@
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
       <c r="H270" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>20</v>
@@ -15547,10 +15561,10 @@
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
       <c r="H271" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>20</v>
@@ -15575,7 +15589,7 @@
         <v>2514</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>25</v>
@@ -15625,7 +15639,7 @@
         <v>2514</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>25</v>
@@ -15643,10 +15657,10 @@
         <v>46080</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>20</v>
@@ -15664,10 +15678,10 @@
         <v>165</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P273" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="274">
@@ -15675,7 +15689,7 @@
         <v>2514</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>25</v>
@@ -15693,10 +15707,10 @@
         <v>46080</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>20</v>
@@ -15714,10 +15728,10 @@
         <v>104.5</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="P274" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="275">
@@ -15725,7 +15739,7 @@
         <v>2514</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>25</v>
@@ -15775,7 +15789,7 @@
         <v>2514</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>25</v>
@@ -15814,10 +15828,10 @@
         <v>2311.2</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P276" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="277">
@@ -15825,7 +15839,7 @@
         <v>2514</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>25</v>
@@ -15843,10 +15857,10 @@
         <v>46083</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>20</v>
@@ -15875,7 +15889,7 @@
         <v>2514</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>25</v>
@@ -15893,10 +15907,10 @@
         <v>46083</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J278" s="1" t="s">
         <v>20</v>
@@ -15914,10 +15928,10 @@
         <v>4998.9</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P278" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="279">
@@ -15925,7 +15939,7 @@
         <v>2514</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>25</v>
@@ -15943,10 +15957,10 @@
         <v>46083</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J279" s="1" t="s">
         <v>20</v>
@@ -15964,10 +15978,10 @@
         <v>533.1</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P279" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="280">
@@ -15975,7 +15989,7 @@
         <v>2514</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>25</v>
@@ -15993,10 +16007,10 @@
         <v>46083</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>20</v>
@@ -16014,10 +16028,10 @@
         <v>255.84</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P280" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="281">
@@ -16025,7 +16039,7 @@
         <v>2514</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>25</v>
@@ -16043,10 +16057,10 @@
         <v>46083</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>20</v>
@@ -16064,10 +16078,10 @@
         <v>449.8</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P281" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="282">
@@ -16075,7 +16089,7 @@
         <v>2514</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>25</v>
@@ -16093,10 +16107,10 @@
         <v>46083</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J282" s="1" t="s">
         <v>20</v>
@@ -16114,10 +16128,10 @@
         <v>535.2</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P282" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="283">
@@ -16125,7 +16139,7 @@
         <v>2514</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>25</v>
@@ -16143,10 +16157,10 @@
         <v>46083</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>20</v>
@@ -16164,10 +16178,10 @@
         <v>682.8</v>
       </c>
       <c r="O283" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P283" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="284">
@@ -16175,7 +16189,7 @@
         <v>2514</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>25</v>
@@ -16193,10 +16207,10 @@
         <v>46080</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>20</v>
@@ -16225,7 +16239,7 @@
         <v>2514</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>25</v>
@@ -16243,10 +16257,10 @@
         <v>46080</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>20</v>
@@ -16264,10 +16278,10 @@
         <v>315</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P285" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="286">
@@ -16293,10 +16307,10 @@
         <v>46080</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="J286" s="1" t="s">
         <v>20</v>
@@ -16443,10 +16457,10 @@
         <v>46080</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="J289" s="1" t="s">
         <v>20</v>
@@ -16493,10 +16507,10 @@
         <v>46080</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J290" s="1" t="s">
         <v>20</v>
@@ -16543,10 +16557,10 @@
         <v>46080</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>20</v>
@@ -16558,10 +16572,10 @@
         <v>1</v>
       </c>
       <c r="M291" s="4">
-        <v>229</v>
+        <v>515</v>
       </c>
       <c r="N291" s="4">
-        <v>229</v>
+        <v>515</v>
       </c>
       <c r="O291" s="1" t="s">
         <v>49</v>
@@ -16593,10 +16607,10 @@
         <v>46080</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="J292" s="1" t="s">
         <v>20</v>
@@ -16643,10 +16657,10 @@
         <v>46080</v>
       </c>
       <c r="H293" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="J293" s="1" t="s">
         <v>20</v>
@@ -16693,10 +16707,10 @@
         <v>46080</v>
       </c>
       <c r="H294" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="J294" s="1" t="s">
         <v>20</v>
@@ -16714,10 +16728,10 @@
         <v>145800</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="P294" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="295">
@@ -16739,16 +16753,16 @@
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
       <c r="H295" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J295" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K295" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L295" s="4">
         <v>3000</v>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="620">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1403,6 +1403,12 @@
     <t>CADEIRA PVC</t>
   </si>
   <si>
+    <t>C.05.0260</t>
+  </si>
+  <si>
+    <t>LIXEIRA DE PLÁSTICO 20 LTS</t>
+  </si>
+  <si>
     <t>C.05.0206</t>
   </si>
   <si>
@@ -1439,6 +1445,18 @@
     <t>FITA ZEBRADA - 7 CM X 200 M</t>
   </si>
   <si>
+    <t>E.02.0106</t>
+  </si>
+  <si>
+    <t>EXTINTOR DE INCEDIO ABC 6 KG</t>
+  </si>
+  <si>
+    <t>E.02.0107</t>
+  </si>
+  <si>
+    <t>SUPORTE DE EXTINTOR TRIPÉ COM HASTE DE SINALIZAÇÃO</t>
+  </si>
+  <si>
     <t>E.03.0291</t>
   </si>
   <si>
@@ -1487,16 +1505,28 @@
     <t>TAMBOR DE 200L ( PARA RESERVATORIO DE AGUA.)</t>
   </si>
   <si>
+    <t>K.01.0870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIDADE COMBINADA  - ROBOZINHO</t>
+  </si>
+  <si>
+    <t>00000000009700</t>
+  </si>
+  <si>
+    <t>RDW</t>
+  </si>
+  <si>
     <t>K.01.0271</t>
   </si>
   <si>
     <t>CABO FLEXÍVEL PP - 750 V - 3 X 2,5 MM²</t>
   </si>
   <si>
-    <t>00000000009700</t>
-  </si>
-  <si>
-    <t>RDW</t>
+    <t>K.07.0500</t>
+  </si>
+  <si>
+    <t>LÂMPADA MISTA BOCAL E 27 160W 220V</t>
   </si>
   <si>
     <t>K.01.1531</t>
@@ -1565,6 +1595,12 @@
     <t>DISPENSADOR DE PAPEL TOALHA</t>
   </si>
   <si>
+    <t>W.01.0043</t>
+  </si>
+  <si>
+    <t>PREGO DE AÇO COM CABEÇA 15 X 15</t>
+  </si>
+  <si>
     <t>W.01.0004</t>
   </si>
   <si>
@@ -1583,42 +1619,6 @@
     <t>CHUMBADOR QUIMICO DE INJEÇÃO</t>
   </si>
   <si>
-    <t>C.05.0260</t>
-  </si>
-  <si>
-    <t>LIXEIRA DE PLÁSTICO 20 LTS</t>
-  </si>
-  <si>
-    <t>E.02.0106</t>
-  </si>
-  <si>
-    <t>EXTINTOR DE INCEDIO ABC 6 KG</t>
-  </si>
-  <si>
-    <t>E.02.0107</t>
-  </si>
-  <si>
-    <t>SUPORTE DE EXTINTOR TRIPÉ COM HASTE DE SINALIZAÇÃO</t>
-  </si>
-  <si>
-    <t>K.01.0870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIDADE COMBINADA  - ROBOZINHO</t>
-  </si>
-  <si>
-    <t>K.07.0500</t>
-  </si>
-  <si>
-    <t>LÂMPADA MISTA BOCAL E 27 160W 220V</t>
-  </si>
-  <si>
-    <t>W.01.0043</t>
-  </si>
-  <si>
-    <t>PREGO DE AÇO COM CABEÇA 15 X 15</t>
-  </si>
-  <si>
     <t>K.08.0033</t>
   </si>
   <si>
@@ -1700,6 +1700,12 @@
     <t>DAIKIN</t>
   </si>
   <si>
+    <t>O.01.0116</t>
+  </si>
+  <si>
+    <t>CHAPA PLASTIFICADO 14 MM - 2,20 X 1,10 M</t>
+  </si>
+  <si>
     <t>E.04.0892</t>
   </si>
   <si>
@@ -1712,12 +1718,6 @@
     <t>REGUA DE ALUMINIO 3 X 1'' C/ 3 M</t>
   </si>
   <si>
-    <t>O.01.0116</t>
-  </si>
-  <si>
-    <t>CHAPA PLASTIFICADO 14 MM - 2,20 X 1,10 M</t>
-  </si>
-  <si>
     <t>P2.01.0024</t>
   </si>
   <si>
@@ -1866,6 +1866,12 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>00000000009361</t>
+  </si>
+  <si>
+    <t>PETROVERA</t>
   </si>
 </sst>
 </file>
@@ -12237,10 +12243,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F202" s="2">
-        <v>82361</v>
+        <v>82392</v>
       </c>
       <c r="G202" s="3">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H202" s="1" t="s">
         <v>463</v>
@@ -12255,19 +12261,19 @@
         <v>28</v>
       </c>
       <c r="L202" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M202" s="4">
-        <v>735</v>
+        <v>55.9</v>
       </c>
       <c r="N202" s="4">
-        <v>735</v>
+        <v>111.8</v>
       </c>
       <c r="O202" s="1" t="s">
-        <v>453</v>
+        <v>40</v>
       </c>
       <c r="P202" s="1" t="s">
-        <v>454</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="203">
@@ -12305,13 +12311,13 @@
         <v>28</v>
       </c>
       <c r="L203" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M203" s="4">
-        <v>689.3</v>
+        <v>735</v>
       </c>
       <c r="N203" s="4">
-        <v>1378.6</v>
+        <v>735</v>
       </c>
       <c r="O203" s="1" t="s">
         <v>453</v>
@@ -12337,10 +12343,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F204" s="2">
-        <v>82311</v>
+        <v>82361</v>
       </c>
       <c r="G204" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>467</v>
@@ -12355,19 +12361,19 @@
         <v>28</v>
       </c>
       <c r="L204" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M204" s="4">
-        <v>1691.98</v>
+        <v>689.3</v>
       </c>
       <c r="N204" s="4">
-        <v>1691.98</v>
+        <v>1378.6</v>
       </c>
       <c r="O204" s="1" t="s">
-        <v>62</v>
+        <v>453</v>
       </c>
       <c r="P204" s="1" t="s">
-        <v>63</v>
+        <v>454</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="205">
@@ -12387,10 +12393,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F205" s="2">
-        <v>82385</v>
+        <v>82311</v>
       </c>
       <c r="G205" s="3">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="H205" s="1" t="s">
         <v>469</v>
@@ -12402,22 +12408,22 @@
         <v>20</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L205" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M205" s="4">
-        <v>100</v>
+        <v>1691.98</v>
       </c>
       <c r="N205" s="4">
-        <v>200</v>
+        <v>1691.98</v>
       </c>
       <c r="O205" s="1" t="s">
-        <v>471</v>
+        <v>62</v>
       </c>
       <c r="P205" s="1" t="s">
-        <v>472</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="206">
@@ -12437,37 +12443,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F206" s="2">
-        <v>82311</v>
+        <v>82392</v>
       </c>
       <c r="G206" s="3">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>262</v>
+        <v>315</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K206" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L206" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M206" s="4">
-        <v>23.43</v>
+        <v>305</v>
       </c>
       <c r="N206" s="4">
-        <v>234.3</v>
+        <v>610</v>
       </c>
       <c r="O206" s="1" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="P206" s="1" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="207">
@@ -12487,16 +12493,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F207" s="2">
-        <v>82313</v>
+        <v>82385</v>
       </c>
       <c r="G207" s="3">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>218</v>
+        <v>471</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>219</v>
+        <v>472</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>20</v>
@@ -12505,19 +12511,19 @@
         <v>39</v>
       </c>
       <c r="L207" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M207" s="4">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="N207" s="4">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="O207" s="1" t="s">
-        <v>49</v>
+        <v>473</v>
       </c>
       <c r="P207" s="1" t="s">
-        <v>50</v>
+        <v>474</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="208">
@@ -12537,16 +12543,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F208" s="2">
-        <v>82313</v>
+        <v>82311</v>
       </c>
       <c r="G208" s="3">
         <v>46078</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>473</v>
+        <v>262</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>474</v>
+        <v>263</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>20</v>
@@ -12555,19 +12561,19 @@
         <v>28</v>
       </c>
       <c r="L208" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M208" s="4">
-        <v>8.5</v>
+        <v>23.43</v>
       </c>
       <c r="N208" s="4">
-        <v>17</v>
+        <v>234.3</v>
       </c>
       <c r="O208" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="P208" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="209">
@@ -12593,31 +12599,31 @@
         <v>46078</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K209" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="L209" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M209" s="4">
-        <v>3.5</v>
+        <v>129.05</v>
       </c>
       <c r="N209" s="4">
-        <v>52.5</v>
+        <v>129.05</v>
       </c>
       <c r="O209" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="P209" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="210">
@@ -12637,10 +12643,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F210" s="2">
-        <v>82361</v>
+        <v>82392</v>
       </c>
       <c r="G210" s="3">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>475</v>
@@ -12655,19 +12661,19 @@
         <v>28</v>
       </c>
       <c r="L210" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M210" s="4">
-        <v>54.68</v>
+        <v>14.9</v>
       </c>
       <c r="N210" s="4">
-        <v>54.68</v>
+        <v>29.8</v>
       </c>
       <c r="O210" s="1" t="s">
-        <v>453</v>
+        <v>40</v>
       </c>
       <c r="P210" s="1" t="s">
-        <v>454</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="211">
@@ -12687,16 +12693,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F211" s="2">
-        <v>82313</v>
+        <v>82392</v>
       </c>
       <c r="G211" s="3">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>477</v>
+        <v>296</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>478</v>
+        <v>297</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>20</v>
@@ -12705,19 +12711,19 @@
         <v>28</v>
       </c>
       <c r="L211" s="4">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="M211" s="4">
-        <v>1.5</v>
+        <v>87.9</v>
       </c>
       <c r="N211" s="4">
-        <v>112.5</v>
+        <v>439.5</v>
       </c>
       <c r="O211" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="P211" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="212">
@@ -12737,16 +12743,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F212" s="2">
-        <v>82361</v>
+        <v>82313</v>
       </c>
       <c r="G212" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>20</v>
@@ -12755,19 +12761,19 @@
         <v>28</v>
       </c>
       <c r="L212" s="4">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M212" s="4">
-        <v>1.23</v>
+        <v>232</v>
       </c>
       <c r="N212" s="4">
-        <v>18.45</v>
+        <v>928</v>
       </c>
       <c r="O212" s="1" t="s">
-        <v>453</v>
+        <v>62</v>
       </c>
       <c r="P212" s="1" t="s">
-        <v>454</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="213">
@@ -12787,16 +12793,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F213" s="2">
-        <v>82361</v>
+        <v>82313</v>
       </c>
       <c r="G213" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>298</v>
+        <v>479</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>299</v>
+        <v>480</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>20</v>
@@ -12805,19 +12811,19 @@
         <v>28</v>
       </c>
       <c r="L213" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M213" s="4">
-        <v>31.46</v>
+        <v>98.23</v>
       </c>
       <c r="N213" s="4">
-        <v>94.38</v>
+        <v>392.92</v>
       </c>
       <c r="O213" s="1" t="s">
-        <v>453</v>
+        <v>62</v>
       </c>
       <c r="P213" s="1" t="s">
-        <v>454</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="214">
@@ -12843,31 +12849,31 @@
         <v>46078</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>481</v>
+        <v>170</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>482</v>
+        <v>171</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K214" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L214" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M214" s="4">
-        <v>92.5</v>
+        <v>2.16</v>
       </c>
       <c r="N214" s="4">
-        <v>555</v>
+        <v>32.4</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="P214" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="215">
@@ -12887,16 +12893,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F215" s="2">
-        <v>82311</v>
+        <v>82361</v>
       </c>
       <c r="G215" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>20</v>
@@ -12905,19 +12911,19 @@
         <v>28</v>
       </c>
       <c r="L215" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M215" s="4">
-        <v>11.39</v>
+        <v>54.68</v>
       </c>
       <c r="N215" s="4">
-        <v>170.85</v>
+        <v>54.68</v>
       </c>
       <c r="O215" s="1" t="s">
-        <v>62</v>
+        <v>453</v>
       </c>
       <c r="P215" s="1" t="s">
-        <v>63</v>
+        <v>454</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="216">
@@ -12943,10 +12949,10 @@
         <v>46078</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>20</v>
@@ -12955,19 +12961,19 @@
         <v>28</v>
       </c>
       <c r="L216" s="4">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="M216" s="4">
-        <v>165</v>
+        <v>1.25</v>
       </c>
       <c r="N216" s="4">
-        <v>495</v>
+        <v>93.75</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="P216" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="217">
@@ -12987,37 +12993,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F217" s="2">
-        <v>82313</v>
+        <v>82361</v>
       </c>
       <c r="G217" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K217" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L217" s="4">
         <v>15</v>
       </c>
       <c r="M217" s="4">
-        <v>11.5</v>
+        <v>1.23</v>
       </c>
       <c r="N217" s="4">
-        <v>172.5</v>
+        <v>18.45</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>49</v>
+        <v>453</v>
       </c>
       <c r="P217" s="1" t="s">
-        <v>50</v>
+        <v>454</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="218">
@@ -13043,10 +13049,10 @@
         <v>46080</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>489</v>
+        <v>298</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>490</v>
+        <v>299</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>20</v>
@@ -13055,13 +13061,13 @@
         <v>28</v>
       </c>
       <c r="L218" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M218" s="4">
-        <v>170.09</v>
+        <v>31.46</v>
       </c>
       <c r="N218" s="4">
-        <v>340.18</v>
+        <v>94.38</v>
       </c>
       <c r="O218" s="1" t="s">
         <v>453</v>
@@ -13087,37 +13093,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F219" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="G219" s="3">
         <v>46078</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="J219" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L219" s="4">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="M219" s="4">
-        <v>8</v>
+        <v>69.6</v>
       </c>
       <c r="N219" s="4">
-        <v>800</v>
+        <v>417.6</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>493</v>
+        <v>62</v>
       </c>
       <c r="P219" s="1" t="s">
-        <v>494</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="220">
@@ -13137,16 +13143,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F220" s="2">
-        <v>82314</v>
+        <v>82311</v>
       </c>
       <c r="G220" s="3">
         <v>46078</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>20</v>
@@ -13155,19 +13161,19 @@
         <v>28</v>
       </c>
       <c r="L220" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M220" s="4">
-        <v>3.65</v>
+        <v>11.39</v>
       </c>
       <c r="N220" s="4">
-        <v>73</v>
+        <v>170.85</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>493</v>
+        <v>62</v>
       </c>
       <c r="P220" s="1" t="s">
-        <v>494</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="221">
@@ -13187,16 +13193,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F221" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="G221" s="3">
         <v>46078</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>20</v>
@@ -13205,19 +13211,19 @@
         <v>28</v>
       </c>
       <c r="L221" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M221" s="4">
-        <v>4.05</v>
+        <v>166.75</v>
       </c>
       <c r="N221" s="4">
-        <v>81</v>
+        <v>500.25</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>493</v>
+        <v>62</v>
       </c>
       <c r="P221" s="1" t="s">
-        <v>494</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="222">
@@ -13237,37 +13243,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F222" s="2">
-        <v>82314</v>
+        <v>82313</v>
       </c>
       <c r="G222" s="3">
         <v>46078</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K222" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L222" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M222" s="4">
-        <v>4.8</v>
+        <v>4.48</v>
       </c>
       <c r="N222" s="4">
-        <v>96</v>
+        <v>67.2</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>493</v>
+        <v>62</v>
       </c>
       <c r="P222" s="1" t="s">
-        <v>494</v>
+        <v>63</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="223">
@@ -13287,16 +13293,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F223" s="2">
-        <v>82314</v>
+        <v>82361</v>
       </c>
       <c r="G223" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>20</v>
@@ -13305,19 +13311,19 @@
         <v>28</v>
       </c>
       <c r="L223" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M223" s="4">
-        <v>4.54</v>
+        <v>170.09</v>
       </c>
       <c r="N223" s="4">
-        <v>90.8</v>
+        <v>340.18</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="P223" s="1" t="s">
-        <v>494</v>
+        <v>454</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="224">
@@ -13337,37 +13343,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F224" s="2">
-        <v>82346</v>
+        <v>82391</v>
       </c>
       <c r="G224" s="3">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K224" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L224" s="4">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="M224" s="4">
-        <v>8.4</v>
+        <v>532.185</v>
       </c>
       <c r="N224" s="4">
-        <v>630</v>
+        <v>1596.555</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="P224" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="225">
@@ -13387,37 +13393,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F225" s="2">
-        <v>82346</v>
+        <v>82314</v>
       </c>
       <c r="G225" s="3">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K225" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="L225" s="4">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="M225" s="4">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="N225" s="4">
-        <v>224</v>
+        <v>800</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="P225" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="226">
@@ -13437,37 +13443,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F226" s="2">
-        <v>82346</v>
+        <v>82391</v>
       </c>
       <c r="G226" s="3">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="H226" s="1" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="J226" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L226" s="4">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="M226" s="4">
-        <v>9</v>
+        <v>32.42</v>
       </c>
       <c r="N226" s="4">
-        <v>540</v>
+        <v>324.2</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="P226" s="1" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="227">
@@ -13487,16 +13493,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F227" s="2">
-        <v>82311</v>
+        <v>82314</v>
       </c>
       <c r="G227" s="3">
         <v>46078</v>
       </c>
       <c r="H227" s="1" t="s">
-        <v>60</v>
+        <v>505</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>61</v>
+        <v>506</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>20</v>
@@ -13505,19 +13511,19 @@
         <v>28</v>
       </c>
       <c r="L227" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M227" s="4">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="N227" s="4">
-        <v>40.5</v>
+        <v>73</v>
       </c>
       <c r="O227" s="1" t="s">
-        <v>62</v>
+        <v>499</v>
       </c>
       <c r="P227" s="1" t="s">
-        <v>63</v>
+        <v>500</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="228">
@@ -13537,16 +13543,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F228" s="2">
-        <v>82311</v>
+        <v>82314</v>
       </c>
       <c r="G228" s="3">
         <v>46078</v>
       </c>
       <c r="H228" s="1" t="s">
-        <v>60</v>
+        <v>507</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>61</v>
+        <v>508</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>20</v>
@@ -13555,19 +13561,19 @@
         <v>28</v>
       </c>
       <c r="L228" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M228" s="4">
-        <v>13.5</v>
+        <v>4.05</v>
       </c>
       <c r="N228" s="4">
-        <v>40.5</v>
+        <v>81</v>
       </c>
       <c r="O228" s="1" t="s">
-        <v>62</v>
+        <v>499</v>
       </c>
       <c r="P228" s="1" t="s">
-        <v>63</v>
+        <v>500</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="229">
@@ -13587,16 +13593,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F229" s="2">
-        <v>82311</v>
+        <v>82314</v>
       </c>
       <c r="G229" s="3">
         <v>46078</v>
       </c>
       <c r="H229" s="1" t="s">
-        <v>60</v>
+        <v>509</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>61</v>
+        <v>510</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>20</v>
@@ -13605,19 +13611,19 @@
         <v>28</v>
       </c>
       <c r="L229" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M229" s="4">
-        <v>13.5</v>
+        <v>4.8</v>
       </c>
       <c r="N229" s="4">
-        <v>40.5</v>
+        <v>96</v>
       </c>
       <c r="O229" s="1" t="s">
-        <v>62</v>
+        <v>499</v>
       </c>
       <c r="P229" s="1" t="s">
-        <v>63</v>
+        <v>500</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="230">
@@ -13637,7 +13643,7 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F230" s="2">
-        <v>82311</v>
+        <v>82314</v>
       </c>
       <c r="G230" s="3">
         <v>46078</v>
@@ -13655,19 +13661,19 @@
         <v>28</v>
       </c>
       <c r="L230" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M230" s="4">
-        <v>87.92</v>
+        <v>4.54</v>
       </c>
       <c r="N230" s="4">
-        <v>87.92</v>
+        <v>90.8</v>
       </c>
       <c r="O230" s="1" t="s">
-        <v>62</v>
+        <v>499</v>
       </c>
       <c r="P230" s="1" t="s">
-        <v>63</v>
+        <v>500</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="231">
@@ -13687,10 +13693,10 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F231" s="2">
-        <v>82312</v>
+        <v>82346</v>
       </c>
       <c r="G231" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H231" s="1" t="s">
         <v>513</v>
@@ -13702,22 +13708,22 @@
         <v>20</v>
       </c>
       <c r="K231" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="L231" s="4">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="M231" s="4">
-        <v>47.5</v>
+        <v>8.4</v>
       </c>
       <c r="N231" s="4">
-        <v>95</v>
+        <v>630</v>
       </c>
       <c r="O231" s="1" t="s">
-        <v>29</v>
+        <v>515</v>
       </c>
       <c r="P231" s="1" t="s">
-        <v>30</v>
+        <v>516</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="232">
@@ -13737,16 +13743,16 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F232" s="2">
-        <v>82312</v>
+        <v>82346</v>
       </c>
       <c r="G232" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>20</v>
@@ -13758,16 +13764,16 @@
         <v>2</v>
       </c>
       <c r="M232" s="4">
-        <v>47.5</v>
+        <v>112</v>
       </c>
       <c r="N232" s="4">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="O232" s="1" t="s">
-        <v>29</v>
+        <v>515</v>
       </c>
       <c r="P232" s="1" t="s">
-        <v>30</v>
+        <v>516</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="233">
@@ -13787,37 +13793,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F233" s="2">
-        <v>82311</v>
+        <v>82346</v>
       </c>
       <c r="G233" s="3">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>257</v>
+        <v>73</v>
       </c>
       <c r="L233" s="4">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="M233" s="4">
-        <v>18.95</v>
+        <v>9</v>
       </c>
       <c r="N233" s="4">
-        <v>37.9</v>
+        <v>540</v>
       </c>
       <c r="O233" s="1" t="s">
-        <v>62</v>
+        <v>515</v>
       </c>
       <c r="P233" s="1" t="s">
-        <v>63</v>
+        <v>516</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="234">
@@ -13837,37 +13843,37 @@
         <v>46078.6702738773</v>
       </c>
       <c r="F234" s="2">
-        <v>82311</v>
+        <v>82392</v>
       </c>
       <c r="G234" s="3">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>519</v>
+        <v>55</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>520</v>
+        <v>56</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>257</v>
+        <v>57</v>
       </c>
       <c r="L234" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M234" s="4">
-        <v>10.83</v>
+        <v>255.9</v>
       </c>
       <c r="N234" s="4">
-        <v>21.66</v>
+        <v>255.9</v>
       </c>
       <c r="O234" s="1" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="P234" s="1" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="235">
@@ -13893,10 +13899,10 @@
         <v>46078</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>521</v>
+        <v>60</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>522</v>
+        <v>61</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>20</v>
@@ -13905,13 +13911,13 @@
         <v>28</v>
       </c>
       <c r="L235" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M235" s="4">
-        <v>169.4</v>
+        <v>13.5</v>
       </c>
       <c r="N235" s="4">
-        <v>169.4</v>
+        <v>40.5</v>
       </c>
       <c r="O235" s="1" t="s">
         <v>62</v>
@@ -13936,13 +13942,17 @@
       <c r="E236" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F236" s="1"/>
-      <c r="G236" s="1"/>
+      <c r="F236" s="2">
+        <v>82311</v>
+      </c>
+      <c r="G236" s="3">
+        <v>46078</v>
+      </c>
       <c r="H236" s="1" t="s">
-        <v>523</v>
+        <v>60</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>524</v>
+        <v>61</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>20</v>
@@ -13951,16 +13961,20 @@
         <v>28</v>
       </c>
       <c r="L236" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M236" s="4">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="N236" s="4">
-        <v>0</v>
-      </c>
-      <c r="O236" s="1"/>
-      <c r="P236" s="1"/>
+        <v>40.5</v>
+      </c>
+      <c r="O236" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P236" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="237">
       <c r="A237" s="2">
@@ -13978,31 +13992,39 @@
       <c r="E237" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F237" s="1"/>
-      <c r="G237" s="1"/>
+      <c r="F237" s="2">
+        <v>82311</v>
+      </c>
+      <c r="G237" s="3">
+        <v>46078</v>
+      </c>
       <c r="H237" s="1" t="s">
-        <v>315</v>
+        <v>60</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>316</v>
+        <v>61</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K237" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L237" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M237" s="4">
-        <v>305</v>
+        <v>13.5</v>
       </c>
       <c r="N237" s="4">
-        <v>610</v>
-      </c>
-      <c r="O237" s="1"/>
-      <c r="P237" s="1"/>
+        <v>40.5</v>
+      </c>
+      <c r="O237" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P237" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="238">
       <c r="A238" s="2">
@@ -14020,13 +14042,17 @@
       <c r="E238" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F238" s="1"/>
-      <c r="G238" s="1"/>
+      <c r="F238" s="2">
+        <v>82311</v>
+      </c>
+      <c r="G238" s="3">
+        <v>46078</v>
+      </c>
       <c r="H238" s="1" t="s">
-        <v>296</v>
+        <v>521</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>297</v>
+        <v>522</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>20</v>
@@ -14035,16 +14061,20 @@
         <v>28</v>
       </c>
       <c r="L238" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M238" s="4">
-        <v>0</v>
+        <v>87.92</v>
       </c>
       <c r="N238" s="4">
-        <v>0</v>
-      </c>
-      <c r="O238" s="1"/>
-      <c r="P238" s="1"/>
+        <v>87.92</v>
+      </c>
+      <c r="O238" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P238" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="239">
       <c r="A239" s="2">
@@ -14062,13 +14092,17 @@
       <c r="E239" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F239" s="1"/>
-      <c r="G239" s="1"/>
+      <c r="F239" s="2">
+        <v>82312</v>
+      </c>
+      <c r="G239" s="3">
+        <v>46078</v>
+      </c>
       <c r="H239" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="J239" s="1" t="s">
         <v>20</v>
@@ -14077,16 +14111,20 @@
         <v>28</v>
       </c>
       <c r="L239" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M239" s="4">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="N239" s="4">
-        <v>0</v>
-      </c>
-      <c r="O239" s="1"/>
-      <c r="P239" s="1"/>
+        <v>95</v>
+      </c>
+      <c r="O239" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P239" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="240">
       <c r="A240" s="2">
@@ -14104,13 +14142,17 @@
       <c r="E240" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F240" s="1"/>
-      <c r="G240" s="1"/>
+      <c r="F240" s="2">
+        <v>82312</v>
+      </c>
+      <c r="G240" s="3">
+        <v>46078</v>
+      </c>
       <c r="H240" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>20</v>
@@ -14119,16 +14161,20 @@
         <v>28</v>
       </c>
       <c r="L240" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M240" s="4">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="N240" s="4">
-        <v>0</v>
-      </c>
-      <c r="O240" s="1"/>
-      <c r="P240" s="1"/>
+        <v>95</v>
+      </c>
+      <c r="O240" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P240" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="241">
       <c r="A241" s="2">
@@ -14146,31 +14192,39 @@
       <c r="E241" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F241" s="1"/>
-      <c r="G241" s="1"/>
+      <c r="F241" s="2">
+        <v>82313</v>
+      </c>
+      <c r="G241" s="3">
+        <v>46078</v>
+      </c>
       <c r="H241" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K241" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="L241" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M241" s="4">
-        <v>0</v>
+        <v>37.4</v>
       </c>
       <c r="N241" s="4">
-        <v>0</v>
-      </c>
-      <c r="O241" s="1"/>
-      <c r="P241" s="1"/>
+        <v>74.8</v>
+      </c>
+      <c r="O241" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P241" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="242">
       <c r="A242" s="2">
@@ -14188,31 +14242,39 @@
       <c r="E242" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F242" s="1"/>
-      <c r="G242" s="1"/>
+      <c r="F242" s="2">
+        <v>82311</v>
+      </c>
+      <c r="G242" s="3">
+        <v>46078</v>
+      </c>
       <c r="H242" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K242" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="L242" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M242" s="4">
-        <v>0</v>
+        <v>18.95</v>
       </c>
       <c r="N242" s="4">
-        <v>0</v>
-      </c>
-      <c r="O242" s="1"/>
-      <c r="P242" s="1"/>
+        <v>37.9</v>
+      </c>
+      <c r="O242" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P242" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="243">
       <c r="A243" s="2">
@@ -14230,31 +14292,39 @@
       <c r="E243" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F243" s="1"/>
-      <c r="G243" s="1"/>
+      <c r="F243" s="2">
+        <v>82311</v>
+      </c>
+      <c r="G243" s="3">
+        <v>46078</v>
+      </c>
       <c r="H243" s="1" t="s">
-        <v>55</v>
+        <v>531</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>56</v>
+        <v>532</v>
       </c>
       <c r="J243" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K243" s="1" t="s">
-        <v>57</v>
+        <v>257</v>
       </c>
       <c r="L243" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M243" s="4">
-        <v>0</v>
+        <v>10.83</v>
       </c>
       <c r="N243" s="4">
-        <v>0</v>
-      </c>
-      <c r="O243" s="1"/>
-      <c r="P243" s="1"/>
+        <v>21.66</v>
+      </c>
+      <c r="O243" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P243" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="244">
       <c r="A244" s="2">
@@ -14272,8 +14342,12 @@
       <c r="E244" s="3">
         <v>46078.6702738773</v>
       </c>
-      <c r="F244" s="1"/>
-      <c r="G244" s="1"/>
+      <c r="F244" s="2">
+        <v>82311</v>
+      </c>
+      <c r="G244" s="3">
+        <v>46078</v>
+      </c>
       <c r="H244" s="1" t="s">
         <v>533</v>
       </c>
@@ -14284,19 +14358,23 @@
         <v>20</v>
       </c>
       <c r="K244" s="1" t="s">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="L244" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M244" s="4">
-        <v>0</v>
+        <v>169.4</v>
       </c>
       <c r="N244" s="4">
-        <v>0</v>
-      </c>
-      <c r="O244" s="1"/>
-      <c r="P244" s="1"/>
+        <v>169.4</v>
+      </c>
+      <c r="O244" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P244" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="245">
       <c r="A245" s="2">
@@ -15165,10 +15243,10 @@
         <v>46079.5787315972</v>
       </c>
       <c r="F262" s="2">
-        <v>82337</v>
+        <v>82388</v>
       </c>
       <c r="G262" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="H262" s="1" t="s">
         <v>285</v>
@@ -15186,16 +15264,16 @@
         <v>30</v>
       </c>
       <c r="M262" s="4">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="N262" s="4">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="O262" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="P262" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="263">
@@ -15215,16 +15293,16 @@
         <v>46079.5787315972</v>
       </c>
       <c r="F263" s="2">
-        <v>82337</v>
+        <v>82388</v>
       </c>
       <c r="G263" s="3">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>334</v>
+        <v>33</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>335</v>
+        <v>34</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>20</v>
@@ -15233,19 +15311,19 @@
         <v>28</v>
       </c>
       <c r="L263" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M263" s="4">
-        <v>6</v>
+        <v>58.96</v>
       </c>
       <c r="N263" s="4">
-        <v>60</v>
+        <v>58.96</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="P263" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="264">
@@ -15264,31 +15342,39 @@
       <c r="E264" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F264" s="1"/>
-      <c r="G264" s="1"/>
+      <c r="F264" s="2">
+        <v>82389</v>
+      </c>
+      <c r="G264" s="3">
+        <v>46083</v>
+      </c>
       <c r="H264" s="1" t="s">
-        <v>33</v>
+        <v>207</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>34</v>
+        <v>208</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K264" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="L264" s="4">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="M264" s="4">
-        <v>34.72</v>
+        <v>5.6</v>
       </c>
       <c r="N264" s="4">
-        <v>34.72</v>
-      </c>
-      <c r="O264" s="1"/>
-      <c r="P264" s="1"/>
+        <v>100.8</v>
+      </c>
+      <c r="O264" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P264" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="265">
       <c r="A265" s="2">
@@ -15306,8 +15392,12 @@
       <c r="E265" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F265" s="1"/>
-      <c r="G265" s="1"/>
+      <c r="F265" s="2">
+        <v>82389</v>
+      </c>
+      <c r="G265" s="3">
+        <v>46083</v>
+      </c>
       <c r="H265" s="1" t="s">
         <v>562</v>
       </c>
@@ -15321,16 +15411,20 @@
         <v>28</v>
       </c>
       <c r="L265" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M265" s="4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="N265" s="4">
-        <v>0</v>
-      </c>
-      <c r="O265" s="1"/>
-      <c r="P265" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="O265" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P265" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="266">
       <c r="A266" s="2">
@@ -15363,13 +15457,13 @@
         <v>28</v>
       </c>
       <c r="L266" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M266" s="4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N266" s="4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O266" s="1"/>
       <c r="P266" s="1"/>
@@ -15393,19 +15487,19 @@
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
       <c r="H267" s="1" t="s">
-        <v>207</v>
+        <v>566</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>208</v>
+        <v>567</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K267" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L267" s="4">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="M267" s="4">
         <v>0</v>
@@ -15435,10 +15529,10 @@
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
       <c r="H268" s="1" t="s">
-        <v>566</v>
+        <v>334</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>567</v>
+        <v>335</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>20</v>
@@ -15447,13 +15541,13 @@
         <v>28</v>
       </c>
       <c r="L268" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M268" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N268" s="4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O268" s="1"/>
       <c r="P268" s="1"/>
@@ -15519,10 +15613,10 @@
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
       <c r="H270" s="1" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>20</v>
@@ -15534,10 +15628,10 @@
         <v>5</v>
       </c>
       <c r="M270" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N270" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O270" s="1"/>
       <c r="P270" s="1"/>
@@ -16750,8 +16844,12 @@
       <c r="E295" s="3">
         <v>46080.6289065162</v>
       </c>
-      <c r="F295" s="1"/>
-      <c r="G295" s="1"/>
+      <c r="F295" s="2">
+        <v>82387</v>
+      </c>
+      <c r="G295" s="3">
+        <v>46083</v>
+      </c>
       <c r="H295" s="1" t="s">
         <v>615</v>
       </c>
@@ -16768,13 +16866,17 @@
         <v>3000</v>
       </c>
       <c r="M295" s="4">
-        <v>0</v>
+        <v>7.99</v>
       </c>
       <c r="N295" s="4">
-        <v>0</v>
-      </c>
-      <c r="O295" s="1"/>
-      <c r="P295" s="1"/>
+        <v>23970</v>
+      </c>
+      <c r="O295" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="P295" s="1" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="296">
       <c r="A296" s="2">

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="646">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1700,24 +1700,24 @@
     <t>DAIKIN</t>
   </si>
   <si>
+    <t>E.04.0892</t>
+  </si>
+  <si>
+    <t>DISCO DE CORTE AÇO INOX 4 1/2''</t>
+  </si>
+  <si>
+    <t>E.04.0775</t>
+  </si>
+  <si>
+    <t>REGUA DE ALUMINIO 3 X 1'' C/ 3 M</t>
+  </si>
+  <si>
     <t>O.01.0116</t>
   </si>
   <si>
     <t>CHAPA PLASTIFICADO 14 MM - 2,20 X 1,10 M</t>
   </si>
   <si>
-    <t>E.04.0892</t>
-  </si>
-  <si>
-    <t>DISCO DE CORTE AÇO INOX 4 1/2''</t>
-  </si>
-  <si>
-    <t>E.04.0775</t>
-  </si>
-  <si>
-    <t>REGUA DE ALUMINIO 3 X 1'' C/ 3 M</t>
-  </si>
-  <si>
     <t>P2.01.0024</t>
   </si>
   <si>
@@ -1872,6 +1872,84 @@
   </si>
   <si>
     <t>PETROVERA</t>
+  </si>
+  <si>
+    <t>E.04.0680</t>
+  </si>
+  <si>
+    <t>PÁ QUADRADA C/ CABO - Nº 4</t>
+  </si>
+  <si>
+    <t>E.06.0007</t>
+  </si>
+  <si>
+    <t>OLEO LUBRIFICANTE WD40</t>
+  </si>
+  <si>
+    <t>E.04.1170</t>
+  </si>
+  <si>
+    <t>LÁPIS PARA CARPINTEIRO IRWIN</t>
+  </si>
+  <si>
+    <t>C.04.0205</t>
+  </si>
+  <si>
+    <t>SABONETE LIQUIDO 5 L</t>
+  </si>
+  <si>
+    <t>E.01.0069</t>
+  </si>
+  <si>
+    <t>REFIL PARA ASPIRADOR DE PÓ</t>
+  </si>
+  <si>
+    <t>J.05.0002</t>
+  </si>
+  <si>
+    <t>CIMENTO CP II - E-32 - 25 KG</t>
+  </si>
+  <si>
+    <t>M.09.0020</t>
+  </si>
+  <si>
+    <t>ARAME RECOZIDO NØ 10</t>
+  </si>
+  <si>
+    <t>U.02.2800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIXA DE DESCARGA EMBUTIDA  HYDRA MECÂNICA 2500 CX.MC.AF ( BACIA DE PISO )</t>
+  </si>
+  <si>
+    <t>U.02.0700</t>
+  </si>
+  <si>
+    <t>SIFÃO PARA LAVATÓRIO - DECA 1680 C 100 112</t>
+  </si>
+  <si>
+    <t>U.03.6000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RALO  LINHA SQUARE LINE 15 X 15</t>
+  </si>
+  <si>
+    <t>U.03.6004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RALO  LINHA SQUARE LINE 10 X 10</t>
+  </si>
+  <si>
+    <t>U.02.21021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACABAMENTO PARA REGISTRO  DE GAVETA  ATÉ 1''  REDONDO  DARK ANTRACITE  DECA YOU REF 4900  GF104</t>
+  </si>
+  <si>
+    <t>E.01.0070</t>
+  </si>
+  <si>
+    <t>CADEADO 20 MM</t>
   </si>
 </sst>
 </file>
@@ -2170,7 +2248,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P297"/>
+  <dimension ref="A1:P319"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -6372,10 +6450,10 @@
         <v>1</v>
       </c>
       <c r="M84" s="4">
-        <v>95.3</v>
+        <v>77.03</v>
       </c>
       <c r="N84" s="4">
-        <v>95.3</v>
+        <v>77.03</v>
       </c>
       <c r="O84" s="1" t="s">
         <v>231</v>
@@ -15343,37 +15421,37 @@
         <v>46079.5787315972</v>
       </c>
       <c r="F264" s="2">
-        <v>82389</v>
+        <v>82397</v>
       </c>
       <c r="G264" s="3">
         <v>46083</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>207</v>
+        <v>562</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>208</v>
+        <v>563</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K264" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L264" s="4">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="M264" s="4">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="N264" s="4">
-        <v>100.8</v>
+        <v>38</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="P264" s="1" t="s">
-        <v>206</v>
+        <v>259</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="265">
@@ -15393,16 +15471,16 @@
         <v>46079.5787315972</v>
       </c>
       <c r="F265" s="2">
-        <v>82389</v>
+        <v>82397</v>
       </c>
       <c r="G265" s="3">
         <v>46083</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>20</v>
@@ -15411,19 +15489,19 @@
         <v>28</v>
       </c>
       <c r="L265" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M265" s="4">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="N265" s="4">
-        <v>220</v>
+        <v>576</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="P265" s="1" t="s">
-        <v>206</v>
+        <v>259</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="266">
@@ -15442,13 +15520,17 @@
       <c r="E266" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F266" s="1"/>
-      <c r="G266" s="1"/>
+      <c r="F266" s="2">
+        <v>82397</v>
+      </c>
+      <c r="G266" s="3">
+        <v>46083</v>
+      </c>
       <c r="H266" s="1" t="s">
-        <v>564</v>
+        <v>334</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>565</v>
+        <v>335</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>20</v>
@@ -15460,13 +15542,17 @@
         <v>10</v>
       </c>
       <c r="M266" s="4">
-        <v>3.6</v>
+        <v>5.3</v>
       </c>
       <c r="N266" s="4">
-        <v>36</v>
-      </c>
-      <c r="O266" s="1"/>
-      <c r="P266" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="O266" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P266" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="267">
       <c r="A267" s="2">
@@ -15484,31 +15570,39 @@
       <c r="E267" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F267" s="1"/>
-      <c r="G267" s="1"/>
+      <c r="F267" s="2">
+        <v>82389</v>
+      </c>
+      <c r="G267" s="3">
+        <v>46083</v>
+      </c>
       <c r="H267" s="1" t="s">
-        <v>566</v>
+        <v>207</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>567</v>
+        <v>208</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K267" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="L267" s="4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M267" s="4">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N267" s="4">
-        <v>0</v>
-      </c>
-      <c r="O267" s="1"/>
-      <c r="P267" s="1"/>
+        <v>100.8</v>
+      </c>
+      <c r="O267" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P267" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="268">
       <c r="A268" s="2">
@@ -15526,13 +15620,17 @@
       <c r="E268" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F268" s="1"/>
-      <c r="G268" s="1"/>
+      <c r="F268" s="2">
+        <v>82389</v>
+      </c>
+      <c r="G268" s="3">
+        <v>46083</v>
+      </c>
       <c r="H268" s="1" t="s">
-        <v>334</v>
+        <v>566</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>335</v>
+        <v>567</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>20</v>
@@ -15541,16 +15639,20 @@
         <v>28</v>
       </c>
       <c r="L268" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M268" s="4">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="N268" s="4">
-        <v>60</v>
-      </c>
-      <c r="O268" s="1"/>
-      <c r="P268" s="1"/>
+        <v>220</v>
+      </c>
+      <c r="O268" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="P268" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="269">
       <c r="A269" s="2">
@@ -15568,8 +15670,12 @@
       <c r="E269" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F269" s="1"/>
-      <c r="G269" s="1"/>
+      <c r="F269" s="2">
+        <v>82397</v>
+      </c>
+      <c r="G269" s="3">
+        <v>46083</v>
+      </c>
       <c r="H269" s="1" t="s">
         <v>96</v>
       </c>
@@ -15586,13 +15692,17 @@
         <v>2</v>
       </c>
       <c r="M269" s="4">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="N269" s="4">
-        <v>0</v>
-      </c>
-      <c r="O269" s="1"/>
-      <c r="P269" s="1"/>
+        <v>1260</v>
+      </c>
+      <c r="O269" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P269" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="270">
       <c r="A270" s="2">
@@ -15610,8 +15720,12 @@
       <c r="E270" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F270" s="1"/>
-      <c r="G270" s="1"/>
+      <c r="F270" s="2">
+        <v>82397</v>
+      </c>
+      <c r="G270" s="3">
+        <v>46083</v>
+      </c>
       <c r="H270" s="1" t="s">
         <v>527</v>
       </c>
@@ -15628,13 +15742,17 @@
         <v>5</v>
       </c>
       <c r="M270" s="4">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="N270" s="4">
-        <v>15</v>
-      </c>
-      <c r="O270" s="1"/>
-      <c r="P270" s="1"/>
+        <v>550</v>
+      </c>
+      <c r="O270" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P270" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="271">
       <c r="A271" s="2">
@@ -15652,8 +15770,12 @@
       <c r="E271" s="3">
         <v>46079.5787315972</v>
       </c>
-      <c r="F271" s="1"/>
-      <c r="G271" s="1"/>
+      <c r="F271" s="2">
+        <v>82396</v>
+      </c>
+      <c r="G271" s="3">
+        <v>46083</v>
+      </c>
       <c r="H271" s="1" t="s">
         <v>568</v>
       </c>
@@ -15670,13 +15792,17 @@
         <v>13</v>
       </c>
       <c r="M271" s="4">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="N271" s="4">
-        <v>0</v>
-      </c>
-      <c r="O271" s="1"/>
-      <c r="P271" s="1"/>
+        <v>5044</v>
+      </c>
+      <c r="O271" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P271" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="272">
       <c r="A272" s="2">
@@ -16977,6 +17103,986 @@
       <c r="P297" s="1" t="s">
         <v>23</v>
       </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="298">
+      <c r="A298" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D298" s="2">
+        <v>15</v>
+      </c>
+      <c r="E298" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F298" s="2">
+        <v>82400</v>
+      </c>
+      <c r="G298" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H298" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="J298" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K298" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L298" s="4">
+        <v>2</v>
+      </c>
+      <c r="M298" s="4">
+        <v>68</v>
+      </c>
+      <c r="N298" s="4">
+        <v>136</v>
+      </c>
+      <c r="O298" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P298" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="299">
+      <c r="A299" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D299" s="2">
+        <v>15</v>
+      </c>
+      <c r="E299" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F299" s="2">
+        <v>82399</v>
+      </c>
+      <c r="G299" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H299" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="I299" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="J299" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K299" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L299" s="4">
+        <v>4</v>
+      </c>
+      <c r="M299" s="4">
+        <v>54.85</v>
+      </c>
+      <c r="N299" s="4">
+        <v>219.4</v>
+      </c>
+      <c r="O299" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P299" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="300">
+      <c r="A300" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B300" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D300" s="2">
+        <v>15</v>
+      </c>
+      <c r="E300" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F300" s="2">
+        <v>82401</v>
+      </c>
+      <c r="G300" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H300" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I300" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J300" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K300" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L300" s="4">
+        <v>3</v>
+      </c>
+      <c r="M300" s="4">
+        <v>29.99</v>
+      </c>
+      <c r="N300" s="4">
+        <v>89.97</v>
+      </c>
+      <c r="O300" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P300" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="301">
+      <c r="A301" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B301" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C301" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D301" s="2">
+        <v>15</v>
+      </c>
+      <c r="E301" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F301" s="2">
+        <v>82401</v>
+      </c>
+      <c r="G301" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H301" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="I301" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="J301" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K301" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L301" s="4">
+        <v>3</v>
+      </c>
+      <c r="M301" s="4">
+        <v>50.9</v>
+      </c>
+      <c r="N301" s="4">
+        <v>152.7</v>
+      </c>
+      <c r="O301" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P301" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="302">
+      <c r="A302" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D302" s="2">
+        <v>15</v>
+      </c>
+      <c r="E302" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F302" s="2">
+        <v>82399</v>
+      </c>
+      <c r="G302" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H302" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="I302" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="J302" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K302" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L302" s="4">
+        <v>20</v>
+      </c>
+      <c r="M302" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="N302" s="4">
+        <v>44</v>
+      </c>
+      <c r="O302" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P302" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="303">
+      <c r="A303" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B303" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C303" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D303" s="2">
+        <v>15</v>
+      </c>
+      <c r="E303" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F303" s="2">
+        <v>82401</v>
+      </c>
+      <c r="G303" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H303" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I303" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J303" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K303" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L303" s="4">
+        <v>200</v>
+      </c>
+      <c r="M303" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="N303" s="4">
+        <v>1160</v>
+      </c>
+      <c r="O303" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P303" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="304">
+      <c r="A304" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D304" s="2">
+        <v>15</v>
+      </c>
+      <c r="E304" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F304" s="2">
+        <v>82401</v>
+      </c>
+      <c r="G304" s="3">
+        <v>46083</v>
+      </c>
+      <c r="H304" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I304" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J304" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K304" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L304" s="4">
+        <v>50</v>
+      </c>
+      <c r="M304" s="4">
+        <v>34.5</v>
+      </c>
+      <c r="N304" s="4">
+        <v>1725</v>
+      </c>
+      <c r="O304" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P304" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="305">
+      <c r="A305" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B305" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C305" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D305" s="2">
+        <v>15</v>
+      </c>
+      <c r="E305" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1"/>
+      <c r="H305" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="I305" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="J305" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K305" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L305" s="4">
+        <v>6</v>
+      </c>
+      <c r="M305" s="4">
+        <v>0</v>
+      </c>
+      <c r="N305" s="4">
+        <v>0</v>
+      </c>
+      <c r="O305" s="1"/>
+      <c r="P305" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="306">
+      <c r="A306" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D306" s="2">
+        <v>15</v>
+      </c>
+      <c r="E306" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F306" s="1"/>
+      <c r="G306" s="1"/>
+      <c r="H306" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="I306" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="J306" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K306" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L306" s="4">
+        <v>10</v>
+      </c>
+      <c r="M306" s="4">
+        <v>0</v>
+      </c>
+      <c r="N306" s="4">
+        <v>0</v>
+      </c>
+      <c r="O306" s="1"/>
+      <c r="P306" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="307">
+      <c r="A307" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B307" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D307" s="2">
+        <v>15</v>
+      </c>
+      <c r="E307" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F307" s="1"/>
+      <c r="G307" s="1"/>
+      <c r="H307" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="I307" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="J307" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K307" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L307" s="4">
+        <v>20</v>
+      </c>
+      <c r="M307" s="4">
+        <v>0</v>
+      </c>
+      <c r="N307" s="4">
+        <v>0</v>
+      </c>
+      <c r="O307" s="1"/>
+      <c r="P307" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="308">
+      <c r="A308" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B308" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C308" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D308" s="2">
+        <v>15</v>
+      </c>
+      <c r="E308" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F308" s="1"/>
+      <c r="G308" s="1"/>
+      <c r="H308" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="I308" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="J308" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K308" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L308" s="4">
+        <v>5</v>
+      </c>
+      <c r="M308" s="4">
+        <v>0</v>
+      </c>
+      <c r="N308" s="4">
+        <v>0</v>
+      </c>
+      <c r="O308" s="1"/>
+      <c r="P308" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="309">
+      <c r="A309" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B309" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C309" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D309" s="2">
+        <v>15</v>
+      </c>
+      <c r="E309" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F309" s="1"/>
+      <c r="G309" s="1"/>
+      <c r="H309" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I309" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="J309" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K309" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L309" s="4">
+        <v>5</v>
+      </c>
+      <c r="M309" s="4">
+        <v>0</v>
+      </c>
+      <c r="N309" s="4">
+        <v>0</v>
+      </c>
+      <c r="O309" s="1"/>
+      <c r="P309" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="310">
+      <c r="A310" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B310" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D310" s="2">
+        <v>15</v>
+      </c>
+      <c r="E310" s="3">
+        <v>46083.6671321991</v>
+      </c>
+      <c r="F310" s="1"/>
+      <c r="G310" s="1"/>
+      <c r="H310" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="I310" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="J310" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K310" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L310" s="4">
+        <v>5</v>
+      </c>
+      <c r="M310" s="4">
+        <v>0</v>
+      </c>
+      <c r="N310" s="4">
+        <v>0</v>
+      </c>
+      <c r="O310" s="1"/>
+      <c r="P310" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="311">
+      <c r="A311" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B311" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C311" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D311" s="2">
+        <v>26</v>
+      </c>
+      <c r="E311" s="3">
+        <v>46083.6694849421</v>
+      </c>
+      <c r="F311" s="1"/>
+      <c r="G311" s="1"/>
+      <c r="H311" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="I311" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="J311" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K311" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L311" s="4">
+        <v>1</v>
+      </c>
+      <c r="M311" s="4">
+        <v>0</v>
+      </c>
+      <c r="N311" s="4">
+        <v>0</v>
+      </c>
+      <c r="O311" s="1"/>
+      <c r="P311" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="312">
+      <c r="A312" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D312" s="2">
+        <v>26</v>
+      </c>
+      <c r="E312" s="3">
+        <v>46083.6694849421</v>
+      </c>
+      <c r="F312" s="1"/>
+      <c r="G312" s="1"/>
+      <c r="H312" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="I312" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="J312" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K312" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L312" s="4">
+        <v>3</v>
+      </c>
+      <c r="M312" s="4">
+        <v>0</v>
+      </c>
+      <c r="N312" s="4">
+        <v>0</v>
+      </c>
+      <c r="O312" s="1"/>
+      <c r="P312" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="313">
+      <c r="A313" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D313" s="2">
+        <v>26</v>
+      </c>
+      <c r="E313" s="3">
+        <v>46083.6694849421</v>
+      </c>
+      <c r="F313" s="1"/>
+      <c r="G313" s="1"/>
+      <c r="H313" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="I313" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K313" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L313" s="4">
+        <v>5</v>
+      </c>
+      <c r="M313" s="4">
+        <v>0</v>
+      </c>
+      <c r="N313" s="4">
+        <v>0</v>
+      </c>
+      <c r="O313" s="1"/>
+      <c r="P313" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="314">
+      <c r="A314" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B314" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C314" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D314" s="2">
+        <v>26</v>
+      </c>
+      <c r="E314" s="3">
+        <v>46083.6694849421</v>
+      </c>
+      <c r="F314" s="1"/>
+      <c r="G314" s="1"/>
+      <c r="H314" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="I314" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="J314" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K314" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L314" s="4">
+        <v>12</v>
+      </c>
+      <c r="M314" s="4">
+        <v>0</v>
+      </c>
+      <c r="N314" s="4">
+        <v>0</v>
+      </c>
+      <c r="O314" s="1"/>
+      <c r="P314" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="315">
+      <c r="A315" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D315" s="2">
+        <v>74</v>
+      </c>
+      <c r="E315" s="3">
+        <v>46083.6704391782</v>
+      </c>
+      <c r="F315" s="1"/>
+      <c r="G315" s="1"/>
+      <c r="H315" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I315" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K315" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L315" s="4">
+        <v>4</v>
+      </c>
+      <c r="M315" s="4">
+        <v>0</v>
+      </c>
+      <c r="N315" s="4">
+        <v>0</v>
+      </c>
+      <c r="O315" s="1"/>
+      <c r="P315" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="316">
+      <c r="A316" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C316" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D316" s="2">
+        <v>74</v>
+      </c>
+      <c r="E316" s="3">
+        <v>46083.6704391782</v>
+      </c>
+      <c r="F316" s="1"/>
+      <c r="G316" s="1"/>
+      <c r="H316" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I316" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J316" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K316" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L316" s="4">
+        <v>10</v>
+      </c>
+      <c r="M316" s="4">
+        <v>0</v>
+      </c>
+      <c r="N316" s="4">
+        <v>0</v>
+      </c>
+      <c r="O316" s="1"/>
+      <c r="P316" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="317">
+      <c r="A317" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D317" s="2">
+        <v>74</v>
+      </c>
+      <c r="E317" s="3">
+        <v>46083.6704391782</v>
+      </c>
+      <c r="F317" s="1"/>
+      <c r="G317" s="1"/>
+      <c r="H317" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="I317" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="J317" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K317" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L317" s="4">
+        <v>4</v>
+      </c>
+      <c r="M317" s="4">
+        <v>0</v>
+      </c>
+      <c r="N317" s="4">
+        <v>0</v>
+      </c>
+      <c r="O317" s="1"/>
+      <c r="P317" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="318">
+      <c r="A318" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B318" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C318" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D318" s="2">
+        <v>74</v>
+      </c>
+      <c r="E318" s="3">
+        <v>46083.6704391782</v>
+      </c>
+      <c r="F318" s="1"/>
+      <c r="G318" s="1"/>
+      <c r="H318" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I318" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="J318" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K318" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L318" s="4">
+        <v>50</v>
+      </c>
+      <c r="M318" s="4">
+        <v>0</v>
+      </c>
+      <c r="N318" s="4">
+        <v>0</v>
+      </c>
+      <c r="O318" s="1"/>
+      <c r="P318" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="319">
+      <c r="A319" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B319" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C319" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D319" s="2">
+        <v>74</v>
+      </c>
+      <c r="E319" s="3">
+        <v>46083.6704391782</v>
+      </c>
+      <c r="F319" s="1"/>
+      <c r="G319" s="1"/>
+      <c r="H319" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I319" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J319" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K319" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L319" s="4">
+        <v>2</v>
+      </c>
+      <c r="M319" s="4">
+        <v>0</v>
+      </c>
+      <c r="N319" s="4">
+        <v>0</v>
+      </c>
+      <c r="O319" s="1"/>
+      <c r="P319" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="702">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1874,6 +1874,18 @@
     <t>PETROVERA</t>
   </si>
   <si>
+    <t>C.04.0205</t>
+  </si>
+  <si>
+    <t>SABONETE LIQUIDO 5 L</t>
+  </si>
+  <si>
+    <t>E.01.0069</t>
+  </si>
+  <si>
+    <t>REFIL PARA ASPIRADOR DE PÓ</t>
+  </si>
+  <si>
     <t>E.04.0680</t>
   </si>
   <si>
@@ -1892,36 +1904,24 @@
     <t>LÁPIS PARA CARPINTEIRO IRWIN</t>
   </si>
   <si>
-    <t>C.04.0205</t>
-  </si>
-  <si>
-    <t>SABONETE LIQUIDO 5 L</t>
-  </si>
-  <si>
-    <t>E.01.0069</t>
-  </si>
-  <si>
-    <t>REFIL PARA ASPIRADOR DE PÓ</t>
-  </si>
-  <si>
     <t>J.05.0002</t>
   </si>
   <si>
     <t>CIMENTO CP II - E-32 - 25 KG</t>
   </si>
   <si>
+    <t>U.02.2800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIXA DE DESCARGA EMBUTIDA  HYDRA MECÂNICA 2500 CX.MC.AF ( BACIA DE PISO )</t>
+  </si>
+  <si>
     <t>M.09.0020</t>
   </si>
   <si>
     <t>ARAME RECOZIDO NØ 10</t>
   </si>
   <si>
-    <t>U.02.2800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAIXA DE DESCARGA EMBUTIDA  HYDRA MECÂNICA 2500 CX.MC.AF ( BACIA DE PISO )</t>
-  </si>
-  <si>
     <t>U.02.0700</t>
   </si>
   <si>
@@ -1950,6 +1950,174 @@
   </si>
   <si>
     <t>CADEADO 20 MM</t>
+  </si>
+  <si>
+    <t>TESTE SIECON</t>
+  </si>
+  <si>
+    <t>W.01.0080</t>
+  </si>
+  <si>
+    <t>PREGO COM DUAS CABEÇA 17 X 27</t>
+  </si>
+  <si>
+    <t>W.01.0081</t>
+  </si>
+  <si>
+    <t>PREGO COM DUAS CABEÇA 18 X 27</t>
+  </si>
+  <si>
+    <t>00000000009969</t>
+  </si>
+  <si>
+    <t>LIMPO SOLUÇÕES</t>
+  </si>
+  <si>
+    <t>C.04.0001</t>
+  </si>
+  <si>
+    <t>ÁGUA SANITÁRIA 1 LT</t>
+  </si>
+  <si>
+    <t>W.01.0006</t>
+  </si>
+  <si>
+    <t>PREGO COMUM C/ CABEÇA 17 X 27</t>
+  </si>
+  <si>
+    <t>F.04.0035</t>
+  </si>
+  <si>
+    <t>TRADO MOTORIZADO À GASOLINA</t>
+  </si>
+  <si>
+    <t>DIA</t>
+  </si>
+  <si>
+    <t>H.11.0014</t>
+  </si>
+  <si>
+    <t>AÇO CA25 10,0 MM - VARA</t>
+  </si>
+  <si>
+    <t>O.01.0118</t>
+  </si>
+  <si>
+    <t>CHAPA PLASTIFICADO 17 MM - 2,20 X 1,10 M</t>
+  </si>
+  <si>
+    <t>J.10.0012</t>
+  </si>
+  <si>
+    <t>SUPER GRAUTE QUARTZOLIT</t>
+  </si>
+  <si>
+    <t>SC25</t>
+  </si>
+  <si>
+    <t>W.07.0002</t>
+  </si>
+  <si>
+    <t>ADESIVO ESTRUTURAL A BASE DE RESINA EPÓXI - FLUIDO - SIKADUR 32 - 1 KG</t>
+  </si>
+  <si>
+    <t>E.02.0062</t>
+  </si>
+  <si>
+    <t>TELA FACHADEIRA</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>K.02.0831</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 25 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.0832</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 32 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.0833</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 40 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.0834</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 50 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.0835</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 60 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.1806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLUÇÃO PREPARADORA  PARA TUBOS E CONEXÕS PVC 1 L</t>
+  </si>
+  <si>
+    <t>K.02.4669</t>
+  </si>
+  <si>
+    <t>ADESIVO ESPECIAL CPVC - FRASCO AQUATHERM - 850G</t>
+  </si>
+  <si>
+    <t>P.02.0012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERFIL  ALUMÍNIO  PERFURADO</t>
+  </si>
+  <si>
+    <t>00000000002393</t>
+  </si>
+  <si>
+    <t>SPW3</t>
+  </si>
+  <si>
+    <t>R.02.0180</t>
+  </si>
+  <si>
+    <t>TRINCHA 1"</t>
+  </si>
+  <si>
+    <t>J.02.0904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG CINZA</t>
+  </si>
+  <si>
+    <t>J.02.0905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG BRANCA</t>
+  </si>
+  <si>
+    <t>R.02.0181</t>
+  </si>
+  <si>
+    <t>TRINCHA 2"</t>
+  </si>
+  <si>
+    <t>W.06.0014</t>
+  </si>
+  <si>
+    <t>ADESIVO ESTRUTURAL DE CONSISTENCIA FLUIDA - DENVERPOXI</t>
+  </si>
+  <si>
+    <t>P2.01.0027</t>
+  </si>
+  <si>
+    <t>CANTONEIRA DE ALUMINIO 2 X 2 CM</t>
   </si>
 </sst>
 </file>
@@ -2248,7 +2416,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P319"/>
+  <dimension ref="A1:P368"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -13492,10 +13660,10 @@
         <v>100</v>
       </c>
       <c r="M225" s="4">
-        <v>8</v>
+        <v>10.15</v>
       </c>
       <c r="N225" s="4">
-        <v>800</v>
+        <v>1015</v>
       </c>
       <c r="O225" s="1" t="s">
         <v>499</v>
@@ -15448,10 +15616,10 @@
         <v>38</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="P264" s="1" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="265">
@@ -15498,10 +15666,10 @@
         <v>576</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="P265" s="1" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="266">
@@ -15548,10 +15716,10 @@
         <v>53</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="P266" s="1" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="267">
@@ -15698,10 +15866,10 @@
         <v>1260</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="P269" s="1" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="270">
@@ -15748,10 +15916,10 @@
         <v>550</v>
       </c>
       <c r="O270" s="1" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="P270" s="1" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="271">
@@ -15798,10 +15966,10 @@
         <v>5044</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>258</v>
+        <v>84</v>
       </c>
       <c r="P271" s="1" t="s">
-        <v>259</v>
+        <v>85</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="272">
@@ -17171,7 +17339,7 @@
         <v>46083.6671321991</v>
       </c>
       <c r="F299" s="2">
-        <v>82399</v>
+        <v>82400</v>
       </c>
       <c r="G299" s="3">
         <v>46083</v>
@@ -17189,19 +17357,19 @@
         <v>28</v>
       </c>
       <c r="L299" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M299" s="4">
-        <v>54.85</v>
+        <v>27.9</v>
       </c>
       <c r="N299" s="4">
-        <v>219.4</v>
+        <v>167.4</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="P299" s="1" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="300">
@@ -17221,16 +17389,16 @@
         <v>46083.6671321991</v>
       </c>
       <c r="F300" s="2">
-        <v>82401</v>
+        <v>82399</v>
       </c>
       <c r="G300" s="3">
         <v>46083</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>88</v>
+        <v>622</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>89</v>
+        <v>623</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>20</v>
@@ -17239,19 +17407,19 @@
         <v>28</v>
       </c>
       <c r="L300" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M300" s="4">
-        <v>29.99</v>
+        <v>43.3</v>
       </c>
       <c r="N300" s="4">
-        <v>89.97</v>
+        <v>433</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="P300" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="301">
@@ -17271,16 +17439,16 @@
         <v>46083.6671321991</v>
       </c>
       <c r="F301" s="2">
-        <v>82401</v>
+        <v>82399</v>
       </c>
       <c r="G301" s="3">
         <v>46083</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>20</v>
@@ -17289,19 +17457,19 @@
         <v>28</v>
       </c>
       <c r="L301" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M301" s="4">
-        <v>50.9</v>
+        <v>54.85</v>
       </c>
       <c r="N301" s="4">
-        <v>152.7</v>
+        <v>219.4</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="P301" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="302">
@@ -17321,16 +17489,16 @@
         <v>46083.6671321991</v>
       </c>
       <c r="F302" s="2">
-        <v>82399</v>
+        <v>82401</v>
       </c>
       <c r="G302" s="3">
         <v>46083</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>624</v>
+        <v>88</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>625</v>
+        <v>89</v>
       </c>
       <c r="J302" s="1" t="s">
         <v>20</v>
@@ -17339,19 +17507,19 @@
         <v>28</v>
       </c>
       <c r="L302" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M302" s="4">
-        <v>2.2</v>
+        <v>29.99</v>
       </c>
       <c r="N302" s="4">
-        <v>44</v>
+        <v>89.97</v>
       </c>
       <c r="O302" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="P302" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="303">
@@ -17377,25 +17545,25 @@
         <v>46083</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>215</v>
+        <v>626</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>216</v>
+        <v>627</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K303" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L303" s="4">
-        <v>200</v>
+        <v>3</v>
       </c>
       <c r="M303" s="4">
-        <v>5.8</v>
+        <v>50.9</v>
       </c>
       <c r="N303" s="4">
-        <v>1160</v>
+        <v>152.7</v>
       </c>
       <c r="O303" s="1" t="s">
         <v>40</v>
@@ -17421,37 +17589,37 @@
         <v>46083.6671321991</v>
       </c>
       <c r="F304" s="2">
-        <v>82401</v>
+        <v>82399</v>
       </c>
       <c r="G304" s="3">
         <v>46083</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>53</v>
+        <v>628</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>54</v>
+        <v>629</v>
       </c>
       <c r="J304" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K304" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L304" s="4">
+        <v>20</v>
+      </c>
+      <c r="M304" s="4">
+        <v>2.2</v>
+      </c>
+      <c r="N304" s="4">
+        <v>44</v>
+      </c>
+      <c r="O304" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P304" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="M304" s="4">
-        <v>34.5</v>
-      </c>
-      <c r="N304" s="4">
-        <v>1725</v>
-      </c>
-      <c r="O304" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="P304" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="305">
@@ -17470,31 +17638,39 @@
       <c r="E305" s="3">
         <v>46083.6671321991</v>
       </c>
-      <c r="F305" s="1"/>
-      <c r="G305" s="1"/>
+      <c r="F305" s="2">
+        <v>82401</v>
+      </c>
+      <c r="G305" s="3">
+        <v>46083</v>
+      </c>
       <c r="H305" s="1" t="s">
-        <v>626</v>
+        <v>215</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>627</v>
+        <v>216</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K305" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L305" s="4">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="M305" s="4">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N305" s="4">
-        <v>0</v>
-      </c>
-      <c r="O305" s="1"/>
-      <c r="P305" s="1"/>
+        <v>1160</v>
+      </c>
+      <c r="O305" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P305" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="306">
       <c r="A306" s="2">
@@ -17512,31 +17688,39 @@
       <c r="E306" s="3">
         <v>46083.6671321991</v>
       </c>
-      <c r="F306" s="1"/>
-      <c r="G306" s="1"/>
+      <c r="F306" s="2">
+        <v>82401</v>
+      </c>
+      <c r="G306" s="3">
+        <v>46083</v>
+      </c>
       <c r="H306" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K306" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L306" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M306" s="4">
-        <v>0</v>
+        <v>37.95</v>
       </c>
       <c r="N306" s="4">
-        <v>0</v>
-      </c>
-      <c r="O306" s="1"/>
-      <c r="P306" s="1"/>
+        <v>759</v>
+      </c>
+      <c r="O306" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P306" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="307">
       <c r="A307" s="2">
@@ -17554,13 +17738,17 @@
       <c r="E307" s="3">
         <v>46083.6671321991</v>
       </c>
-      <c r="F307" s="1"/>
-      <c r="G307" s="1"/>
+      <c r="F307" s="2">
+        <v>82401</v>
+      </c>
+      <c r="G307" s="3">
+        <v>46083</v>
+      </c>
       <c r="H307" s="1" t="s">
-        <v>630</v>
+        <v>53</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>631</v>
+        <v>54</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>20</v>
@@ -17569,16 +17757,20 @@
         <v>21</v>
       </c>
       <c r="L307" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="M307" s="4">
-        <v>0</v>
+        <v>34.5</v>
       </c>
       <c r="N307" s="4">
-        <v>0</v>
-      </c>
-      <c r="O307" s="1"/>
-      <c r="P307" s="1"/>
+        <v>1725</v>
+      </c>
+      <c r="O307" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P307" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="308">
       <c r="A308" s="2">
@@ -17596,31 +17788,39 @@
       <c r="E308" s="3">
         <v>46083.6671321991</v>
       </c>
-      <c r="F308" s="1"/>
-      <c r="G308" s="1"/>
+      <c r="F308" s="2">
+        <v>82412</v>
+      </c>
+      <c r="G308" s="3">
+        <v>46084</v>
+      </c>
       <c r="H308" s="1" t="s">
-        <v>632</v>
+        <v>566</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>633</v>
+        <v>567</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>257</v>
+        <v>28</v>
       </c>
       <c r="L308" s="4">
         <v>5</v>
       </c>
       <c r="M308" s="4">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="N308" s="4">
-        <v>0</v>
-      </c>
-      <c r="O308" s="1"/>
-      <c r="P308" s="1"/>
+        <v>745</v>
+      </c>
+      <c r="O308" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="P308" s="1" t="s">
+        <v>516</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="309">
       <c r="A309" s="2">
@@ -17638,13 +17838,17 @@
       <c r="E309" s="3">
         <v>46083.6671321991</v>
       </c>
-      <c r="F309" s="1"/>
-      <c r="G309" s="1"/>
+      <c r="F309" s="2">
+        <v>82415</v>
+      </c>
+      <c r="G309" s="3">
+        <v>46084</v>
+      </c>
       <c r="H309" s="1" t="s">
-        <v>566</v>
+        <v>632</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>567</v>
+        <v>633</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>20</v>
@@ -17656,13 +17860,17 @@
         <v>5</v>
       </c>
       <c r="M309" s="4">
-        <v>0</v>
+        <v>1242.36</v>
       </c>
       <c r="N309" s="4">
-        <v>0</v>
-      </c>
-      <c r="O309" s="1"/>
-      <c r="P309" s="1"/>
+        <v>6211.8</v>
+      </c>
+      <c r="O309" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P309" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="310">
       <c r="A310" s="2">
@@ -17689,10 +17897,10 @@
         <v>635</v>
       </c>
       <c r="J310" s="1" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="K310" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="L310" s="4">
         <v>5</v>
@@ -17722,8 +17930,12 @@
       <c r="E311" s="3">
         <v>46083.6694849421</v>
       </c>
-      <c r="F311" s="1"/>
-      <c r="G311" s="1"/>
+      <c r="F311" s="2">
+        <v>82417</v>
+      </c>
+      <c r="G311" s="3">
+        <v>46084</v>
+      </c>
       <c r="H311" s="1" t="s">
         <v>636</v>
       </c>
@@ -17740,13 +17952,17 @@
         <v>1</v>
       </c>
       <c r="M311" s="4">
-        <v>0</v>
+        <v>335.35</v>
       </c>
       <c r="N311" s="4">
-        <v>0</v>
-      </c>
-      <c r="O311" s="1"/>
-      <c r="P311" s="1"/>
+        <v>335.35</v>
+      </c>
+      <c r="O311" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P311" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="312">
       <c r="A312" s="2">
@@ -17764,8 +17980,12 @@
       <c r="E312" s="3">
         <v>46083.6694849421</v>
       </c>
-      <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
+      <c r="F312" s="2">
+        <v>82417</v>
+      </c>
+      <c r="G312" s="3">
+        <v>46084</v>
+      </c>
       <c r="H312" s="1" t="s">
         <v>638</v>
       </c>
@@ -17782,13 +18002,17 @@
         <v>3</v>
       </c>
       <c r="M312" s="4">
-        <v>0</v>
+        <v>237.99</v>
       </c>
       <c r="N312" s="4">
-        <v>0</v>
-      </c>
-      <c r="O312" s="1"/>
-      <c r="P312" s="1"/>
+        <v>713.97</v>
+      </c>
+      <c r="O312" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P312" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="313">
       <c r="A313" s="2">
@@ -17806,8 +18030,12 @@
       <c r="E313" s="3">
         <v>46083.6694849421</v>
       </c>
-      <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
+      <c r="F313" s="2">
+        <v>82417</v>
+      </c>
+      <c r="G313" s="3">
+        <v>46084</v>
+      </c>
       <c r="H313" s="1" t="s">
         <v>640</v>
       </c>
@@ -17824,13 +18052,17 @@
         <v>5</v>
       </c>
       <c r="M313" s="4">
-        <v>0</v>
+        <v>202.3</v>
       </c>
       <c r="N313" s="4">
-        <v>0</v>
-      </c>
-      <c r="O313" s="1"/>
-      <c r="P313" s="1"/>
+        <v>1011.5</v>
+      </c>
+      <c r="O313" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P313" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="314">
       <c r="A314" s="2">
@@ -17848,8 +18080,12 @@
       <c r="E314" s="3">
         <v>46083.6694849421</v>
       </c>
-      <c r="F314" s="1"/>
-      <c r="G314" s="1"/>
+      <c r="F314" s="2">
+        <v>82417</v>
+      </c>
+      <c r="G314" s="3">
+        <v>46084</v>
+      </c>
       <c r="H314" s="1" t="s">
         <v>642</v>
       </c>
@@ -17866,13 +18102,17 @@
         <v>12</v>
       </c>
       <c r="M314" s="4">
-        <v>0</v>
+        <v>1229.07</v>
       </c>
       <c r="N314" s="4">
-        <v>0</v>
-      </c>
-      <c r="O314" s="1"/>
-      <c r="P314" s="1"/>
+        <v>14748.84</v>
+      </c>
+      <c r="O314" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P314" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="315">
       <c r="A315" s="2">
@@ -17890,8 +18130,12 @@
       <c r="E315" s="3">
         <v>46083.6704391782</v>
       </c>
-      <c r="F315" s="1"/>
-      <c r="G315" s="1"/>
+      <c r="F315" s="2">
+        <v>82406</v>
+      </c>
+      <c r="G315" s="3">
+        <v>46084</v>
+      </c>
       <c r="H315" s="1" t="s">
         <v>644</v>
       </c>
@@ -17908,13 +18152,17 @@
         <v>4</v>
       </c>
       <c r="M315" s="4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N315" s="4">
-        <v>0</v>
-      </c>
-      <c r="O315" s="1"/>
-      <c r="P315" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="O315" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P315" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="316">
       <c r="A316" s="2">
@@ -17932,8 +18180,12 @@
       <c r="E316" s="3">
         <v>46083.6704391782</v>
       </c>
-      <c r="F316" s="1"/>
-      <c r="G316" s="1"/>
+      <c r="F316" s="2">
+        <v>82405</v>
+      </c>
+      <c r="G316" s="3">
+        <v>46084</v>
+      </c>
       <c r="H316" s="1" t="s">
         <v>262</v>
       </c>
@@ -17950,13 +18202,17 @@
         <v>10</v>
       </c>
       <c r="M316" s="4">
-        <v>0</v>
+        <v>23.43</v>
       </c>
       <c r="N316" s="4">
-        <v>0</v>
-      </c>
-      <c r="O316" s="1"/>
-      <c r="P316" s="1"/>
+        <v>234.3</v>
+      </c>
+      <c r="O316" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P316" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="317">
       <c r="A317" s="2">
@@ -17974,8 +18230,12 @@
       <c r="E317" s="3">
         <v>46083.6704391782</v>
       </c>
-      <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
+      <c r="F317" s="2">
+        <v>82405</v>
+      </c>
+      <c r="G317" s="3">
+        <v>46084</v>
+      </c>
       <c r="H317" s="1" t="s">
         <v>575</v>
       </c>
@@ -17992,13 +18252,17 @@
         <v>4</v>
       </c>
       <c r="M317" s="4">
-        <v>0</v>
+        <v>8.86</v>
       </c>
       <c r="N317" s="4">
-        <v>0</v>
-      </c>
-      <c r="O317" s="1"/>
-      <c r="P317" s="1"/>
+        <v>35.44</v>
+      </c>
+      <c r="O317" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="P317" s="1" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="318">
       <c r="A318" s="2">
@@ -18016,8 +18280,12 @@
       <c r="E318" s="3">
         <v>46083.6704391782</v>
       </c>
-      <c r="F318" s="1"/>
-      <c r="G318" s="1"/>
+      <c r="F318" s="2">
+        <v>82406</v>
+      </c>
+      <c r="G318" s="3">
+        <v>46084</v>
+      </c>
       <c r="H318" s="1" t="s">
         <v>319</v>
       </c>
@@ -18034,13 +18302,17 @@
         <v>50</v>
       </c>
       <c r="M318" s="4">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="N318" s="4">
-        <v>0</v>
-      </c>
-      <c r="O318" s="1"/>
-      <c r="P318" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="O318" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P318" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="319">
       <c r="A319" s="2">
@@ -18058,8 +18330,12 @@
       <c r="E319" s="3">
         <v>46083.6704391782</v>
       </c>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
+      <c r="F319" s="2">
+        <v>82406</v>
+      </c>
+      <c r="G319" s="3">
+        <v>46084</v>
+      </c>
       <c r="H319" s="1" t="s">
         <v>60</v>
       </c>
@@ -18076,13 +18352,2239 @@
         <v>2</v>
       </c>
       <c r="M319" s="4">
+        <v>28</v>
+      </c>
+      <c r="N319" s="4">
+        <v>56</v>
+      </c>
+      <c r="O319" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P319" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="320">
+      <c r="A320" s="2">
+        <v>500</v>
+      </c>
+      <c r="B320" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C320" s="1"/>
+      <c r="D320" s="2">
+        <v>6</v>
+      </c>
+      <c r="E320" s="3">
+        <v>46084.4672411921</v>
+      </c>
+      <c r="F320" s="1"/>
+      <c r="G320" s="1"/>
+      <c r="H320" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I320" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="J320" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K320" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L320" s="4">
+        <v>10</v>
+      </c>
+      <c r="M320" s="4">
+        <v>15</v>
+      </c>
+      <c r="N320" s="4">
+        <v>150</v>
+      </c>
+      <c r="O320" s="1"/>
+      <c r="P320" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="321">
+      <c r="A321" s="2">
+        <v>500</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C321" s="1"/>
+      <c r="D321" s="2">
+        <v>6</v>
+      </c>
+      <c r="E321" s="3">
+        <v>46084.4672411921</v>
+      </c>
+      <c r="F321" s="1"/>
+      <c r="G321" s="1"/>
+      <c r="H321" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="I321" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="J321" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K321" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L321" s="4">
+        <v>5</v>
+      </c>
+      <c r="M321" s="4">
+        <v>20</v>
+      </c>
+      <c r="N321" s="4">
+        <v>100</v>
+      </c>
+      <c r="O321" s="1"/>
+      <c r="P321" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="322">
+      <c r="A322" s="2">
+        <v>2512</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D322" s="2">
+        <v>20</v>
+      </c>
+      <c r="E322" s="3">
+        <v>46084.5055666204</v>
+      </c>
+      <c r="F322" s="2">
+        <v>82409</v>
+      </c>
+      <c r="G322" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H322" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I322" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="J322" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K322" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L322" s="4">
+        <v>30</v>
+      </c>
+      <c r="M322" s="4">
+        <v>34.5</v>
+      </c>
+      <c r="N322" s="4">
+        <v>1035</v>
+      </c>
+      <c r="O322" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P322" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="323">
+      <c r="A323" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B323" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C323" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D323" s="2">
+        <v>46</v>
+      </c>
+      <c r="E323" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F323" s="2">
+        <v>82411</v>
+      </c>
+      <c r="G323" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H323" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I323" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J323" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K323" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L323" s="4">
+        <v>4</v>
+      </c>
+      <c r="M323" s="4">
+        <v>22.5</v>
+      </c>
+      <c r="N323" s="4">
+        <v>90</v>
+      </c>
+      <c r="O323" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="P323" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="324">
+      <c r="A324" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D324" s="2">
+        <v>46</v>
+      </c>
+      <c r="E324" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F324" s="2">
+        <v>82411</v>
+      </c>
+      <c r="G324" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="I324" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="J324" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K324" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L324" s="4">
+        <v>20</v>
+      </c>
+      <c r="M324" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="N324" s="4">
+        <v>198</v>
+      </c>
+      <c r="O324" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="P324" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="325">
+      <c r="A325" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B325" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C325" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D325" s="2">
+        <v>46</v>
+      </c>
+      <c r="E325" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F325" s="2">
+        <v>82411</v>
+      </c>
+      <c r="G325" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H325" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="I325" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J325" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K325" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L325" s="4">
+        <v>4</v>
+      </c>
+      <c r="M325" s="4">
+        <v>6.99</v>
+      </c>
+      <c r="N325" s="4">
+        <v>27.96</v>
+      </c>
+      <c r="O325" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="P325" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="326">
+      <c r="A326" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B326" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D326" s="2">
+        <v>46</v>
+      </c>
+      <c r="E326" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F326" s="2">
+        <v>82411</v>
+      </c>
+      <c r="G326" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H326" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="I326" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="J326" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K326" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L326" s="4">
+        <v>2</v>
+      </c>
+      <c r="M326" s="4">
+        <v>19.9</v>
+      </c>
+      <c r="N326" s="4">
+        <v>39.8</v>
+      </c>
+      <c r="O326" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="P326" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="327">
+      <c r="A327" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D327" s="2">
+        <v>46</v>
+      </c>
+      <c r="E327" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F327" s="2">
+        <v>82411</v>
+      </c>
+      <c r="G327" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H327" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I327" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="J327" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K327" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L327" s="4">
+        <v>1</v>
+      </c>
+      <c r="M327" s="4">
+        <v>55.9</v>
+      </c>
+      <c r="N327" s="4">
+        <v>55.9</v>
+      </c>
+      <c r="O327" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="P327" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="328">
+      <c r="A328" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D328" s="2">
+        <v>46</v>
+      </c>
+      <c r="E328" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F328" s="2">
+        <v>82411</v>
+      </c>
+      <c r="G328" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H328" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I328" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J328" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K328" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L328" s="4">
+        <v>2</v>
+      </c>
+      <c r="M328" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="N328" s="4">
+        <v>19.8</v>
+      </c>
+      <c r="O328" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="P328" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="329">
+      <c r="A329" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D329" s="2">
+        <v>46</v>
+      </c>
+      <c r="E329" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F329" s="2">
+        <v>82411</v>
+      </c>
+      <c r="G329" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H329" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I329" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J329" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K329" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L329" s="4">
+        <v>3</v>
+      </c>
+      <c r="M329" s="4">
+        <v>24.85</v>
+      </c>
+      <c r="N329" s="4">
+        <v>74.55</v>
+      </c>
+      <c r="O329" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="P329" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="330">
+      <c r="A330" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D330" s="2">
+        <v>46</v>
+      </c>
+      <c r="E330" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F330" s="2">
+        <v>82410</v>
+      </c>
+      <c r="G330" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H330" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="I330" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="J330" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K330" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L330" s="4">
+        <v>10</v>
+      </c>
+      <c r="M330" s="4">
+        <v>12</v>
+      </c>
+      <c r="N330" s="4">
+        <v>120</v>
+      </c>
+      <c r="O330" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P330" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="331">
+      <c r="A331" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D331" s="2">
+        <v>46</v>
+      </c>
+      <c r="E331" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F331" s="1"/>
+      <c r="G331" s="1"/>
+      <c r="H331" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I331" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="J331" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K331" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="L331" s="4">
+        <v>30</v>
+      </c>
+      <c r="M331" s="4">
         <v>0</v>
       </c>
-      <c r="N319" s="4">
+      <c r="N331" s="4">
         <v>0</v>
       </c>
-      <c r="O319" s="1"/>
-      <c r="P319" s="1"/>
+      <c r="O331" s="1"/>
+      <c r="P331" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="332">
+      <c r="A332" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D332" s="2">
+        <v>46</v>
+      </c>
+      <c r="E332" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F332" s="1"/>
+      <c r="G332" s="1"/>
+      <c r="H332" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="I332" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="J332" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K332" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L332" s="4">
+        <v>8</v>
+      </c>
+      <c r="M332" s="4">
+        <v>0</v>
+      </c>
+      <c r="N332" s="4">
+        <v>0</v>
+      </c>
+      <c r="O332" s="1"/>
+      <c r="P332" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="333">
+      <c r="A333" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D333" s="2">
+        <v>46</v>
+      </c>
+      <c r="E333" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F333" s="1"/>
+      <c r="G333" s="1"/>
+      <c r="H333" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J333" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K333" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L333" s="4">
+        <v>90</v>
+      </c>
+      <c r="M333" s="4">
+        <v>0</v>
+      </c>
+      <c r="N333" s="4">
+        <v>0</v>
+      </c>
+      <c r="O333" s="1"/>
+      <c r="P333" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="334">
+      <c r="A334" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D334" s="2">
+        <v>46</v>
+      </c>
+      <c r="E334" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
+      <c r="H334" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I334" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J334" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K334" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L334" s="4">
+        <v>90</v>
+      </c>
+      <c r="M334" s="4">
+        <v>0</v>
+      </c>
+      <c r="N334" s="4">
+        <v>0</v>
+      </c>
+      <c r="O334" s="1"/>
+      <c r="P334" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="335">
+      <c r="A335" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D335" s="2">
+        <v>46</v>
+      </c>
+      <c r="E335" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F335" s="1"/>
+      <c r="G335" s="1"/>
+      <c r="H335" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I335" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J335" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K335" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L335" s="4">
+        <v>90</v>
+      </c>
+      <c r="M335" s="4">
+        <v>0</v>
+      </c>
+      <c r="N335" s="4">
+        <v>0</v>
+      </c>
+      <c r="O335" s="1"/>
+      <c r="P335" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="336">
+      <c r="A336" s="2">
+        <v>2505</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D336" s="2">
+        <v>46</v>
+      </c>
+      <c r="E336" s="3">
+        <v>46084.5060569213</v>
+      </c>
+      <c r="F336" s="1"/>
+      <c r="G336" s="1"/>
+      <c r="H336" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="I336" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="J336" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K336" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L336" s="4">
+        <v>10</v>
+      </c>
+      <c r="M336" s="4">
+        <v>0</v>
+      </c>
+      <c r="N336" s="4">
+        <v>0</v>
+      </c>
+      <c r="O336" s="1"/>
+      <c r="P336" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="337">
+      <c r="A337" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D337" s="2">
+        <v>32</v>
+      </c>
+      <c r="E337" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F337" s="2">
+        <v>82421</v>
+      </c>
+      <c r="G337" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H337" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I337" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J337" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K337" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L337" s="4">
+        <v>12</v>
+      </c>
+      <c r="M337" s="4">
+        <v>10.85</v>
+      </c>
+      <c r="N337" s="4">
+        <v>130.2</v>
+      </c>
+      <c r="O337" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P337" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="338">
+      <c r="A338" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D338" s="2">
+        <v>32</v>
+      </c>
+      <c r="E338" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F338" s="2">
+        <v>82420</v>
+      </c>
+      <c r="G338" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H338" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J338" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K338" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L338" s="4">
+        <v>2</v>
+      </c>
+      <c r="M338" s="4">
+        <v>270</v>
+      </c>
+      <c r="N338" s="4">
+        <v>540</v>
+      </c>
+      <c r="O338" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P338" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="339">
+      <c r="A339" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D339" s="2">
+        <v>32</v>
+      </c>
+      <c r="E339" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F339" s="2">
+        <v>82422</v>
+      </c>
+      <c r="G339" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H339" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J339" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K339" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L339" s="4">
+        <v>100</v>
+      </c>
+      <c r="M339" s="4">
+        <v>5</v>
+      </c>
+      <c r="N339" s="4">
+        <v>500</v>
+      </c>
+      <c r="O339" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="P339" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="340">
+      <c r="A340" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D340" s="2">
+        <v>32</v>
+      </c>
+      <c r="E340" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F340" s="2">
+        <v>82423</v>
+      </c>
+      <c r="G340" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H340" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="J340" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K340" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="L340" s="4">
+        <v>10</v>
+      </c>
+      <c r="M340" s="4">
+        <v>39</v>
+      </c>
+      <c r="N340" s="4">
+        <v>390</v>
+      </c>
+      <c r="O340" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P340" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="341">
+      <c r="A341" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D341" s="2">
+        <v>32</v>
+      </c>
+      <c r="E341" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F341" s="2">
+        <v>82419</v>
+      </c>
+      <c r="G341" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H341" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J341" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K341" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L341" s="4">
+        <v>50</v>
+      </c>
+      <c r="M341" s="4">
+        <v>34.5</v>
+      </c>
+      <c r="N341" s="4">
+        <v>1725</v>
+      </c>
+      <c r="O341" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P341" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="342">
+      <c r="A342" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D342" s="2">
+        <v>32</v>
+      </c>
+      <c r="E342" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F342" s="2">
+        <v>82420</v>
+      </c>
+      <c r="G342" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H342" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="J342" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K342" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L342" s="4">
+        <v>6</v>
+      </c>
+      <c r="M342" s="4">
+        <v>90.74</v>
+      </c>
+      <c r="N342" s="4">
+        <v>544.44</v>
+      </c>
+      <c r="O342" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P342" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="343">
+      <c r="A343" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D343" s="2">
+        <v>32</v>
+      </c>
+      <c r="E343" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F343" s="1"/>
+      <c r="G343" s="1"/>
+      <c r="H343" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="I343" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J343" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K343" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L343" s="4">
+        <v>6</v>
+      </c>
+      <c r="M343" s="4">
+        <v>0</v>
+      </c>
+      <c r="N343" s="4">
+        <v>0</v>
+      </c>
+      <c r="O343" s="1"/>
+      <c r="P343" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="344">
+      <c r="A344" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D344" s="2">
+        <v>32</v>
+      </c>
+      <c r="E344" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F344" s="1"/>
+      <c r="G344" s="1"/>
+      <c r="H344" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J344" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K344" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L344" s="4">
+        <v>20</v>
+      </c>
+      <c r="M344" s="4">
+        <v>0</v>
+      </c>
+      <c r="N344" s="4">
+        <v>0</v>
+      </c>
+      <c r="O344" s="1"/>
+      <c r="P344" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="345">
+      <c r="A345" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D345" s="2">
+        <v>32</v>
+      </c>
+      <c r="E345" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F345" s="1"/>
+      <c r="G345" s="1"/>
+      <c r="H345" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="I345" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="J345" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K345" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="L345" s="4">
+        <v>1</v>
+      </c>
+      <c r="M345" s="4">
+        <v>0</v>
+      </c>
+      <c r="N345" s="4">
+        <v>0</v>
+      </c>
+      <c r="O345" s="1"/>
+      <c r="P345" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="346">
+      <c r="A346" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D346" s="2">
+        <v>32</v>
+      </c>
+      <c r="E346" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F346" s="1"/>
+      <c r="G346" s="1"/>
+      <c r="H346" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I346" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J346" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K346" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L346" s="4">
+        <v>200</v>
+      </c>
+      <c r="M346" s="4">
+        <v>0</v>
+      </c>
+      <c r="N346" s="4">
+        <v>0</v>
+      </c>
+      <c r="O346" s="1"/>
+      <c r="P346" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="347">
+      <c r="A347" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D347" s="2">
+        <v>32</v>
+      </c>
+      <c r="E347" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F347" s="1"/>
+      <c r="G347" s="1"/>
+      <c r="H347" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I347" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J347" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K347" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L347" s="4">
+        <v>500</v>
+      </c>
+      <c r="M347" s="4">
+        <v>0</v>
+      </c>
+      <c r="N347" s="4">
+        <v>0</v>
+      </c>
+      <c r="O347" s="1"/>
+      <c r="P347" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="348">
+      <c r="A348" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D348" s="2">
+        <v>32</v>
+      </c>
+      <c r="E348" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F348" s="1"/>
+      <c r="G348" s="1"/>
+      <c r="H348" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="I348" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="J348" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K348" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L348" s="4">
+        <v>5</v>
+      </c>
+      <c r="M348" s="4">
+        <v>0</v>
+      </c>
+      <c r="N348" s="4">
+        <v>0</v>
+      </c>
+      <c r="O348" s="1"/>
+      <c r="P348" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="349">
+      <c r="A349" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D349" s="2">
+        <v>32</v>
+      </c>
+      <c r="E349" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F349" s="1"/>
+      <c r="G349" s="1"/>
+      <c r="H349" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="I349" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="J349" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K349" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L349" s="4">
+        <v>5</v>
+      </c>
+      <c r="M349" s="4">
+        <v>0</v>
+      </c>
+      <c r="N349" s="4">
+        <v>0</v>
+      </c>
+      <c r="O349" s="1"/>
+      <c r="P349" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="350">
+      <c r="A350" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D350" s="2">
+        <v>32</v>
+      </c>
+      <c r="E350" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F350" s="1"/>
+      <c r="G350" s="1"/>
+      <c r="H350" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="I350" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="J350" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K350" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L350" s="4">
+        <v>5</v>
+      </c>
+      <c r="M350" s="4">
+        <v>0</v>
+      </c>
+      <c r="N350" s="4">
+        <v>0</v>
+      </c>
+      <c r="O350" s="1"/>
+      <c r="P350" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="351">
+      <c r="A351" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C351" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D351" s="2">
+        <v>32</v>
+      </c>
+      <c r="E351" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F351" s="1"/>
+      <c r="G351" s="1"/>
+      <c r="H351" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="I351" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="J351" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K351" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L351" s="4">
+        <v>5</v>
+      </c>
+      <c r="M351" s="4">
+        <v>0</v>
+      </c>
+      <c r="N351" s="4">
+        <v>0</v>
+      </c>
+      <c r="O351" s="1"/>
+      <c r="P351" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="352">
+      <c r="A352" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D352" s="2">
+        <v>32</v>
+      </c>
+      <c r="E352" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F352" s="1"/>
+      <c r="G352" s="1"/>
+      <c r="H352" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="I352" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="J352" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K352" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L352" s="4">
+        <v>5</v>
+      </c>
+      <c r="M352" s="4">
+        <v>0</v>
+      </c>
+      <c r="N352" s="4">
+        <v>0</v>
+      </c>
+      <c r="O352" s="1"/>
+      <c r="P352" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="353">
+      <c r="A353" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D353" s="2">
+        <v>32</v>
+      </c>
+      <c r="E353" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F353" s="1"/>
+      <c r="G353" s="1"/>
+      <c r="H353" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="I353" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="J353" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K353" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L353" s="4">
+        <v>1</v>
+      </c>
+      <c r="M353" s="4">
+        <v>0</v>
+      </c>
+      <c r="N353" s="4">
+        <v>0</v>
+      </c>
+      <c r="O353" s="1"/>
+      <c r="P353" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="354">
+      <c r="A354" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D354" s="2">
+        <v>32</v>
+      </c>
+      <c r="E354" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F354" s="1"/>
+      <c r="G354" s="1"/>
+      <c r="H354" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="I354" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="J354" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K354" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L354" s="4">
+        <v>1</v>
+      </c>
+      <c r="M354" s="4">
+        <v>0</v>
+      </c>
+      <c r="N354" s="4">
+        <v>0</v>
+      </c>
+      <c r="O354" s="1"/>
+      <c r="P354" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="355">
+      <c r="A355" s="2">
+        <v>2509</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D355" s="2">
+        <v>32</v>
+      </c>
+      <c r="E355" s="3">
+        <v>46084.7378501505</v>
+      </c>
+      <c r="F355" s="1"/>
+      <c r="G355" s="1"/>
+      <c r="H355" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="I355" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="J355" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K355" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="L355" s="4">
+        <v>30</v>
+      </c>
+      <c r="M355" s="4">
+        <v>0</v>
+      </c>
+      <c r="N355" s="4">
+        <v>0</v>
+      </c>
+      <c r="O355" s="1"/>
+      <c r="P355" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="356">
+      <c r="A356" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D356" s="2">
+        <v>55</v>
+      </c>
+      <c r="E356" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F356" s="2">
+        <v>82424</v>
+      </c>
+      <c r="G356" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H356" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I356" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J356" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K356" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L356" s="4">
+        <v>20</v>
+      </c>
+      <c r="M356" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="N356" s="4">
+        <v>78</v>
+      </c>
+      <c r="O356" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P356" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="357">
+      <c r="A357" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D357" s="2">
+        <v>55</v>
+      </c>
+      <c r="E357" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F357" s="2">
+        <v>82426</v>
+      </c>
+      <c r="G357" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H357" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I357" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J357" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K357" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L357" s="4">
+        <v>5</v>
+      </c>
+      <c r="M357" s="4">
+        <v>10.85</v>
+      </c>
+      <c r="N357" s="4">
+        <v>54.25</v>
+      </c>
+      <c r="O357" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P357" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="358">
+      <c r="A358" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D358" s="2">
+        <v>55</v>
+      </c>
+      <c r="E358" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F358" s="2">
+        <v>82424</v>
+      </c>
+      <c r="G358" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H358" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I358" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J358" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K358" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L358" s="4">
+        <v>5</v>
+      </c>
+      <c r="M358" s="4">
+        <v>90</v>
+      </c>
+      <c r="N358" s="4">
+        <v>450</v>
+      </c>
+      <c r="O358" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P358" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="359">
+      <c r="A359" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D359" s="2">
+        <v>55</v>
+      </c>
+      <c r="E359" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F359" s="2">
+        <v>82425</v>
+      </c>
+      <c r="G359" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H359" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I359" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J359" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K359" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L359" s="4">
+        <v>20</v>
+      </c>
+      <c r="M359" s="4">
+        <v>16</v>
+      </c>
+      <c r="N359" s="4">
+        <v>320</v>
+      </c>
+      <c r="O359" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="P359" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="360">
+      <c r="A360" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D360" s="2">
+        <v>55</v>
+      </c>
+      <c r="E360" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F360" s="2">
+        <v>82424</v>
+      </c>
+      <c r="G360" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H360" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I360" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J360" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K360" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L360" s="4">
+        <v>2</v>
+      </c>
+      <c r="M360" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="N360" s="4">
+        <v>11.8</v>
+      </c>
+      <c r="O360" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P360" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="361">
+      <c r="A361" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C361" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D361" s="2">
+        <v>55</v>
+      </c>
+      <c r="E361" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F361" s="2">
+        <v>82424</v>
+      </c>
+      <c r="G361" s="3">
+        <v>46084</v>
+      </c>
+      <c r="H361" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I361" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="J361" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K361" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L361" s="4">
+        <v>2</v>
+      </c>
+      <c r="M361" s="4">
+        <v>2.15</v>
+      </c>
+      <c r="N361" s="4">
+        <v>4.3</v>
+      </c>
+      <c r="O361" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P361" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="362">
+      <c r="A362" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D362" s="2">
+        <v>55</v>
+      </c>
+      <c r="E362" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F362" s="1"/>
+      <c r="G362" s="1"/>
+      <c r="H362" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I362" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J362" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K362" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L362" s="4">
+        <v>8</v>
+      </c>
+      <c r="M362" s="4">
+        <v>0</v>
+      </c>
+      <c r="N362" s="4">
+        <v>0</v>
+      </c>
+      <c r="O362" s="1"/>
+      <c r="P362" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="363">
+      <c r="A363" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C363" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D363" s="2">
+        <v>55</v>
+      </c>
+      <c r="E363" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F363" s="1"/>
+      <c r="G363" s="1"/>
+      <c r="H363" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="I363" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="J363" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K363" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L363" s="4">
+        <v>10</v>
+      </c>
+      <c r="M363" s="4">
+        <v>0</v>
+      </c>
+      <c r="N363" s="4">
+        <v>0</v>
+      </c>
+      <c r="O363" s="1"/>
+      <c r="P363" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="364">
+      <c r="A364" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D364" s="2">
+        <v>55</v>
+      </c>
+      <c r="E364" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F364" s="1"/>
+      <c r="G364" s="1"/>
+      <c r="H364" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I364" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="J364" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K364" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L364" s="4">
+        <v>10</v>
+      </c>
+      <c r="M364" s="4">
+        <v>0</v>
+      </c>
+      <c r="N364" s="4">
+        <v>0</v>
+      </c>
+      <c r="O364" s="1"/>
+      <c r="P364" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="365">
+      <c r="A365" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D365" s="2">
+        <v>55</v>
+      </c>
+      <c r="E365" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F365" s="1"/>
+      <c r="G365" s="1"/>
+      <c r="H365" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="I365" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="J365" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K365" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L365" s="4">
+        <v>2</v>
+      </c>
+      <c r="M365" s="4">
+        <v>10.85</v>
+      </c>
+      <c r="N365" s="4">
+        <v>21.7</v>
+      </c>
+      <c r="O365" s="1"/>
+      <c r="P365" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="366">
+      <c r="A366" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D366" s="2">
+        <v>55</v>
+      </c>
+      <c r="E366" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F366" s="1"/>
+      <c r="G366" s="1"/>
+      <c r="H366" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I366" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J366" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K366" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L366" s="4">
+        <v>6</v>
+      </c>
+      <c r="M366" s="4">
+        <v>0</v>
+      </c>
+      <c r="N366" s="4">
+        <v>0</v>
+      </c>
+      <c r="O366" s="1"/>
+      <c r="P366" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="367">
+      <c r="A367" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D367" s="2">
+        <v>55</v>
+      </c>
+      <c r="E367" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F367" s="1"/>
+      <c r="G367" s="1"/>
+      <c r="H367" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="I367" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="J367" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K367" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L367" s="4">
+        <v>6</v>
+      </c>
+      <c r="M367" s="4">
+        <v>0</v>
+      </c>
+      <c r="N367" s="4">
+        <v>0</v>
+      </c>
+      <c r="O367" s="1"/>
+      <c r="P367" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="368">
+      <c r="A368" s="2">
+        <v>2504</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D368" s="2">
+        <v>55</v>
+      </c>
+      <c r="E368" s="3">
+        <v>46084.741264838</v>
+      </c>
+      <c r="F368" s="1"/>
+      <c r="G368" s="1"/>
+      <c r="H368" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="I368" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="J368" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K368" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L368" s="4">
+        <v>16</v>
+      </c>
+      <c r="M368" s="4">
+        <v>0</v>
+      </c>
+      <c r="N368" s="4">
+        <v>0</v>
+      </c>
+      <c r="O368" s="1"/>
+      <c r="P368" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="704">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1979,6 +1979,12 @@
     <t>ÁGUA SANITÁRIA 1 LT</t>
   </si>
   <si>
+    <t>O.01.0118</t>
+  </si>
+  <si>
+    <t>CHAPA PLASTIFICADO 17 MM - 2,20 X 1,10 M</t>
+  </si>
+  <si>
     <t>W.01.0006</t>
   </si>
   <si>
@@ -2000,10 +2006,19 @@
     <t>AÇO CA25 10,0 MM - VARA</t>
   </si>
   <si>
-    <t>O.01.0118</t>
-  </si>
-  <si>
-    <t>CHAPA PLASTIFICADO 17 MM - 2,20 X 1,10 M</t>
+    <t>00000000002393</t>
+  </si>
+  <si>
+    <t>SPW3</t>
+  </si>
+  <si>
+    <t>E.02.0062</t>
+  </si>
+  <si>
+    <t>TELA FACHADEIRA</t>
+  </si>
+  <si>
+    <t>M2</t>
   </si>
   <si>
     <t>J.10.0012</t>
@@ -2021,15 +2036,6 @@
     <t>ADESIVO ESTRUTURAL A BASE DE RESINA EPÓXI - FLUIDO - SIKADUR 32 - 1 KG</t>
   </si>
   <si>
-    <t>E.02.0062</t>
-  </si>
-  <si>
-    <t>TELA FACHADEIRA</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
     <t>K.02.0831</t>
   </si>
   <si>
@@ -2078,28 +2084,28 @@
     <t xml:space="preserve">PERFIL  ALUMÍNIO  PERFURADO</t>
   </si>
   <si>
-    <t>00000000002393</t>
-  </si>
-  <si>
-    <t>SPW3</t>
+    <t>00000000009021</t>
+  </si>
+  <si>
+    <t>AKEMI REPRESENTANTE</t>
+  </si>
+  <si>
+    <t>J.02.0904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG CINZA</t>
+  </si>
+  <si>
+    <t>J.02.0905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG BRANCA</t>
   </si>
   <si>
     <t>R.02.0180</t>
   </si>
   <si>
     <t>TRINCHA 1"</t>
-  </si>
-  <si>
-    <t>J.02.0904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG CINZA</t>
-  </si>
-  <si>
-    <t>J.02.0905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG BRANCA</t>
   </si>
   <si>
     <t>R.02.0181</t>
@@ -18861,37 +18867,37 @@
         <v>46084.5060569213</v>
       </c>
       <c r="F330" s="2">
-        <v>82410</v>
+        <v>82432</v>
       </c>
       <c r="G330" s="3">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>655</v>
+        <v>245</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>656</v>
+        <v>246</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K330" s="1" t="s">
-        <v>257</v>
+        <v>73</v>
       </c>
       <c r="L330" s="4">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="M330" s="4">
-        <v>12</v>
+        <v>3.33333</v>
       </c>
       <c r="N330" s="4">
-        <v>120</v>
+        <v>299.9997</v>
       </c>
       <c r="O330" s="1" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="P330" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="331">
@@ -18910,31 +18916,39 @@
       <c r="E331" s="3">
         <v>46084.5060569213</v>
       </c>
-      <c r="F331" s="1"/>
-      <c r="G331" s="1"/>
+      <c r="F331" s="2">
+        <v>82432</v>
+      </c>
+      <c r="G331" s="3">
+        <v>46085</v>
+      </c>
       <c r="H331" s="1" t="s">
-        <v>657</v>
+        <v>251</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>658</v>
+        <v>252</v>
       </c>
       <c r="J331" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K331" s="1" t="s">
-        <v>659</v>
+        <v>73</v>
       </c>
       <c r="L331" s="4">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M331" s="4">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="N331" s="4">
-        <v>0</v>
-      </c>
-      <c r="O331" s="1"/>
-      <c r="P331" s="1"/>
+        <v>864</v>
+      </c>
+      <c r="O331" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="P331" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="332">
       <c r="A332" s="2">
@@ -18952,31 +18966,39 @@
       <c r="E332" s="3">
         <v>46084.5060569213</v>
       </c>
-      <c r="F332" s="1"/>
-      <c r="G332" s="1"/>
+      <c r="F332" s="2">
+        <v>82432</v>
+      </c>
+      <c r="G332" s="3">
+        <v>46085</v>
+      </c>
       <c r="H332" s="1" t="s">
-        <v>660</v>
+        <v>253</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>661</v>
+        <v>254</v>
       </c>
       <c r="J332" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K332" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="L332" s="4">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="M332" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N332" s="4">
-        <v>0</v>
-      </c>
-      <c r="O332" s="1"/>
-      <c r="P332" s="1"/>
+        <v>1260</v>
+      </c>
+      <c r="O332" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="P332" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="333">
       <c r="A333" s="2">
@@ -18994,31 +19016,39 @@
       <c r="E333" s="3">
         <v>46084.5060569213</v>
       </c>
-      <c r="F333" s="1"/>
-      <c r="G333" s="1"/>
+      <c r="F333" s="2">
+        <v>82432</v>
+      </c>
+      <c r="G333" s="3">
+        <v>46085</v>
+      </c>
       <c r="H333" s="1" t="s">
-        <v>245</v>
+        <v>655</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>246</v>
+        <v>656</v>
       </c>
       <c r="J333" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K333" s="1" t="s">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="L333" s="4">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="M333" s="4">
-        <v>0</v>
+        <v>172.9</v>
       </c>
       <c r="N333" s="4">
-        <v>0</v>
-      </c>
-      <c r="O333" s="1"/>
-      <c r="P333" s="1"/>
+        <v>1729</v>
+      </c>
+      <c r="O333" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="P333" s="1" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="334">
       <c r="A334" s="2">
@@ -19036,31 +19066,39 @@
       <c r="E334" s="3">
         <v>46084.5060569213</v>
       </c>
-      <c r="F334" s="1"/>
-      <c r="G334" s="1"/>
+      <c r="F334" s="2">
+        <v>82410</v>
+      </c>
+      <c r="G334" s="3">
+        <v>46084</v>
+      </c>
       <c r="H334" s="1" t="s">
-        <v>251</v>
+        <v>657</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>252</v>
+        <v>658</v>
       </c>
       <c r="J334" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K334" s="1" t="s">
-        <v>73</v>
+        <v>257</v>
       </c>
       <c r="L334" s="4">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="M334" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N334" s="4">
-        <v>0</v>
-      </c>
-      <c r="O334" s="1"/>
-      <c r="P334" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="O334" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="P334" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="335">
       <c r="A335" s="2">
@@ -19081,19 +19119,19 @@
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
       <c r="H335" s="1" t="s">
-        <v>253</v>
+        <v>659</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>254</v>
+        <v>660</v>
       </c>
       <c r="J335" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K335" s="1" t="s">
-        <v>73</v>
+        <v>661</v>
       </c>
       <c r="L335" s="4">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="M335" s="4">
         <v>0</v>
@@ -19135,7 +19173,7 @@
         <v>28</v>
       </c>
       <c r="L336" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M336" s="4">
         <v>0</v>
@@ -19169,10 +19207,10 @@
         <v>46084</v>
       </c>
       <c r="H337" s="1" t="s">
-        <v>26</v>
+        <v>599</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>27</v>
+        <v>600</v>
       </c>
       <c r="J337" s="1" t="s">
         <v>20</v>
@@ -19181,13 +19219,13 @@
         <v>28</v>
       </c>
       <c r="L337" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M337" s="4">
-        <v>10.85</v>
+        <v>5.5</v>
       </c>
       <c r="N337" s="4">
-        <v>130.2</v>
+        <v>33</v>
       </c>
       <c r="O337" s="1" t="s">
         <v>191</v>
@@ -19213,37 +19251,37 @@
         <v>46084.7378501505</v>
       </c>
       <c r="F338" s="2">
-        <v>82420</v>
+        <v>82421</v>
       </c>
       <c r="G338" s="3">
         <v>46084</v>
       </c>
       <c r="H338" s="1" t="s">
-        <v>315</v>
+        <v>26</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>316</v>
+        <v>27</v>
       </c>
       <c r="J338" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K338" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L338" s="4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M338" s="4">
-        <v>270</v>
+        <v>10.85</v>
       </c>
       <c r="N338" s="4">
-        <v>540</v>
+        <v>130.2</v>
       </c>
       <c r="O338" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="P338" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="339">
@@ -19263,37 +19301,37 @@
         <v>46084.7378501505</v>
       </c>
       <c r="F339" s="2">
-        <v>82422</v>
+        <v>82434</v>
       </c>
       <c r="G339" s="3">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="H339" s="1" t="s">
-        <v>168</v>
+        <v>315</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>169</v>
+        <v>316</v>
       </c>
       <c r="J339" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K339" s="1" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="L339" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="M339" s="4">
-        <v>5</v>
+        <v>295</v>
       </c>
       <c r="N339" s="4">
-        <v>500</v>
+        <v>590</v>
       </c>
       <c r="O339" s="1" t="s">
-        <v>388</v>
+        <v>664</v>
       </c>
       <c r="P339" s="1" t="s">
-        <v>389</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="340">
@@ -19313,37 +19351,37 @@
         <v>46084.7378501505</v>
       </c>
       <c r="F340" s="2">
-        <v>82423</v>
+        <v>82422</v>
       </c>
       <c r="G340" s="3">
         <v>46084</v>
       </c>
       <c r="H340" s="1" t="s">
-        <v>664</v>
+        <v>168</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>665</v>
+        <v>169</v>
       </c>
       <c r="J340" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K340" s="1" t="s">
-        <v>666</v>
+        <v>73</v>
       </c>
       <c r="L340" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M340" s="4">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="N340" s="4">
-        <v>390</v>
+        <v>500</v>
       </c>
       <c r="O340" s="1" t="s">
-        <v>180</v>
+        <v>388</v>
       </c>
       <c r="P340" s="1" t="s">
-        <v>181</v>
+        <v>389</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="341">
@@ -19363,37 +19401,37 @@
         <v>46084.7378501505</v>
       </c>
       <c r="F341" s="2">
-        <v>82419</v>
+        <v>82434</v>
       </c>
       <c r="G341" s="3">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="H341" s="1" t="s">
-        <v>306</v>
+        <v>262</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="J341" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K341" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L341" s="4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M341" s="4">
-        <v>34.5</v>
+        <v>15.5</v>
       </c>
       <c r="N341" s="4">
-        <v>1725</v>
+        <v>310</v>
       </c>
       <c r="O341" s="1" t="s">
-        <v>22</v>
+        <v>664</v>
       </c>
       <c r="P341" s="1" t="s">
-        <v>23</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="342">
@@ -19413,37 +19451,37 @@
         <v>46084.7378501505</v>
       </c>
       <c r="F342" s="2">
-        <v>82420</v>
+        <v>82433</v>
       </c>
       <c r="G342" s="3">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="H342" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="I342" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="I342" s="1" t="s">
+      <c r="J342" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K342" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="J342" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K342" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="L342" s="4">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="M342" s="4">
-        <v>90.74</v>
+        <v>2.9</v>
       </c>
       <c r="N342" s="4">
-        <v>544.44</v>
+        <v>870</v>
       </c>
       <c r="O342" s="1" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="P342" s="1" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="343">
@@ -19462,31 +19500,39 @@
       <c r="E343" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F343" s="1"/>
-      <c r="G343" s="1"/>
+      <c r="F343" s="2">
+        <v>82423</v>
+      </c>
+      <c r="G343" s="3">
+        <v>46084</v>
+      </c>
       <c r="H343" s="1" t="s">
-        <v>599</v>
+        <v>669</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="J343" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K343" s="1" t="s">
-        <v>28</v>
+        <v>671</v>
       </c>
       <c r="L343" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M343" s="4">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="N343" s="4">
-        <v>0</v>
-      </c>
-      <c r="O343" s="1"/>
-      <c r="P343" s="1"/>
+        <v>425</v>
+      </c>
+      <c r="O343" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P343" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="344">
       <c r="A344" s="2">
@@ -19504,31 +19550,39 @@
       <c r="E344" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F344" s="1"/>
-      <c r="G344" s="1"/>
+      <c r="F344" s="2">
+        <v>82419</v>
+      </c>
+      <c r="G344" s="3">
+        <v>46084</v>
+      </c>
       <c r="H344" s="1" t="s">
-        <v>262</v>
+        <v>18</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>263</v>
+        <v>19</v>
       </c>
       <c r="J344" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K344" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L344" s="4">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="M344" s="4">
-        <v>0</v>
+        <v>33.99</v>
       </c>
       <c r="N344" s="4">
-        <v>0</v>
-      </c>
-      <c r="O344" s="1"/>
-      <c r="P344" s="1"/>
+        <v>6798</v>
+      </c>
+      <c r="O344" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P344" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="345">
       <c r="A345" s="2">
@@ -19546,31 +19600,39 @@
       <c r="E345" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F345" s="1"/>
-      <c r="G345" s="1"/>
+      <c r="F345" s="2">
+        <v>82419</v>
+      </c>
+      <c r="G345" s="3">
+        <v>46084</v>
+      </c>
       <c r="H345" s="1" t="s">
-        <v>669</v>
+        <v>215</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>670</v>
+        <v>216</v>
       </c>
       <c r="J345" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K345" s="1" t="s">
-        <v>671</v>
+        <v>21</v>
       </c>
       <c r="L345" s="4">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="M345" s="4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N345" s="4">
-        <v>0</v>
-      </c>
-      <c r="O345" s="1"/>
-      <c r="P345" s="1"/>
+        <v>1750</v>
+      </c>
+      <c r="O345" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P345" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="346">
       <c r="A346" s="2">
@@ -19588,13 +19650,17 @@
       <c r="E346" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F346" s="1"/>
-      <c r="G346" s="1"/>
+      <c r="F346" s="2">
+        <v>82423</v>
+      </c>
+      <c r="G346" s="3">
+        <v>46084</v>
+      </c>
       <c r="H346" s="1" t="s">
-        <v>18</v>
+        <v>306</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>19</v>
+        <v>307</v>
       </c>
       <c r="J346" s="1" t="s">
         <v>20</v>
@@ -19603,16 +19669,20 @@
         <v>21</v>
       </c>
       <c r="L346" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M346" s="4">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="N346" s="4">
-        <v>0</v>
-      </c>
-      <c r="O346" s="1"/>
-      <c r="P346" s="1"/>
+        <v>1875</v>
+      </c>
+      <c r="O346" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P346" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="347">
       <c r="A347" s="2">
@@ -19630,31 +19700,39 @@
       <c r="E347" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F347" s="1"/>
-      <c r="G347" s="1"/>
+      <c r="F347" s="2">
+        <v>82420</v>
+      </c>
+      <c r="G347" s="3">
+        <v>46084</v>
+      </c>
       <c r="H347" s="1" t="s">
-        <v>215</v>
+        <v>672</v>
       </c>
       <c r="I347" s="1" t="s">
-        <v>216</v>
+        <v>673</v>
       </c>
       <c r="J347" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K347" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L347" s="4">
-        <v>500</v>
+        <v>6</v>
       </c>
       <c r="M347" s="4">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="N347" s="4">
-        <v>0</v>
-      </c>
-      <c r="O347" s="1"/>
-      <c r="P347" s="1"/>
+        <v>594</v>
+      </c>
+      <c r="O347" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P347" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="348">
       <c r="A348" s="2">
@@ -19675,10 +19753,10 @@
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
       <c r="H348" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="J348" s="1" t="s">
         <v>20</v>
@@ -19717,10 +19795,10 @@
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
       <c r="H349" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J349" s="1" t="s">
         <v>20</v>
@@ -19759,10 +19837,10 @@
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
       <c r="H350" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J350" s="1" t="s">
         <v>20</v>
@@ -19801,10 +19879,10 @@
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
       <c r="H351" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J351" s="1" t="s">
         <v>20</v>
@@ -19843,10 +19921,10 @@
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
       <c r="H352" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="J352" s="1" t="s">
         <v>20</v>
@@ -19885,10 +19963,10 @@
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
       <c r="H353" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J353" s="1" t="s">
         <v>20</v>
@@ -19927,10 +20005,10 @@
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
       <c r="H354" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J354" s="1" t="s">
         <v>20</v>
@@ -19969,10 +20047,10 @@
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
       <c r="H355" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J355" s="1" t="s">
         <v>20</v>
@@ -20009,7 +20087,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="F356" s="2">
-        <v>82424</v>
+        <v>82426</v>
       </c>
       <c r="G356" s="3">
         <v>46084</v>
@@ -20030,16 +20108,16 @@
         <v>20</v>
       </c>
       <c r="M356" s="4">
-        <v>3.9</v>
+        <v>4.53</v>
       </c>
       <c r="N356" s="4">
-        <v>78</v>
+        <v>90.6</v>
       </c>
       <c r="O356" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="P356" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="357">
@@ -20109,7 +20187,7 @@
         <v>46084.741264838</v>
       </c>
       <c r="F358" s="2">
-        <v>82424</v>
+        <v>82425</v>
       </c>
       <c r="G358" s="3">
         <v>46084</v>
@@ -20136,10 +20214,10 @@
         <v>450</v>
       </c>
       <c r="O358" s="1" t="s">
-        <v>165</v>
+        <v>664</v>
       </c>
       <c r="P358" s="1" t="s">
-        <v>166</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="359">
@@ -20180,16 +20258,16 @@
         <v>20</v>
       </c>
       <c r="M359" s="4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="N359" s="4">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="O359" s="1" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="P359" s="1" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="360">
@@ -20209,37 +20287,37 @@
         <v>46084.741264838</v>
       </c>
       <c r="F360" s="2">
-        <v>82424</v>
+        <v>82431</v>
       </c>
       <c r="G360" s="3">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="H360" s="1" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
       <c r="I360" s="1" t="s">
-        <v>267</v>
+        <v>43</v>
       </c>
       <c r="J360" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K360" s="1" t="s">
-        <v>268</v>
+        <v>39</v>
       </c>
       <c r="L360" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M360" s="4">
-        <v>5.9</v>
+        <v>755.01</v>
       </c>
       <c r="N360" s="4">
-        <v>11.8</v>
+        <v>6040.08</v>
       </c>
       <c r="O360" s="1" t="s">
-        <v>165</v>
+        <v>690</v>
       </c>
       <c r="P360" s="1" t="s">
-        <v>166</v>
+        <v>691</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="361">
@@ -20259,37 +20337,37 @@
         <v>46084.741264838</v>
       </c>
       <c r="F361" s="2">
-        <v>82424</v>
+        <v>82425</v>
       </c>
       <c r="G361" s="3">
         <v>46084</v>
       </c>
       <c r="H361" s="1" t="s">
-        <v>690</v>
+        <v>266</v>
       </c>
       <c r="I361" s="1" t="s">
-        <v>691</v>
+        <v>267</v>
       </c>
       <c r="J361" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K361" s="1" t="s">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="L361" s="4">
         <v>2</v>
       </c>
       <c r="M361" s="4">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="N361" s="4">
-        <v>4.3</v>
+        <v>11.8</v>
       </c>
       <c r="O361" s="1" t="s">
-        <v>165</v>
+        <v>664</v>
       </c>
       <c r="P361" s="1" t="s">
-        <v>166</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="362">
@@ -20308,31 +20386,39 @@
       <c r="E362" s="3">
         <v>46084.741264838</v>
       </c>
-      <c r="F362" s="1"/>
-      <c r="G362" s="1"/>
+      <c r="F362" s="2">
+        <v>82430</v>
+      </c>
+      <c r="G362" s="3">
+        <v>46085</v>
+      </c>
       <c r="H362" s="1" t="s">
-        <v>42</v>
+        <v>692</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>43</v>
+        <v>693</v>
       </c>
       <c r="J362" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K362" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L362" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M362" s="4">
-        <v>0</v>
+        <v>38.6</v>
       </c>
       <c r="N362" s="4">
-        <v>0</v>
-      </c>
-      <c r="O362" s="1"/>
-      <c r="P362" s="1"/>
+        <v>386</v>
+      </c>
+      <c r="O362" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P362" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="363">
       <c r="A363" s="2">
@@ -20350,13 +20436,17 @@
       <c r="E363" s="3">
         <v>46084.741264838</v>
       </c>
-      <c r="F363" s="1"/>
-      <c r="G363" s="1"/>
+      <c r="F363" s="2">
+        <v>82430</v>
+      </c>
+      <c r="G363" s="3">
+        <v>46085</v>
+      </c>
       <c r="H363" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I363" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="J363" s="1" t="s">
         <v>20</v>
@@ -20368,13 +20458,17 @@
         <v>10</v>
       </c>
       <c r="M363" s="4">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="N363" s="4">
-        <v>0</v>
-      </c>
-      <c r="O363" s="1"/>
-      <c r="P363" s="1"/>
+        <v>650</v>
+      </c>
+      <c r="O363" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P363" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="364">
       <c r="A364" s="2">
@@ -20392,13 +20486,17 @@
       <c r="E364" s="3">
         <v>46084.741264838</v>
       </c>
-      <c r="F364" s="1"/>
-      <c r="G364" s="1"/>
+      <c r="F364" s="2">
+        <v>82425</v>
+      </c>
+      <c r="G364" s="3">
+        <v>46084</v>
+      </c>
       <c r="H364" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J364" s="1" t="s">
         <v>20</v>
@@ -20407,16 +20505,20 @@
         <v>28</v>
       </c>
       <c r="L364" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M364" s="4">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="N364" s="4">
-        <v>0</v>
-      </c>
-      <c r="O364" s="1"/>
-      <c r="P364" s="1"/>
+        <v>4.3</v>
+      </c>
+      <c r="O364" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P364" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="365">
       <c r="A365" s="2">
@@ -20434,13 +20536,17 @@
       <c r="E365" s="3">
         <v>46084.741264838</v>
       </c>
-      <c r="F365" s="1"/>
-      <c r="G365" s="1"/>
+      <c r="F365" s="2">
+        <v>82425</v>
+      </c>
+      <c r="G365" s="3">
+        <v>46084</v>
+      </c>
       <c r="H365" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I365" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J365" s="1" t="s">
         <v>20</v>
@@ -20457,8 +20563,12 @@
       <c r="N365" s="4">
         <v>21.7</v>
       </c>
-      <c r="O365" s="1"/>
-      <c r="P365" s="1"/>
+      <c r="O365" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P365" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="366">
       <c r="A366" s="2">
@@ -20476,8 +20586,12 @@
       <c r="E366" s="3">
         <v>46084.741264838</v>
       </c>
-      <c r="F366" s="1"/>
-      <c r="G366" s="1"/>
+      <c r="F366" s="2">
+        <v>82425</v>
+      </c>
+      <c r="G366" s="3">
+        <v>46084</v>
+      </c>
       <c r="H366" s="1" t="s">
         <v>60</v>
       </c>
@@ -20494,13 +20608,17 @@
         <v>6</v>
       </c>
       <c r="M366" s="4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="N366" s="4">
-        <v>0</v>
-      </c>
-      <c r="O366" s="1"/>
-      <c r="P366" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="O366" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P366" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="367">
       <c r="A367" s="2">
@@ -20518,13 +20636,17 @@
       <c r="E367" s="3">
         <v>46084.741264838</v>
       </c>
-      <c r="F367" s="1"/>
-      <c r="G367" s="1"/>
+      <c r="F367" s="2">
+        <v>82425</v>
+      </c>
+      <c r="G367" s="3">
+        <v>46084</v>
+      </c>
       <c r="H367" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="J367" s="1" t="s">
         <v>20</v>
@@ -20536,13 +20658,17 @@
         <v>6</v>
       </c>
       <c r="M367" s="4">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="N367" s="4">
-        <v>0</v>
-      </c>
-      <c r="O367" s="1"/>
-      <c r="P367" s="1"/>
+        <v>147</v>
+      </c>
+      <c r="O367" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P367" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="368">
       <c r="A368" s="2">
@@ -20560,13 +20686,17 @@
       <c r="E368" s="3">
         <v>46084.741264838</v>
       </c>
-      <c r="F368" s="1"/>
-      <c r="G368" s="1"/>
+      <c r="F368" s="2">
+        <v>82425</v>
+      </c>
+      <c r="G368" s="3">
+        <v>46084</v>
+      </c>
       <c r="H368" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I368" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J368" s="1" t="s">
         <v>20</v>
@@ -20575,16 +20705,20 @@
         <v>73</v>
       </c>
       <c r="L368" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M368" s="4">
-        <v>0</v>
+        <v>26.9</v>
       </c>
       <c r="N368" s="4">
-        <v>0</v>
-      </c>
-      <c r="O368" s="1"/>
-      <c r="P368" s="1"/>
+        <v>484.2</v>
+      </c>
+      <c r="O368" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P368" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="730">
   <si>
     <t>EMPRD</t>
   </si>
@@ -2124,6 +2124,84 @@
   </si>
   <si>
     <t>CANTONEIRA DE ALUMINIO 2 X 2 CM</t>
+  </si>
+  <si>
+    <t>00000000000474</t>
+  </si>
+  <si>
+    <t>TROX</t>
+  </si>
+  <si>
+    <t>C.01.0001</t>
+  </si>
+  <si>
+    <t>AGUA CARRO PIPA</t>
+  </si>
+  <si>
+    <t>E.02.0027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONA TERREIRO PRETA  8 X 100M</t>
+  </si>
+  <si>
+    <t>U.02.0829</t>
+  </si>
+  <si>
+    <t>TORNEIRA 1198 C LAVATÓRIO MESA LINK DECA</t>
+  </si>
+  <si>
+    <t>U.01.3091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUBA DE APOIO REDONDA  40 X 40 CM DECA  L 12040  17 SLIM BRANCA</t>
+  </si>
+  <si>
+    <t>00000000000573</t>
+  </si>
+  <si>
+    <t>AGILIZE</t>
+  </si>
+  <si>
+    <t>C.04.0025</t>
+  </si>
+  <si>
+    <t>SACO PLÁSTICO P/ LIXO - 300 L C/ 100 UN REFORÇADO</t>
+  </si>
+  <si>
+    <t>E.04.0047</t>
+  </si>
+  <si>
+    <t>PONTEIRO FORJADO EM AÇO REDONDO - 12''</t>
+  </si>
+  <si>
+    <t>E.03.0041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA DE LATEX  PRETA SEM FORRO ESPESSURA: 0,62 MM MUCAMBO</t>
+  </si>
+  <si>
+    <t>E.03.0259</t>
+  </si>
+  <si>
+    <t>MACACÃO TREVIRA KP500 COM LUVA E BOTA ACOPLADO</t>
+  </si>
+  <si>
+    <t>L.01.0004</t>
+  </si>
+  <si>
+    <t>BLOCO CERÂMICO 09 X 19 X 39</t>
+  </si>
+  <si>
+    <t>M.09.0074</t>
+  </si>
+  <si>
+    <t>TELA</t>
+  </si>
+  <si>
+    <t>W.06.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLA PVA  X 0 35  PULVITEC C/ 50KG</t>
   </si>
 </sst>
 </file>
@@ -2422,7 +2500,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P368"/>
+  <dimension ref="A1:P394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -20720,6 +20798,1194 @@
         <v>665</v>
       </c>
     </row>
+    <row ht="12.75" customHeight="1" r="369">
+      <c r="A369" s="2">
+        <v>2510</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D369" s="2">
+        <v>36</v>
+      </c>
+      <c r="E369" s="3">
+        <v>46085.6249659838</v>
+      </c>
+      <c r="F369" s="2">
+        <v>82435</v>
+      </c>
+      <c r="G369" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H369" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="J369" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K369" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L369" s="4">
+        <v>1</v>
+      </c>
+      <c r="M369" s="4">
+        <v>12860.35</v>
+      </c>
+      <c r="N369" s="4">
+        <v>12860.35</v>
+      </c>
+      <c r="O369" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="P369" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="370">
+      <c r="A370" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D370" s="2">
+        <v>284</v>
+      </c>
+      <c r="E370" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F370" s="2">
+        <v>82439</v>
+      </c>
+      <c r="G370" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H370" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I370" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J370" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K370" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L370" s="4">
+        <v>30</v>
+      </c>
+      <c r="M370" s="4">
+        <v>1.88</v>
+      </c>
+      <c r="N370" s="4">
+        <v>56.4</v>
+      </c>
+      <c r="O370" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P370" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="371">
+      <c r="A371" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D371" s="2">
+        <v>284</v>
+      </c>
+      <c r="E371" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F371" s="2">
+        <v>82440</v>
+      </c>
+      <c r="G371" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H371" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I371" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J371" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K371" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L371" s="4">
+        <v>10</v>
+      </c>
+      <c r="M371" s="4">
+        <v>10.85</v>
+      </c>
+      <c r="N371" s="4">
+        <v>108.5</v>
+      </c>
+      <c r="O371" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P371" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="372">
+      <c r="A372" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D372" s="2">
+        <v>284</v>
+      </c>
+      <c r="E372" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F372" s="2">
+        <v>82439</v>
+      </c>
+      <c r="G372" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H372" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I372" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J372" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K372" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L372" s="4">
+        <v>3</v>
+      </c>
+      <c r="M372" s="4">
+        <v>270</v>
+      </c>
+      <c r="N372" s="4">
+        <v>810</v>
+      </c>
+      <c r="O372" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P372" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="373">
+      <c r="A373" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D373" s="2">
+        <v>284</v>
+      </c>
+      <c r="E373" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F373" s="2">
+        <v>82439</v>
+      </c>
+      <c r="G373" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H373" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I373" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J373" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K373" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L373" s="4">
+        <v>3</v>
+      </c>
+      <c r="M373" s="4">
+        <v>90</v>
+      </c>
+      <c r="N373" s="4">
+        <v>270</v>
+      </c>
+      <c r="O373" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P373" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="374">
+      <c r="A374" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D374" s="2">
+        <v>284</v>
+      </c>
+      <c r="E374" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F374" s="2">
+        <v>82442</v>
+      </c>
+      <c r="G374" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H374" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="I374" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J374" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K374" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L374" s="4">
+        <v>10</v>
+      </c>
+      <c r="M374" s="4">
+        <v>16</v>
+      </c>
+      <c r="N374" s="4">
+        <v>160</v>
+      </c>
+      <c r="O374" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P374" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="375">
+      <c r="A375" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D375" s="2">
+        <v>284</v>
+      </c>
+      <c r="E375" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F375" s="2">
+        <v>82439</v>
+      </c>
+      <c r="G375" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H375" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="J375" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K375" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L375" s="4">
+        <v>20</v>
+      </c>
+      <c r="M375" s="4">
+        <v>6</v>
+      </c>
+      <c r="N375" s="4">
+        <v>120</v>
+      </c>
+      <c r="O375" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P375" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="376">
+      <c r="A376" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D376" s="2">
+        <v>284</v>
+      </c>
+      <c r="E376" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F376" s="1"/>
+      <c r="G376" s="1"/>
+      <c r="H376" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="J376" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K376" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="L376" s="4">
+        <v>20000</v>
+      </c>
+      <c r="M376" s="4">
+        <v>0</v>
+      </c>
+      <c r="N376" s="4">
+        <v>0</v>
+      </c>
+      <c r="O376" s="1"/>
+      <c r="P376" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="377">
+      <c r="A377" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D377" s="2">
+        <v>284</v>
+      </c>
+      <c r="E377" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F377" s="1"/>
+      <c r="G377" s="1"/>
+      <c r="H377" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="I377" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="J377" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K377" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L377" s="4">
+        <v>3</v>
+      </c>
+      <c r="M377" s="4">
+        <v>0</v>
+      </c>
+      <c r="N377" s="4">
+        <v>0</v>
+      </c>
+      <c r="O377" s="1"/>
+      <c r="P377" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="378">
+      <c r="A378" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D378" s="2">
+        <v>284</v>
+      </c>
+      <c r="E378" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F378" s="1"/>
+      <c r="G378" s="1"/>
+      <c r="H378" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I378" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J378" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K378" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L378" s="4">
+        <v>5</v>
+      </c>
+      <c r="M378" s="4">
+        <v>0</v>
+      </c>
+      <c r="N378" s="4">
+        <v>0</v>
+      </c>
+      <c r="O378" s="1"/>
+      <c r="P378" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="379">
+      <c r="A379" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D379" s="2">
+        <v>284</v>
+      </c>
+      <c r="E379" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F379" s="1"/>
+      <c r="G379" s="1"/>
+      <c r="H379" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="J379" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K379" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L379" s="4">
+        <v>1</v>
+      </c>
+      <c r="M379" s="4">
+        <v>0</v>
+      </c>
+      <c r="N379" s="4">
+        <v>0</v>
+      </c>
+      <c r="O379" s="1"/>
+      <c r="P379" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="380">
+      <c r="A380" s="2">
+        <v>2212</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D380" s="2">
+        <v>284</v>
+      </c>
+      <c r="E380" s="3">
+        <v>46085.6561570255</v>
+      </c>
+      <c r="F380" s="1"/>
+      <c r="G380" s="1"/>
+      <c r="H380" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="J380" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K380" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L380" s="4">
+        <v>1</v>
+      </c>
+      <c r="M380" s="4">
+        <v>0</v>
+      </c>
+      <c r="N380" s="4">
+        <v>0</v>
+      </c>
+      <c r="O380" s="1"/>
+      <c r="P380" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="381">
+      <c r="A381" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D381" s="2">
+        <v>31</v>
+      </c>
+      <c r="E381" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F381" s="2">
+        <v>82446</v>
+      </c>
+      <c r="G381" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H381" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I381" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J381" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K381" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L381" s="4">
+        <v>2</v>
+      </c>
+      <c r="M381" s="4">
+        <v>34.72</v>
+      </c>
+      <c r="N381" s="4">
+        <v>69.44</v>
+      </c>
+      <c r="O381" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="P381" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="382">
+      <c r="A382" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D382" s="2">
+        <v>31</v>
+      </c>
+      <c r="E382" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F382" s="2">
+        <v>82447</v>
+      </c>
+      <c r="G382" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H382" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I382" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="J382" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K382" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L382" s="4">
+        <v>2</v>
+      </c>
+      <c r="M382" s="4">
+        <v>101.31</v>
+      </c>
+      <c r="N382" s="4">
+        <v>202.62</v>
+      </c>
+      <c r="O382" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P382" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="383">
+      <c r="A383" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D383" s="2">
+        <v>31</v>
+      </c>
+      <c r="E383" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F383" s="2">
+        <v>82443</v>
+      </c>
+      <c r="G383" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H383" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I383" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J383" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K383" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L383" s="4">
+        <v>6</v>
+      </c>
+      <c r="M383" s="4">
+        <v>47.93</v>
+      </c>
+      <c r="N383" s="4">
+        <v>287.58</v>
+      </c>
+      <c r="O383" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P383" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="384">
+      <c r="A384" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D384" s="2">
+        <v>31</v>
+      </c>
+      <c r="E384" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F384" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G384" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H384" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I384" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J384" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K384" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L384" s="4">
+        <v>5</v>
+      </c>
+      <c r="M384" s="4">
+        <v>23.5</v>
+      </c>
+      <c r="N384" s="4">
+        <v>117.5</v>
+      </c>
+      <c r="O384" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P384" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="385">
+      <c r="A385" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D385" s="2">
+        <v>31</v>
+      </c>
+      <c r="E385" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F385" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G385" s="3">
+        <v>46085</v>
+      </c>
+      <c r="H385" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I385" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="J385" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K385" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L385" s="4">
+        <v>6</v>
+      </c>
+      <c r="M385" s="4">
+        <v>13.6</v>
+      </c>
+      <c r="N385" s="4">
+        <v>81.6</v>
+      </c>
+      <c r="O385" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P385" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="386">
+      <c r="A386" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D386" s="2">
+        <v>31</v>
+      </c>
+      <c r="E386" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F386" s="1"/>
+      <c r="G386" s="1"/>
+      <c r="H386" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="I386" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J386" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K386" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L386" s="4">
+        <v>10</v>
+      </c>
+      <c r="M386" s="4">
+        <v>0</v>
+      </c>
+      <c r="N386" s="4">
+        <v>0</v>
+      </c>
+      <c r="O386" s="1"/>
+      <c r="P386" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="387">
+      <c r="A387" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D387" s="2">
+        <v>31</v>
+      </c>
+      <c r="E387" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F387" s="1"/>
+      <c r="G387" s="1"/>
+      <c r="H387" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="J387" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K387" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L387" s="4">
+        <v>30</v>
+      </c>
+      <c r="M387" s="4">
+        <v>0</v>
+      </c>
+      <c r="N387" s="4">
+        <v>0</v>
+      </c>
+      <c r="O387" s="1"/>
+      <c r="P387" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="388">
+      <c r="A388" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D388" s="2">
+        <v>31</v>
+      </c>
+      <c r="E388" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F388" s="1"/>
+      <c r="G388" s="1"/>
+      <c r="H388" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="J388" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K388" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L388" s="4">
+        <v>3</v>
+      </c>
+      <c r="M388" s="4">
+        <v>0</v>
+      </c>
+      <c r="N388" s="4">
+        <v>0</v>
+      </c>
+      <c r="O388" s="1"/>
+      <c r="P388" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="389">
+      <c r="A389" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D389" s="2">
+        <v>31</v>
+      </c>
+      <c r="E389" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F389" s="1"/>
+      <c r="G389" s="1"/>
+      <c r="H389" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="J389" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K389" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L389" s="4">
+        <v>3</v>
+      </c>
+      <c r="M389" s="4">
+        <v>0</v>
+      </c>
+      <c r="N389" s="4">
+        <v>0</v>
+      </c>
+      <c r="O389" s="1"/>
+      <c r="P389" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="390">
+      <c r="A390" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B390" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D390" s="2">
+        <v>31</v>
+      </c>
+      <c r="E390" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F390" s="1"/>
+      <c r="G390" s="1"/>
+      <c r="H390" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J390" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K390" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L390" s="4">
+        <v>100</v>
+      </c>
+      <c r="M390" s="4">
+        <v>0</v>
+      </c>
+      <c r="N390" s="4">
+        <v>0</v>
+      </c>
+      <c r="O390" s="1"/>
+      <c r="P390" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="391">
+      <c r="A391" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B391" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D391" s="2">
+        <v>31</v>
+      </c>
+      <c r="E391" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F391" s="1"/>
+      <c r="G391" s="1"/>
+      <c r="H391" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="I391" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="J391" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K391" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L391" s="4">
+        <v>250</v>
+      </c>
+      <c r="M391" s="4">
+        <v>0</v>
+      </c>
+      <c r="N391" s="4">
+        <v>0</v>
+      </c>
+      <c r="O391" s="1"/>
+      <c r="P391" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="392">
+      <c r="A392" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B392" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D392" s="2">
+        <v>31</v>
+      </c>
+      <c r="E392" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F392" s="1"/>
+      <c r="G392" s="1"/>
+      <c r="H392" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="I392" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="J392" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K392" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="L392" s="4">
+        <v>1</v>
+      </c>
+      <c r="M392" s="4">
+        <v>0</v>
+      </c>
+      <c r="N392" s="4">
+        <v>0</v>
+      </c>
+      <c r="O392" s="1"/>
+      <c r="P392" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="393">
+      <c r="A393" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D393" s="2">
+        <v>31</v>
+      </c>
+      <c r="E393" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F393" s="1"/>
+      <c r="G393" s="1"/>
+      <c r="H393" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="I393" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K393" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L393" s="4">
+        <v>1</v>
+      </c>
+      <c r="M393" s="4">
+        <v>0</v>
+      </c>
+      <c r="N393" s="4">
+        <v>0</v>
+      </c>
+      <c r="O393" s="1"/>
+      <c r="P393" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="394">
+      <c r="A394" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D394" s="2">
+        <v>31</v>
+      </c>
+      <c r="E394" s="3">
+        <v>46085.6581644213</v>
+      </c>
+      <c r="F394" s="1"/>
+      <c r="G394" s="1"/>
+      <c r="H394" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="I394" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="J394" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K394" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L394" s="4">
+        <v>1</v>
+      </c>
+      <c r="M394" s="4">
+        <v>0</v>
+      </c>
+      <c r="N394" s="4">
+        <v>0</v>
+      </c>
+      <c r="O394" s="1"/>
+      <c r="P394" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="728">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1985,27 +1985,27 @@
     <t>CHAPA PLASTIFICADO 17 MM - 2,20 X 1,10 M</t>
   </si>
   <si>
+    <t>F.04.0035</t>
+  </si>
+  <si>
+    <t>TRADO MOTORIZADO À GASOLINA</t>
+  </si>
+  <si>
+    <t>DIA</t>
+  </si>
+  <si>
+    <t>H.11.0014</t>
+  </si>
+  <si>
+    <t>AÇO CA25 10,0 MM - VARA</t>
+  </si>
+  <si>
     <t>W.01.0006</t>
   </si>
   <si>
     <t>PREGO COMUM C/ CABEÇA 17 X 27</t>
   </si>
   <si>
-    <t>F.04.0035</t>
-  </si>
-  <si>
-    <t>TRADO MOTORIZADO À GASOLINA</t>
-  </si>
-  <si>
-    <t>DIA</t>
-  </si>
-  <si>
-    <t>H.11.0014</t>
-  </si>
-  <si>
-    <t>AÇO CA25 10,0 MM - VARA</t>
-  </si>
-  <si>
     <t>00000000002393</t>
   </si>
   <si>
@@ -2156,12 +2156,6 @@
     <t xml:space="preserve">CUBA DE APOIO REDONDA  40 X 40 CM DECA  L 12040  17 SLIM BRANCA</t>
   </si>
   <si>
-    <t>00000000000573</t>
-  </si>
-  <si>
-    <t>AGILIZE</t>
-  </si>
-  <si>
     <t>C.04.0025</t>
   </si>
   <si>
@@ -2174,6 +2168,12 @@
     <t>PONTEIRO FORJADO EM AÇO REDONDO - 12''</t>
   </si>
   <si>
+    <t>E.02.0071</t>
+  </si>
+  <si>
+    <t>TELA DE POLIETILENO DE 1'' GRAMATURA SUPERIOR A 120GM/M3 TR 350 - C/50M</t>
+  </si>
+  <si>
     <t>E.03.0041</t>
   </si>
   <si>
@@ -2190,12 +2190,6 @@
   </si>
   <si>
     <t>BLOCO CERÂMICO 09 X 19 X 39</t>
-  </si>
-  <si>
-    <t>M.09.0074</t>
-  </si>
-  <si>
-    <t>TELA</t>
   </si>
   <si>
     <t>W.06.0001</t>
@@ -2500,7 +2494,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P394"/>
+  <dimension ref="A1:P395"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -19144,12 +19138,8 @@
       <c r="E334" s="3">
         <v>46084.5060569213</v>
       </c>
-      <c r="F334" s="2">
-        <v>82410</v>
-      </c>
-      <c r="G334" s="3">
-        <v>46084</v>
-      </c>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
       <c r="H334" s="1" t="s">
         <v>657</v>
       </c>
@@ -19160,23 +19150,19 @@
         <v>20</v>
       </c>
       <c r="K334" s="1" t="s">
-        <v>257</v>
+        <v>659</v>
       </c>
       <c r="L334" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M334" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N334" s="4">
-        <v>120</v>
-      </c>
-      <c r="O334" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="P334" s="1" t="s">
-        <v>259</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O334" s="1"/>
+      <c r="P334" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="335">
       <c r="A335" s="2">
@@ -19197,19 +19183,19 @@
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
       <c r="H335" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="J335" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K335" s="1" t="s">
-        <v>661</v>
+        <v>28</v>
       </c>
       <c r="L335" s="4">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="M335" s="4">
         <v>0</v>
@@ -19248,16 +19234,16 @@
         <v>20</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>28</v>
+        <v>257</v>
       </c>
       <c r="L336" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M336" s="4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N336" s="4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O336" s="1"/>
       <c r="P336" s="1"/>
@@ -21115,37 +21101,37 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F375" s="2">
-        <v>82439</v>
+        <v>82454</v>
       </c>
       <c r="G375" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>334</v>
+        <v>42</v>
       </c>
       <c r="I375" s="1" t="s">
-        <v>335</v>
+        <v>43</v>
       </c>
       <c r="J375" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K375" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L375" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M375" s="4">
-        <v>6</v>
+        <v>755.01</v>
       </c>
       <c r="N375" s="4">
-        <v>120</v>
+        <v>3775.05</v>
       </c>
       <c r="O375" s="1" t="s">
-        <v>165</v>
+        <v>690</v>
       </c>
       <c r="P375" s="1" t="s">
-        <v>166</v>
+        <v>691</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="376">
@@ -21164,31 +21150,39 @@
       <c r="E376" s="3">
         <v>46085.6561570255</v>
       </c>
-      <c r="F376" s="1"/>
-      <c r="G376" s="1"/>
+      <c r="F376" s="2">
+        <v>82439</v>
+      </c>
+      <c r="G376" s="3">
+        <v>46085</v>
+      </c>
       <c r="H376" s="1" t="s">
-        <v>706</v>
+        <v>334</v>
       </c>
       <c r="I376" s="1" t="s">
-        <v>707</v>
+        <v>335</v>
       </c>
       <c r="J376" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K376" s="1" t="s">
-        <v>617</v>
+        <v>28</v>
       </c>
       <c r="L376" s="4">
-        <v>20000</v>
+        <v>20</v>
       </c>
       <c r="M376" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N376" s="4">
-        <v>0</v>
-      </c>
-      <c r="O376" s="1"/>
-      <c r="P376" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="O376" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P376" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="377">
       <c r="A377" s="2">
@@ -21209,19 +21203,19 @@
       <c r="F377" s="1"/>
       <c r="G377" s="1"/>
       <c r="H377" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="I377" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="J377" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K377" s="1" t="s">
-        <v>39</v>
+        <v>617</v>
       </c>
       <c r="L377" s="4">
-        <v>3</v>
+        <v>20000</v>
       </c>
       <c r="M377" s="4">
         <v>0</v>
@@ -21251,10 +21245,10 @@
       <c r="F378" s="1"/>
       <c r="G378" s="1"/>
       <c r="H378" s="1" t="s">
-        <v>42</v>
+        <v>708</v>
       </c>
       <c r="I378" s="1" t="s">
-        <v>43</v>
+        <v>709</v>
       </c>
       <c r="J378" s="1" t="s">
         <v>20</v>
@@ -21263,7 +21257,7 @@
         <v>39</v>
       </c>
       <c r="L378" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M378" s="4">
         <v>0</v>
@@ -21375,16 +21369,16 @@
         <v>46085.6581644213</v>
       </c>
       <c r="F381" s="2">
-        <v>82446</v>
+        <v>82447</v>
       </c>
       <c r="G381" s="3">
         <v>46085</v>
       </c>
       <c r="H381" s="1" t="s">
-        <v>33</v>
+        <v>599</v>
       </c>
       <c r="I381" s="1" t="s">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="J381" s="1" t="s">
         <v>20</v>
@@ -21393,19 +21387,19 @@
         <v>28</v>
       </c>
       <c r="L381" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M381" s="4">
-        <v>34.72</v>
+        <v>5.5</v>
       </c>
       <c r="N381" s="4">
-        <v>69.44</v>
+        <v>55</v>
       </c>
       <c r="O381" s="1" t="s">
-        <v>714</v>
+        <v>191</v>
       </c>
       <c r="P381" s="1" t="s">
-        <v>715</v>
+        <v>192</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="382">
@@ -21431,10 +21425,10 @@
         <v>46085</v>
       </c>
       <c r="H382" s="1" t="s">
-        <v>716</v>
+        <v>33</v>
       </c>
       <c r="I382" s="1" t="s">
-        <v>717</v>
+        <v>34</v>
       </c>
       <c r="J382" s="1" t="s">
         <v>20</v>
@@ -21446,10 +21440,10 @@
         <v>2</v>
       </c>
       <c r="M382" s="4">
-        <v>101.31</v>
+        <v>58.96</v>
       </c>
       <c r="N382" s="4">
-        <v>202.62</v>
+        <v>117.92</v>
       </c>
       <c r="O382" s="1" t="s">
         <v>191</v>
@@ -21475,16 +21469,16 @@
         <v>46085.6581644213</v>
       </c>
       <c r="F383" s="2">
-        <v>82443</v>
+        <v>82447</v>
       </c>
       <c r="G383" s="3">
         <v>46085</v>
       </c>
       <c r="H383" s="1" t="s">
-        <v>300</v>
+        <v>714</v>
       </c>
       <c r="I383" s="1" t="s">
-        <v>301</v>
+        <v>715</v>
       </c>
       <c r="J383" s="1" t="s">
         <v>20</v>
@@ -21493,19 +21487,19 @@
         <v>28</v>
       </c>
       <c r="L383" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M383" s="4">
-        <v>47.93</v>
+        <v>147.3</v>
       </c>
       <c r="N383" s="4">
-        <v>287.58</v>
+        <v>294.6</v>
       </c>
       <c r="O383" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="P383" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="384">
@@ -21581,10 +21575,10 @@
         <v>46085</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="I385" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J385" s="1" t="s">
         <v>20</v>
@@ -21624,31 +21618,39 @@
       <c r="E386" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F386" s="1"/>
-      <c r="G386" s="1"/>
+      <c r="F386" s="2">
+        <v>82453</v>
+      </c>
+      <c r="G386" s="3">
+        <v>46086</v>
+      </c>
       <c r="H386" s="1" t="s">
-        <v>599</v>
+        <v>18</v>
       </c>
       <c r="I386" s="1" t="s">
-        <v>600</v>
+        <v>19</v>
       </c>
       <c r="J386" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K386" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L386" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M386" s="4">
-        <v>0</v>
+        <v>33.99</v>
       </c>
       <c r="N386" s="4">
-        <v>0</v>
-      </c>
-      <c r="O386" s="1"/>
-      <c r="P386" s="1"/>
+        <v>3399</v>
+      </c>
+      <c r="O386" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P386" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="387">
       <c r="A387" s="2">
@@ -21669,19 +21671,19 @@
       <c r="F387" s="1"/>
       <c r="G387" s="1"/>
       <c r="H387" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="J387" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K387" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="L387" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="M387" s="4">
         <v>0</v>
@@ -21711,19 +21713,19 @@
       <c r="F388" s="1"/>
       <c r="G388" s="1"/>
       <c r="H388" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="I388" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="J388" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K388" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L388" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="M388" s="4">
         <v>0</v>
@@ -21795,19 +21797,19 @@
       <c r="F390" s="1"/>
       <c r="G390" s="1"/>
       <c r="H390" s="1" t="s">
-        <v>18</v>
+        <v>722</v>
       </c>
       <c r="I390" s="1" t="s">
-        <v>19</v>
+        <v>723</v>
       </c>
       <c r="J390" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K390" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L390" s="4">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="M390" s="4">
         <v>0</v>
@@ -21837,10 +21839,10 @@
       <c r="F391" s="1"/>
       <c r="G391" s="1"/>
       <c r="H391" s="1" t="s">
-        <v>724</v>
+        <v>300</v>
       </c>
       <c r="I391" s="1" t="s">
-        <v>725</v>
+        <v>301</v>
       </c>
       <c r="J391" s="1" t="s">
         <v>20</v>
@@ -21849,13 +21851,13 @@
         <v>28</v>
       </c>
       <c r="L391" s="4">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="M391" s="4">
-        <v>0</v>
+        <v>47.93</v>
       </c>
       <c r="N391" s="4">
-        <v>0</v>
+        <v>287.58</v>
       </c>
       <c r="O391" s="1"/>
       <c r="P391" s="1"/>
@@ -21879,19 +21881,19 @@
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
       <c r="H392" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="I392" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="J392" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K392" s="1" t="s">
-        <v>668</v>
+        <v>28</v>
       </c>
       <c r="L392" s="4">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="M392" s="4">
         <v>0</v>
@@ -21963,10 +21965,10 @@
       <c r="F394" s="1"/>
       <c r="G394" s="1"/>
       <c r="H394" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="I394" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="J394" s="1" t="s">
         <v>20</v>
@@ -21985,6 +21987,48 @@
       </c>
       <c r="O394" s="1"/>
       <c r="P394" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="395">
+      <c r="A395" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D395" s="2">
+        <v>27</v>
+      </c>
+      <c r="E395" s="3">
+        <v>46085.7157723032</v>
+      </c>
+      <c r="F395" s="1"/>
+      <c r="G395" s="1"/>
+      <c r="H395" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="I395" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="J395" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K395" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L395" s="4">
+        <v>60</v>
+      </c>
+      <c r="M395" s="4">
+        <v>0</v>
+      </c>
+      <c r="N395" s="4">
+        <v>0</v>
+      </c>
+      <c r="O395" s="1"/>
+      <c r="P395" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="739">
   <si>
     <t>EMPRD</t>
   </si>
@@ -2030,54 +2030,60 @@
     <t>SC25</t>
   </si>
   <si>
+    <t>K.02.0831</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 25 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>00000000009726</t>
+  </si>
+  <si>
+    <t>MINI ELETRO</t>
+  </si>
+  <si>
+    <t>K.02.0832</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 32 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.0833</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 40 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.0834</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 50 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.0835</t>
+  </si>
+  <si>
+    <t>CAP SOLDÁVEL 60 MM ( MARROM )</t>
+  </si>
+  <si>
+    <t>K.02.1806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOLUÇÃO PREPARADORA  PARA TUBOS E CONEXÕS PVC 1 L</t>
+  </si>
+  <si>
+    <t>K.02.4669</t>
+  </si>
+  <si>
+    <t>ADESIVO ESPECIAL CPVC - FRASCO AQUATHERM - 850G</t>
+  </si>
+  <si>
     <t>W.07.0002</t>
   </si>
   <si>
     <t>ADESIVO ESTRUTURAL A BASE DE RESINA EPÓXI - FLUIDO - SIKADUR 32 - 1 KG</t>
   </si>
   <si>
-    <t>K.02.0831</t>
-  </si>
-  <si>
-    <t>CAP SOLDÁVEL 25 MM ( MARROM )</t>
-  </si>
-  <si>
-    <t>K.02.0832</t>
-  </si>
-  <si>
-    <t>CAP SOLDÁVEL 32 MM ( MARROM )</t>
-  </si>
-  <si>
-    <t>K.02.0833</t>
-  </si>
-  <si>
-    <t>CAP SOLDÁVEL 40 MM ( MARROM )</t>
-  </si>
-  <si>
-    <t>K.02.0834</t>
-  </si>
-  <si>
-    <t>CAP SOLDÁVEL 50 MM ( MARROM )</t>
-  </si>
-  <si>
-    <t>K.02.0835</t>
-  </si>
-  <si>
-    <t>CAP SOLDÁVEL 60 MM ( MARROM )</t>
-  </si>
-  <si>
-    <t>K.02.1806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOLUÇÃO PREPARADORA  PARA TUBOS E CONEXÕS PVC 1 L</t>
-  </si>
-  <si>
-    <t>K.02.4669</t>
-  </si>
-  <si>
-    <t>ADESIVO ESPECIAL CPVC - FRASCO AQUATHERM - 850G</t>
-  </si>
-  <si>
     <t>P.02.0012</t>
   </si>
   <si>
@@ -2138,6 +2144,12 @@
     <t>AGUA CARRO PIPA</t>
   </si>
   <si>
+    <t>00000000007748</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CARRO PIPA</t>
+  </si>
+  <si>
     <t>E.02.0027</t>
   </si>
   <si>
@@ -2150,6 +2162,12 @@
     <t>TORNEIRA 1198 C LAVATÓRIO MESA LINK DECA</t>
   </si>
   <si>
+    <t>00000000007902</t>
+  </si>
+  <si>
+    <t>DECA RED</t>
+  </si>
+  <si>
     <t>U.01.3091</t>
   </si>
   <si>
@@ -2162,30 +2180,30 @@
     <t>SACO PLÁSTICO P/ LIXO - 300 L C/ 100 UN REFORÇADO</t>
   </si>
   <si>
+    <t>E.02.0071</t>
+  </si>
+  <si>
+    <t>TELA DE POLIETILENO DE 1'' GRAMATURA SUPERIOR A 120GM/M3 TR 350 - C/50M</t>
+  </si>
+  <si>
+    <t>E.03.0041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA DE LATEX  PRETA SEM FORRO ESPESSURA: 0,62 MM MUCAMBO</t>
+  </si>
+  <si>
+    <t>E.03.0259</t>
+  </si>
+  <si>
+    <t>MACACÃO TREVIRA KP500 COM LUVA E BOTA ACOPLADO</t>
+  </si>
+  <si>
     <t>E.04.0047</t>
   </si>
   <si>
     <t>PONTEIRO FORJADO EM AÇO REDONDO - 12''</t>
   </si>
   <si>
-    <t>E.02.0071</t>
-  </si>
-  <si>
-    <t>TELA DE POLIETILENO DE 1'' GRAMATURA SUPERIOR A 120GM/M3 TR 350 - C/50M</t>
-  </si>
-  <si>
-    <t>E.03.0041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA DE LATEX  PRETA SEM FORRO ESPESSURA: 0,62 MM MUCAMBO</t>
-  </si>
-  <si>
-    <t>E.03.0259</t>
-  </si>
-  <si>
-    <t>MACACÃO TREVIRA KP500 COM LUVA E BOTA ACOPLADO</t>
-  </si>
-  <si>
     <t>L.01.0004</t>
   </si>
   <si>
@@ -2196,6 +2214,21 @@
   </si>
   <si>
     <t xml:space="preserve">COLA PVA  X 0 35  PULVITEC C/ 50KG</t>
+  </si>
+  <si>
+    <t>N.05.0053</t>
+  </si>
+  <si>
+    <t>PASTILHA COLORMIX</t>
+  </si>
+  <si>
+    <t>M²</t>
+  </si>
+  <si>
+    <t>E.02.0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITA CREPE  VERDE 5CM X 40MM AUTOMOTIVA</t>
   </si>
 </sst>
 </file>
@@ -2494,7 +2527,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P395"/>
+  <dimension ref="A1:P407"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -19765,10 +19798,10 @@
         <v>46084.7378501505</v>
       </c>
       <c r="F347" s="2">
-        <v>82420</v>
+        <v>82464</v>
       </c>
       <c r="G347" s="3">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="H347" s="1" t="s">
         <v>672</v>
@@ -19783,19 +19816,19 @@
         <v>28</v>
       </c>
       <c r="L347" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M347" s="4">
-        <v>99</v>
+        <v>0.91</v>
       </c>
       <c r="N347" s="4">
-        <v>594</v>
+        <v>4.55</v>
       </c>
       <c r="O347" s="1" t="s">
-        <v>165</v>
+        <v>674</v>
       </c>
       <c r="P347" s="1" t="s">
-        <v>166</v>
+        <v>675</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="348">
@@ -19814,13 +19847,17 @@
       <c r="E348" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F348" s="1"/>
-      <c r="G348" s="1"/>
+      <c r="F348" s="2">
+        <v>82464</v>
+      </c>
+      <c r="G348" s="3">
+        <v>46086</v>
+      </c>
       <c r="H348" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J348" s="1" t="s">
         <v>20</v>
@@ -19832,13 +19869,17 @@
         <v>5</v>
       </c>
       <c r="M348" s="4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="N348" s="4">
-        <v>0</v>
-      </c>
-      <c r="O348" s="1"/>
-      <c r="P348" s="1"/>
+        <v>7.05</v>
+      </c>
+      <c r="O348" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="P348" s="1" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="349">
       <c r="A349" s="2">
@@ -19856,13 +19897,17 @@
       <c r="E349" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F349" s="1"/>
-      <c r="G349" s="1"/>
+      <c r="F349" s="2">
+        <v>82464</v>
+      </c>
+      <c r="G349" s="3">
+        <v>46086</v>
+      </c>
       <c r="H349" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J349" s="1" t="s">
         <v>20</v>
@@ -19874,13 +19919,17 @@
         <v>5</v>
       </c>
       <c r="M349" s="4">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N349" s="4">
-        <v>0</v>
-      </c>
-      <c r="O349" s="1"/>
-      <c r="P349" s="1"/>
+        <v>15.85</v>
+      </c>
+      <c r="O349" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="P349" s="1" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="350">
       <c r="A350" s="2">
@@ -19898,13 +19947,17 @@
       <c r="E350" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F350" s="1"/>
-      <c r="G350" s="1"/>
+      <c r="F350" s="2">
+        <v>82464</v>
+      </c>
+      <c r="G350" s="3">
+        <v>46086</v>
+      </c>
       <c r="H350" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J350" s="1" t="s">
         <v>20</v>
@@ -19916,13 +19969,17 @@
         <v>5</v>
       </c>
       <c r="M350" s="4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N350" s="4">
-        <v>0</v>
-      </c>
-      <c r="O350" s="1"/>
-      <c r="P350" s="1"/>
+        <v>18.75</v>
+      </c>
+      <c r="O350" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="P350" s="1" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="351">
       <c r="A351" s="2">
@@ -19940,13 +19997,17 @@
       <c r="E351" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F351" s="1"/>
-      <c r="G351" s="1"/>
+      <c r="F351" s="2">
+        <v>82464</v>
+      </c>
+      <c r="G351" s="3">
+        <v>46086</v>
+      </c>
       <c r="H351" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="J351" s="1" t="s">
         <v>20</v>
@@ -19958,13 +20019,17 @@
         <v>5</v>
       </c>
       <c r="M351" s="4">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="N351" s="4">
-        <v>0</v>
-      </c>
-      <c r="O351" s="1"/>
-      <c r="P351" s="1"/>
+        <v>30.4</v>
+      </c>
+      <c r="O351" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="P351" s="1" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="352">
       <c r="A352" s="2">
@@ -19982,13 +20047,17 @@
       <c r="E352" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F352" s="1"/>
-      <c r="G352" s="1"/>
+      <c r="F352" s="2">
+        <v>82464</v>
+      </c>
+      <c r="G352" s="3">
+        <v>46086</v>
+      </c>
       <c r="H352" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J352" s="1" t="s">
         <v>20</v>
@@ -19997,16 +20066,20 @@
         <v>28</v>
       </c>
       <c r="L352" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M352" s="4">
-        <v>0</v>
+        <v>51.5</v>
       </c>
       <c r="N352" s="4">
-        <v>0</v>
-      </c>
-      <c r="O352" s="1"/>
-      <c r="P352" s="1"/>
+        <v>51.5</v>
+      </c>
+      <c r="O352" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="P352" s="1" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="353">
       <c r="A353" s="2">
@@ -20024,13 +20097,17 @@
       <c r="E353" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F353" s="1"/>
-      <c r="G353" s="1"/>
+      <c r="F353" s="2">
+        <v>82464</v>
+      </c>
+      <c r="G353" s="3">
+        <v>46086</v>
+      </c>
       <c r="H353" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J353" s="1" t="s">
         <v>20</v>
@@ -20042,13 +20119,17 @@
         <v>1</v>
       </c>
       <c r="M353" s="4">
-        <v>0</v>
+        <v>103.77</v>
       </c>
       <c r="N353" s="4">
-        <v>0</v>
-      </c>
-      <c r="O353" s="1"/>
-      <c r="P353" s="1"/>
+        <v>103.77</v>
+      </c>
+      <c r="O353" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="P353" s="1" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="354">
       <c r="A354" s="2">
@@ -20066,13 +20147,17 @@
       <c r="E354" s="3">
         <v>46084.7378501505</v>
       </c>
-      <c r="F354" s="1"/>
-      <c r="G354" s="1"/>
+      <c r="F354" s="2">
+        <v>82420</v>
+      </c>
+      <c r="G354" s="3">
+        <v>46084</v>
+      </c>
       <c r="H354" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J354" s="1" t="s">
         <v>20</v>
@@ -20081,16 +20166,20 @@
         <v>28</v>
       </c>
       <c r="L354" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M354" s="4">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="N354" s="4">
-        <v>0</v>
-      </c>
-      <c r="O354" s="1"/>
-      <c r="P354" s="1"/>
+        <v>594</v>
+      </c>
+      <c r="O354" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P354" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="355">
       <c r="A355" s="2">
@@ -20111,10 +20200,10 @@
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
       <c r="H355" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="I355" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="J355" s="1" t="s">
         <v>20</v>
@@ -20378,10 +20467,10 @@
         <v>6040.08</v>
       </c>
       <c r="O360" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="P360" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="361">
@@ -20457,10 +20546,10 @@
         <v>46085</v>
       </c>
       <c r="H362" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="J362" s="1" t="s">
         <v>20</v>
@@ -20507,10 +20596,10 @@
         <v>46085</v>
       </c>
       <c r="H363" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I363" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J363" s="1" t="s">
         <v>20</v>
@@ -20557,10 +20646,10 @@
         <v>46084</v>
       </c>
       <c r="H364" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J364" s="1" t="s">
         <v>20</v>
@@ -20607,10 +20696,10 @@
         <v>46084</v>
       </c>
       <c r="H365" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I365" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="J365" s="1" t="s">
         <v>20</v>
@@ -20707,10 +20796,10 @@
         <v>46084</v>
       </c>
       <c r="H367" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J367" s="1" t="s">
         <v>20</v>
@@ -20757,10 +20846,10 @@
         <v>46084</v>
       </c>
       <c r="H368" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I368" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J368" s="1" t="s">
         <v>20</v>
@@ -20828,10 +20917,10 @@
         <v>12860.35</v>
       </c>
       <c r="O369" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="P369" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="370">
@@ -20851,37 +20940,37 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F370" s="2">
-        <v>82439</v>
+        <v>82466</v>
       </c>
       <c r="G370" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H370" s="1" t="s">
-        <v>187</v>
+        <v>708</v>
       </c>
       <c r="I370" s="1" t="s">
-        <v>188</v>
+        <v>709</v>
       </c>
       <c r="J370" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K370" s="1" t="s">
-        <v>28</v>
+        <v>617</v>
       </c>
       <c r="L370" s="4">
-        <v>30</v>
+        <v>20000</v>
       </c>
       <c r="M370" s="4">
-        <v>1.88</v>
+        <v>0.0933</v>
       </c>
       <c r="N370" s="4">
-        <v>56.4</v>
+        <v>1866</v>
       </c>
       <c r="O370" s="1" t="s">
-        <v>165</v>
+        <v>710</v>
       </c>
       <c r="P370" s="1" t="s">
-        <v>166</v>
+        <v>711</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="371">
@@ -20901,16 +20990,16 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F371" s="2">
-        <v>82440</v>
+        <v>82465</v>
       </c>
       <c r="G371" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H371" s="1" t="s">
-        <v>26</v>
+        <v>187</v>
       </c>
       <c r="I371" s="1" t="s">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="J371" s="1" t="s">
         <v>20</v>
@@ -20919,19 +21008,19 @@
         <v>28</v>
       </c>
       <c r="L371" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="M371" s="4">
-        <v>10.85</v>
+        <v>1.88</v>
       </c>
       <c r="N371" s="4">
-        <v>108.5</v>
+        <v>56.4</v>
       </c>
       <c r="O371" s="1" t="s">
-        <v>191</v>
+        <v>664</v>
       </c>
       <c r="P371" s="1" t="s">
-        <v>192</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="372">
@@ -20951,37 +21040,37 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F372" s="2">
-        <v>82439</v>
+        <v>82440</v>
       </c>
       <c r="G372" s="3">
         <v>46085</v>
       </c>
       <c r="H372" s="1" t="s">
-        <v>315</v>
+        <v>26</v>
       </c>
       <c r="I372" s="1" t="s">
-        <v>316</v>
+        <v>27</v>
       </c>
       <c r="J372" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K372" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L372" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M372" s="4">
-        <v>270</v>
+        <v>10.85</v>
       </c>
       <c r="N372" s="4">
-        <v>810</v>
+        <v>108.5</v>
       </c>
       <c r="O372" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="P372" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="373">
@@ -21001,16 +21090,16 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F373" s="2">
-        <v>82439</v>
+        <v>82465</v>
       </c>
       <c r="G373" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H373" s="1" t="s">
-        <v>37</v>
+        <v>315</v>
       </c>
       <c r="I373" s="1" t="s">
-        <v>38</v>
+        <v>316</v>
       </c>
       <c r="J373" s="1" t="s">
         <v>20</v>
@@ -21022,16 +21111,16 @@
         <v>3</v>
       </c>
       <c r="M373" s="4">
-        <v>90</v>
+        <v>310</v>
       </c>
       <c r="N373" s="4">
-        <v>270</v>
+        <v>930</v>
       </c>
       <c r="O373" s="1" t="s">
-        <v>165</v>
+        <v>664</v>
       </c>
       <c r="P373" s="1" t="s">
-        <v>166</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="374">
@@ -21051,31 +21140,31 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F374" s="2">
-        <v>82442</v>
+        <v>82465</v>
       </c>
       <c r="G374" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H374" s="1" t="s">
-        <v>195</v>
+        <v>37</v>
       </c>
       <c r="I374" s="1" t="s">
-        <v>196</v>
+        <v>38</v>
       </c>
       <c r="J374" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K374" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L374" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M374" s="4">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="N374" s="4">
-        <v>160</v>
+        <v>270</v>
       </c>
       <c r="O374" s="1" t="s">
         <v>664</v>
@@ -21101,37 +21190,37 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F375" s="2">
-        <v>82454</v>
+        <v>82442</v>
       </c>
       <c r="G375" s="3">
-        <v>46086</v>
+        <v>46085</v>
       </c>
       <c r="H375" s="1" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
       <c r="I375" s="1" t="s">
-        <v>43</v>
+        <v>196</v>
       </c>
       <c r="J375" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K375" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L375" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M375" s="4">
-        <v>755.01</v>
+        <v>16</v>
       </c>
       <c r="N375" s="4">
-        <v>3775.05</v>
+        <v>160</v>
       </c>
       <c r="O375" s="1" t="s">
-        <v>690</v>
+        <v>664</v>
       </c>
       <c r="P375" s="1" t="s">
-        <v>691</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="376">
@@ -21151,37 +21240,37 @@
         <v>46085.6561570255</v>
       </c>
       <c r="F376" s="2">
-        <v>82439</v>
+        <v>82465</v>
       </c>
       <c r="G376" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H376" s="1" t="s">
-        <v>334</v>
+        <v>712</v>
       </c>
       <c r="I376" s="1" t="s">
-        <v>335</v>
+        <v>713</v>
       </c>
       <c r="J376" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K376" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L376" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M376" s="4">
-        <v>6</v>
+        <v>980</v>
       </c>
       <c r="N376" s="4">
-        <v>120</v>
+        <v>2940</v>
       </c>
       <c r="O376" s="1" t="s">
-        <v>165</v>
+        <v>664</v>
       </c>
       <c r="P376" s="1" t="s">
-        <v>166</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="377">
@@ -21200,31 +21289,39 @@
       <c r="E377" s="3">
         <v>46085.6561570255</v>
       </c>
-      <c r="F377" s="1"/>
-      <c r="G377" s="1"/>
+      <c r="F377" s="2">
+        <v>82454</v>
+      </c>
+      <c r="G377" s="3">
+        <v>46086</v>
+      </c>
       <c r="H377" s="1" t="s">
-        <v>706</v>
+        <v>42</v>
       </c>
       <c r="I377" s="1" t="s">
-        <v>707</v>
+        <v>43</v>
       </c>
       <c r="J377" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K377" s="1" t="s">
-        <v>617</v>
+        <v>39</v>
       </c>
       <c r="L377" s="4">
-        <v>20000</v>
+        <v>5</v>
       </c>
       <c r="M377" s="4">
-        <v>0</v>
+        <v>755.01</v>
       </c>
       <c r="N377" s="4">
-        <v>0</v>
-      </c>
-      <c r="O377" s="1"/>
-      <c r="P377" s="1"/>
+        <v>3775.05</v>
+      </c>
+      <c r="O377" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="P377" s="1" t="s">
+        <v>693</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="378">
       <c r="A378" s="2">
@@ -21242,31 +21339,39 @@
       <c r="E378" s="3">
         <v>46085.6561570255</v>
       </c>
-      <c r="F378" s="1"/>
-      <c r="G378" s="1"/>
+      <c r="F378" s="2">
+        <v>82465</v>
+      </c>
+      <c r="G378" s="3">
+        <v>46086</v>
+      </c>
       <c r="H378" s="1" t="s">
-        <v>708</v>
+        <v>334</v>
       </c>
       <c r="I378" s="1" t="s">
-        <v>709</v>
+        <v>335</v>
       </c>
       <c r="J378" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K378" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L378" s="4">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M378" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N378" s="4">
-        <v>0</v>
-      </c>
-      <c r="O378" s="1"/>
-      <c r="P378" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="O378" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P378" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="379">
       <c r="A379" s="2">
@@ -21284,13 +21389,17 @@
       <c r="E379" s="3">
         <v>46085.6561570255</v>
       </c>
-      <c r="F379" s="1"/>
-      <c r="G379" s="1"/>
+      <c r="F379" s="2">
+        <v>82456</v>
+      </c>
+      <c r="G379" s="3">
+        <v>46086</v>
+      </c>
       <c r="H379" s="1" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="I379" s="1" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="J379" s="1" t="s">
         <v>20</v>
@@ -21302,13 +21411,17 @@
         <v>1</v>
       </c>
       <c r="M379" s="4">
-        <v>0</v>
+        <v>400.54</v>
       </c>
       <c r="N379" s="4">
-        <v>0</v>
-      </c>
-      <c r="O379" s="1"/>
-      <c r="P379" s="1"/>
+        <v>400.54</v>
+      </c>
+      <c r="O379" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="P379" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="380">
       <c r="A380" s="2">
@@ -21326,13 +21439,17 @@
       <c r="E380" s="3">
         <v>46085.6561570255</v>
       </c>
-      <c r="F380" s="1"/>
-      <c r="G380" s="1"/>
+      <c r="F380" s="2">
+        <v>82456</v>
+      </c>
+      <c r="G380" s="3">
+        <v>46086</v>
+      </c>
       <c r="H380" s="1" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="I380" s="1" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="J380" s="1" t="s">
         <v>20</v>
@@ -21344,13 +21461,17 @@
         <v>1</v>
       </c>
       <c r="M380" s="4">
-        <v>0</v>
+        <v>685.67</v>
       </c>
       <c r="N380" s="4">
-        <v>0</v>
-      </c>
-      <c r="O380" s="1"/>
-      <c r="P380" s="1"/>
+        <v>685.67</v>
+      </c>
+      <c r="O380" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="P380" s="1" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="381">
       <c r="A381" s="2">
@@ -21475,10 +21596,10 @@
         <v>46085</v>
       </c>
       <c r="H383" s="1" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="I383" s="1" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="J383" s="1" t="s">
         <v>20</v>
@@ -21525,31 +21646,31 @@
         <v>46085</v>
       </c>
       <c r="H384" s="1" t="s">
-        <v>51</v>
+        <v>722</v>
       </c>
       <c r="I384" s="1" t="s">
-        <v>52</v>
+        <v>723</v>
       </c>
       <c r="J384" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K384" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="L384" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M384" s="4">
-        <v>23.5</v>
+        <v>160</v>
       </c>
       <c r="N384" s="4">
-        <v>117.5</v>
+        <v>160</v>
       </c>
       <c r="O384" s="1" t="s">
-        <v>180</v>
+        <v>664</v>
       </c>
       <c r="P384" s="1" t="s">
-        <v>181</v>
+        <v>665</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="385">
@@ -21569,37 +21690,37 @@
         <v>46085.6581644213</v>
       </c>
       <c r="F385" s="2">
-        <v>82445</v>
+        <v>82468</v>
       </c>
       <c r="G385" s="3">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="H385" s="1" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="I385" s="1" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="J385" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K385" s="1" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L385" s="4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M385" s="4">
-        <v>13.6</v>
+        <v>16.9</v>
       </c>
       <c r="N385" s="4">
-        <v>81.6</v>
+        <v>507</v>
       </c>
       <c r="O385" s="1" t="s">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="P385" s="1" t="s">
-        <v>181</v>
+        <v>79</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="386">
@@ -21619,37 +21740,37 @@
         <v>46085.6581644213</v>
       </c>
       <c r="F386" s="2">
-        <v>82453</v>
+        <v>82468</v>
       </c>
       <c r="G386" s="3">
         <v>46086</v>
       </c>
       <c r="H386" s="1" t="s">
-        <v>18</v>
+        <v>726</v>
       </c>
       <c r="I386" s="1" t="s">
-        <v>19</v>
+        <v>727</v>
       </c>
       <c r="J386" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K386" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L386" s="4">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="M386" s="4">
-        <v>33.99</v>
+        <v>316</v>
       </c>
       <c r="N386" s="4">
-        <v>3399</v>
+        <v>948</v>
       </c>
       <c r="O386" s="1" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="P386" s="1" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="387">
@@ -21668,31 +21789,39 @@
       <c r="E387" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F387" s="1"/>
-      <c r="G387" s="1"/>
+      <c r="F387" s="2">
+        <v>82468</v>
+      </c>
+      <c r="G387" s="3">
+        <v>46086</v>
+      </c>
       <c r="H387" s="1" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="J387" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K387" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="L387" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M387" s="4">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="N387" s="4">
-        <v>0</v>
-      </c>
-      <c r="O387" s="1"/>
-      <c r="P387" s="1"/>
+        <v>948</v>
+      </c>
+      <c r="O387" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P387" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="388">
       <c r="A388" s="2">
@@ -21710,31 +21839,39 @@
       <c r="E388" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F388" s="1"/>
-      <c r="G388" s="1"/>
+      <c r="F388" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G388" s="3">
+        <v>46085</v>
+      </c>
       <c r="H388" s="1" t="s">
-        <v>720</v>
+        <v>300</v>
       </c>
       <c r="I388" s="1" t="s">
-        <v>721</v>
+        <v>301</v>
       </c>
       <c r="J388" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K388" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="L388" s="4">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M388" s="4">
-        <v>0</v>
+        <v>44.9</v>
       </c>
       <c r="N388" s="4">
-        <v>0</v>
-      </c>
-      <c r="O388" s="1"/>
-      <c r="P388" s="1"/>
+        <v>269.4</v>
+      </c>
+      <c r="O388" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P388" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="389">
       <c r="A389" s="2">
@@ -21752,13 +21889,17 @@
       <c r="E389" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F389" s="1"/>
-      <c r="G389" s="1"/>
+      <c r="F389" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G389" s="3">
+        <v>46085</v>
+      </c>
       <c r="H389" s="1" t="s">
-        <v>722</v>
+        <v>51</v>
       </c>
       <c r="I389" s="1" t="s">
-        <v>723</v>
+        <v>52</v>
       </c>
       <c r="J389" s="1" t="s">
         <v>20</v>
@@ -21767,16 +21908,20 @@
         <v>28</v>
       </c>
       <c r="L389" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M389" s="4">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="N389" s="4">
-        <v>0</v>
-      </c>
-      <c r="O389" s="1"/>
-      <c r="P389" s="1"/>
+        <v>117.5</v>
+      </c>
+      <c r="O389" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P389" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="390">
       <c r="A390" s="2">
@@ -21794,13 +21939,17 @@
       <c r="E390" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F390" s="1"/>
-      <c r="G390" s="1"/>
+      <c r="F390" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G390" s="3">
+        <v>46085</v>
+      </c>
       <c r="H390" s="1" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="I390" s="1" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="J390" s="1" t="s">
         <v>20</v>
@@ -21809,16 +21958,20 @@
         <v>28</v>
       </c>
       <c r="L390" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M390" s="4">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="N390" s="4">
-        <v>0</v>
-      </c>
-      <c r="O390" s="1"/>
-      <c r="P390" s="1"/>
+        <v>81.6</v>
+      </c>
+      <c r="O390" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P390" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="391">
       <c r="A391" s="2">
@@ -21836,31 +21989,39 @@
       <c r="E391" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F391" s="1"/>
-      <c r="G391" s="1"/>
+      <c r="F391" s="2">
+        <v>82453</v>
+      </c>
+      <c r="G391" s="3">
+        <v>46086</v>
+      </c>
       <c r="H391" s="1" t="s">
-        <v>300</v>
+        <v>18</v>
       </c>
       <c r="I391" s="1" t="s">
-        <v>301</v>
+        <v>19</v>
       </c>
       <c r="J391" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K391" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L391" s="4">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="M391" s="4">
-        <v>47.93</v>
+        <v>33.99</v>
       </c>
       <c r="N391" s="4">
-        <v>287.58</v>
-      </c>
-      <c r="O391" s="1"/>
-      <c r="P391" s="1"/>
+        <v>3399</v>
+      </c>
+      <c r="O391" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P391" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="392">
       <c r="A392" s="2">
@@ -21878,13 +22039,17 @@
       <c r="E392" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F392" s="1"/>
-      <c r="G392" s="1"/>
+      <c r="F392" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G392" s="3">
+        <v>46085</v>
+      </c>
       <c r="H392" s="1" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="I392" s="1" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="J392" s="1" t="s">
         <v>20</v>
@@ -21896,13 +22061,17 @@
         <v>250</v>
       </c>
       <c r="M392" s="4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N392" s="4">
-        <v>0</v>
-      </c>
-      <c r="O392" s="1"/>
-      <c r="P392" s="1"/>
+        <v>625</v>
+      </c>
+      <c r="O392" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P392" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="393">
       <c r="A393" s="2">
@@ -21920,8 +22089,12 @@
       <c r="E393" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F393" s="1"/>
-      <c r="G393" s="1"/>
+      <c r="F393" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G393" s="3">
+        <v>46085</v>
+      </c>
       <c r="H393" s="1" t="s">
         <v>344</v>
       </c>
@@ -21938,13 +22111,17 @@
         <v>1</v>
       </c>
       <c r="M393" s="4">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="N393" s="4">
-        <v>0</v>
-      </c>
-      <c r="O393" s="1"/>
-      <c r="P393" s="1"/>
+        <v>155</v>
+      </c>
+      <c r="O393" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P393" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="394">
       <c r="A394" s="2">
@@ -21962,13 +22139,17 @@
       <c r="E394" s="3">
         <v>46085.6581644213</v>
       </c>
-      <c r="F394" s="1"/>
-      <c r="G394" s="1"/>
+      <c r="F394" s="2">
+        <v>82445</v>
+      </c>
+      <c r="G394" s="3">
+        <v>46085</v>
+      </c>
       <c r="H394" s="1" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="I394" s="1" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="J394" s="1" t="s">
         <v>20</v>
@@ -21980,13 +22161,17 @@
         <v>1</v>
       </c>
       <c r="M394" s="4">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="N394" s="4">
-        <v>0</v>
-      </c>
-      <c r="O394" s="1"/>
-      <c r="P394" s="1"/>
+        <v>430</v>
+      </c>
+      <c r="O394" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P394" s="1" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="395">
       <c r="A395" s="2">
@@ -22004,13 +22189,17 @@
       <c r="E395" s="3">
         <v>46085.7157723032</v>
       </c>
-      <c r="F395" s="1"/>
-      <c r="G395" s="1"/>
+      <c r="F395" s="2">
+        <v>82457</v>
+      </c>
+      <c r="G395" s="3">
+        <v>46086</v>
+      </c>
       <c r="H395" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I395" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J395" s="1" t="s">
         <v>20</v>
@@ -22022,13 +22211,561 @@
         <v>60</v>
       </c>
       <c r="M395" s="4">
+        <v>55</v>
+      </c>
+      <c r="N395" s="4">
+        <v>3300</v>
+      </c>
+      <c r="O395" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="P395" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="396">
+      <c r="A396" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D396" s="2">
+        <v>16</v>
+      </c>
+      <c r="E396" s="3">
+        <v>46086.6312882639</v>
+      </c>
+      <c r="F396" s="1"/>
+      <c r="G396" s="1"/>
+      <c r="H396" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I396" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="J396" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K396" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="L396" s="4">
+        <v>9</v>
+      </c>
+      <c r="M396" s="4">
         <v>0</v>
       </c>
-      <c r="N395" s="4">
+      <c r="N396" s="4">
         <v>0</v>
       </c>
-      <c r="O395" s="1"/>
-      <c r="P395" s="1"/>
+      <c r="O396" s="1"/>
+      <c r="P396" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="397">
+      <c r="A397" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D397" s="2">
+        <v>16</v>
+      </c>
+      <c r="E397" s="3">
+        <v>46086.6312882639</v>
+      </c>
+      <c r="F397" s="1"/>
+      <c r="G397" s="1"/>
+      <c r="H397" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I397" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="J397" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K397" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="L397" s="4">
+        <v>11</v>
+      </c>
+      <c r="M397" s="4">
+        <v>0</v>
+      </c>
+      <c r="N397" s="4">
+        <v>0</v>
+      </c>
+      <c r="O397" s="1"/>
+      <c r="P397" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="398">
+      <c r="A398" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D398" s="2">
+        <v>16</v>
+      </c>
+      <c r="E398" s="3">
+        <v>46086.6312882639</v>
+      </c>
+      <c r="F398" s="1"/>
+      <c r="G398" s="1"/>
+      <c r="H398" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I398" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="J398" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K398" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="L398" s="4">
+        <v>12</v>
+      </c>
+      <c r="M398" s="4">
+        <v>0</v>
+      </c>
+      <c r="N398" s="4">
+        <v>0</v>
+      </c>
+      <c r="O398" s="1"/>
+      <c r="P398" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="399">
+      <c r="A399" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D399" s="2">
+        <v>16</v>
+      </c>
+      <c r="E399" s="3">
+        <v>46086.6312882639</v>
+      </c>
+      <c r="F399" s="1"/>
+      <c r="G399" s="1"/>
+      <c r="H399" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I399" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="J399" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K399" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="L399" s="4">
+        <v>16</v>
+      </c>
+      <c r="M399" s="4">
+        <v>0</v>
+      </c>
+      <c r="N399" s="4">
+        <v>0</v>
+      </c>
+      <c r="O399" s="1"/>
+      <c r="P399" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="400">
+      <c r="A400" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D400" s="2">
+        <v>92</v>
+      </c>
+      <c r="E400" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F400" s="2">
+        <v>82471</v>
+      </c>
+      <c r="G400" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H400" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I400" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J400" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K400" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L400" s="4">
+        <v>1</v>
+      </c>
+      <c r="M400" s="4">
+        <v>65.6</v>
+      </c>
+      <c r="N400" s="4">
+        <v>65.6</v>
+      </c>
+      <c r="O400" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P400" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="401">
+      <c r="A401" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D401" s="2">
+        <v>92</v>
+      </c>
+      <c r="E401" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F401" s="2">
+        <v>82471</v>
+      </c>
+      <c r="G401" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H401" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I401" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J401" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K401" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L401" s="4">
+        <v>10</v>
+      </c>
+      <c r="M401" s="4">
+        <v>10.85</v>
+      </c>
+      <c r="N401" s="4">
+        <v>108.5</v>
+      </c>
+      <c r="O401" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="P401" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="402">
+      <c r="A402" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D402" s="2">
+        <v>92</v>
+      </c>
+      <c r="E402" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F402" s="2">
+        <v>82470</v>
+      </c>
+      <c r="G402" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H402" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I402" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J402" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K402" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L402" s="4">
+        <v>1</v>
+      </c>
+      <c r="M402" s="4">
+        <v>12.09</v>
+      </c>
+      <c r="N402" s="4">
+        <v>12.09</v>
+      </c>
+      <c r="O402" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P402" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="403">
+      <c r="A403" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D403" s="2">
+        <v>92</v>
+      </c>
+      <c r="E403" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F403" s="2">
+        <v>82470</v>
+      </c>
+      <c r="G403" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H403" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="I403" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J403" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K403" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L403" s="4">
+        <v>2</v>
+      </c>
+      <c r="M403" s="4">
+        <v>270</v>
+      </c>
+      <c r="N403" s="4">
+        <v>540</v>
+      </c>
+      <c r="O403" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P403" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="404">
+      <c r="A404" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D404" s="2">
+        <v>92</v>
+      </c>
+      <c r="E404" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F404" s="2">
+        <v>82470</v>
+      </c>
+      <c r="G404" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H404" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="I404" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J404" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K404" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L404" s="4">
+        <v>10</v>
+      </c>
+      <c r="M404" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="N404" s="4">
+        <v>27.5</v>
+      </c>
+      <c r="O404" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P404" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="405">
+      <c r="A405" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D405" s="2">
+        <v>92</v>
+      </c>
+      <c r="E405" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F405" s="1"/>
+      <c r="G405" s="1"/>
+      <c r="H405" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="I405" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J405" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K405" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L405" s="4">
+        <v>3</v>
+      </c>
+      <c r="M405" s="4">
+        <v>0</v>
+      </c>
+      <c r="N405" s="4">
+        <v>0</v>
+      </c>
+      <c r="O405" s="1"/>
+      <c r="P405" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="406">
+      <c r="A406" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D406" s="2">
+        <v>92</v>
+      </c>
+      <c r="E406" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F406" s="1"/>
+      <c r="G406" s="1"/>
+      <c r="H406" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I406" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J406" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K406" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L406" s="4">
+        <v>4</v>
+      </c>
+      <c r="M406" s="4">
+        <v>0</v>
+      </c>
+      <c r="N406" s="4">
+        <v>0</v>
+      </c>
+      <c r="O406" s="1"/>
+      <c r="P406" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="407">
+      <c r="A407" s="2">
+        <v>2409</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D407" s="2">
+        <v>92</v>
+      </c>
+      <c r="E407" s="3">
+        <v>46086.632572419</v>
+      </c>
+      <c r="F407" s="1"/>
+      <c r="G407" s="1"/>
+      <c r="H407" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="I407" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="J407" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K407" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L407" s="4">
+        <v>20</v>
+      </c>
+      <c r="M407" s="4">
+        <v>0</v>
+      </c>
+      <c r="N407" s="4">
+        <v>0</v>
+      </c>
+      <c r="O407" s="1"/>
+      <c r="P407" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="645">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1935,6 +1935,18 @@
   </si>
   <si>
     <t xml:space="preserve">FITA CREPE  VERDE 5CM X 40MM AUTOMOTIVA</t>
+  </si>
+  <si>
+    <t>F.01.0009</t>
+  </si>
+  <si>
+    <t>ESCADA</t>
+  </si>
+  <si>
+    <t>J.02.1502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARGAMASSA TK PLUS TECNOKOLL INTERNA E EXTERNA  ATÉ  90X90CM 1.4MPA ACIII BRANCA 20KG</t>
   </si>
 </sst>
 </file>
@@ -2233,7 +2245,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P340"/>
+  <dimension ref="A1:P344"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -19187,6 +19199,182 @@
         <v>559</v>
       </c>
     </row>
+    <row ht="12.75" customHeight="1" r="341">
+      <c r="A341" s="2">
+        <v>2407</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D341" s="2">
+        <v>85</v>
+      </c>
+      <c r="E341" s="3">
+        <v>46087.643003044</v>
+      </c>
+      <c r="F341" s="2">
+        <v>82489</v>
+      </c>
+      <c r="G341" s="3">
+        <v>46087</v>
+      </c>
+      <c r="H341" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="J341" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K341" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L341" s="4">
+        <v>4</v>
+      </c>
+      <c r="M341" s="4">
+        <v>89.9</v>
+      </c>
+      <c r="N341" s="4">
+        <v>359.6</v>
+      </c>
+      <c r="O341" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P341" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="342">
+      <c r="A342" s="2">
+        <v>2407</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D342" s="2">
+        <v>85</v>
+      </c>
+      <c r="E342" s="3">
+        <v>46087.643003044</v>
+      </c>
+      <c r="F342" s="1"/>
+      <c r="G342" s="1"/>
+      <c r="H342" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J342" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K342" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L342" s="4">
+        <v>30</v>
+      </c>
+      <c r="M342" s="4">
+        <v>0</v>
+      </c>
+      <c r="N342" s="4">
+        <v>0</v>
+      </c>
+      <c r="O342" s="1"/>
+      <c r="P342" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="343">
+      <c r="A343" s="2">
+        <v>2407</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D343" s="2">
+        <v>85</v>
+      </c>
+      <c r="E343" s="3">
+        <v>46087.643003044</v>
+      </c>
+      <c r="F343" s="1"/>
+      <c r="G343" s="1"/>
+      <c r="H343" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="I343" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J343" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K343" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L343" s="4">
+        <v>2</v>
+      </c>
+      <c r="M343" s="4">
+        <v>0</v>
+      </c>
+      <c r="N343" s="4">
+        <v>0</v>
+      </c>
+      <c r="O343" s="1"/>
+      <c r="P343" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="344">
+      <c r="A344" s="2">
+        <v>2407</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D344" s="2">
+        <v>85</v>
+      </c>
+      <c r="E344" s="3">
+        <v>46087.643003044</v>
+      </c>
+      <c r="F344" s="1"/>
+      <c r="G344" s="1"/>
+      <c r="H344" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="J344" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K344" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L344" s="4">
+        <v>3</v>
+      </c>
+      <c r="M344" s="4">
+        <v>0</v>
+      </c>
+      <c r="N344" s="4">
+        <v>0</v>
+      </c>
+      <c r="O344" s="1"/>
+      <c r="P344" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
   <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1805,6 +1805,12 @@
     <t xml:space="preserve">FITA CREPE  VERDE 5CM X 40MM AUTOMOTIVA</t>
   </si>
   <si>
+    <t>F.01.0009</t>
+  </si>
+  <si>
+    <t>ESCADA</t>
+  </si>
+  <si>
     <t>J.02.1502</t>
   </si>
   <si>
@@ -1815,12 +1821,6 @@
   </si>
   <si>
     <t>TECNOKOLL</t>
-  </si>
-  <si>
-    <t>F.01.0009</t>
-  </si>
-  <si>
-    <t>ESCADA</t>
   </si>
 </sst>
 </file>
@@ -17598,37 +17598,37 @@
         <v>46087.643003044</v>
       </c>
       <c r="F311" s="2">
-        <v>82496</v>
+        <v>82497</v>
       </c>
       <c r="G311" s="3">
         <v>46090</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>597</v>
+        <v>278</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>598</v>
+        <v>279</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K311" s="1" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="L311" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="M311" s="4">
-        <v>57.2</v>
+        <v>23.43</v>
       </c>
       <c r="N311" s="4">
-        <v>171.6</v>
+        <v>702.9</v>
       </c>
       <c r="O311" s="1" t="s">
-        <v>599</v>
+        <v>159</v>
       </c>
       <c r="P311" s="1" t="s">
-        <v>600</v>
+        <v>160</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="312">
@@ -17647,13 +17647,17 @@
       <c r="E312" s="3">
         <v>46087.643003044</v>
       </c>
-      <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
+      <c r="F312" s="2">
+        <v>82497</v>
+      </c>
+      <c r="G312" s="3">
+        <v>46090</v>
+      </c>
       <c r="H312" s="1" t="s">
-        <v>278</v>
+        <v>597</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>279</v>
+        <v>598</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>20</v>
@@ -17662,16 +17666,20 @@
         <v>21</v>
       </c>
       <c r="L312" s="4">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="M312" s="4">
-        <v>0</v>
+        <v>239.75</v>
       </c>
       <c r="N312" s="4">
-        <v>0</v>
-      </c>
-      <c r="O312" s="1"/>
-      <c r="P312" s="1"/>
+        <v>479.5</v>
+      </c>
+      <c r="O312" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P312" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="313">
       <c r="A313" s="2">
@@ -17689,31 +17697,39 @@
       <c r="E313" s="3">
         <v>46087.643003044</v>
       </c>
-      <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
+      <c r="F313" s="2">
+        <v>82496</v>
+      </c>
+      <c r="G313" s="3">
+        <v>46090</v>
+      </c>
       <c r="H313" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="I313" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="J313" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K313" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L313" s="4">
+        <v>3</v>
+      </c>
+      <c r="M313" s="4">
+        <v>57.2</v>
+      </c>
+      <c r="N313" s="4">
+        <v>171.6</v>
+      </c>
+      <c r="O313" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="I313" s="1" t="s">
+      <c r="P313" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="J313" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K313" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L313" s="4">
-        <v>2</v>
-      </c>
-      <c r="M313" s="4">
-        <v>0</v>
-      </c>
-      <c r="N313" s="4">
-        <v>0</v>
-      </c>
-      <c r="O313" s="1"/>
-      <c r="P313" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1,18 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/RelatoriosSiecon/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_DAC86EC901EAF00A78D189249382C3234C503B46" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83ED3F71-DAFA-4041-8756-4395BD5A0EC5}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId5"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$P$313</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="603">
   <si>
     <t>EMPRD</t>
   </si>
@@ -215,7 +226,7 @@
     <t>E.03.0162</t>
   </si>
   <si>
-    <t xml:space="preserve">CINTA ERGÔNOMICA ABDOMINAL  PROTETOR LOMBAR</t>
+    <t>CINTA ERGÔNOMICA ABDOMINAL  PROTETOR LOMBAR</t>
   </si>
   <si>
     <t>00000000008882</t>
@@ -266,7 +277,7 @@
     <t>R.02.0182</t>
   </si>
   <si>
-    <t xml:space="preserve">TRINCHA  2 1/2"</t>
+    <t>TRINCHA  2 1/2"</t>
   </si>
   <si>
     <t>R.02.0115</t>
@@ -284,7 +295,7 @@
     <t>00000000009713</t>
   </si>
   <si>
-    <t xml:space="preserve">P&amp;G  PEDRO</t>
+    <t>P&amp;G  PEDRO</t>
   </si>
   <si>
     <t>LUIZ ALBERTO HESS BORGES</t>
@@ -383,7 +394,7 @@
     <t>S.08.0291</t>
   </si>
   <si>
-    <t xml:space="preserve">MANTA AUTOCOLANTE   ALUMINIO</t>
+    <t>MANTA AUTOCOLANTE   ALUMINIO</t>
   </si>
   <si>
     <t>CX</t>
@@ -392,7 +403,7 @@
     <t>S.08.0202</t>
   </si>
   <si>
-    <t xml:space="preserve">VIAPLUS 5000  IMPER. BI-COMPONENTE(A+B)  - EMB. 18KG</t>
+    <t>VIAPLUS 5000  IMPER. BI-COMPONENTE(A+B)  - EMB. 18KG</t>
   </si>
   <si>
     <t>EW ADMINISTRADORA LTDA</t>
@@ -407,7 +418,7 @@
     <t>00000000009973</t>
   </si>
   <si>
-    <t xml:space="preserve">CASA DA  AGUA</t>
+    <t>CASA DA  AGUA</t>
   </si>
   <si>
     <t>E.03.0001</t>
@@ -419,25 +430,25 @@
     <t>E.03.0253</t>
   </si>
   <si>
-    <t xml:space="preserve">CAPA DE CHUVA TREVISA COM FORRO MANGA COMPRIDA  G</t>
+    <t>CAPA DE CHUVA TREVISA COM FORRO MANGA COMPRIDA  G</t>
   </si>
   <si>
     <t>E.04.0380</t>
   </si>
   <si>
-    <t xml:space="preserve">BROCA SDS PLUS WIDIA DE ENCAIXE -  8MM X 210MM</t>
+    <t>BROCA SDS PLUS WIDIA DE ENCAIXE -  8MM X 210MM</t>
   </si>
   <si>
     <t>E.04.0382</t>
   </si>
   <si>
-    <t xml:space="preserve">BROCA SDS PLUS WIDIA DE ENCAIXE -  10MM X 210MM</t>
+    <t>BROCA SDS PLUS WIDIA DE ENCAIXE -  10MM X 210MM</t>
   </si>
   <si>
     <t>E.04.0385</t>
   </si>
   <si>
-    <t xml:space="preserve">BROCA SDS PLUS WIDIA DE ENCAIXE -  12MM X 210MM</t>
+    <t>BROCA SDS PLUS WIDIA DE ENCAIXE -  12MM X 210MM</t>
   </si>
   <si>
     <t>G.01.0001</t>
@@ -488,7 +499,7 @@
     <t>E.05.0002</t>
   </si>
   <si>
-    <t xml:space="preserve">PROPÉ SAPATILHA DESCARTAVEL  PCT COM 50 UNID</t>
+    <t>PROPÉ SAPATILHA DESCARTAVEL  PCT COM 50 UNID</t>
   </si>
   <si>
     <t>00000000010258</t>
@@ -548,7 +559,7 @@
     <t>E.03.0130</t>
   </si>
   <si>
-    <t xml:space="preserve">PROTETOR  AURICULAR TIPO ABAFADOR ( TIPO CONCHA )  14 DECIBÉIS</t>
+    <t>PROTETOR  AURICULAR TIPO ABAFADOR ( TIPO CONCHA )  14 DECIBÉIS</t>
   </si>
   <si>
     <t>PC</t>
@@ -647,31 +658,31 @@
     <t>K.02.0979</t>
   </si>
   <si>
-    <t xml:space="preserve">ADAPTADOR PVC SOLDÁVEL  COM FLANGES LIVRES PARA CAIXA D'ÁGUA  25 X 3/4"</t>
+    <t>ADAPTADOR PVC SOLDÁVEL  COM FLANGES LIVRES PARA CAIXA D'ÁGUA  25 X 3/4"</t>
   </si>
   <si>
     <t>K.02.1300</t>
   </si>
   <si>
-    <t xml:space="preserve">TUBO PVC SOLDÁVEL DE 25MM  ( MARRON ) C/ 6M</t>
+    <t>TUBO PVC SOLDÁVEL DE 25MM  ( MARRON ) C/ 6M</t>
   </si>
   <si>
     <t>K.02.1350</t>
   </si>
   <si>
-    <t xml:space="preserve">JOELHO PVC SOLDÁVEL (MARRON )  20MM X90º</t>
+    <t>JOELHO PVC SOLDÁVEL (MARRON )  20MM X90º</t>
   </si>
   <si>
     <t>K.02.1401</t>
   </si>
   <si>
-    <t xml:space="preserve">LUVA PVC SOLDAVEL  ( MARRON ) 25MM</t>
+    <t>LUVA PVC SOLDAVEL  ( MARRON ) 25MM</t>
   </si>
   <si>
     <t>K.02.1011</t>
   </si>
   <si>
-    <t xml:space="preserve">ADAPTADOR  PVC SOLDAVEL CURTO 25MM X 3/4"</t>
+    <t>ADAPTADOR  PVC SOLDAVEL CURTO 25MM X 3/4"</t>
   </si>
   <si>
     <t>K.02.1436</t>
@@ -683,13 +694,13 @@
     <t>K.02.1428</t>
   </si>
   <si>
-    <t xml:space="preserve">LUVA PVC SOLDAVEL  C/ ROSCA  ( MARRON LR ) 25MM X 3/4</t>
+    <t>LUVA PVC SOLDAVEL  C/ ROSCA  ( MARRON LR ) 25MM X 3/4</t>
   </si>
   <si>
     <t>K.02.4674</t>
   </si>
   <si>
-    <t xml:space="preserve">FITA VEDA ROSCA  - 18MM X 50M</t>
+    <t>FITA VEDA ROSCA  - 18MM X 50M</t>
   </si>
   <si>
     <t>U.02.0106</t>
@@ -737,7 +748,7 @@
     <t>C.04.0020</t>
   </si>
   <si>
-    <t xml:space="preserve">SACO DE RAFIA  50 L</t>
+    <t>SACO DE RAFIA  50 L</t>
   </si>
   <si>
     <t>C.04.0141</t>
@@ -821,7 +832,7 @@
     <t>C.05.0206</t>
   </si>
   <si>
-    <t xml:space="preserve">GAVETEIRO C/ 2 GAVETAS E 1 GAVETÃO  - 0,64 M X 0,50 M X 0,47 M</t>
+    <t>GAVETEIRO C/ 2 GAVETAS E 1 GAVETÃO  - 0,64 M X 0,50 M X 0,47 M</t>
   </si>
   <si>
     <t>D.01.0031</t>
@@ -839,7 +850,7 @@
     <t>E.02.0211</t>
   </si>
   <si>
-    <t xml:space="preserve">FILME DE POLIETILENO  ADESIVADO SEM COLA REMOVIVEL  PROTEÇÃO DE CAIXILHO  PROCAIXILHO 200MM/100M =20M² PROMAFLEX</t>
+    <t>FILME DE POLIETILENO  ADESIVADO SEM COLA REMOVIVEL  PROTEÇÃO DE CAIXILHO  PROCAIXILHO 200MM/100M =20M² PROMAFLEX</t>
   </si>
   <si>
     <t>00000000006868</t>
@@ -851,7 +862,7 @@
     <t>E.02.0012</t>
   </si>
   <si>
-    <t xml:space="preserve">FITA CREPE LARANJA 45 MM X  50M</t>
+    <t>FITA CREPE LARANJA 45 MM X  50M</t>
   </si>
   <si>
     <t>E.02.0072</t>
@@ -929,7 +940,7 @@
     <t>K.01.0870</t>
   </si>
   <si>
-    <t xml:space="preserve">UNIDADE COMBINADA  - ROBOZINHO</t>
+    <t>UNIDADE COMBINADA  - ROBOZINHO</t>
   </si>
   <si>
     <t>00000000009700</t>
@@ -977,7 +988,7 @@
     <t>O.01.0111</t>
   </si>
   <si>
-    <t xml:space="preserve">TABUA DE PINUS  1" X 10"</t>
+    <t>TABUA DE PINUS  1" X 10"</t>
   </si>
   <si>
     <t>00000000008356</t>
@@ -1013,7 +1024,7 @@
     <t>U.03.0500</t>
   </si>
   <si>
-    <t xml:space="preserve">DISPENSER  PARA SABONETE</t>
+    <t>DISPENSER  PARA SABONETE</t>
   </si>
   <si>
     <t>U.02.7201</t>
@@ -1070,7 +1081,7 @@
     <t>K.08.0158</t>
   </si>
   <si>
-    <t xml:space="preserve">TOMADA 2P +T 20A  LG BTICINO BIANCO LIGHT SN4166S</t>
+    <t>TOMADA 2P +T 20A  LG BTICINO BIANCO LIGHT SN4166S</t>
   </si>
   <si>
     <t>K.08.6000</t>
@@ -1082,25 +1093,25 @@
     <t>K.08.6161</t>
   </si>
   <si>
-    <t xml:space="preserve">SUPORTE PARA 3 MÓDULOS REDONDO E QUADRADO SLN 4703M  LIVING LIGHT</t>
+    <t>SUPORTE PARA 3 MÓDULOS REDONDO E QUADRADO SLN 4703M  LIVING LIGHT</t>
   </si>
   <si>
     <t>K.08.6012</t>
   </si>
   <si>
-    <t xml:space="preserve">PULSADOR 1P NO 10A 250VCA SN 4005NF  LIVING LIGHT</t>
+    <t>PULSADOR 1P NO 10A 250VCA SN 4005NF  LIVING LIGHT</t>
   </si>
   <si>
     <t>K.08.6004</t>
   </si>
   <si>
-    <t xml:space="preserve">INTERRUPTOR PARALELO  1P 16A X 250 VAC  SN 4003NF  LIVING LIGHT</t>
+    <t>INTERRUPTOR PARALELO  1P 16A X 250 VAC  SN 4003NF  LIVING LIGHT</t>
   </si>
   <si>
     <t>K.08.6166</t>
   </si>
   <si>
-    <t xml:space="preserve">PLACA QUADRADA BIANCO  LNA 4803BIF LIVING LIGHT</t>
+    <t>PLACA QUADRADA BIANCO  LNA 4803BIF LIVING LIGHT</t>
   </si>
   <si>
     <t>MARIA BELTRÃO SALDANHA COELHO</t>
@@ -1166,7 +1177,7 @@
     <t>O.01.0102</t>
   </si>
   <si>
-    <t xml:space="preserve">TABUA DE PINUS  1" X 6"</t>
+    <t>TABUA DE PINUS  1" X 6"</t>
   </si>
   <si>
     <t>00000000009484</t>
@@ -1241,7 +1252,7 @@
     <t>K.02.0128</t>
   </si>
   <si>
-    <t xml:space="preserve">TUBO PVC ESGOTO SERIE R  100MM C/ 6 M  AMANCO</t>
+    <t>TUBO PVC ESGOTO SERIE R  100MM C/ 6 M  AMANCO</t>
   </si>
   <si>
     <t>00000000008485</t>
@@ -1265,19 +1276,19 @@
     <t>K.02.3577</t>
   </si>
   <si>
-    <t xml:space="preserve">TÊ  PVC P/ ESG. SÉRIE R DN 100 X 100MM TIGRE</t>
+    <t>TÊ  PVC P/ ESG. SÉRIE R DN 100 X 100MM TIGRE</t>
   </si>
   <si>
     <t>K.02.3568</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNÇÃO SIMPLES  PVC P/ ESG. SÉRIE R DN 100 X 75MM TIGRE</t>
+    <t>JUNÇÃO SIMPLES  PVC P/ ESG. SÉRIE R DN 100 X 75MM TIGRE</t>
   </si>
   <si>
     <t>K.02.3569</t>
   </si>
   <si>
-    <t xml:space="preserve">JUNÇÃO SIMPLES  PVC P/ ESG. SÉRIE R DN 100 X 100MM TIGRE</t>
+    <t>JUNÇÃO SIMPLES  PVC P/ ESG. SÉRIE R DN 100 X 100MM TIGRE</t>
   </si>
   <si>
     <t>S.08.0611</t>
@@ -1310,7 +1321,7 @@
     <t>E.03.0370</t>
   </si>
   <si>
-    <t xml:space="preserve">CORRENTE  PLÁSTICA PARA SINALIZAÇÃO.</t>
+    <t>CORRENTE  PLÁSTICA PARA SINALIZAÇÃO.</t>
   </si>
   <si>
     <t>E.04.0263</t>
@@ -1403,7 +1414,7 @@
     <t>U.02.2800</t>
   </si>
   <si>
-    <t xml:space="preserve">CAIXA DE DESCARGA EMBUTIDA  HYDRA MECÂNICA 2500 CX.MC.AF ( BACIA DE PISO )</t>
+    <t>CAIXA DE DESCARGA EMBUTIDA  HYDRA MECÂNICA 2500 CX.MC.AF ( BACIA DE PISO )</t>
   </si>
   <si>
     <t>00000000008165</t>
@@ -1430,19 +1441,19 @@
     <t>U.03.6000</t>
   </si>
   <si>
-    <t xml:space="preserve">RALO  LINHA SQUARE LINE 15 X 15</t>
+    <t>RALO  LINHA SQUARE LINE 15 X 15</t>
   </si>
   <si>
     <t>U.03.6004</t>
   </si>
   <si>
-    <t xml:space="preserve">RALO  LINHA SQUARE LINE 10 X 10</t>
+    <t>RALO  LINHA SQUARE LINE 10 X 10</t>
   </si>
   <si>
     <t>U.02.21021</t>
   </si>
   <si>
-    <t xml:space="preserve">ACABAMENTO PARA REGISTRO  DE GAVETA  ATÉ 1''  REDONDO  DARK ANTRACITE  DECA YOU REF 4900  GF104</t>
+    <t>ACABAMENTO PARA REGISTRO  DE GAVETA  ATÉ 1''  REDONDO  DARK ANTRACITE  DECA YOU REF 4900  GF104</t>
   </si>
   <si>
     <t>E.01.0070</t>
@@ -1508,7 +1519,7 @@
     <t>O.01.0110</t>
   </si>
   <si>
-    <t xml:space="preserve">TABUA DE PINUS  1" X 4"</t>
+    <t>TABUA DE PINUS  1" X 4"</t>
   </si>
   <si>
     <t>00000000009980</t>
@@ -1520,13 +1531,13 @@
     <t>O.01.0121</t>
   </si>
   <si>
-    <t xml:space="preserve">TABUA DE PINUS  3" X 3"</t>
+    <t>TABUA DE PINUS  3" X 3"</t>
   </si>
   <si>
     <t>O.01.0142</t>
   </si>
   <si>
-    <t xml:space="preserve">TABUA DE PINUS  1" X 12"</t>
+    <t>TABUA DE PINUS  1" X 12"</t>
   </si>
   <si>
     <t>O.01.0118</t>
@@ -1610,7 +1621,7 @@
     <t>K.02.1806</t>
   </si>
   <si>
-    <t xml:space="preserve">SOLUÇÃO PREPARADORA  PARA TUBOS E CONEXÕS PVC 1 L</t>
+    <t>SOLUÇÃO PREPARADORA  PARA TUBOS E CONEXÕS PVC 1 L</t>
   </si>
   <si>
     <t>K.02.4669</t>
@@ -1622,7 +1633,7 @@
     <t>P.02.0012</t>
   </si>
   <si>
-    <t xml:space="preserve">PERFIL  ALUMÍNIO  PERFURADO</t>
+    <t>PERFIL  ALUMÍNIO  PERFURADO</t>
   </si>
   <si>
     <t>00000000008655</t>
@@ -1640,7 +1651,7 @@
     <t>E.02.0039</t>
   </si>
   <si>
-    <t xml:space="preserve">TK MANTA DE PROTEÇÃO  1,00 X 25,00M X 5MM ( TECNOKOLL )</t>
+    <t>TK MANTA DE PROTEÇÃO  1,00 X 25,00M X 5MM ( TECNOKOLL )</t>
   </si>
   <si>
     <t>00000000009021</t>
@@ -1658,13 +1669,13 @@
     <t>J.02.0904</t>
   </si>
   <si>
-    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG CINZA</t>
+    <t>ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG CINZA</t>
   </si>
   <si>
     <t>J.02.0905</t>
   </si>
   <si>
-    <t xml:space="preserve">ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG BRANCA</t>
+    <t>ARGAMASSA ESPECIAL  SUPERFLEX AC III - PORTOKOLL 20KG BRANCA</t>
   </si>
   <si>
     <t>R.02.0180</t>
@@ -1721,7 +1732,7 @@
     <t>E.02.0027</t>
   </si>
   <si>
-    <t xml:space="preserve">LONA TERREIRO PRETA  8 X 100M</t>
+    <t>LONA TERREIRO PRETA  8 X 100M</t>
   </si>
   <si>
     <t>U.02.0829</t>
@@ -1739,7 +1750,7 @@
     <t>U.01.3091</t>
   </si>
   <si>
-    <t xml:space="preserve">CUBA DE APOIO REDONDA  40 X 40 CM DECA  L 12040  17 SLIM BRANCA</t>
+    <t>CUBA DE APOIO REDONDA  40 X 40 CM DECA  L 12040  17 SLIM BRANCA</t>
   </si>
   <si>
     <t>C.04.0025</t>
@@ -1757,7 +1768,7 @@
     <t>E.03.0041</t>
   </si>
   <si>
-    <t xml:space="preserve">LUVA DE LATEX  PRETA SEM FORRO ESPESSURA: 0,62 MM MUCAMBO</t>
+    <t>LUVA DE LATEX  PRETA SEM FORRO ESPESSURA: 0,62 MM MUCAMBO</t>
   </si>
   <si>
     <t>E.03.0259</t>
@@ -1787,7 +1798,7 @@
     <t>W.06.0001</t>
   </si>
   <si>
-    <t xml:space="preserve">COLA PVA  X 0 35  PULVITEC C/ 50KG</t>
+    <t>COLA PVA  X 0 35  PULVITEC C/ 50KG</t>
   </si>
   <si>
     <t>N.05.0053</t>
@@ -1802,7 +1813,7 @@
     <t>E.02.0017</t>
   </si>
   <si>
-    <t xml:space="preserve">FITA CREPE  VERDE 5CM X 40MM AUTOMOTIVA</t>
+    <t>FITA CREPE  VERDE 5CM X 40MM AUTOMOTIVA</t>
   </si>
   <si>
     <t>F.01.0009</t>
@@ -1814,7 +1825,7 @@
     <t>J.02.1502</t>
   </si>
   <si>
-    <t xml:space="preserve">ARGAMASSA TK PLUS TECNOKOLL INTERNA E EXTERNA  ATÉ  90X90CM 1.4MPA ACIII BRANCA 20KG</t>
+    <t>ARGAMASSA TK PLUS TECNOKOLL INTERNA E EXTERNA  ATÉ  90X90CM 1.4MPA ACIII BRANCA 20KG</t>
   </si>
   <si>
     <t>00000000002811</t>
@@ -1826,17 +1837,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="30">
-    <numFmt numFmtId="193" formatCode="0;\-0"/>
-    <numFmt numFmtId="194" formatCode="#,##0.00;\-#,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0;\-0"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1852,47 +1858,51 @@
   </fills>
   <borders count="1">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="193" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="194" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1930,19 +1940,79 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2115,33 +2185,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P313"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
-    <col min="2" max="2" width="39.8571428571429" customWidth="1" style="1"/>
-    <col min="3" max="3" width="11.1428571428571" customWidth="1" style="1"/>
-    <col min="4" max="4" width="10" customWidth="1" style="1"/>
-    <col min="5" max="5" width="10.5714285714286" customWidth="1" style="1"/>
-    <col min="6" max="6" width="8.57142857142857" customWidth="1" style="1"/>
-    <col min="7" max="7" width="10.1428571428571" customWidth="1" style="1"/>
-    <col min="8" max="8" width="13.2857142857143" customWidth="1" style="1"/>
-    <col min="9" max="9" width="121.428571428571" customWidth="1" style="1"/>
-    <col min="10" max="10" width="18.5714285714286" customWidth="1" style="1"/>
-    <col min="11" max="11" width="17.4285714285714" customWidth="1" style="1"/>
-    <col min="12" max="12" width="9.57142857142857" customWidth="1" style="1"/>
-    <col min="13" max="13" width="17.5714285714286" customWidth="1" style="1"/>
-    <col min="14" max="14" width="16.1428571428571" customWidth="1" style="1"/>
-    <col min="15" max="15" width="19" customWidth="1" style="1"/>
-    <col min="16" max="16" width="25.1428571428571" customWidth="1" style="1"/>
-    <col min="17" max="16384" width="11.4285714285714" style="1"/>
+    <col min="1" max="1" width="7.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="121.44140625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="19" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25.109375" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row ht="12.75" customHeight="1" r="1">
+    <row r="1" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2191,7 +2258,7 @@
         <v>15</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="2">
+    <row r="2" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2509</v>
       </c>
@@ -2205,7 +2272,7 @@
         <v>30</v>
       </c>
       <c r="E2" s="3">
-        <v>46076.7244851042</v>
+        <v>46076.724485104198</v>
       </c>
       <c r="F2" s="2">
         <v>82277</v>
@@ -2241,7 +2308,7 @@
         <v>23</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="3">
+    <row r="3" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2509</v>
       </c>
@@ -2255,7 +2322,7 @@
         <v>30</v>
       </c>
       <c r="E3" s="3">
-        <v>46076.7244851042</v>
+        <v>46076.724485104198</v>
       </c>
       <c r="F3" s="2">
         <v>82257</v>
@@ -2291,7 +2358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="4">
+    <row r="4" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2509</v>
       </c>
@@ -2305,7 +2372,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="3">
-        <v>46076.7244851042</v>
+        <v>46076.724485104198</v>
       </c>
       <c r="F4" s="2">
         <v>82277</v>
@@ -2341,7 +2408,7 @@
         <v>23</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="5">
+    <row r="5" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2509</v>
       </c>
@@ -2355,7 +2422,7 @@
         <v>30</v>
       </c>
       <c r="E5" s="3">
-        <v>46076.7244851042</v>
+        <v>46076.724485104198</v>
       </c>
       <c r="F5" s="2">
         <v>82293</v>
@@ -2391,7 +2458,7 @@
         <v>34</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="6">
+    <row r="6" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2509</v>
       </c>
@@ -2405,7 +2472,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="3">
-        <v>46076.7244851042</v>
+        <v>46076.724485104198</v>
       </c>
       <c r="F6" s="2">
         <v>82276</v>
@@ -2441,7 +2508,7 @@
         <v>39</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="7">
+    <row r="7" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2509</v>
       </c>
@@ -2455,7 +2522,7 @@
         <v>30</v>
       </c>
       <c r="E7" s="3">
-        <v>46076.7244851042</v>
+        <v>46076.724485104198</v>
       </c>
       <c r="F7" s="2">
         <v>82276</v>
@@ -2491,7 +2558,7 @@
         <v>39</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="8">
+    <row r="8" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2512</v>
       </c>
@@ -2505,7 +2572,7 @@
         <v>19</v>
       </c>
       <c r="E8" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F8" s="2">
         <v>82259</v>
@@ -2541,7 +2608,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="9">
+    <row r="9" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2512</v>
       </c>
@@ -2555,7 +2622,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F9" s="2">
         <v>82259</v>
@@ -2591,7 +2658,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="10">
+    <row r="10" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2512</v>
       </c>
@@ -2605,7 +2672,7 @@
         <v>19</v>
       </c>
       <c r="E10" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F10" s="2">
         <v>82259</v>
@@ -2641,7 +2708,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="11">
+    <row r="11" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>2512</v>
       </c>
@@ -2655,7 +2722,7 @@
         <v>19</v>
       </c>
       <c r="E11" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F11" s="2">
         <v>82259</v>
@@ -2679,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="M11" s="4">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="N11" s="4">
         <v>169</v>
@@ -2691,7 +2758,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="12">
+    <row r="12" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>2512</v>
       </c>
@@ -2705,7 +2772,7 @@
         <v>19</v>
       </c>
       <c r="E12" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F12" s="2">
         <v>82259</v>
@@ -2741,7 +2808,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="13">
+    <row r="13" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>2512</v>
       </c>
@@ -2755,7 +2822,7 @@
         <v>19</v>
       </c>
       <c r="E13" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F13" s="2">
         <v>82259</v>
@@ -2791,7 +2858,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="14">
+    <row r="14" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2512</v>
       </c>
@@ -2805,7 +2872,7 @@
         <v>19</v>
       </c>
       <c r="E14" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F14" s="2">
         <v>82259</v>
@@ -2841,7 +2908,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="15">
+    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>2512</v>
       </c>
@@ -2855,7 +2922,7 @@
         <v>19</v>
       </c>
       <c r="E15" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F15" s="2">
         <v>82258</v>
@@ -2891,7 +2958,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="16">
+    <row r="16" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>2512</v>
       </c>
@@ -2905,7 +2972,7 @@
         <v>19</v>
       </c>
       <c r="E16" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F16" s="2">
         <v>82260</v>
@@ -2941,7 +3008,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="17">
+    <row r="17" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>2512</v>
       </c>
@@ -2955,7 +3022,7 @@
         <v>19</v>
       </c>
       <c r="E17" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F17" s="2">
         <v>82260</v>
@@ -2991,7 +3058,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="18">
+    <row r="18" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2512</v>
       </c>
@@ -3005,7 +3072,7 @@
         <v>19</v>
       </c>
       <c r="E18" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F18" s="2">
         <v>82260</v>
@@ -3029,10 +3096,10 @@
         <v>2</v>
       </c>
       <c r="M18" s="4">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="N18" s="4">
-        <v>39.8</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>68</v>
@@ -3041,7 +3108,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="19">
+    <row r="19" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2512</v>
       </c>
@@ -3055,7 +3122,7 @@
         <v>19</v>
       </c>
       <c r="E19" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F19" s="2">
         <v>82260</v>
@@ -3091,7 +3158,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="20">
+    <row r="20" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2512</v>
       </c>
@@ -3105,7 +3172,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F20" s="2">
         <v>82258</v>
@@ -3141,7 +3208,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="21">
+    <row r="21" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2512</v>
       </c>
@@ -3155,7 +3222,7 @@
         <v>19</v>
       </c>
       <c r="E21" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F21" s="2">
         <v>82258</v>
@@ -3179,7 +3246,7 @@
         <v>3</v>
       </c>
       <c r="M21" s="4">
-        <v>37.95</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="N21" s="4">
         <v>113.85</v>
@@ -3191,7 +3258,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="22">
+    <row r="22" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>2512</v>
       </c>
@@ -3205,7 +3272,7 @@
         <v>19</v>
       </c>
       <c r="E22" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F22" s="2">
         <v>82258</v>
@@ -3241,7 +3308,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="23">
+    <row r="23" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>2512</v>
       </c>
@@ -3255,7 +3322,7 @@
         <v>19</v>
       </c>
       <c r="E23" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F23" s="2">
         <v>82260</v>
@@ -3291,7 +3358,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="24">
+    <row r="24" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>2512</v>
       </c>
@@ -3305,7 +3372,7 @@
         <v>19</v>
       </c>
       <c r="E24" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F24" s="2">
         <v>82260</v>
@@ -3332,7 +3399,7 @@
         <v>25.3</v>
       </c>
       <c r="N24" s="4">
-        <v>303.6</v>
+        <v>303.60000000000002</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>68</v>
@@ -3341,7 +3408,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="25">
+    <row r="25" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>2512</v>
       </c>
@@ -3355,7 +3422,7 @@
         <v>19</v>
       </c>
       <c r="E25" s="3">
-        <v>46076.7259125116</v>
+        <v>46076.725912511603</v>
       </c>
       <c r="F25" s="2">
         <v>82274</v>
@@ -3391,7 +3458,7 @@
         <v>90</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="26">
+    <row r="26" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2317</v>
       </c>
@@ -3405,7 +3472,7 @@
         <v>72</v>
       </c>
       <c r="E26" s="3">
-        <v>46076.7291292477</v>
+        <v>46076.729129247702</v>
       </c>
       <c r="F26" s="2">
         <v>82261</v>
@@ -3441,7 +3508,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="27">
+    <row r="27" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2317</v>
       </c>
@@ -3455,7 +3522,7 @@
         <v>72</v>
       </c>
       <c r="E27" s="3">
-        <v>46076.7291292477</v>
+        <v>46076.729129247702</v>
       </c>
       <c r="F27" s="2">
         <v>82261</v>
@@ -3491,7 +3558,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="28">
+    <row r="28" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2317</v>
       </c>
@@ -3505,7 +3572,7 @@
         <v>72</v>
       </c>
       <c r="E28" s="3">
-        <v>46076.7291292477</v>
+        <v>46076.729129247702</v>
       </c>
       <c r="F28" s="2">
         <v>82261</v>
@@ -3541,7 +3608,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="29">
+    <row r="29" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2317</v>
       </c>
@@ -3555,7 +3622,7 @@
         <v>72</v>
       </c>
       <c r="E29" s="3">
-        <v>46076.7291292477</v>
+        <v>46076.729129247702</v>
       </c>
       <c r="F29" s="2">
         <v>82261</v>
@@ -3579,7 +3646,7 @@
         <v>22</v>
       </c>
       <c r="M29" s="4">
-        <v>37.95</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="N29" s="4">
         <v>834.9</v>
@@ -3591,7 +3658,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="30">
+    <row r="30" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2317</v>
       </c>
@@ -3605,7 +3672,7 @@
         <v>72</v>
       </c>
       <c r="E30" s="3">
-        <v>46076.7291292477</v>
+        <v>46076.729129247702</v>
       </c>
       <c r="F30" s="2">
         <v>82261</v>
@@ -3641,7 +3708,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="31">
+    <row r="31" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2317</v>
       </c>
@@ -3655,7 +3722,7 @@
         <v>72</v>
       </c>
       <c r="E31" s="3">
-        <v>46076.7291292477</v>
+        <v>46076.729129247702</v>
       </c>
       <c r="F31" s="2">
         <v>82279</v>
@@ -3691,7 +3758,7 @@
         <v>102</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="32">
+    <row r="32" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2516</v>
       </c>
@@ -3705,7 +3772,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F32" s="2">
         <v>82265</v>
@@ -3741,7 +3808,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="33">
+    <row r="33" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2516</v>
       </c>
@@ -3755,7 +3822,7 @@
         <v>13</v>
       </c>
       <c r="E33" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F33" s="2">
         <v>82281</v>
@@ -3791,7 +3858,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="34">
+    <row r="34" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2516</v>
       </c>
@@ -3805,7 +3872,7 @@
         <v>13</v>
       </c>
       <c r="E34" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F34" s="2">
         <v>82281</v>
@@ -3841,7 +3908,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="35">
+    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2516</v>
       </c>
@@ -3855,7 +3922,7 @@
         <v>13</v>
       </c>
       <c r="E35" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F35" s="2">
         <v>82281</v>
@@ -3891,7 +3958,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="36">
+    <row r="36" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2516</v>
       </c>
@@ -3905,7 +3972,7 @@
         <v>13</v>
       </c>
       <c r="E36" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F36" s="2">
         <v>82262</v>
@@ -3941,7 +4008,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="37">
+    <row r="37" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2516</v>
       </c>
@@ -3955,7 +4022,7 @@
         <v>13</v>
       </c>
       <c r="E37" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F37" s="2">
         <v>82262</v>
@@ -3991,7 +4058,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="38">
+    <row r="38" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2516</v>
       </c>
@@ -4005,7 +4072,7 @@
         <v>13</v>
       </c>
       <c r="E38" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F38" s="2">
         <v>82262</v>
@@ -4041,7 +4108,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="39">
+    <row r="39" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2516</v>
       </c>
@@ -4055,7 +4122,7 @@
         <v>13</v>
       </c>
       <c r="E39" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F39" s="2">
         <v>82262</v>
@@ -4091,7 +4158,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="40">
+    <row r="40" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2516</v>
       </c>
@@ -4105,7 +4172,7 @@
         <v>13</v>
       </c>
       <c r="E40" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F40" s="2">
         <v>82281</v>
@@ -4141,7 +4208,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="41">
+    <row r="41" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2516</v>
       </c>
@@ -4155,7 +4222,7 @@
         <v>13</v>
       </c>
       <c r="E41" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F41" s="2">
         <v>82282</v>
@@ -4191,7 +4258,7 @@
         <v>121</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="42">
+    <row r="42" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2516</v>
       </c>
@@ -4205,7 +4272,7 @@
         <v>13</v>
       </c>
       <c r="E42" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F42" s="2">
         <v>82282</v>
@@ -4241,7 +4308,7 @@
         <v>121</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="43">
+    <row r="43" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2516</v>
       </c>
@@ -4255,7 +4322,7 @@
         <v>13</v>
       </c>
       <c r="E43" s="3">
-        <v>46077.406463831</v>
+        <v>46077.406463831001</v>
       </c>
       <c r="F43" s="2">
         <v>82282</v>
@@ -4291,7 +4358,7 @@
         <v>121</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="44">
+    <row r="44" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>2505</v>
       </c>
@@ -4305,7 +4372,7 @@
         <v>45</v>
       </c>
       <c r="E44" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F44" s="2">
         <v>82266</v>
@@ -4341,7 +4408,7 @@
         <v>131</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="45">
+    <row r="45" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>2505</v>
       </c>
@@ -4355,7 +4422,7 @@
         <v>45</v>
       </c>
       <c r="E45" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F45" s="2">
         <v>82266</v>
@@ -4391,7 +4458,7 @@
         <v>131</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="46">
+    <row r="46" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2505</v>
       </c>
@@ -4405,7 +4472,7 @@
         <v>45</v>
       </c>
       <c r="E46" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F46" s="2">
         <v>82266</v>
@@ -4429,10 +4496,10 @@
         <v>2</v>
       </c>
       <c r="M46" s="4">
-        <v>37.84</v>
+        <v>37.840000000000003</v>
       </c>
       <c r="N46" s="4">
-        <v>75.68</v>
+        <v>75.680000000000007</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>130</v>
@@ -4441,7 +4508,7 @@
         <v>131</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="47">
+    <row r="47" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2505</v>
       </c>
@@ -4455,7 +4522,7 @@
         <v>45</v>
       </c>
       <c r="E47" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F47" s="2">
         <v>82266</v>
@@ -4491,7 +4558,7 @@
         <v>131</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="48">
+    <row r="48" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>2505</v>
       </c>
@@ -4505,7 +4572,7 @@
         <v>45</v>
       </c>
       <c r="E48" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F48" s="2">
         <v>82266</v>
@@ -4541,7 +4608,7 @@
         <v>131</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="49">
+    <row r="49" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2505</v>
       </c>
@@ -4555,7 +4622,7 @@
         <v>45</v>
       </c>
       <c r="E49" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F49" s="2">
         <v>82266</v>
@@ -4591,7 +4658,7 @@
         <v>131</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="50">
+    <row r="50" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2505</v>
       </c>
@@ -4605,7 +4672,7 @@
         <v>45</v>
       </c>
       <c r="E50" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F50" s="2">
         <v>82273</v>
@@ -4641,7 +4708,7 @@
         <v>145</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="51">
+    <row r="51" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2505</v>
       </c>
@@ -4655,7 +4722,7 @@
         <v>45</v>
       </c>
       <c r="E51" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F51" s="2">
         <v>82273</v>
@@ -4691,7 +4758,7 @@
         <v>145</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="52">
+    <row r="52" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2505</v>
       </c>
@@ -4705,7 +4772,7 @@
         <v>45</v>
       </c>
       <c r="E52" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F52" s="2">
         <v>82294</v>
@@ -4741,7 +4808,7 @@
         <v>147</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="53">
+    <row r="53" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2505</v>
       </c>
@@ -4755,7 +4822,7 @@
         <v>45</v>
       </c>
       <c r="E53" s="3">
-        <v>46077.4087697222</v>
+        <v>46077.408769722198</v>
       </c>
       <c r="F53" s="2">
         <v>82266</v>
@@ -4779,7 +4846,7 @@
         <v>500</v>
       </c>
       <c r="M53" s="4">
-        <v>0.924</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="N53" s="4">
         <v>462</v>
@@ -4791,7 +4858,7 @@
         <v>131</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="54">
+    <row r="54" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2509</v>
       </c>
@@ -4805,7 +4872,7 @@
         <v>31</v>
       </c>
       <c r="E54" s="3">
-        <v>46077.4356327431</v>
+        <v>46077.435632743101</v>
       </c>
       <c r="F54" s="2">
         <v>82269</v>
@@ -4841,7 +4908,7 @@
         <v>151</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="55">
+    <row r="55" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>2511</v>
       </c>
@@ -4855,7 +4922,7 @@
         <v>24</v>
       </c>
       <c r="E55" s="3">
-        <v>46077.5084780324</v>
+        <v>46077.508478032403</v>
       </c>
       <c r="F55" s="2">
         <v>82270</v>
@@ -4891,7 +4958,7 @@
         <v>156</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="56">
+    <row r="56" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2317</v>
       </c>
@@ -4905,7 +4972,7 @@
         <v>73</v>
       </c>
       <c r="E56" s="3">
-        <v>46077.5089671528</v>
+        <v>46077.508967152797</v>
       </c>
       <c r="F56" s="2">
         <v>82271</v>
@@ -4929,7 +4996,7 @@
         <v>6</v>
       </c>
       <c r="M56" s="4">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="N56" s="4">
         <v>101.4</v>
@@ -4941,7 +5008,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="57">
+    <row r="57" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2317</v>
       </c>
@@ -4955,7 +5022,7 @@
         <v>73</v>
       </c>
       <c r="E57" s="3">
-        <v>46077.5089671528</v>
+        <v>46077.508967152797</v>
       </c>
       <c r="F57" s="2">
         <v>82272</v>
@@ -4991,7 +5058,7 @@
         <v>165</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="58">
+    <row r="58" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2511</v>
       </c>
@@ -5005,7 +5072,7 @@
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>46077.721037037</v>
+        <v>46077.721037037001</v>
       </c>
       <c r="F58" s="2">
         <v>82285</v>
@@ -5041,7 +5108,7 @@
         <v>169</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="59">
+    <row r="59" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2511</v>
       </c>
@@ -5055,7 +5122,7 @@
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>46077.721037037</v>
+        <v>46077.721037037001</v>
       </c>
       <c r="F59" s="2">
         <v>82285</v>
@@ -5091,7 +5158,7 @@
         <v>169</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="60">
+    <row r="60" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2507</v>
       </c>
@@ -5105,7 +5172,7 @@
         <v>29</v>
       </c>
       <c r="E60" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F60" s="2">
         <v>82304</v>
@@ -5141,7 +5208,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="61">
+    <row r="61" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>2507</v>
       </c>
@@ -5155,7 +5222,7 @@
         <v>29</v>
       </c>
       <c r="E61" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F61" s="2">
         <v>82288</v>
@@ -5191,7 +5258,7 @@
         <v>181</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="62">
+    <row r="62" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2507</v>
       </c>
@@ -5205,7 +5272,7 @@
         <v>29</v>
       </c>
       <c r="E62" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F62" s="2">
         <v>82288</v>
@@ -5241,7 +5308,7 @@
         <v>181</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="63">
+    <row r="63" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2507</v>
       </c>
@@ -5255,7 +5322,7 @@
         <v>29</v>
       </c>
       <c r="E63" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F63" s="2">
         <v>82304</v>
@@ -5279,7 +5346,7 @@
         <v>50</v>
       </c>
       <c r="M63" s="4">
-        <v>3.8886</v>
+        <v>3.8885999999999998</v>
       </c>
       <c r="N63" s="4">
         <v>194.43</v>
@@ -5291,7 +5358,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="64">
+    <row r="64" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2507</v>
       </c>
@@ -5305,7 +5372,7 @@
         <v>29</v>
       </c>
       <c r="E64" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F64" s="2">
         <v>82298</v>
@@ -5341,7 +5408,7 @@
         <v>187</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="65">
+    <row r="65" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>2507</v>
       </c>
@@ -5355,7 +5422,7 @@
         <v>29</v>
       </c>
       <c r="E65" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F65" s="2">
         <v>82298</v>
@@ -5391,7 +5458,7 @@
         <v>187</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="66">
+    <row r="66" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>2507</v>
       </c>
@@ -5405,7 +5472,7 @@
         <v>29</v>
       </c>
       <c r="E66" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F66" s="2">
         <v>82298</v>
@@ -5429,7 +5496,7 @@
         <v>100</v>
       </c>
       <c r="M66" s="4">
-        <v>40.3</v>
+        <v>40.299999999999997</v>
       </c>
       <c r="N66" s="4">
         <v>4030</v>
@@ -5441,7 +5508,7 @@
         <v>187</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="67">
+    <row r="67" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>2507</v>
       </c>
@@ -5455,7 +5522,7 @@
         <v>29</v>
       </c>
       <c r="E67" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F67" s="2">
         <v>82298</v>
@@ -5491,7 +5558,7 @@
         <v>187</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="68">
+    <row r="68" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>2507</v>
       </c>
@@ -5505,7 +5572,7 @@
         <v>29</v>
       </c>
       <c r="E68" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F68" s="2">
         <v>82298</v>
@@ -5541,7 +5608,7 @@
         <v>187</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="69">
+    <row r="69" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>2507</v>
       </c>
@@ -5555,7 +5622,7 @@
         <v>29</v>
       </c>
       <c r="E69" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F69" s="2">
         <v>82298</v>
@@ -5591,7 +5658,7 @@
         <v>187</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="70">
+    <row r="70" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>2507</v>
       </c>
@@ -5605,7 +5672,7 @@
         <v>29</v>
       </c>
       <c r="E70" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F70" s="2">
         <v>82301</v>
@@ -5641,7 +5708,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="71">
+    <row r="71" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>2507</v>
       </c>
@@ -5655,7 +5722,7 @@
         <v>29</v>
       </c>
       <c r="E71" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F71" s="2">
         <v>82287</v>
@@ -5691,7 +5758,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="72">
+    <row r="72" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>2507</v>
       </c>
@@ -5705,7 +5772,7 @@
         <v>29</v>
       </c>
       <c r="E72" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F72" s="2">
         <v>82287</v>
@@ -5741,7 +5808,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="73">
+    <row r="73" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>2507</v>
       </c>
@@ -5755,7 +5822,7 @@
         <v>29</v>
       </c>
       <c r="E73" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F73" s="2">
         <v>82304</v>
@@ -5791,7 +5858,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="74">
+    <row r="74" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>2507</v>
       </c>
@@ -5805,7 +5872,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F74" s="2">
         <v>82304</v>
@@ -5841,7 +5908,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="75">
+    <row r="75" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>2507</v>
       </c>
@@ -5855,7 +5922,7 @@
         <v>29</v>
       </c>
       <c r="E75" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F75" s="2">
         <v>82304</v>
@@ -5891,7 +5958,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="76">
+    <row r="76" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>2507</v>
       </c>
@@ -5905,7 +5972,7 @@
         <v>29</v>
       </c>
       <c r="E76" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F76" s="2">
         <v>82304</v>
@@ -5941,7 +6008,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="77">
+    <row r="77" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>2507</v>
       </c>
@@ -5955,7 +6022,7 @@
         <v>29</v>
       </c>
       <c r="E77" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F77" s="2">
         <v>82304</v>
@@ -5991,7 +6058,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="78">
+    <row r="78" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>2507</v>
       </c>
@@ -6005,7 +6072,7 @@
         <v>29</v>
       </c>
       <c r="E78" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F78" s="2">
         <v>82304</v>
@@ -6041,7 +6108,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="79">
+    <row r="79" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>2507</v>
       </c>
@@ -6055,7 +6122,7 @@
         <v>29</v>
       </c>
       <c r="E79" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F79" s="2">
         <v>82304</v>
@@ -6091,7 +6158,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="80">
+    <row r="80" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>2507</v>
       </c>
@@ -6105,7 +6172,7 @@
         <v>29</v>
       </c>
       <c r="E80" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F80" s="2">
         <v>82304</v>
@@ -6141,7 +6208,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="81">
+    <row r="81" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>2507</v>
       </c>
@@ -6155,7 +6222,7 @@
         <v>29</v>
       </c>
       <c r="E81" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F81" s="2">
         <v>82304</v>
@@ -6191,7 +6258,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="82">
+    <row r="82" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>2507</v>
       </c>
@@ -6205,7 +6272,7 @@
         <v>29</v>
       </c>
       <c r="E82" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F82" s="2">
         <v>82304</v>
@@ -6241,7 +6308,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="83">
+    <row r="83" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>2507</v>
       </c>
@@ -6255,7 +6322,7 @@
         <v>29</v>
       </c>
       <c r="E83" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F83" s="2">
         <v>82304</v>
@@ -6291,7 +6358,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="84">
+    <row r="84" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>2507</v>
       </c>
@@ -6305,7 +6372,7 @@
         <v>29</v>
       </c>
       <c r="E84" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F84" s="2">
         <v>82308</v>
@@ -6329,7 +6396,7 @@
         <v>1000</v>
       </c>
       <c r="M84" s="4">
-        <v>0.696</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="N84" s="4">
         <v>696</v>
@@ -6341,7 +6408,7 @@
         <v>229</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="85">
+    <row r="85" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>2507</v>
       </c>
@@ -6355,7 +6422,7 @@
         <v>29</v>
       </c>
       <c r="E85" s="3">
-        <v>46077.7216803356</v>
+        <v>46077.721680335599</v>
       </c>
       <c r="F85" s="2">
         <v>82304</v>
@@ -6391,7 +6458,7 @@
         <v>176</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="86">
+    <row r="86" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>2504</v>
       </c>
@@ -6441,7 +6508,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="87">
+    <row r="87" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>2504</v>
       </c>
@@ -6491,7 +6558,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="88">
+    <row r="88" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>2601</v>
       </c>
@@ -6505,7 +6572,7 @@
         <v>1</v>
       </c>
       <c r="E88" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F88" s="2">
         <v>82312</v>
@@ -6541,7 +6608,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="89">
+    <row r="89" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>2601</v>
       </c>
@@ -6555,7 +6622,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F89" s="2">
         <v>82312</v>
@@ -6591,7 +6658,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="90">
+    <row r="90" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>2601</v>
       </c>
@@ -6605,7 +6672,7 @@
         <v>1</v>
       </c>
       <c r="E90" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F90" s="2">
         <v>82311</v>
@@ -6641,7 +6708,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="91">
+    <row r="91" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>2601</v>
       </c>
@@ -6655,7 +6722,7 @@
         <v>1</v>
       </c>
       <c r="E91" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F91" s="2">
         <v>82312</v>
@@ -6691,7 +6758,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="92">
+    <row r="92" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>2601</v>
       </c>
@@ -6705,7 +6772,7 @@
         <v>1</v>
       </c>
       <c r="E92" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F92" s="2">
         <v>82312</v>
@@ -6729,7 +6796,7 @@
         <v>10</v>
       </c>
       <c r="M92" s="4">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="N92" s="4">
         <v>199</v>
@@ -6741,7 +6808,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="93">
+    <row r="93" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>2601</v>
       </c>
@@ -6755,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="E93" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F93" s="2">
         <v>82312</v>
@@ -6791,7 +6858,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="94">
+    <row r="94" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>2601</v>
       </c>
@@ -6805,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="E94" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F94" s="2">
         <v>82312</v>
@@ -6841,7 +6908,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="95">
+    <row r="95" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>2601</v>
       </c>
@@ -6855,7 +6922,7 @@
         <v>1</v>
       </c>
       <c r="E95" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F95" s="2">
         <v>82312</v>
@@ -6891,7 +6958,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="96">
+    <row r="96" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>2601</v>
       </c>
@@ -6905,7 +6972,7 @@
         <v>1</v>
       </c>
       <c r="E96" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F96" s="2">
         <v>82312</v>
@@ -6941,7 +7008,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="97">
+    <row r="97" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>2601</v>
       </c>
@@ -6955,7 +7022,7 @@
         <v>1</v>
       </c>
       <c r="E97" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F97" s="2">
         <v>82361</v>
@@ -6991,7 +7058,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="98">
+    <row r="98" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>2601</v>
       </c>
@@ -7005,7 +7072,7 @@
         <v>1</v>
       </c>
       <c r="E98" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F98" s="2">
         <v>82312</v>
@@ -7041,7 +7108,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="99">
+    <row r="99" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>2601</v>
       </c>
@@ -7055,7 +7122,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F99" s="2">
         <v>82312</v>
@@ -7082,7 +7149,7 @@
         <v>1.79</v>
       </c>
       <c r="N99" s="4">
-        <v>35.8</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>47</v>
@@ -7091,7 +7158,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="100">
+    <row r="100" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>2601</v>
       </c>
@@ -7105,7 +7172,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F100" s="2">
         <v>82312</v>
@@ -7141,7 +7208,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="101">
+    <row r="101" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>2601</v>
       </c>
@@ -7155,7 +7222,7 @@
         <v>1</v>
       </c>
       <c r="E101" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F101" s="2">
         <v>82312</v>
@@ -7191,7 +7258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="102">
+    <row r="102" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>2601</v>
       </c>
@@ -7205,7 +7272,7 @@
         <v>1</v>
       </c>
       <c r="E102" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F102" s="2">
         <v>82312</v>
@@ -7241,7 +7308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="103">
+    <row r="103" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>2601</v>
       </c>
@@ -7255,7 +7322,7 @@
         <v>1</v>
       </c>
       <c r="E103" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F103" s="2">
         <v>82361</v>
@@ -7291,7 +7358,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="104">
+    <row r="104" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>2601</v>
       </c>
@@ -7305,7 +7372,7 @@
         <v>1</v>
       </c>
       <c r="E104" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F104" s="2">
         <v>82392</v>
@@ -7341,7 +7408,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="105">
+    <row r="105" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>2601</v>
       </c>
@@ -7355,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="E105" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F105" s="2">
         <v>82361</v>
@@ -7391,7 +7458,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="106">
+    <row r="106" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>2601</v>
       </c>
@@ -7405,7 +7472,7 @@
         <v>1</v>
       </c>
       <c r="E106" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F106" s="2">
         <v>82361</v>
@@ -7441,7 +7508,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="107">
+    <row r="107" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>2601</v>
       </c>
@@ -7455,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="E107" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F107" s="2">
         <v>82311</v>
@@ -7491,7 +7558,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="108">
+    <row r="108" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>2601</v>
       </c>
@@ -7505,7 +7572,7 @@
         <v>1</v>
       </c>
       <c r="E108" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F108" s="2">
         <v>82392</v>
@@ -7541,7 +7608,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="109">
+    <row r="109" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>2601</v>
       </c>
@@ -7555,7 +7622,7 @@
         <v>1</v>
       </c>
       <c r="E109" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F109" s="2">
         <v>82385</v>
@@ -7591,7 +7658,7 @@
         <v>277</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="110">
+    <row r="110" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>2601</v>
       </c>
@@ -7605,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="E110" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F110" s="2">
         <v>82311</v>
@@ -7641,7 +7708,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="111">
+    <row r="111" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>2601</v>
       </c>
@@ -7655,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="E111" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F111" s="2">
         <v>82313</v>
@@ -7679,10 +7746,10 @@
         <v>1</v>
       </c>
       <c r="M111" s="4">
-        <v>129.05</v>
+        <v>129.05000000000001</v>
       </c>
       <c r="N111" s="4">
-        <v>129.05</v>
+        <v>129.05000000000001</v>
       </c>
       <c r="O111" s="1" t="s">
         <v>159</v>
@@ -7691,7 +7758,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="112">
+    <row r="112" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>2601</v>
       </c>
@@ -7705,7 +7772,7 @@
         <v>1</v>
       </c>
       <c r="E112" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F112" s="2">
         <v>82392</v>
@@ -7741,7 +7808,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="113">
+    <row r="113" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>2601</v>
       </c>
@@ -7755,7 +7822,7 @@
         <v>1</v>
       </c>
       <c r="E113" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F113" s="2">
         <v>82392</v>
@@ -7791,7 +7858,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="114">
+    <row r="114" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>2601</v>
       </c>
@@ -7805,7 +7872,7 @@
         <v>1</v>
       </c>
       <c r="E114" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F114" s="2">
         <v>82313</v>
@@ -7841,7 +7908,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="115">
+    <row r="115" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>2601</v>
       </c>
@@ -7855,7 +7922,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F115" s="2">
         <v>82313</v>
@@ -7891,7 +7958,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="116">
+    <row r="116" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>2601</v>
       </c>
@@ -7905,7 +7972,7 @@
         <v>1</v>
       </c>
       <c r="E116" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F116" s="2">
         <v>82313</v>
@@ -7941,7 +8008,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="117">
+    <row r="117" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>2601</v>
       </c>
@@ -7955,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="E117" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F117" s="2">
         <v>82361</v>
@@ -7991,7 +8058,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="118">
+    <row r="118" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>2601</v>
       </c>
@@ -8005,7 +8072,7 @@
         <v>1</v>
       </c>
       <c r="E118" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F118" s="2">
         <v>82313</v>
@@ -8041,7 +8108,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="119">
+    <row r="119" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>2601</v>
       </c>
@@ -8055,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="E119" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F119" s="2">
         <v>82361</v>
@@ -8091,7 +8158,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="120">
+    <row r="120" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>2601</v>
       </c>
@@ -8105,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="E120" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F120" s="2">
         <v>82361</v>
@@ -8141,7 +8208,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="121">
+    <row r="121" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>2601</v>
       </c>
@@ -8155,7 +8222,7 @@
         <v>1</v>
       </c>
       <c r="E121" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F121" s="2">
         <v>82313</v>
@@ -8179,7 +8246,7 @@
         <v>6</v>
       </c>
       <c r="M121" s="4">
-        <v>69.6</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="N121" s="4">
         <v>417.6</v>
@@ -8191,7 +8258,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="122">
+    <row r="122" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>2601</v>
       </c>
@@ -8205,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="E122" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F122" s="2">
         <v>82311</v>
@@ -8241,7 +8308,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="123">
+    <row r="123" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>2601</v>
       </c>
@@ -8255,7 +8322,7 @@
         <v>1</v>
       </c>
       <c r="E123" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F123" s="2">
         <v>82313</v>
@@ -8291,7 +8358,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="124">
+    <row r="124" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>2601</v>
       </c>
@@ -8305,7 +8372,7 @@
         <v>1</v>
       </c>
       <c r="E124" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F124" s="2">
         <v>82313</v>
@@ -8329,7 +8396,7 @@
         <v>15</v>
       </c>
       <c r="M124" s="4">
-        <v>4.48</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="N124" s="4">
         <v>67.2</v>
@@ -8341,7 +8408,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="125">
+    <row r="125" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>2601</v>
       </c>
@@ -8355,7 +8422,7 @@
         <v>1</v>
       </c>
       <c r="E125" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F125" s="2">
         <v>82361</v>
@@ -8391,7 +8458,7 @@
         <v>255</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="126">
+    <row r="126" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>2601</v>
       </c>
@@ -8405,7 +8472,7 @@
         <v>1</v>
       </c>
       <c r="E126" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F126" s="2">
         <v>82391</v>
@@ -8429,10 +8496,10 @@
         <v>3</v>
       </c>
       <c r="M126" s="4">
-        <v>532.185</v>
+        <v>532.18499999999995</v>
       </c>
       <c r="N126" s="4">
-        <v>1596.555</v>
+        <v>1596.5550000000001</v>
       </c>
       <c r="O126" s="1" t="s">
         <v>306</v>
@@ -8441,7 +8508,7 @@
         <v>307</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="127">
+    <row r="127" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>2601</v>
       </c>
@@ -8455,7 +8522,7 @@
         <v>1</v>
       </c>
       <c r="E127" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F127" s="2">
         <v>82314</v>
@@ -8491,7 +8558,7 @@
         <v>307</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="128">
+    <row r="128" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>2601</v>
       </c>
@@ -8505,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="E128" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F128" s="2">
         <v>82391</v>
@@ -8541,7 +8608,7 @@
         <v>307</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="129">
+    <row r="129" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>2601</v>
       </c>
@@ -8555,7 +8622,7 @@
         <v>1</v>
       </c>
       <c r="E129" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F129" s="2">
         <v>82314</v>
@@ -8591,7 +8658,7 @@
         <v>307</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="130">
+    <row r="130" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>2601</v>
       </c>
@@ -8605,7 +8672,7 @@
         <v>1</v>
       </c>
       <c r="E130" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F130" s="2">
         <v>82314</v>
@@ -8641,7 +8708,7 @@
         <v>307</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="131">
+    <row r="131" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>2601</v>
       </c>
@@ -8655,7 +8722,7 @@
         <v>1</v>
       </c>
       <c r="E131" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F131" s="2">
         <v>82314</v>
@@ -8691,7 +8758,7 @@
         <v>307</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="132">
+    <row r="132" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>2601</v>
       </c>
@@ -8705,7 +8772,7 @@
         <v>1</v>
       </c>
       <c r="E132" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F132" s="2">
         <v>82314</v>
@@ -8741,7 +8808,7 @@
         <v>307</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="133">
+    <row r="133" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>2601</v>
       </c>
@@ -8755,7 +8822,7 @@
         <v>1</v>
       </c>
       <c r="E133" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F133" s="2">
         <v>82346</v>
@@ -8791,7 +8858,7 @@
         <v>323</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="134">
+    <row r="134" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>2601</v>
       </c>
@@ -8805,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="E134" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F134" s="2">
         <v>82346</v>
@@ -8841,7 +8908,7 @@
         <v>323</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="135">
+    <row r="135" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>2601</v>
       </c>
@@ -8855,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="E135" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F135" s="2">
         <v>82346</v>
@@ -8891,7 +8958,7 @@
         <v>323</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="136">
+    <row r="136" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>2601</v>
       </c>
@@ -8905,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="E136" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F136" s="2">
         <v>82392</v>
@@ -8941,7 +9008,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="137">
+    <row r="137" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>2601</v>
       </c>
@@ -8955,7 +9022,7 @@
         <v>1</v>
       </c>
       <c r="E137" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F137" s="2">
         <v>82311</v>
@@ -8991,7 +9058,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="138">
+    <row r="138" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>2601</v>
       </c>
@@ -9005,7 +9072,7 @@
         <v>1</v>
       </c>
       <c r="E138" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F138" s="2">
         <v>82311</v>
@@ -9041,7 +9108,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="139">
+    <row r="139" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>2601</v>
       </c>
@@ -9055,7 +9122,7 @@
         <v>1</v>
       </c>
       <c r="E139" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F139" s="2">
         <v>82311</v>
@@ -9091,7 +9158,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="140">
+    <row r="140" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>2601</v>
       </c>
@@ -9105,7 +9172,7 @@
         <v>1</v>
       </c>
       <c r="E140" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F140" s="2">
         <v>82311</v>
@@ -9141,7 +9208,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="141">
+    <row r="141" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>2601</v>
       </c>
@@ -9155,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="E141" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F141" s="2">
         <v>82312</v>
@@ -9191,7 +9258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="142">
+    <row r="142" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>2601</v>
       </c>
@@ -9205,7 +9272,7 @@
         <v>1</v>
       </c>
       <c r="E142" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F142" s="2">
         <v>82312</v>
@@ -9241,7 +9308,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="143">
+    <row r="143" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>2601</v>
       </c>
@@ -9255,7 +9322,7 @@
         <v>1</v>
       </c>
       <c r="E143" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F143" s="2">
         <v>82313</v>
@@ -9291,7 +9358,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="144">
+    <row r="144" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>2601</v>
       </c>
@@ -9305,7 +9372,7 @@
         <v>1</v>
       </c>
       <c r="E144" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F144" s="2">
         <v>82311</v>
@@ -9341,7 +9408,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="145">
+    <row r="145" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>2601</v>
       </c>
@@ -9355,7 +9422,7 @@
         <v>1</v>
       </c>
       <c r="E145" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F145" s="2">
         <v>82311</v>
@@ -9391,7 +9458,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="146">
+    <row r="146" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>2601</v>
       </c>
@@ -9405,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="E146" s="3">
-        <v>46078.6702738773</v>
+        <v>46078.670273877302</v>
       </c>
       <c r="F146" s="2">
         <v>82311</v>
@@ -9441,7 +9508,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="147">
+    <row r="147" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>2504</v>
       </c>
@@ -9479,7 +9546,7 @@
         <v>38</v>
       </c>
       <c r="M147" s="4">
-        <v>6.096</v>
+        <v>6.0960000000000001</v>
       </c>
       <c r="N147" s="4">
         <v>231.648</v>
@@ -9491,7 +9558,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="148">
+    <row r="148" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>2504</v>
       </c>
@@ -9541,7 +9608,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="149">
+    <row r="149" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>2504</v>
       </c>
@@ -9591,7 +9658,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="150">
+    <row r="150" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>2504</v>
       </c>
@@ -9629,10 +9696,10 @@
         <v>21</v>
       </c>
       <c r="M150" s="4">
-        <v>54.096</v>
+        <v>54.095999999999997</v>
       </c>
       <c r="N150" s="4">
-        <v>1136.016</v>
+        <v>1136.0160000000001</v>
       </c>
       <c r="O150" s="1" t="s">
         <v>202</v>
@@ -9641,7 +9708,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="151">
+    <row r="151" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>2504</v>
       </c>
@@ -9679,10 +9746,10 @@
         <v>11</v>
       </c>
       <c r="M151" s="4">
-        <v>28.656</v>
+        <v>28.655999999999999</v>
       </c>
       <c r="N151" s="4">
-        <v>315.216</v>
+        <v>315.21600000000001</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>202</v>
@@ -9691,7 +9758,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="152">
+    <row r="152" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>2504</v>
       </c>
@@ -9729,7 +9796,7 @@
         <v>29</v>
       </c>
       <c r="M152" s="4">
-        <v>10.656</v>
+        <v>10.656000000000001</v>
       </c>
       <c r="N152" s="4">
         <v>309.024</v>
@@ -9741,7 +9808,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="153">
+    <row r="153" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>2504</v>
       </c>
@@ -9779,10 +9846,10 @@
         <v>2</v>
       </c>
       <c r="M153" s="4">
-        <v>29.088</v>
+        <v>29.088000000000001</v>
       </c>
       <c r="N153" s="4">
-        <v>58.176</v>
+        <v>58.176000000000002</v>
       </c>
       <c r="O153" s="1" t="s">
         <v>202</v>
@@ -9791,7 +9858,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="154">
+    <row r="154" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>2504</v>
       </c>
@@ -9829,10 +9896,10 @@
         <v>4</v>
       </c>
       <c r="M154" s="4">
-        <v>36.496</v>
+        <v>36.496000000000002</v>
       </c>
       <c r="N154" s="4">
-        <v>145.984</v>
+        <v>145.98400000000001</v>
       </c>
       <c r="O154" s="1" t="s">
         <v>202</v>
@@ -9841,7 +9908,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="155">
+    <row r="155" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>2504</v>
       </c>
@@ -9879,7 +9946,7 @@
         <v>29</v>
       </c>
       <c r="M155" s="4">
-        <v>34.752</v>
+        <v>34.752000000000002</v>
       </c>
       <c r="N155" s="4">
         <v>1007.808</v>
@@ -9891,7 +9958,7 @@
         <v>203</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="156">
+    <row r="156" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>2409</v>
       </c>
@@ -9905,7 +9972,7 @@
         <v>90</v>
       </c>
       <c r="E156" s="3">
-        <v>46078.6817048032</v>
+        <v>46078.681704803203</v>
       </c>
       <c r="F156" s="2">
         <v>82316</v>
@@ -9941,7 +10008,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="157">
+    <row r="157" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>2409</v>
       </c>
@@ -9955,7 +10022,7 @@
         <v>90</v>
       </c>
       <c r="E157" s="3">
-        <v>46078.6817048032</v>
+        <v>46078.681704803203</v>
       </c>
       <c r="F157" s="2">
         <v>82316</v>
@@ -9991,7 +10058,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="158">
+    <row r="158" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>2409</v>
       </c>
@@ -10005,7 +10072,7 @@
         <v>90</v>
       </c>
       <c r="E158" s="3">
-        <v>46078.6817048032</v>
+        <v>46078.681704803203</v>
       </c>
       <c r="F158" s="2">
         <v>82316</v>
@@ -10041,7 +10108,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="159">
+    <row r="159" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>2409</v>
       </c>
@@ -10055,7 +10122,7 @@
         <v>90</v>
       </c>
       <c r="E159" s="3">
-        <v>46078.6817048032</v>
+        <v>46078.681704803203</v>
       </c>
       <c r="F159" s="2">
         <v>82316</v>
@@ -10091,7 +10158,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="160">
+    <row r="160" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>2409</v>
       </c>
@@ -10105,7 +10172,7 @@
         <v>90</v>
       </c>
       <c r="E160" s="3">
-        <v>46078.6817048032</v>
+        <v>46078.681704803203</v>
       </c>
       <c r="F160" s="2">
         <v>82325</v>
@@ -10141,7 +10208,7 @@
         <v>151</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="161">
+    <row r="161" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>2409</v>
       </c>
@@ -10155,7 +10222,7 @@
         <v>90</v>
       </c>
       <c r="E161" s="3">
-        <v>46078.6817048032</v>
+        <v>46078.681704803203</v>
       </c>
       <c r="F161" s="2">
         <v>82327</v>
@@ -10191,7 +10258,7 @@
         <v>369</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="162">
+    <row r="162" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>2409</v>
       </c>
@@ -10205,7 +10272,7 @@
         <v>90</v>
       </c>
       <c r="E162" s="3">
-        <v>46078.6817048032</v>
+        <v>46078.681704803203</v>
       </c>
       <c r="F162" s="2">
         <v>82316</v>
@@ -10241,7 +10308,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="163">
+    <row r="163" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>2516</v>
       </c>
@@ -10255,7 +10322,7 @@
         <v>14</v>
       </c>
       <c r="E163" s="3">
-        <v>46079.5782408912</v>
+        <v>46079.578240891198</v>
       </c>
       <c r="F163" s="2">
         <v>82340</v>
@@ -10291,7 +10358,7 @@
         <v>373</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="164">
+    <row r="164" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>2510</v>
       </c>
@@ -10305,7 +10372,7 @@
         <v>35</v>
       </c>
       <c r="E164" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F164" s="2">
         <v>82388</v>
@@ -10341,7 +10408,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="165">
+    <row r="165" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>2510</v>
       </c>
@@ -10355,7 +10422,7 @@
         <v>35</v>
       </c>
       <c r="E165" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F165" s="2">
         <v>82388</v>
@@ -10391,7 +10458,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="166">
+    <row r="166" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>2510</v>
       </c>
@@ -10405,7 +10472,7 @@
         <v>35</v>
       </c>
       <c r="E166" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F166" s="2">
         <v>82397</v>
@@ -10441,7 +10508,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="167">
+    <row r="167" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>2510</v>
       </c>
@@ -10455,7 +10522,7 @@
         <v>35</v>
       </c>
       <c r="E167" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F167" s="2">
         <v>82397</v>
@@ -10491,7 +10558,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="168">
+    <row r="168" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>2510</v>
       </c>
@@ -10505,7 +10572,7 @@
         <v>35</v>
       </c>
       <c r="E168" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F168" s="2">
         <v>82397</v>
@@ -10541,7 +10608,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="169">
+    <row r="169" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>2510</v>
       </c>
@@ -10555,7 +10622,7 @@
         <v>35</v>
       </c>
       <c r="E169" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F169" s="2">
         <v>82389</v>
@@ -10591,7 +10658,7 @@
         <v>386</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="170">
+    <row r="170" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>2510</v>
       </c>
@@ -10605,7 +10672,7 @@
         <v>35</v>
       </c>
       <c r="E170" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F170" s="2">
         <v>82389</v>
@@ -10641,7 +10708,7 @@
         <v>386</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="171">
+    <row r="171" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>2510</v>
       </c>
@@ -10655,7 +10722,7 @@
         <v>35</v>
       </c>
       <c r="E171" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F171" s="2">
         <v>82397</v>
@@ -10691,7 +10758,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="172">
+    <row r="172" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>2510</v>
       </c>
@@ -10705,7 +10772,7 @@
         <v>35</v>
       </c>
       <c r="E172" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F172" s="2">
         <v>82397</v>
@@ -10741,7 +10808,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="173">
+    <row r="173" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>2510</v>
       </c>
@@ -10755,7 +10822,7 @@
         <v>35</v>
       </c>
       <c r="E173" s="3">
-        <v>46079.5787315972</v>
+        <v>46079.578731597197</v>
       </c>
       <c r="F173" s="2">
         <v>82396</v>
@@ -10791,7 +10858,7 @@
         <v>236</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="174">
+    <row r="174" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>2514</v>
       </c>
@@ -10805,7 +10872,7 @@
         <v>13</v>
       </c>
       <c r="E174" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F174" s="2">
         <v>82365</v>
@@ -10841,7 +10908,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="175">
+    <row r="175" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>2514</v>
       </c>
@@ -10855,7 +10922,7 @@
         <v>13</v>
       </c>
       <c r="E175" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F175" s="2">
         <v>82371</v>
@@ -10891,7 +10958,7 @@
         <v>397</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="176">
+    <row r="176" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>2514</v>
       </c>
@@ -10905,7 +10972,7 @@
         <v>13</v>
       </c>
       <c r="E176" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F176" s="2">
         <v>82371</v>
@@ -10941,7 +11008,7 @@
         <v>397</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="177">
+    <row r="177" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>2514</v>
       </c>
@@ -10955,7 +11022,7 @@
         <v>13</v>
       </c>
       <c r="E177" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F177" s="2">
         <v>82365</v>
@@ -10991,7 +11058,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="178">
+    <row r="178" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>2514</v>
       </c>
@@ -11005,7 +11072,7 @@
         <v>13</v>
       </c>
       <c r="E178" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F178" s="2">
         <v>82366</v>
@@ -11029,10 +11096,10 @@
         <v>30</v>
       </c>
       <c r="M178" s="4">
-        <v>77.04</v>
+        <v>77.040000000000006</v>
       </c>
       <c r="N178" s="4">
-        <v>2311.2</v>
+        <v>2311.1999999999998</v>
       </c>
       <c r="O178" s="1" t="s">
         <v>404</v>
@@ -11041,7 +11108,7 @@
         <v>405</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="179">
+    <row r="179" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>2514</v>
       </c>
@@ -11055,7 +11122,7 @@
         <v>13</v>
       </c>
       <c r="E179" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F179" s="2">
         <v>82384</v>
@@ -11091,7 +11158,7 @@
         <v>156</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="180">
+    <row r="180" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>2514</v>
       </c>
@@ -11105,7 +11172,7 @@
         <v>13</v>
       </c>
       <c r="E180" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F180" s="2">
         <v>82383</v>
@@ -11132,7 +11199,7 @@
         <v>166.63</v>
       </c>
       <c r="N180" s="4">
-        <v>4998.9</v>
+        <v>4998.8999999999996</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>410</v>
@@ -11141,7 +11208,7 @@
         <v>411</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="181">
+    <row r="181" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>2514</v>
       </c>
@@ -11155,7 +11222,7 @@
         <v>13</v>
       </c>
       <c r="E181" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F181" s="2">
         <v>82383</v>
@@ -11191,7 +11258,7 @@
         <v>411</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="182">
+    <row r="182" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>2514</v>
       </c>
@@ -11205,7 +11272,7 @@
         <v>13</v>
       </c>
       <c r="E182" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F182" s="2">
         <v>82383</v>
@@ -11241,7 +11308,7 @@
         <v>411</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="183">
+    <row r="183" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>2514</v>
       </c>
@@ -11255,7 +11322,7 @@
         <v>13</v>
       </c>
       <c r="E183" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F183" s="2">
         <v>82383</v>
@@ -11291,7 +11358,7 @@
         <v>411</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="184">
+    <row r="184" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>2514</v>
       </c>
@@ -11305,7 +11372,7 @@
         <v>13</v>
       </c>
       <c r="E184" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F184" s="2">
         <v>82383</v>
@@ -11332,7 +11399,7 @@
         <v>53.52</v>
       </c>
       <c r="N184" s="4">
-        <v>535.2</v>
+        <v>535.20000000000005</v>
       </c>
       <c r="O184" s="1" t="s">
         <v>410</v>
@@ -11341,7 +11408,7 @@
         <v>411</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="185">
+    <row r="185" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>2514</v>
       </c>
@@ -11355,7 +11422,7 @@
         <v>13</v>
       </c>
       <c r="E185" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F185" s="2">
         <v>82383</v>
@@ -11391,7 +11458,7 @@
         <v>411</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="186">
+    <row r="186" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>2514</v>
       </c>
@@ -11405,7 +11472,7 @@
         <v>13</v>
       </c>
       <c r="E186" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F186" s="2">
         <v>82365</v>
@@ -11441,7 +11508,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="187">
+    <row r="187" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>2514</v>
       </c>
@@ -11455,7 +11522,7 @@
         <v>13</v>
       </c>
       <c r="E187" s="3">
-        <v>46080.4604712616</v>
+        <v>46080.460471261598</v>
       </c>
       <c r="F187" s="2">
         <v>82366</v>
@@ -11491,7 +11558,7 @@
         <v>405</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="188">
+    <row r="188" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>2407</v>
       </c>
@@ -11505,7 +11572,7 @@
         <v>84</v>
       </c>
       <c r="E188" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F188" s="2">
         <v>82360</v>
@@ -11541,7 +11608,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="189">
+    <row r="189" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>2407</v>
       </c>
@@ -11555,7 +11622,7 @@
         <v>84</v>
       </c>
       <c r="E189" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F189" s="2">
         <v>82360</v>
@@ -11579,7 +11646,7 @@
         <v>30</v>
       </c>
       <c r="M189" s="4">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="N189" s="4">
         <v>597</v>
@@ -11591,7 +11658,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="190">
+    <row r="190" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>2407</v>
       </c>
@@ -11605,7 +11672,7 @@
         <v>84</v>
       </c>
       <c r="E190" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F190" s="2">
         <v>82360</v>
@@ -11641,7 +11708,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="191">
+    <row r="191" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>2407</v>
       </c>
@@ -11655,7 +11722,7 @@
         <v>84</v>
       </c>
       <c r="E191" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F191" s="2">
         <v>82376</v>
@@ -11691,7 +11758,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="192">
+    <row r="192" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>2407</v>
       </c>
@@ -11705,7 +11772,7 @@
         <v>84</v>
       </c>
       <c r="E192" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F192" s="2">
         <v>82376</v>
@@ -11741,7 +11808,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="193">
+    <row r="193" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>2407</v>
       </c>
@@ -11755,7 +11822,7 @@
         <v>84</v>
       </c>
       <c r="E193" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F193" s="2">
         <v>82376</v>
@@ -11791,7 +11858,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="194">
+    <row r="194" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>2407</v>
       </c>
@@ -11805,7 +11872,7 @@
         <v>84</v>
       </c>
       <c r="E194" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F194" s="2">
         <v>82359</v>
@@ -11841,7 +11908,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="195">
+    <row r="195" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>2407</v>
       </c>
@@ -11855,7 +11922,7 @@
         <v>84</v>
       </c>
       <c r="E195" s="3">
-        <v>46080.46293125</v>
+        <v>46080.462931249996</v>
       </c>
       <c r="F195" s="2">
         <v>82359</v>
@@ -11891,7 +11958,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="196">
+    <row r="196" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>2507</v>
       </c>
@@ -11905,7 +11972,7 @@
         <v>30</v>
       </c>
       <c r="E196" s="3">
-        <v>46080.628344919</v>
+        <v>46080.628344919001</v>
       </c>
       <c r="F196" s="2">
         <v>82373</v>
@@ -11941,7 +12008,7 @@
         <v>442</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="197">
+    <row r="197" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>2506</v>
       </c>
@@ -11955,7 +12022,7 @@
         <v>31</v>
       </c>
       <c r="E197" s="3">
-        <v>46080.6289065162</v>
+        <v>46080.628906516198</v>
       </c>
       <c r="F197" s="2">
         <v>82387</v>
@@ -11991,7 +12058,7 @@
         <v>447</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="198">
+    <row r="198" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>2504</v>
       </c>
@@ -12005,7 +12072,7 @@
         <v>54</v>
       </c>
       <c r="E198" s="3">
-        <v>46080.6294471412</v>
+        <v>46080.629447141197</v>
       </c>
       <c r="F198" s="2">
         <v>82368</v>
@@ -12041,7 +12108,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="199">
+    <row r="199" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>2504</v>
       </c>
@@ -12055,7 +12122,7 @@
         <v>54</v>
       </c>
       <c r="E199" s="3">
-        <v>46080.6294471412</v>
+        <v>46080.629447141197</v>
       </c>
       <c r="F199" s="2">
         <v>82368</v>
@@ -12091,7 +12158,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="200">
+    <row r="200" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>2516</v>
       </c>
@@ -12105,7 +12172,7 @@
         <v>15</v>
       </c>
       <c r="E200" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F200" s="2">
         <v>82400</v>
@@ -12141,7 +12208,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="201">
+    <row r="201" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>2516</v>
       </c>
@@ -12155,7 +12222,7 @@
         <v>15</v>
       </c>
       <c r="E201" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F201" s="2">
         <v>82400</v>
@@ -12191,7 +12258,7 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="202">
+    <row r="202" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>2516</v>
       </c>
@@ -12205,7 +12272,7 @@
         <v>15</v>
       </c>
       <c r="E202" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F202" s="2">
         <v>82399</v>
@@ -12241,7 +12308,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="203">
+    <row r="203" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>2516</v>
       </c>
@@ -12255,7 +12322,7 @@
         <v>15</v>
       </c>
       <c r="E203" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F203" s="2">
         <v>82399</v>
@@ -12291,7 +12358,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="204">
+    <row r="204" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>2516</v>
       </c>
@@ -12305,7 +12372,7 @@
         <v>15</v>
       </c>
       <c r="E204" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F204" s="2">
         <v>82401</v>
@@ -12341,7 +12408,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="205">
+    <row r="205" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>2516</v>
       </c>
@@ -12355,7 +12422,7 @@
         <v>15</v>
       </c>
       <c r="E205" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F205" s="2">
         <v>82401</v>
@@ -12382,7 +12449,7 @@
         <v>50.9</v>
       </c>
       <c r="N205" s="4">
-        <v>152.7</v>
+        <v>152.69999999999999</v>
       </c>
       <c r="O205" s="1" t="s">
         <v>64</v>
@@ -12391,7 +12458,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="206">
+    <row r="206" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>2516</v>
       </c>
@@ -12405,7 +12472,7 @@
         <v>15</v>
       </c>
       <c r="E206" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F206" s="2">
         <v>82399</v>
@@ -12429,7 +12496,7 @@
         <v>20</v>
       </c>
       <c r="M206" s="4">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N206" s="4">
         <v>44</v>
@@ -12441,7 +12508,7 @@
         <v>69</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="207">
+    <row r="207" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>2516</v>
       </c>
@@ -12455,7 +12522,7 @@
         <v>15</v>
       </c>
       <c r="E207" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F207" s="2">
         <v>82401</v>
@@ -12491,7 +12558,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="208">
+    <row r="208" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>2516</v>
       </c>
@@ -12505,7 +12572,7 @@
         <v>15</v>
       </c>
       <c r="E208" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F208" s="2">
         <v>82401</v>
@@ -12529,7 +12596,7 @@
         <v>20</v>
       </c>
       <c r="M208" s="4">
-        <v>37.95</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="N208" s="4">
         <v>759</v>
@@ -12541,7 +12608,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="209">
+    <row r="209" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>2516</v>
       </c>
@@ -12555,7 +12622,7 @@
         <v>15</v>
       </c>
       <c r="E209" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F209" s="2">
         <v>82401</v>
@@ -12591,7 +12658,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="210">
+    <row r="210" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>2516</v>
       </c>
@@ -12605,7 +12672,7 @@
         <v>15</v>
       </c>
       <c r="E210" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F210" s="2">
         <v>82412</v>
@@ -12641,7 +12708,7 @@
         <v>323</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="211">
+    <row r="211" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>2516</v>
       </c>
@@ -12655,7 +12722,7 @@
         <v>15</v>
       </c>
       <c r="E211" s="3">
-        <v>46083.6671321991</v>
+        <v>46083.667132199102</v>
       </c>
       <c r="F211" s="2">
         <v>82415</v>
@@ -12679,7 +12746,7 @@
         <v>5</v>
       </c>
       <c r="M211" s="4">
-        <v>1242.36</v>
+        <v>1242.3599999999999</v>
       </c>
       <c r="N211" s="4">
         <v>6211.8</v>
@@ -12691,7 +12758,7 @@
         <v>465</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="212">
+    <row r="212" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>2516</v>
       </c>
@@ -12705,10 +12772,8 @@
         <v>15</v>
       </c>
       <c r="E212" s="3">
-        <v>46083.6671321991</v>
-      </c>
-      <c r="F212" s="1"/>
-      <c r="G212" s="1"/>
+        <v>46083.667132199102</v>
+      </c>
       <c r="H212" s="1" t="s">
         <v>466</v>
       </c>
@@ -12730,10 +12795,8 @@
       <c r="N212" s="4">
         <v>0</v>
       </c>
-      <c r="O212" s="1"/>
-      <c r="P212" s="1"/>
-    </row>
-    <row ht="12.75" customHeight="1" r="213">
+    </row>
+    <row r="213" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>2511</v>
       </c>
@@ -12747,7 +12810,7 @@
         <v>26</v>
       </c>
       <c r="E213" s="3">
-        <v>46083.6694849421</v>
+        <v>46083.669484942096</v>
       </c>
       <c r="F213" s="2">
         <v>82417</v>
@@ -12783,7 +12846,7 @@
         <v>465</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="214">
+    <row r="214" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>2511</v>
       </c>
@@ -12797,7 +12860,7 @@
         <v>26</v>
       </c>
       <c r="E214" s="3">
-        <v>46083.6694849421</v>
+        <v>46083.669484942096</v>
       </c>
       <c r="F214" s="2">
         <v>82417</v>
@@ -12833,7 +12896,7 @@
         <v>465</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="215">
+    <row r="215" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>2511</v>
       </c>
@@ -12847,7 +12910,7 @@
         <v>26</v>
       </c>
       <c r="E215" s="3">
-        <v>46083.6694849421</v>
+        <v>46083.669484942096</v>
       </c>
       <c r="F215" s="2">
         <v>82417</v>
@@ -12883,7 +12946,7 @@
         <v>465</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="216">
+    <row r="216" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>2511</v>
       </c>
@@ -12897,7 +12960,7 @@
         <v>26</v>
       </c>
       <c r="E216" s="3">
-        <v>46083.6694849421</v>
+        <v>46083.669484942096</v>
       </c>
       <c r="F216" s="2">
         <v>82417</v>
@@ -12933,7 +12996,7 @@
         <v>465</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="217">
+    <row r="217" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>2317</v>
       </c>
@@ -12947,7 +13010,7 @@
         <v>74</v>
       </c>
       <c r="E217" s="3">
-        <v>46083.6704391782</v>
+        <v>46083.670439178197</v>
       </c>
       <c r="F217" s="2">
         <v>82406</v>
@@ -12983,7 +13046,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="218">
+    <row r="218" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>2317</v>
       </c>
@@ -12997,7 +13060,7 @@
         <v>74</v>
       </c>
       <c r="E218" s="3">
-        <v>46083.6704391782</v>
+        <v>46083.670439178197</v>
       </c>
       <c r="F218" s="2">
         <v>82405</v>
@@ -13033,7 +13096,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="219">
+    <row r="219" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>2317</v>
       </c>
@@ -13047,7 +13110,7 @@
         <v>74</v>
       </c>
       <c r="E219" s="3">
-        <v>46083.6704391782</v>
+        <v>46083.670439178197</v>
       </c>
       <c r="F219" s="2">
         <v>82405</v>
@@ -13083,7 +13146,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="220">
+    <row r="220" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>2317</v>
       </c>
@@ -13097,7 +13160,7 @@
         <v>74</v>
       </c>
       <c r="E220" s="3">
-        <v>46083.6704391782</v>
+        <v>46083.670439178197</v>
       </c>
       <c r="F220" s="2">
         <v>82406</v>
@@ -13133,7 +13196,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="221">
+    <row r="221" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>2317</v>
       </c>
@@ -13147,7 +13210,7 @@
         <v>74</v>
       </c>
       <c r="E221" s="3">
-        <v>46083.6704391782</v>
+        <v>46083.670439178197</v>
       </c>
       <c r="F221" s="2">
         <v>82406</v>
@@ -13183,22 +13246,19 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="222">
+    <row r="222" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>500</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C222" s="1"/>
       <c r="D222" s="2">
         <v>6</v>
       </c>
       <c r="E222" s="3">
-        <v>46084.4672411921</v>
-      </c>
-      <c r="F222" s="1"/>
-      <c r="G222" s="1"/>
+        <v>46084.467241192098</v>
+      </c>
       <c r="H222" s="1" t="s">
         <v>480</v>
       </c>
@@ -13220,25 +13280,20 @@
       <c r="N222" s="4">
         <v>150</v>
       </c>
-      <c r="O222" s="1"/>
-      <c r="P222" s="1"/>
-    </row>
-    <row ht="12.75" customHeight="1" r="223">
+    </row>
+    <row r="223" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>500</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C223" s="1"/>
       <c r="D223" s="2">
         <v>6</v>
       </c>
       <c r="E223" s="3">
-        <v>46084.4672411921</v>
-      </c>
-      <c r="F223" s="1"/>
-      <c r="G223" s="1"/>
+        <v>46084.467241192098</v>
+      </c>
       <c r="H223" s="1" t="s">
         <v>482</v>
       </c>
@@ -13260,10 +13315,8 @@
       <c r="N223" s="4">
         <v>100</v>
       </c>
-      <c r="O223" s="1"/>
-      <c r="P223" s="1"/>
-    </row>
-    <row ht="12.75" customHeight="1" r="224">
+    </row>
+    <row r="224" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>2512</v>
       </c>
@@ -13277,7 +13330,7 @@
         <v>20</v>
       </c>
       <c r="E224" s="3">
-        <v>46084.5055666204</v>
+        <v>46084.505566620399</v>
       </c>
       <c r="F224" s="2">
         <v>82409</v>
@@ -13313,7 +13366,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="225">
+    <row r="225" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>2505</v>
       </c>
@@ -13327,7 +13380,7 @@
         <v>46</v>
       </c>
       <c r="E225" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F225" s="2">
         <v>82411</v>
@@ -13363,7 +13416,7 @@
         <v>485</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="226">
+    <row r="226" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>2505</v>
       </c>
@@ -13377,7 +13430,7 @@
         <v>46</v>
       </c>
       <c r="E226" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F226" s="2">
         <v>82411</v>
@@ -13413,7 +13466,7 @@
         <v>485</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="227">
+    <row r="227" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>2505</v>
       </c>
@@ -13427,7 +13480,7 @@
         <v>46</v>
       </c>
       <c r="E227" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F227" s="2">
         <v>82411</v>
@@ -13463,7 +13516,7 @@
         <v>485</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="228">
+    <row r="228" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>2505</v>
       </c>
@@ -13477,7 +13530,7 @@
         <v>46</v>
       </c>
       <c r="E228" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F228" s="2">
         <v>82411</v>
@@ -13501,10 +13554,10 @@
         <v>2</v>
       </c>
       <c r="M228" s="4">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="N228" s="4">
-        <v>39.8</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="O228" s="1" t="s">
         <v>484</v>
@@ -13513,7 +13566,7 @@
         <v>485</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="229">
+    <row r="229" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>2505</v>
       </c>
@@ -13527,7 +13580,7 @@
         <v>46</v>
       </c>
       <c r="E229" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F229" s="2">
         <v>82411</v>
@@ -13563,7 +13616,7 @@
         <v>485</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="230">
+    <row r="230" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>2505</v>
       </c>
@@ -13577,7 +13630,7 @@
         <v>46</v>
       </c>
       <c r="E230" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F230" s="2">
         <v>82411</v>
@@ -13613,7 +13666,7 @@
         <v>485</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="231">
+    <row r="231" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>2505</v>
       </c>
@@ -13627,7 +13680,7 @@
         <v>46</v>
       </c>
       <c r="E231" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F231" s="2">
         <v>82411</v>
@@ -13663,7 +13716,7 @@
         <v>485</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="232">
+    <row r="232" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>2505</v>
       </c>
@@ -13677,7 +13730,7 @@
         <v>46</v>
       </c>
       <c r="E232" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F232" s="2">
         <v>82473</v>
@@ -13713,7 +13766,7 @@
         <v>492</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="233">
+    <row r="233" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>2505</v>
       </c>
@@ -13727,7 +13780,7 @@
         <v>46</v>
       </c>
       <c r="E233" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F233" s="2">
         <v>82474</v>
@@ -13763,7 +13816,7 @@
         <v>496</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="234">
+    <row r="234" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>2505</v>
       </c>
@@ -13777,7 +13830,7 @@
         <v>46</v>
       </c>
       <c r="E234" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F234" s="2">
         <v>82432</v>
@@ -13801,10 +13854,10 @@
         <v>90</v>
       </c>
       <c r="M234" s="4">
-        <v>3.33333</v>
+        <v>3.3333300000000001</v>
       </c>
       <c r="N234" s="4">
-        <v>299.9997</v>
+        <v>299.99970000000002</v>
       </c>
       <c r="O234" s="1" t="s">
         <v>499</v>
@@ -13813,7 +13866,7 @@
         <v>500</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="235">
+    <row r="235" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>2505</v>
       </c>
@@ -13827,7 +13880,7 @@
         <v>46</v>
       </c>
       <c r="E235" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F235" s="2">
         <v>82432</v>
@@ -13863,7 +13916,7 @@
         <v>500</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="236">
+    <row r="236" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>2505</v>
       </c>
@@ -13877,7 +13930,7 @@
         <v>46</v>
       </c>
       <c r="E236" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F236" s="2">
         <v>82432</v>
@@ -13913,7 +13966,7 @@
         <v>500</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="237">
+    <row r="237" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>2505</v>
       </c>
@@ -13927,7 +13980,7 @@
         <v>46</v>
       </c>
       <c r="E237" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F237" s="2">
         <v>82432</v>
@@ -13963,7 +14016,7 @@
         <v>500</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="238">
+    <row r="238" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>2505</v>
       </c>
@@ -13977,7 +14030,7 @@
         <v>46</v>
       </c>
       <c r="E238" s="3">
-        <v>46084.5060569213</v>
+        <v>46084.506056921302</v>
       </c>
       <c r="F238" s="2">
         <v>82474</v>
@@ -14001,7 +14054,7 @@
         <v>10</v>
       </c>
       <c r="M238" s="4">
-        <v>17.4</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="N238" s="4">
         <v>174</v>
@@ -14013,7 +14066,7 @@
         <v>496</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="239">
+    <row r="239" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>2509</v>
       </c>
@@ -14027,7 +14080,7 @@
         <v>32</v>
       </c>
       <c r="E239" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F239" s="2">
         <v>82421</v>
@@ -14063,7 +14116,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="240">
+    <row r="240" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>2509</v>
       </c>
@@ -14077,7 +14130,7 @@
         <v>32</v>
       </c>
       <c r="E240" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F240" s="2">
         <v>82421</v>
@@ -14104,7 +14157,7 @@
         <v>10.85</v>
       </c>
       <c r="N240" s="4">
-        <v>130.2</v>
+        <v>130.19999999999999</v>
       </c>
       <c r="O240" s="1" t="s">
         <v>375</v>
@@ -14113,7 +14166,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="241">
+    <row r="241" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>2509</v>
       </c>
@@ -14127,7 +14180,7 @@
         <v>32</v>
       </c>
       <c r="E241" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F241" s="2">
         <v>82434</v>
@@ -14163,7 +14216,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="242">
+    <row r="242" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>2509</v>
       </c>
@@ -14177,7 +14230,7 @@
         <v>32</v>
       </c>
       <c r="E242" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F242" s="2">
         <v>82422</v>
@@ -14213,7 +14266,7 @@
         <v>181</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="243">
+    <row r="243" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>2509</v>
       </c>
@@ -14227,7 +14280,7 @@
         <v>32</v>
       </c>
       <c r="E243" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F243" s="2">
         <v>82434</v>
@@ -14263,7 +14316,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="244">
+    <row r="244" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>2509</v>
       </c>
@@ -14277,7 +14330,7 @@
         <v>32</v>
       </c>
       <c r="E244" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F244" s="2">
         <v>82433</v>
@@ -14313,7 +14366,7 @@
         <v>28</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="245">
+    <row r="245" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>2509</v>
       </c>
@@ -14327,7 +14380,7 @@
         <v>32</v>
       </c>
       <c r="E245" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F245" s="2">
         <v>82423</v>
@@ -14363,7 +14416,7 @@
         <v>23</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="246">
+    <row r="246" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>2509</v>
       </c>
@@ -14377,7 +14430,7 @@
         <v>32</v>
       </c>
       <c r="E246" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F246" s="2">
         <v>82419</v>
@@ -14413,7 +14466,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="247">
+    <row r="247" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>2509</v>
       </c>
@@ -14427,7 +14480,7 @@
         <v>32</v>
       </c>
       <c r="E247" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F247" s="2">
         <v>82419</v>
@@ -14463,7 +14516,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="248">
+    <row r="248" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>2509</v>
       </c>
@@ -14477,7 +14530,7 @@
         <v>32</v>
       </c>
       <c r="E248" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F248" s="2">
         <v>82423</v>
@@ -14513,7 +14566,7 @@
         <v>23</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="249">
+    <row r="249" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>2509</v>
       </c>
@@ -14527,7 +14580,7 @@
         <v>32</v>
       </c>
       <c r="E249" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F249" s="2">
         <v>82464</v>
@@ -14563,7 +14616,7 @@
         <v>522</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="250">
+    <row r="250" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>2509</v>
       </c>
@@ -14577,7 +14630,7 @@
         <v>32</v>
       </c>
       <c r="E250" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F250" s="2">
         <v>82464</v>
@@ -14613,7 +14666,7 @@
         <v>522</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="251">
+    <row r="251" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>2509</v>
       </c>
@@ -14627,7 +14680,7 @@
         <v>32</v>
       </c>
       <c r="E251" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F251" s="2">
         <v>82464</v>
@@ -14663,7 +14716,7 @@
         <v>522</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="252">
+    <row r="252" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>2509</v>
       </c>
@@ -14677,7 +14730,7 @@
         <v>32</v>
       </c>
       <c r="E252" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F252" s="2">
         <v>82464</v>
@@ -14713,7 +14766,7 @@
         <v>522</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="253">
+    <row r="253" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>2509</v>
       </c>
@@ -14727,7 +14780,7 @@
         <v>32</v>
       </c>
       <c r="E253" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F253" s="2">
         <v>82464</v>
@@ -14763,7 +14816,7 @@
         <v>522</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="254">
+    <row r="254" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>2509</v>
       </c>
@@ -14777,7 +14830,7 @@
         <v>32</v>
       </c>
       <c r="E254" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F254" s="2">
         <v>82464</v>
@@ -14813,7 +14866,7 @@
         <v>522</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="255">
+    <row r="255" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>2509</v>
       </c>
@@ -14827,7 +14880,7 @@
         <v>32</v>
       </c>
       <c r="E255" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F255" s="2">
         <v>82464</v>
@@ -14863,7 +14916,7 @@
         <v>522</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="256">
+    <row r="256" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>2509</v>
       </c>
@@ -14877,7 +14930,7 @@
         <v>32</v>
       </c>
       <c r="E256" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F256" s="2">
         <v>82472</v>
@@ -14913,7 +14966,7 @@
         <v>538</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="257">
+    <row r="257" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>2509</v>
       </c>
@@ -14927,7 +14980,7 @@
         <v>32</v>
       </c>
       <c r="E257" s="3">
-        <v>46084.7378501505</v>
+        <v>46084.737850150501</v>
       </c>
       <c r="F257" s="2">
         <v>82420</v>
@@ -14963,7 +15016,7 @@
         <v>538</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="258">
+    <row r="258" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>2504</v>
       </c>
@@ -14977,7 +15030,7 @@
         <v>55</v>
       </c>
       <c r="E258" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F258" s="2">
         <v>82426</v>
@@ -15013,7 +15066,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="259">
+    <row r="259" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>2504</v>
       </c>
@@ -15027,7 +15080,7 @@
         <v>55</v>
       </c>
       <c r="E259" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F259" s="2">
         <v>82426</v>
@@ -15063,7 +15116,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="260">
+    <row r="260" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>2504</v>
       </c>
@@ -15077,7 +15130,7 @@
         <v>55</v>
       </c>
       <c r="E260" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F260" s="2">
         <v>82425</v>
@@ -15113,7 +15166,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="261">
+    <row r="261" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>2504</v>
       </c>
@@ -15127,7 +15180,7 @@
         <v>55</v>
       </c>
       <c r="E261" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F261" s="2">
         <v>82425</v>
@@ -15163,7 +15216,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="262">
+    <row r="262" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>2504</v>
       </c>
@@ -15177,7 +15230,7 @@
         <v>55</v>
       </c>
       <c r="E262" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F262" s="2">
         <v>82431</v>
@@ -15213,7 +15266,7 @@
         <v>544</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="263">
+    <row r="263" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>2504</v>
       </c>
@@ -15227,7 +15280,7 @@
         <v>55</v>
       </c>
       <c r="E263" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F263" s="2">
         <v>82425</v>
@@ -15263,7 +15316,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="264">
+    <row r="264" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>2504</v>
       </c>
@@ -15277,7 +15330,7 @@
         <v>55</v>
       </c>
       <c r="E264" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F264" s="2">
         <v>82430</v>
@@ -15313,7 +15366,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="265">
+    <row r="265" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>2504</v>
       </c>
@@ -15327,7 +15380,7 @@
         <v>55</v>
       </c>
       <c r="E265" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F265" s="2">
         <v>82430</v>
@@ -15363,7 +15416,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="266">
+    <row r="266" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>2504</v>
       </c>
@@ -15377,7 +15430,7 @@
         <v>55</v>
       </c>
       <c r="E266" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F266" s="2">
         <v>82425</v>
@@ -15413,7 +15466,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="267">
+    <row r="267" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>2504</v>
       </c>
@@ -15427,7 +15480,7 @@
         <v>55</v>
       </c>
       <c r="E267" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F267" s="2">
         <v>82425</v>
@@ -15463,7 +15516,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="268">
+    <row r="268" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>2504</v>
       </c>
@@ -15477,7 +15530,7 @@
         <v>55</v>
       </c>
       <c r="E268" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F268" s="2">
         <v>82425</v>
@@ -15513,7 +15566,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="269">
+    <row r="269" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>2504</v>
       </c>
@@ -15527,7 +15580,7 @@
         <v>55</v>
       </c>
       <c r="E269" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F269" s="2">
         <v>82425</v>
@@ -15563,7 +15616,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="270">
+    <row r="270" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>2504</v>
       </c>
@@ -15577,7 +15630,7 @@
         <v>55</v>
       </c>
       <c r="E270" s="3">
-        <v>46084.741264838</v>
+        <v>46084.741264837998</v>
       </c>
       <c r="F270" s="2">
         <v>82425</v>
@@ -15613,7 +15666,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="271">
+    <row r="271" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>2510</v>
       </c>
@@ -15627,7 +15680,7 @@
         <v>36</v>
       </c>
       <c r="E271" s="3">
-        <v>46085.6249659838</v>
+        <v>46085.624965983799</v>
       </c>
       <c r="F271" s="2">
         <v>82435</v>
@@ -15663,7 +15716,7 @@
         <v>560</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="272">
+    <row r="272" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>2212</v>
       </c>
@@ -15701,7 +15754,7 @@
         <v>20000</v>
       </c>
       <c r="M272" s="4">
-        <v>0.0933</v>
+        <v>9.3299999999999994E-2</v>
       </c>
       <c r="N272" s="4">
         <v>1866</v>
@@ -15713,7 +15766,7 @@
         <v>565</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="273">
+    <row r="273" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>2212</v>
       </c>
@@ -15763,7 +15816,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="274">
+    <row r="274" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>2212</v>
       </c>
@@ -15813,7 +15866,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="275">
+    <row r="275" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>2212</v>
       </c>
@@ -15863,7 +15916,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="276">
+    <row r="276" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>2212</v>
       </c>
@@ -15913,7 +15966,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="277">
+    <row r="277" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>2212</v>
       </c>
@@ -15963,7 +16016,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="278">
+    <row r="278" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>2212</v>
       </c>
@@ -16013,7 +16066,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="279">
+    <row r="279" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>2212</v>
       </c>
@@ -16063,7 +16116,7 @@
         <v>544</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="280">
+    <row r="280" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>2212</v>
       </c>
@@ -16113,7 +16166,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="281">
+    <row r="281" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>2212</v>
       </c>
@@ -16163,7 +16216,7 @@
         <v>573</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="282">
+    <row r="282" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>2212</v>
       </c>
@@ -16213,7 +16266,7 @@
         <v>573</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="283">
+    <row r="283" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>2507</v>
       </c>
@@ -16263,7 +16316,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="284">
+    <row r="284" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>2507</v>
       </c>
@@ -16313,7 +16366,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="285">
+    <row r="285" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>2507</v>
       </c>
@@ -16351,10 +16404,10 @@
         <v>2</v>
       </c>
       <c r="M285" s="4">
-        <v>147.3</v>
+        <v>147.30000000000001</v>
       </c>
       <c r="N285" s="4">
-        <v>294.6</v>
+        <v>294.60000000000002</v>
       </c>
       <c r="O285" s="1" t="s">
         <v>375</v>
@@ -16363,7 +16416,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="286">
+    <row r="286" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>2507</v>
       </c>
@@ -16413,7 +16466,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="287">
+    <row r="287" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>2507</v>
       </c>
@@ -16451,7 +16504,7 @@
         <v>30</v>
       </c>
       <c r="M287" s="4">
-        <v>16.9</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="N287" s="4">
         <v>507</v>
@@ -16463,7 +16516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="288">
+    <row r="288" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>2507</v>
       </c>
@@ -16513,7 +16566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="289">
+    <row r="289" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>2507</v>
       </c>
@@ -16563,7 +16616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="290">
+    <row r="290" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>2507</v>
       </c>
@@ -16604,7 +16657,7 @@
         <v>44.9</v>
       </c>
       <c r="N290" s="4">
-        <v>269.4</v>
+        <v>269.39999999999998</v>
       </c>
       <c r="O290" s="1" t="s">
         <v>509</v>
@@ -16613,7 +16666,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="291">
+    <row r="291" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>2507</v>
       </c>
@@ -16663,7 +16716,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="292">
+    <row r="292" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>2507</v>
       </c>
@@ -16704,7 +16757,7 @@
         <v>13.6</v>
       </c>
       <c r="N292" s="4">
-        <v>81.6</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="O292" s="1" t="s">
         <v>509</v>
@@ -16713,7 +16766,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="293">
+    <row r="293" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>2507</v>
       </c>
@@ -16763,7 +16816,7 @@
         <v>199</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="294">
+    <row r="294" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>2507</v>
       </c>
@@ -16813,7 +16866,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="295">
+    <row r="295" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>2507</v>
       </c>
@@ -16863,7 +16916,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="296">
+    <row r="296" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>2507</v>
       </c>
@@ -16913,7 +16966,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="297">
+    <row r="297" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>2511</v>
       </c>
@@ -16963,7 +17016,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="298">
+    <row r="298" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>2516</v>
       </c>
@@ -16977,10 +17030,8 @@
         <v>16</v>
       </c>
       <c r="E298" s="3">
-        <v>46086.6312882639</v>
-      </c>
-      <c r="F298" s="1"/>
-      <c r="G298" s="1"/>
+        <v>46086.631288263903</v>
+      </c>
       <c r="H298" s="1" t="s">
         <v>592</v>
       </c>
@@ -17002,10 +17053,8 @@
       <c r="N298" s="4">
         <v>0</v>
       </c>
-      <c r="O298" s="1"/>
-      <c r="P298" s="1"/>
-    </row>
-    <row ht="12.75" customHeight="1" r="299">
+    </row>
+    <row r="299" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>2516</v>
       </c>
@@ -17019,10 +17068,8 @@
         <v>16</v>
       </c>
       <c r="E299" s="3">
-        <v>46086.6312882639</v>
-      </c>
-      <c r="F299" s="1"/>
-      <c r="G299" s="1"/>
+        <v>46086.631288263903</v>
+      </c>
       <c r="H299" s="1" t="s">
         <v>592</v>
       </c>
@@ -17044,10 +17091,8 @@
       <c r="N299" s="4">
         <v>0</v>
       </c>
-      <c r="O299" s="1"/>
-      <c r="P299" s="1"/>
-    </row>
-    <row ht="12.75" customHeight="1" r="300">
+    </row>
+    <row r="300" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>2516</v>
       </c>
@@ -17061,10 +17106,8 @@
         <v>16</v>
       </c>
       <c r="E300" s="3">
-        <v>46086.6312882639</v>
-      </c>
-      <c r="F300" s="1"/>
-      <c r="G300" s="1"/>
+        <v>46086.631288263903</v>
+      </c>
       <c r="H300" s="1" t="s">
         <v>592</v>
       </c>
@@ -17086,10 +17129,8 @@
       <c r="N300" s="4">
         <v>0</v>
       </c>
-      <c r="O300" s="1"/>
-      <c r="P300" s="1"/>
-    </row>
-    <row ht="12.75" customHeight="1" r="301">
+    </row>
+    <row r="301" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>2516</v>
       </c>
@@ -17103,10 +17144,8 @@
         <v>16</v>
       </c>
       <c r="E301" s="3">
-        <v>46086.6312882639</v>
-      </c>
-      <c r="F301" s="1"/>
-      <c r="G301" s="1"/>
+        <v>46086.631288263903</v>
+      </c>
       <c r="H301" s="1" t="s">
         <v>592</v>
       </c>
@@ -17128,10 +17167,8 @@
       <c r="N301" s="4">
         <v>0</v>
       </c>
-      <c r="O301" s="1"/>
-      <c r="P301" s="1"/>
-    </row>
-    <row ht="12.75" customHeight="1" r="302">
+    </row>
+    <row r="302" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>2409</v>
       </c>
@@ -17145,7 +17182,7 @@
         <v>92</v>
       </c>
       <c r="E302" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F302" s="2">
         <v>82471</v>
@@ -17169,10 +17206,10 @@
         <v>1</v>
       </c>
       <c r="M302" s="4">
-        <v>65.6</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="N302" s="4">
-        <v>65.6</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="O302" s="1" t="s">
         <v>375</v>
@@ -17181,7 +17218,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="303">
+    <row r="303" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>2409</v>
       </c>
@@ -17195,7 +17232,7 @@
         <v>92</v>
       </c>
       <c r="E303" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F303" s="2">
         <v>82471</v>
@@ -17231,7 +17268,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="304">
+    <row r="304" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>2409</v>
       </c>
@@ -17245,7 +17282,7 @@
         <v>92</v>
       </c>
       <c r="E304" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F304" s="2">
         <v>82471</v>
@@ -17281,7 +17318,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="305">
+    <row r="305" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>2409</v>
       </c>
@@ -17295,7 +17332,7 @@
         <v>92</v>
       </c>
       <c r="E305" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F305" s="2">
         <v>82471</v>
@@ -17331,7 +17368,7 @@
         <v>376</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="306">
+    <row r="306" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>2409</v>
       </c>
@@ -17345,7 +17382,7 @@
         <v>92</v>
       </c>
       <c r="E306" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F306" s="2">
         <v>82476</v>
@@ -17381,7 +17418,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="307">
+    <row r="307" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>2409</v>
       </c>
@@ -17395,7 +17432,7 @@
         <v>92</v>
       </c>
       <c r="E307" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F307" s="2">
         <v>82476</v>
@@ -17431,7 +17468,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="308">
+    <row r="308" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>2409</v>
       </c>
@@ -17445,7 +17482,7 @@
         <v>92</v>
       </c>
       <c r="E308" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F308" s="2">
         <v>82476</v>
@@ -17481,7 +17518,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="309">
+    <row r="309" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>2409</v>
       </c>
@@ -17495,7 +17532,7 @@
         <v>92</v>
       </c>
       <c r="E309" s="3">
-        <v>46086.632572419</v>
+        <v>46086.632572419003</v>
       </c>
       <c r="F309" s="2">
         <v>82476</v>
@@ -17519,7 +17556,7 @@
         <v>10</v>
       </c>
       <c r="M309" s="4">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N309" s="4">
         <v>22</v>
@@ -17531,7 +17568,7 @@
         <v>510</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="310">
+    <row r="310" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>2407</v>
       </c>
@@ -17545,7 +17582,7 @@
         <v>85</v>
       </c>
       <c r="E310" s="3">
-        <v>46087.643003044</v>
+        <v>46087.643003044002</v>
       </c>
       <c r="F310" s="2">
         <v>82489</v>
@@ -17581,7 +17618,7 @@
         <v>65</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="311">
+    <row r="311" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>2407</v>
       </c>
@@ -17595,7 +17632,7 @@
         <v>85</v>
       </c>
       <c r="E311" s="3">
-        <v>46087.643003044</v>
+        <v>46087.643003044002</v>
       </c>
       <c r="F311" s="2">
         <v>82497</v>
@@ -17631,7 +17668,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="312">
+    <row r="312" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>2407</v>
       </c>
@@ -17645,7 +17682,7 @@
         <v>85</v>
       </c>
       <c r="E312" s="3">
-        <v>46087.643003044</v>
+        <v>46087.643003044002</v>
       </c>
       <c r="F312" s="2">
         <v>82497</v>
@@ -17681,7 +17718,7 @@
         <v>160</v>
       </c>
     </row>
-    <row ht="12.75" customHeight="1" r="313">
+    <row r="313" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>2407</v>
       </c>
@@ -17695,7 +17732,7 @@
         <v>85</v>
       </c>
       <c r="E313" s="3">
-        <v>46087.643003044</v>
+        <v>46087.643003044002</v>
       </c>
       <c r="F313" s="2">
         <v>82496</v>
@@ -17732,7 +17769,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
-  <pageSetup orientation="portrait" pageOrder="downThenOver" paperSize="9" fitToWidth="0" fitToHeight="0"/>
+  <pageMargins left="0.78740157480314998" right="0.78740157480314998" top="0.78740157480314998" bottom="0.78740157480314998" header="0.39370078740157499" footer="0.39370078740157499"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="597">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1553,42 +1553,42 @@
     <t>ESTOPA</t>
   </si>
   <si>
+    <t>C.04.0168</t>
+  </si>
+  <si>
+    <t>BONA SOAP LIMPADOR DE PISOS OLEADOS</t>
+  </si>
+  <si>
+    <t>K.08.0561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMADA PARA INFORMATICA CONECTOR RJ 45  BORNES DE PRESSÃO PRETA  LUMITEK - P/MOVEIS  67 X 43MM</t>
+  </si>
+  <si>
+    <t>K.08.1510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMPA PARA MODULO CEGO WHITE  REF KW00 LIVING NOW</t>
+  </si>
+  <si>
+    <t>K.08.1540</t>
+  </si>
+  <si>
+    <t>PULSADOR 10 A 250V BTICINO LIVING NOW COD K4005</t>
+  </si>
+  <si>
+    <t>K.08.1534</t>
+  </si>
+  <si>
+    <t>CAMPAINHA CIGARRA 80DB</t>
+  </si>
+  <si>
     <t>S.10.0062</t>
   </si>
   <si>
     <t>PU 40 FLEX ADESIVO DE POLIURETANO DE CURA RÁPIDA TUBO 310ML COR BRANCO</t>
   </si>
   <si>
-    <t>C.04.0168</t>
-  </si>
-  <si>
-    <t>BONA SOAP LIMPADOR DE PISOS OLEADOS</t>
-  </si>
-  <si>
-    <t>K.08.0561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMADA PARA INFORMATICA CONECTOR RJ 45  BORNES DE PRESSÃO PRETA  LUMITEK - P/MOVEIS  67 X 43MM</t>
-  </si>
-  <si>
-    <t>K.08.1510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAMPA PARA MODULO CEGO WHITE  REF KW00 LIVING NOW</t>
-  </si>
-  <si>
-    <t>K.08.1540</t>
-  </si>
-  <si>
-    <t>PULSADOR 10 A 250V BTICINO LIVING NOW COD K4005</t>
-  </si>
-  <si>
-    <t>K.08.1534</t>
-  </si>
-  <si>
-    <t>CAMPAINHA CIGARRA 80DB</t>
-  </si>
-  <si>
     <t>S.10.0063</t>
   </si>
   <si>
@@ -1686,6 +1686,123 @@
   </si>
   <si>
     <t xml:space="preserve">TINTA SHERWIN WILLIAMS NOVACOR PISO  EXTERIOR E INTERIOR 3,6 L</t>
+  </si>
+  <si>
+    <t>REGINA CAMPOS SALLES MORAES ABREU</t>
+  </si>
+  <si>
+    <t>C.05.0208</t>
+  </si>
+  <si>
+    <t>CADEIRA SECRETÁRIA FIXA</t>
+  </si>
+  <si>
+    <t>D.04.0010</t>
+  </si>
+  <si>
+    <t>PLACA DE OBRA COM LOGO OSBORNE MEDINDO 2,00 X 1,00</t>
+  </si>
+  <si>
+    <t>E.02.0213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMAPISO 2MM X 600MM X50M  PROMAFLEX</t>
+  </si>
+  <si>
+    <t>E.04.0600</t>
+  </si>
+  <si>
+    <t>CARRINHO DE MÃO REFORÇADO PNEU CÂMARA TRAMONTINA</t>
+  </si>
+  <si>
+    <t>E.04.0122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRUMO METÁLICO PARA PEDREIRO  DE FACE- Nº5 - 900 G</t>
+  </si>
+  <si>
+    <t>E.04.0142</t>
+  </si>
+  <si>
+    <t>NÍVEL DE MADEIRA - 16''</t>
+  </si>
+  <si>
+    <t>E.04.0182</t>
+  </si>
+  <si>
+    <t>TRENA LONGA DE FIBRA- 30 M</t>
+  </si>
+  <si>
+    <t>E.04.0173</t>
+  </si>
+  <si>
+    <t>NÍVEL A LASER</t>
+  </si>
+  <si>
+    <t>E.04.0165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESQUADRO PROFISSIONAL DE ALUMÍNIO  SOLDADO - 1,20 X 0,8 M</t>
+  </si>
+  <si>
+    <t>E.04.0775</t>
+  </si>
+  <si>
+    <t>REGUA DE ALUMINIO 3 X 1'' C/ 3 M</t>
+  </si>
+  <si>
+    <t>E.04.0606</t>
+  </si>
+  <si>
+    <t>BOMBA PARA ENCHER PNEU DE CARRINHO DE MAO</t>
+  </si>
+  <si>
+    <t>E.04.0166</t>
+  </si>
+  <si>
+    <t>ESQUADRO PROFISSIONAL DE ALUMÍNIO SOLDADO - 0,80 X 0,60 M</t>
+  </si>
+  <si>
+    <t>E.04.0176</t>
+  </si>
+  <si>
+    <t>TRENA PROFISSIONAL DE AÇO 5 M</t>
+  </si>
+  <si>
+    <t>E.04.0776</t>
+  </si>
+  <si>
+    <t>REGUA DE ALUMINIO 3 X 1'' C/ 6 M</t>
+  </si>
+  <si>
+    <t>E.04.0177</t>
+  </si>
+  <si>
+    <t>TRIPÉ PARA NIVEL A LASER</t>
+  </si>
+  <si>
+    <t>F.01.0011</t>
+  </si>
+  <si>
+    <t>ESCADA 6 DEGRAUS</t>
+  </si>
+  <si>
+    <t>F.01.0015</t>
+  </si>
+  <si>
+    <t>ESCADA DE FIBRA EXTENSÍVEL VAZADA C/ ALTURA</t>
+  </si>
+  <si>
+    <t>G.03.0002</t>
+  </si>
+  <si>
+    <t>CAÇAMBA - UNIDADE</t>
+  </si>
+  <si>
+    <t>K.02.0752</t>
+  </si>
+  <si>
+    <t>MANGUEIRA</t>
   </si>
 </sst>
 </file>
@@ -1984,11 +2101,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P326"/>
+  <dimension ref="A1:P345"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
-    <col min="2" max="2" width="35.4285714285714" customWidth="1" style="1"/>
+    <col min="2" max="2" width="39.8571428571429" customWidth="1" style="1"/>
     <col min="3" max="3" width="11.1428571428571" customWidth="1" style="1"/>
     <col min="4" max="4" width="10" customWidth="1" style="1"/>
     <col min="5" max="5" width="10.5714285714286" customWidth="1" style="1"/>
@@ -15159,16 +15276,16 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F279" s="2">
-        <v>82634</v>
+        <v>82635</v>
       </c>
       <c r="G279" s="3">
         <v>46094</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>180</v>
+        <v>511</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>181</v>
+        <v>512</v>
       </c>
       <c r="J279" s="1" t="s">
         <v>20</v>
@@ -15177,19 +15294,19 @@
         <v>21</v>
       </c>
       <c r="L279" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M279" s="4">
-        <v>3.9</v>
+        <v>16.8</v>
       </c>
       <c r="N279" s="4">
-        <v>195</v>
+        <v>16.8</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="P279" s="1" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="280">
@@ -15209,16 +15326,16 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F280" s="2">
-        <v>82635</v>
+        <v>82634</v>
       </c>
       <c r="G280" s="3">
         <v>46094</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>511</v>
+        <v>101</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>512</v>
+        <v>102</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>20</v>
@@ -15227,19 +15344,19 @@
         <v>21</v>
       </c>
       <c r="L280" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M280" s="4">
-        <v>16.8</v>
+        <v>12.09</v>
       </c>
       <c r="N280" s="4">
-        <v>16.8</v>
+        <v>36.27</v>
       </c>
       <c r="O280" s="1" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="P280" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="281">
@@ -15265,25 +15382,25 @@
         <v>46094</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>101</v>
+        <v>337</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>102</v>
+        <v>338</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K281" s="1" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="L281" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M281" s="4">
-        <v>12.09</v>
+        <v>175</v>
       </c>
       <c r="N281" s="4">
-        <v>36.27</v>
+        <v>175</v>
       </c>
       <c r="O281" s="1" t="s">
         <v>175</v>
@@ -15309,37 +15426,37 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F282" s="2">
-        <v>82634</v>
+        <v>82635</v>
       </c>
       <c r="G282" s="3">
         <v>46094</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="J282" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K282" s="1" t="s">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="L282" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M282" s="4">
-        <v>270</v>
+        <v>16</v>
       </c>
       <c r="N282" s="4">
-        <v>810</v>
+        <v>160</v>
       </c>
       <c r="O282" s="1" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="P282" s="1" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="283">
@@ -15365,25 +15482,25 @@
         <v>46094</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>337</v>
+        <v>190</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>338</v>
+        <v>191</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K283" s="1" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="L283" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M283" s="4">
-        <v>149</v>
+        <v>5.9</v>
       </c>
       <c r="N283" s="4">
-        <v>149</v>
+        <v>17.7</v>
       </c>
       <c r="O283" s="1" t="s">
         <v>175</v>
@@ -15409,16 +15526,16 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F284" s="2">
-        <v>82635</v>
+        <v>82634</v>
       </c>
       <c r="G284" s="3">
         <v>46094</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>20</v>
@@ -15430,16 +15547,16 @@
         <v>10</v>
       </c>
       <c r="M284" s="4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N284" s="4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="P284" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="285">
@@ -15465,25 +15582,25 @@
         <v>46094</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>191</v>
+        <v>39</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K285" s="1" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L285" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M285" s="4">
-        <v>5.9</v>
+        <v>1.8</v>
       </c>
       <c r="N285" s="4">
-        <v>17.7</v>
+        <v>10.8</v>
       </c>
       <c r="O285" s="1" t="s">
         <v>175</v>
@@ -15508,17 +15625,13 @@
       <c r="E286" s="3">
         <v>46094.4767297338</v>
       </c>
-      <c r="F286" s="2">
-        <v>82634</v>
-      </c>
-      <c r="G286" s="3">
-        <v>46094</v>
-      </c>
+      <c r="F286" s="1"/>
+      <c r="G286" s="1"/>
       <c r="H286" s="1" t="s">
-        <v>295</v>
+        <v>180</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>296</v>
+        <v>181</v>
       </c>
       <c r="J286" s="1" t="s">
         <v>20</v>
@@ -15527,20 +15640,16 @@
         <v>21</v>
       </c>
       <c r="L286" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="M286" s="4">
-        <v>15</v>
+        <v>3.9</v>
       </c>
       <c r="N286" s="4">
-        <v>150</v>
-      </c>
-      <c r="O286" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="P286" s="1" t="s">
-        <v>176</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="O286" s="1"/>
+      <c r="P286" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="287">
       <c r="A287" s="2">
@@ -15558,39 +15667,31 @@
       <c r="E287" s="3">
         <v>46094.4767297338</v>
       </c>
-      <c r="F287" s="2">
-        <v>82634</v>
-      </c>
-      <c r="G287" s="3">
-        <v>46094</v>
-      </c>
+      <c r="F287" s="1"/>
+      <c r="G287" s="1"/>
       <c r="H287" s="1" t="s">
-        <v>38</v>
+        <v>513</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>39</v>
+        <v>514</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K287" s="1" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="L287" s="4">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M287" s="4">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="N287" s="4">
-        <v>10.8</v>
-      </c>
-      <c r="O287" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="P287" s="1" t="s">
-        <v>176</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O287" s="1"/>
+      <c r="P287" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="288">
       <c r="A288" s="2">
@@ -15608,17 +15709,13 @@
       <c r="E288" s="3">
         <v>46094.4767297338</v>
       </c>
-      <c r="F288" s="2">
-        <v>82634</v>
-      </c>
-      <c r="G288" s="3">
-        <v>46094</v>
-      </c>
+      <c r="F288" s="1"/>
+      <c r="G288" s="1"/>
       <c r="H288" s="1" t="s">
-        <v>513</v>
+        <v>26</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>514</v>
+        <v>27</v>
       </c>
       <c r="J288" s="1" t="s">
         <v>20</v>
@@ -15630,17 +15727,13 @@
         <v>5</v>
       </c>
       <c r="M288" s="4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N288" s="4">
-        <v>75</v>
-      </c>
-      <c r="O288" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="P288" s="1" t="s">
-        <v>176</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O288" s="1"/>
+      <c r="P288" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="289">
       <c r="A289" s="2">
@@ -15661,25 +15754,25 @@
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
       <c r="H289" s="1" t="s">
-        <v>515</v>
+        <v>131</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>516</v>
+        <v>132</v>
       </c>
       <c r="J289" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K289" s="1" t="s">
-        <v>213</v>
+        <v>133</v>
       </c>
       <c r="L289" s="4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M289" s="4">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="N289" s="4">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="O289" s="1"/>
       <c r="P289" s="1"/>
@@ -15703,10 +15796,10 @@
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1" t="s">
-        <v>26</v>
+        <v>265</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>27</v>
+        <v>266</v>
       </c>
       <c r="J290" s="1" t="s">
         <v>20</v>
@@ -15715,7 +15808,7 @@
         <v>21</v>
       </c>
       <c r="L290" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M290" s="4">
         <v>0</v>
@@ -15745,10 +15838,10 @@
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>265</v>
+        <v>515</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>266</v>
+        <v>516</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>20</v>
@@ -15757,7 +15850,7 @@
         <v>21</v>
       </c>
       <c r="L291" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M291" s="4">
         <v>0</v>
@@ -15799,7 +15892,7 @@
         <v>21</v>
       </c>
       <c r="L292" s="4">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="M292" s="4">
         <v>0</v>
@@ -15841,7 +15934,7 @@
         <v>21</v>
       </c>
       <c r="L293" s="4">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="M293" s="4">
         <v>0</v>
@@ -15883,7 +15976,7 @@
         <v>21</v>
       </c>
       <c r="L294" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M294" s="4">
         <v>0</v>
@@ -15925,13 +16018,13 @@
         <v>21</v>
       </c>
       <c r="L295" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M295" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N295" s="4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="O295" s="1"/>
       <c r="P295" s="1"/>
@@ -17333,6 +17426,804 @@
       </c>
       <c r="O326" s="1"/>
       <c r="P326" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="327">
+      <c r="A327" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B327" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C327" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D327" s="2">
+        <v>2</v>
+      </c>
+      <c r="E327" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F327" s="1"/>
+      <c r="G327" s="1"/>
+      <c r="H327" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="I327" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="J327" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K327" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L327" s="4">
+        <v>4</v>
+      </c>
+      <c r="M327" s="4">
+        <v>0</v>
+      </c>
+      <c r="N327" s="4">
+        <v>0</v>
+      </c>
+      <c r="O327" s="1"/>
+      <c r="P327" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="328">
+      <c r="A328" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B328" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D328" s="2">
+        <v>2</v>
+      </c>
+      <c r="E328" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F328" s="1"/>
+      <c r="G328" s="1"/>
+      <c r="H328" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="I328" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="J328" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K328" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L328" s="4">
+        <v>1</v>
+      </c>
+      <c r="M328" s="4">
+        <v>0</v>
+      </c>
+      <c r="N328" s="4">
+        <v>0</v>
+      </c>
+      <c r="O328" s="1"/>
+      <c r="P328" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="329">
+      <c r="A329" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D329" s="2">
+        <v>2</v>
+      </c>
+      <c r="E329" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F329" s="1"/>
+      <c r="G329" s="1"/>
+      <c r="H329" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="I329" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="J329" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K329" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L329" s="4">
+        <v>8</v>
+      </c>
+      <c r="M329" s="4">
+        <v>0</v>
+      </c>
+      <c r="N329" s="4">
+        <v>0</v>
+      </c>
+      <c r="O329" s="1"/>
+      <c r="P329" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="330">
+      <c r="A330" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D330" s="2">
+        <v>2</v>
+      </c>
+      <c r="E330" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F330" s="1"/>
+      <c r="G330" s="1"/>
+      <c r="H330" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I330" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="J330" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K330" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L330" s="4">
+        <v>1</v>
+      </c>
+      <c r="M330" s="4">
+        <v>0</v>
+      </c>
+      <c r="N330" s="4">
+        <v>0</v>
+      </c>
+      <c r="O330" s="1"/>
+      <c r="P330" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="331">
+      <c r="A331" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D331" s="2">
+        <v>2</v>
+      </c>
+      <c r="E331" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F331" s="1"/>
+      <c r="G331" s="1"/>
+      <c r="H331" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I331" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="J331" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K331" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L331" s="4">
+        <v>2</v>
+      </c>
+      <c r="M331" s="4">
+        <v>0</v>
+      </c>
+      <c r="N331" s="4">
+        <v>0</v>
+      </c>
+      <c r="O331" s="1"/>
+      <c r="P331" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="332">
+      <c r="A332" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D332" s="2">
+        <v>2</v>
+      </c>
+      <c r="E332" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F332" s="1"/>
+      <c r="G332" s="1"/>
+      <c r="H332" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="I332" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="J332" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K332" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L332" s="4">
+        <v>2</v>
+      </c>
+      <c r="M332" s="4">
+        <v>0</v>
+      </c>
+      <c r="N332" s="4">
+        <v>0</v>
+      </c>
+      <c r="O332" s="1"/>
+      <c r="P332" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="333">
+      <c r="A333" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D333" s="2">
+        <v>2</v>
+      </c>
+      <c r="E333" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F333" s="1"/>
+      <c r="G333" s="1"/>
+      <c r="H333" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="J333" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K333" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L333" s="4">
+        <v>1</v>
+      </c>
+      <c r="M333" s="4">
+        <v>0</v>
+      </c>
+      <c r="N333" s="4">
+        <v>0</v>
+      </c>
+      <c r="O333" s="1"/>
+      <c r="P333" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="334">
+      <c r="A334" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D334" s="2">
+        <v>2</v>
+      </c>
+      <c r="E334" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
+      <c r="H334" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="I334" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="J334" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K334" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L334" s="4">
+        <v>1</v>
+      </c>
+      <c r="M334" s="4">
+        <v>0</v>
+      </c>
+      <c r="N334" s="4">
+        <v>0</v>
+      </c>
+      <c r="O334" s="1"/>
+      <c r="P334" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="335">
+      <c r="A335" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D335" s="2">
+        <v>2</v>
+      </c>
+      <c r="E335" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F335" s="1"/>
+      <c r="G335" s="1"/>
+      <c r="H335" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="I335" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="J335" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K335" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L335" s="4">
+        <v>2</v>
+      </c>
+      <c r="M335" s="4">
+        <v>0</v>
+      </c>
+      <c r="N335" s="4">
+        <v>0</v>
+      </c>
+      <c r="O335" s="1"/>
+      <c r="P335" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="336">
+      <c r="A336" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D336" s="2">
+        <v>2</v>
+      </c>
+      <c r="E336" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F336" s="1"/>
+      <c r="G336" s="1"/>
+      <c r="H336" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="I336" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="J336" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K336" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L336" s="4">
+        <v>2</v>
+      </c>
+      <c r="M336" s="4">
+        <v>0</v>
+      </c>
+      <c r="N336" s="4">
+        <v>0</v>
+      </c>
+      <c r="O336" s="1"/>
+      <c r="P336" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="337">
+      <c r="A337" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D337" s="2">
+        <v>2</v>
+      </c>
+      <c r="E337" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F337" s="1"/>
+      <c r="G337" s="1"/>
+      <c r="H337" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="I337" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="J337" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K337" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L337" s="4">
+        <v>1</v>
+      </c>
+      <c r="M337" s="4">
+        <v>0</v>
+      </c>
+      <c r="N337" s="4">
+        <v>0</v>
+      </c>
+      <c r="O337" s="1"/>
+      <c r="P337" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="338">
+      <c r="A338" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D338" s="2">
+        <v>2</v>
+      </c>
+      <c r="E338" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="J338" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K338" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L338" s="4">
+        <v>2</v>
+      </c>
+      <c r="M338" s="4">
+        <v>0</v>
+      </c>
+      <c r="N338" s="4">
+        <v>0</v>
+      </c>
+      <c r="O338" s="1"/>
+      <c r="P338" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="339">
+      <c r="A339" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D339" s="2">
+        <v>2</v>
+      </c>
+      <c r="E339" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F339" s="1"/>
+      <c r="G339" s="1"/>
+      <c r="H339" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="J339" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K339" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L339" s="4">
+        <v>4</v>
+      </c>
+      <c r="M339" s="4">
+        <v>0</v>
+      </c>
+      <c r="N339" s="4">
+        <v>0</v>
+      </c>
+      <c r="O339" s="1"/>
+      <c r="P339" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="340">
+      <c r="A340" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D340" s="2">
+        <v>2</v>
+      </c>
+      <c r="E340" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F340" s="1"/>
+      <c r="G340" s="1"/>
+      <c r="H340" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="J340" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K340" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L340" s="4">
+        <v>2</v>
+      </c>
+      <c r="M340" s="4">
+        <v>0</v>
+      </c>
+      <c r="N340" s="4">
+        <v>0</v>
+      </c>
+      <c r="O340" s="1"/>
+      <c r="P340" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="341">
+      <c r="A341" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D341" s="2">
+        <v>2</v>
+      </c>
+      <c r="E341" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F341" s="1"/>
+      <c r="G341" s="1"/>
+      <c r="H341" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="J341" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K341" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L341" s="4">
+        <v>1</v>
+      </c>
+      <c r="M341" s="4">
+        <v>0</v>
+      </c>
+      <c r="N341" s="4">
+        <v>0</v>
+      </c>
+      <c r="O341" s="1"/>
+      <c r="P341" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="342">
+      <c r="A342" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D342" s="2">
+        <v>2</v>
+      </c>
+      <c r="E342" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F342" s="1"/>
+      <c r="G342" s="1"/>
+      <c r="H342" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="J342" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K342" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L342" s="4">
+        <v>1</v>
+      </c>
+      <c r="M342" s="4">
+        <v>0</v>
+      </c>
+      <c r="N342" s="4">
+        <v>0</v>
+      </c>
+      <c r="O342" s="1"/>
+      <c r="P342" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="343">
+      <c r="A343" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D343" s="2">
+        <v>2</v>
+      </c>
+      <c r="E343" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F343" s="1"/>
+      <c r="G343" s="1"/>
+      <c r="H343" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="I343" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="J343" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K343" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L343" s="4">
+        <v>1</v>
+      </c>
+      <c r="M343" s="4">
+        <v>0</v>
+      </c>
+      <c r="N343" s="4">
+        <v>0</v>
+      </c>
+      <c r="O343" s="1"/>
+      <c r="P343" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="344">
+      <c r="A344" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D344" s="2">
+        <v>2</v>
+      </c>
+      <c r="E344" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F344" s="1"/>
+      <c r="G344" s="1"/>
+      <c r="H344" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="J344" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K344" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L344" s="4">
+        <v>35</v>
+      </c>
+      <c r="M344" s="4">
+        <v>0</v>
+      </c>
+      <c r="N344" s="4">
+        <v>0</v>
+      </c>
+      <c r="O344" s="1"/>
+      <c r="P344" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="345">
+      <c r="A345" s="2">
+        <v>2601</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D345" s="2">
+        <v>2</v>
+      </c>
+      <c r="E345" s="3">
+        <v>46097.4682502893</v>
+      </c>
+      <c r="F345" s="1"/>
+      <c r="G345" s="1"/>
+      <c r="H345" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="I345" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="J345" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K345" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L345" s="4">
+        <v>50</v>
+      </c>
+      <c r="M345" s="4">
+        <v>0</v>
+      </c>
+      <c r="N345" s="4">
+        <v>0</v>
+      </c>
+      <c r="O345" s="1"/>
+      <c r="P345" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1631,12 +1631,6 @@
     <t>SACO PLÁSTICO P/ LIXO - 60 L C/ 100 UN REFORÇADO</t>
   </si>
   <si>
-    <t>00000000000573</t>
-  </si>
-  <si>
-    <t>AGILIZE</t>
-  </si>
-  <si>
     <t>E.04.0405</t>
   </si>
   <si>
@@ -1680,6 +1674,12 @@
   </si>
   <si>
     <t>ROLO DE ESPUMA - 15 CM COM CABO</t>
+  </si>
+  <si>
+    <t>00000000008674</t>
+  </si>
+  <si>
+    <t>REI DAS TINTAS</t>
   </si>
   <si>
     <t>R.02.0128</t>
@@ -16340,7 +16340,7 @@
         <v>46097.447005</v>
       </c>
       <c r="F303" s="2">
-        <v>82650</v>
+        <v>82662</v>
       </c>
       <c r="G303" s="3">
         <v>46097</v>
@@ -16367,10 +16367,10 @@
         <v>18.12</v>
       </c>
       <c r="O303" s="1" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="P303" s="1" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="304">
@@ -16390,7 +16390,7 @@
         <v>46097.447005</v>
       </c>
       <c r="F304" s="2">
-        <v>82650</v>
+        <v>82662</v>
       </c>
       <c r="G304" s="3">
         <v>46097</v>
@@ -16411,16 +16411,16 @@
         <v>20</v>
       </c>
       <c r="M304" s="4">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="N304" s="4">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="P304" s="1" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="305">
@@ -16490,7 +16490,7 @@
         <v>46097.447005</v>
       </c>
       <c r="F306" s="2">
-        <v>82651</v>
+        <v>82650</v>
       </c>
       <c r="G306" s="3">
         <v>46097</v>
@@ -16517,10 +16517,10 @@
         <v>52.7</v>
       </c>
       <c r="O306" s="1" t="s">
-        <v>539</v>
+        <v>175</v>
       </c>
       <c r="P306" s="1" t="s">
-        <v>540</v>
+        <v>176</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="307">
@@ -16596,10 +16596,10 @@
         <v>46097</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
@@ -16661,10 +16661,10 @@
         <v>10</v>
       </c>
       <c r="M309" s="4">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="N309" s="4">
-        <v>27.5</v>
+        <v>35</v>
       </c>
       <c r="O309" s="1" t="s">
         <v>175</v>
@@ -16692,10 +16692,10 @@
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
       <c r="H310" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>20</v>
@@ -16734,10 +16734,10 @@
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
       <c r="H311" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>20</v>
@@ -16776,10 +16776,10 @@
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
       <c r="H312" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>20</v>
@@ -16818,10 +16818,10 @@
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
       <c r="H313" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>20</v>
@@ -16860,10 +16860,10 @@
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
       <c r="H314" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>20</v>
@@ -16902,16 +16902,16 @@
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
       <c r="H315" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="I315" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="J315" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K315" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="I315" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J315" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K315" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="L315" s="4">
         <v>10</v>
@@ -16944,10 +16944,10 @@
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
       <c r="H316" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>20</v>
@@ -17078,10 +17078,10 @@
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
       <c r="H319" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="J319" s="1" t="s">
         <v>20</v>
@@ -17118,7 +17118,7 @@
         <v>46097.4509044907</v>
       </c>
       <c r="F320" s="2">
-        <v>82655</v>
+        <v>82654</v>
       </c>
       <c r="G320" s="3">
         <v>46097</v>
@@ -17145,10 +17145,10 @@
         <v>52.7</v>
       </c>
       <c r="O320" s="1" t="s">
-        <v>539</v>
+        <v>175</v>
       </c>
       <c r="P320" s="1" t="s">
-        <v>540</v>
+        <v>176</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="321">
@@ -17168,7 +17168,7 @@
         <v>46097.4509044907</v>
       </c>
       <c r="F321" s="2">
-        <v>82654</v>
+        <v>82660</v>
       </c>
       <c r="G321" s="3">
         <v>46097</v>
@@ -17195,10 +17195,10 @@
         <v>180</v>
       </c>
       <c r="O321" s="1" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="P321" s="1" t="s">
-        <v>176</v>
+        <v>135</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="322">
@@ -17268,16 +17268,16 @@
         <v>46097.4509044907</v>
       </c>
       <c r="F323" s="2">
-        <v>82656</v>
+        <v>82661</v>
       </c>
       <c r="G323" s="3">
         <v>46097</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>199</v>
+        <v>552</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>200</v>
+        <v>553</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>20</v>
@@ -17289,16 +17289,16 @@
         <v>1</v>
       </c>
       <c r="M323" s="4">
-        <v>4.7</v>
+        <v>9.5</v>
       </c>
       <c r="N323" s="4">
-        <v>4.7</v>
+        <v>9.5</v>
       </c>
       <c r="O323" s="1" t="s">
-        <v>148</v>
+        <v>554</v>
       </c>
       <c r="P323" s="1" t="s">
-        <v>149</v>
+        <v>555</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="324">
@@ -17317,13 +17317,17 @@
       <c r="E324" s="3">
         <v>46097.4509044907</v>
       </c>
-      <c r="F324" s="1"/>
-      <c r="G324" s="1"/>
+      <c r="F324" s="2">
+        <v>82654</v>
+      </c>
+      <c r="G324" s="3">
+        <v>46097</v>
+      </c>
       <c r="H324" s="1" t="s">
-        <v>554</v>
+        <v>199</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>555</v>
+        <v>200</v>
       </c>
       <c r="J324" s="1" t="s">
         <v>20</v>
@@ -17335,13 +17339,17 @@
         <v>1</v>
       </c>
       <c r="M324" s="4">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N324" s="4">
-        <v>0</v>
-      </c>
-      <c r="O324" s="1"/>
-      <c r="P324" s="1"/>
+        <v>4.7</v>
+      </c>
+      <c r="O324" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="P324" s="1" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="325">
       <c r="A325" s="2">
@@ -17359,8 +17367,12 @@
       <c r="E325" s="3">
         <v>46097.4509044907</v>
       </c>
-      <c r="F325" s="1"/>
-      <c r="G325" s="1"/>
+      <c r="F325" s="2">
+        <v>82661</v>
+      </c>
+      <c r="G325" s="3">
+        <v>46097</v>
+      </c>
       <c r="H325" s="1" t="s">
         <v>556</v>
       </c>
@@ -17377,13 +17389,17 @@
         <v>1</v>
       </c>
       <c r="M325" s="4">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="N325" s="4">
-        <v>0</v>
-      </c>
-      <c r="O325" s="1"/>
-      <c r="P325" s="1"/>
+        <v>140</v>
+      </c>
+      <c r="O325" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="P325" s="1" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="326">
       <c r="A326" s="2">
@@ -17401,8 +17417,12 @@
       <c r="E326" s="3">
         <v>46097.4509044907</v>
       </c>
-      <c r="F326" s="1"/>
-      <c r="G326" s="1"/>
+      <c r="F326" s="2">
+        <v>82660</v>
+      </c>
+      <c r="G326" s="3">
+        <v>46097</v>
+      </c>
       <c r="H326" s="1" t="s">
         <v>203</v>
       </c>
@@ -17416,16 +17436,20 @@
         <v>114</v>
       </c>
       <c r="L326" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M326" s="4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N326" s="4">
-        <v>0</v>
-      </c>
-      <c r="O326" s="1"/>
-      <c r="P326" s="1"/>
+        <v>156</v>
+      </c>
+      <c r="O326" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="P326" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="327">
       <c r="A327" s="2">

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="607">
   <si>
     <t>EMPRD</t>
   </si>
@@ -920,63 +920,69 @@
     <t>GL</t>
   </si>
   <si>
+    <t>E.03.0521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUARDA CORPO  PARA ANDAIME TUBULAR</t>
+  </si>
+  <si>
+    <t>MES</t>
+  </si>
+  <si>
+    <t>00000000007636</t>
+  </si>
+  <si>
+    <t>ABRIL LOC</t>
+  </si>
+  <si>
     <t>E.03.0102</t>
   </si>
   <si>
     <t>MÁSCARA DESCARTÁVEL RESPIRADOR COM VÁLVULA CLASSE PFF2</t>
   </si>
   <si>
+    <t>E.03.0522</t>
+  </si>
+  <si>
+    <t>ESCADA PARA ANDAIME TUBULAR</t>
+  </si>
+  <si>
+    <t>E.03.0523</t>
+  </si>
+  <si>
+    <t>PISO METÁLICO PARA ANDAIME</t>
+  </si>
+  <si>
     <t>E.03.0119</t>
   </si>
   <si>
     <t>ÓCULOS DE SEGURANÇA INCOLOR AGUIA</t>
   </si>
   <si>
+    <t>F.02.0003</t>
+  </si>
+  <si>
+    <t>ANDAIME TUBULAR 1 X 1 -</t>
+  </si>
+  <si>
+    <t>F.02.0009</t>
+  </si>
+  <si>
+    <t>RODIZIO PARA ANDAIME TUBULAR</t>
+  </si>
+  <si>
+    <t>F.05.0011</t>
+  </si>
+  <si>
+    <t>DIAGONAL PARA ANDAIME</t>
+  </si>
+  <si>
     <t>E.01.0056</t>
   </si>
   <si>
     <t>FILTRO PARA ASPIRADOR DE PÓ</t>
   </si>
   <si>
-    <t>E.03.0521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUARDA CORPO  PARA ANDAIME TUBULAR</t>
-  </si>
-  <si>
-    <t>MES</t>
-  </si>
-  <si>
-    <t>E.03.0522</t>
-  </si>
-  <si>
-    <t>ESCADA PARA ANDAIME TUBULAR</t>
-  </si>
-  <si>
-    <t>E.03.0523</t>
-  </si>
-  <si>
-    <t>PISO METÁLICO PARA ANDAIME</t>
-  </si>
-  <si>
-    <t>F.02.0003</t>
-  </si>
-  <si>
-    <t>ANDAIME TUBULAR 1 X 1 -</t>
-  </si>
-  <si>
-    <t>F.02.0009</t>
-  </si>
-  <si>
-    <t>RODIZIO PARA ANDAIME TUBULAR</t>
-  </si>
-  <si>
-    <t>F.05.0011</t>
-  </si>
-  <si>
-    <t>DIAGONAL PARA ANDAIME</t>
-  </si>
-  <si>
     <t>J.10.0005</t>
   </si>
   <si>
@@ -1631,24 +1637,30 @@
     <t>SACO PLÁSTICO P/ LIXO - 60 L C/ 100 UN REFORÇADO</t>
   </si>
   <si>
+    <t>E.03.0254</t>
+  </si>
+  <si>
+    <t>CAPA DE CHUVA TREVISA COM FORRO MANGA COMPRIDA GG</t>
+  </si>
+  <si>
     <t>E.04.0405</t>
   </si>
   <si>
     <t>ESTILETE AUTOMÁTICO EMBORRACHADO 8 LÂMINAS - 18MM</t>
   </si>
   <si>
-    <t>E.03.0254</t>
-  </si>
-  <si>
-    <t>CAPA DE CHUVA TREVISA COM FORRO MANGA COMPRIDA GG</t>
-  </si>
-  <si>
     <t>K.01.0228</t>
   </si>
   <si>
     <t>TOMADA LUMITEK</t>
   </si>
   <si>
+    <t>00000000000587</t>
+  </si>
+  <si>
+    <t>PC 2000</t>
+  </si>
+  <si>
     <t>W.06.2001</t>
   </si>
   <si>
@@ -1664,12 +1676,24 @@
     <t>PRENDEDOR DE PORTA</t>
   </si>
   <si>
+    <t>00000000008792</t>
+  </si>
+  <si>
+    <t>KOHLER</t>
+  </si>
+  <si>
     <t>P2.01.0001</t>
   </si>
   <si>
     <t>CANTONEIRA L METÁLICA C/ PINTURA ELETROSTÁTICA 2 X 2 CM</t>
   </si>
   <si>
+    <t>00000000007677</t>
+  </si>
+  <si>
+    <t>CANTO METAL</t>
+  </si>
+  <si>
     <t>R.02.0061</t>
   </si>
   <si>
@@ -1803,6 +1827,12 @@
   </si>
   <si>
     <t>MANGUEIRA</t>
+  </si>
+  <si>
+    <t>J.02.0813</t>
+  </si>
+  <si>
+    <t>ARGAMASSA ACIII</t>
   </si>
 </sst>
 </file>
@@ -2101,7 +2131,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P345"/>
+  <dimension ref="A1:P348"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -9312,10 +9342,10 @@
         <v>46093.4920058565</v>
       </c>
       <c r="F145" s="2">
-        <v>82581</v>
+        <v>82672</v>
       </c>
       <c r="G145" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>302</v>
@@ -9327,22 +9357,22 @@
         <v>20</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="L145" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="M145" s="4">
-        <v>1.5</v>
+        <v>150</v>
       </c>
       <c r="N145" s="4">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>28</v>
+        <v>305</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="146">
@@ -9368,10 +9398,10 @@
         <v>46093</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J146" s="1" t="s">
         <v>20</v>
@@ -9380,13 +9410,13 @@
         <v>21</v>
       </c>
       <c r="L146" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M146" s="4">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="N146" s="4">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="O146" s="1" t="s">
         <v>28</v>
@@ -9411,31 +9441,39 @@
       <c r="E147" s="3">
         <v>46093.4920058565</v>
       </c>
-      <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
+      <c r="F147" s="2">
+        <v>82672</v>
+      </c>
+      <c r="G147" s="3">
+        <v>46097</v>
+      </c>
       <c r="H147" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K147" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="L147" s="4">
+        <v>2</v>
+      </c>
+      <c r="M147" s="4">
+        <v>30</v>
+      </c>
+      <c r="N147" s="4">
+        <v>60</v>
+      </c>
+      <c r="O147" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P147" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="I147" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J147" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K147" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L147" s="4">
-        <v>1</v>
-      </c>
-      <c r="M147" s="4">
-        <v>0</v>
-      </c>
-      <c r="N147" s="4">
-        <v>0</v>
-      </c>
-      <c r="O147" s="1"/>
-      <c r="P147" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="148">
       <c r="A148" s="2">
@@ -9453,31 +9491,39 @@
       <c r="E148" s="3">
         <v>46093.4920058565</v>
       </c>
-      <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
+      <c r="F148" s="2">
+        <v>82672</v>
+      </c>
+      <c r="G148" s="3">
+        <v>46097</v>
+      </c>
       <c r="H148" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J148" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K148" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="L148" s="4">
+        <v>2</v>
+      </c>
+      <c r="M148" s="4">
+        <v>90</v>
+      </c>
+      <c r="N148" s="4">
+        <v>180</v>
+      </c>
+      <c r="O148" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P148" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="I148" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J148" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K148" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L148" s="4">
-        <v>1</v>
-      </c>
-      <c r="M148" s="4">
-        <v>0</v>
-      </c>
-      <c r="N148" s="4">
-        <v>0</v>
-      </c>
-      <c r="O148" s="1"/>
-      <c r="P148" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="149">
       <c r="A149" s="2">
@@ -9495,13 +9541,17 @@
       <c r="E149" s="3">
         <v>46093.4920058565</v>
       </c>
-      <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
+      <c r="F149" s="2">
+        <v>82581</v>
+      </c>
+      <c r="G149" s="3">
+        <v>46093</v>
+      </c>
       <c r="H149" s="1" t="s">
-        <v>71</v>
+        <v>313</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>72</v>
+        <v>314</v>
       </c>
       <c r="J149" s="1" t="s">
         <v>20</v>
@@ -9513,13 +9563,17 @@
         <v>20</v>
       </c>
       <c r="M149" s="4">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N149" s="4">
-        <v>0</v>
-      </c>
-      <c r="O149" s="1"/>
-      <c r="P149" s="1"/>
+        <v>84</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P149" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="150">
       <c r="A150" s="2">
@@ -9537,31 +9591,39 @@
       <c r="E150" s="3">
         <v>46093.4920058565</v>
       </c>
-      <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
+      <c r="F150" s="2">
+        <v>82672</v>
+      </c>
+      <c r="G150" s="3">
+        <v>46097</v>
+      </c>
       <c r="H150" s="1" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="L150" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M150" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N150" s="4">
-        <v>0</v>
-      </c>
-      <c r="O150" s="1"/>
-      <c r="P150" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="O150" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P150" s="1" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="151">
       <c r="A151" s="2">
@@ -9579,31 +9641,39 @@
       <c r="E151" s="3">
         <v>46093.4920058565</v>
       </c>
-      <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
+      <c r="F151" s="2">
+        <v>82672</v>
+      </c>
+      <c r="G151" s="3">
+        <v>46097</v>
+      </c>
       <c r="H151" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="J151" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="L151" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M151" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N151" s="4">
-        <v>0</v>
-      </c>
-      <c r="O151" s="1"/>
-      <c r="P151" s="1"/>
+        <v>200</v>
+      </c>
+      <c r="O151" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P151" s="1" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="152">
       <c r="A152" s="2">
@@ -9621,31 +9691,39 @@
       <c r="E152" s="3">
         <v>46093.4920058565</v>
       </c>
-      <c r="F152" s="1"/>
-      <c r="G152" s="1"/>
+      <c r="F152" s="2">
+        <v>82672</v>
+      </c>
+      <c r="G152" s="3">
+        <v>46097</v>
+      </c>
       <c r="H152" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="L152" s="4">
+        <v>2</v>
+      </c>
+      <c r="M152" s="4">
         <v>1</v>
       </c>
-      <c r="M152" s="4">
-        <v>0</v>
-      </c>
       <c r="N152" s="4">
-        <v>0</v>
-      </c>
-      <c r="O152" s="1"/>
-      <c r="P152" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P152" s="1" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="153">
       <c r="A153" s="2">
@@ -9666,16 +9744,16 @@
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
       <c r="H153" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="L153" s="4">
         <v>1</v>
@@ -9708,16 +9786,16 @@
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
       <c r="H154" s="1" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J154" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="L154" s="4">
         <v>1</v>
@@ -9750,19 +9828,19 @@
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
       <c r="H155" s="1" t="s">
-        <v>319</v>
+        <v>71</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>320</v>
+        <v>72</v>
       </c>
       <c r="J155" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>310</v>
+        <v>21</v>
       </c>
       <c r="L155" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M155" s="4">
         <v>0</v>
@@ -9792,10 +9870,10 @@
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J156" s="1" t="s">
         <v>20</v>
@@ -9880,10 +9958,10 @@
         <v>46093</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J158" s="1" t="s">
         <v>20</v>
@@ -9901,10 +9979,10 @@
         <v>721</v>
       </c>
       <c r="O158" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P158" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="159">
@@ -9930,10 +10008,10 @@
         <v>46093</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J159" s="1" t="s">
         <v>20</v>
@@ -9951,10 +10029,10 @@
         <v>45.52</v>
       </c>
       <c r="O159" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P159" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="160">
@@ -9980,10 +10058,10 @@
         <v>46093</v>
       </c>
       <c r="H160" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J160" s="1" t="s">
         <v>20</v>
@@ -10001,10 +10079,10 @@
         <v>1060</v>
       </c>
       <c r="O160" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P160" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="161">
@@ -10030,10 +10108,10 @@
         <v>46093</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J161" s="1" t="s">
         <v>20</v>
@@ -10051,10 +10129,10 @@
         <v>109</v>
       </c>
       <c r="O161" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P161" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="162">
@@ -10080,10 +10158,10 @@
         <v>46093</v>
       </c>
       <c r="H162" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J162" s="1" t="s">
         <v>20</v>
@@ -10101,10 +10179,10 @@
         <v>40</v>
       </c>
       <c r="O162" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P162" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="163">
@@ -10430,10 +10508,10 @@
         <v>46093</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J169" s="1" t="s">
         <v>20</v>
@@ -10480,10 +10558,10 @@
         <v>46093</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J170" s="1" t="s">
         <v>20</v>
@@ -10630,10 +10708,10 @@
         <v>46093</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J173" s="1" t="s">
         <v>20</v>
@@ -10680,10 +10758,10 @@
         <v>46093</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J174" s="1" t="s">
         <v>20</v>
@@ -10730,10 +10808,10 @@
         <v>46093</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J175" s="1" t="s">
         <v>20</v>
@@ -10780,10 +10858,10 @@
         <v>46093</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J176" s="1" t="s">
         <v>20</v>
@@ -10801,10 +10879,10 @@
         <v>3350</v>
       </c>
       <c r="O176" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P176" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="177">
@@ -10830,10 +10908,10 @@
         <v>46093</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J177" s="1" t="s">
         <v>20</v>
@@ -10851,10 +10929,10 @@
         <v>20300</v>
       </c>
       <c r="O177" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P177" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="178">
@@ -10930,10 +11008,10 @@
         <v>46093</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J179" s="1" t="s">
         <v>20</v>
@@ -10980,10 +11058,10 @@
         <v>46093</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J180" s="1" t="s">
         <v>20</v>
@@ -11030,10 +11108,10 @@
         <v>46093</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J181" s="1" t="s">
         <v>20</v>
@@ -11051,10 +11129,10 @@
         <v>3300</v>
       </c>
       <c r="O181" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P181" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="182">
@@ -11130,10 +11208,10 @@
         <v>46093</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J183" s="1" t="s">
         <v>20</v>
@@ -11230,10 +11308,10 @@
         <v>46093</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J185" s="1" t="s">
         <v>20</v>
@@ -11251,10 +11329,10 @@
         <v>320</v>
       </c>
       <c r="O185" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P185" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="186">
@@ -11301,10 +11379,10 @@
         <v>570</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P186" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="187">
@@ -11426,10 +11504,10 @@
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
       <c r="H189" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J189" s="1" t="s">
         <v>20</v>
@@ -11468,10 +11546,10 @@
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
       <c r="H190" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>20</v>
@@ -11510,10 +11588,10 @@
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
       <c r="H191" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J191" s="1" t="s">
         <v>20</v>
@@ -11552,10 +11630,10 @@
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
       <c r="H192" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J192" s="1" t="s">
         <v>20</v>
@@ -11594,10 +11672,10 @@
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
       <c r="H193" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J193" s="1" t="s">
         <v>20</v>
@@ -11636,10 +11714,10 @@
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
       <c r="H194" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J194" s="1" t="s">
         <v>20</v>
@@ -11678,10 +11756,10 @@
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
       <c r="H195" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>20</v>
@@ -11720,10 +11798,10 @@
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
       <c r="H196" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J196" s="1" t="s">
         <v>20</v>
@@ -11762,10 +11840,10 @@
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
       <c r="H197" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J197" s="1" t="s">
         <v>20</v>
@@ -11804,10 +11882,10 @@
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
       <c r="H198" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J198" s="1" t="s">
         <v>20</v>
@@ -11846,10 +11924,10 @@
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
       <c r="H199" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J199" s="1" t="s">
         <v>20</v>
@@ -11888,10 +11966,10 @@
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
       <c r="H200" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J200" s="1" t="s">
         <v>20</v>
@@ -11930,10 +12008,10 @@
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
       <c r="H201" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J201" s="1" t="s">
         <v>20</v>
@@ -11972,10 +12050,10 @@
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
       <c r="H202" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J202" s="1" t="s">
         <v>20</v>
@@ -12014,13 +12092,13 @@
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
       <c r="H203" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J203" s="1" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="K203" s="1" t="s">
         <v>21</v>
@@ -12056,10 +12134,10 @@
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
       <c r="H204" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J204" s="1" t="s">
         <v>20</v>
@@ -12098,10 +12176,10 @@
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
       <c r="H205" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J205" s="1" t="s">
         <v>20</v>
@@ -12140,10 +12218,10 @@
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
       <c r="H206" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J206" s="1" t="s">
         <v>20</v>
@@ -12182,10 +12260,10 @@
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
       <c r="H207" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I207" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J207" s="1" t="s">
         <v>20</v>
@@ -12224,10 +12302,10 @@
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
       <c r="H208" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I208" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J208" s="1" t="s">
         <v>20</v>
@@ -12266,10 +12344,10 @@
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
       <c r="H209" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>20</v>
@@ -12308,10 +12386,10 @@
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
       <c r="H210" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J210" s="1" t="s">
         <v>20</v>
@@ -12350,10 +12428,10 @@
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
       <c r="H211" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I211" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J211" s="1" t="s">
         <v>20</v>
@@ -12392,10 +12470,10 @@
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
       <c r="H212" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>20</v>
@@ -12434,10 +12512,10 @@
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
       <c r="H213" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>20</v>
@@ -12476,10 +12554,10 @@
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
       <c r="H214" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I214" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J214" s="1" t="s">
         <v>20</v>
@@ -12518,10 +12596,10 @@
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
       <c r="H215" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>20</v>
@@ -12560,10 +12638,10 @@
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
       <c r="H216" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>20</v>
@@ -12602,10 +12680,10 @@
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
       <c r="H217" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>20</v>
@@ -12644,10 +12722,10 @@
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
       <c r="H218" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>20</v>
@@ -12686,10 +12764,10 @@
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
       <c r="H219" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J219" s="1" t="s">
         <v>20</v>
@@ -12728,10 +12806,10 @@
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
       <c r="H220" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>20</v>
@@ -12770,10 +12848,10 @@
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
       <c r="H221" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>20</v>
@@ -12812,10 +12890,10 @@
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
       <c r="H222" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>20</v>
@@ -12854,10 +12932,10 @@
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
       <c r="H223" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>20</v>
@@ -12938,10 +13016,10 @@
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
       <c r="H225" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>20</v>
@@ -12980,10 +13058,10 @@
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
       <c r="H226" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J226" s="1" t="s">
         <v>20</v>
@@ -13022,10 +13100,10 @@
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
       <c r="H227" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J227" s="1" t="s">
         <v>20</v>
@@ -13064,10 +13142,10 @@
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
       <c r="H228" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>20</v>
@@ -13106,10 +13184,10 @@
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
       <c r="H229" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>20</v>
@@ -13148,10 +13226,10 @@
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
       <c r="H230" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>20</v>
@@ -13190,10 +13268,10 @@
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
       <c r="H231" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J231" s="1" t="s">
         <v>20</v>
@@ -13232,10 +13310,10 @@
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
       <c r="H232" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>20</v>
@@ -13274,10 +13352,10 @@
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
       <c r="H233" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J233" s="1" t="s">
         <v>20</v>
@@ -13316,10 +13394,10 @@
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
       <c r="H234" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>20</v>
@@ -13358,10 +13436,10 @@
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
       <c r="H235" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>20</v>
@@ -13400,10 +13478,10 @@
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
       <c r="H236" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J236" s="1" t="s">
         <v>20</v>
@@ -13442,10 +13520,10 @@
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
       <c r="H237" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>20</v>
@@ -13484,10 +13562,10 @@
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
       <c r="H238" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>20</v>
@@ -13526,10 +13604,10 @@
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
       <c r="H239" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J239" s="1" t="s">
         <v>20</v>
@@ -13568,10 +13646,10 @@
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
       <c r="H240" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>20</v>
@@ -13610,10 +13688,10 @@
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
       <c r="H241" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>20</v>
@@ -13652,10 +13730,10 @@
       <c r="F242" s="1"/>
       <c r="G242" s="1"/>
       <c r="H242" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>20</v>
@@ -13694,10 +13772,10 @@
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
       <c r="H243" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J243" s="1" t="s">
         <v>20</v>
@@ -13736,10 +13814,10 @@
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
       <c r="H244" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>20</v>
@@ -13778,10 +13856,10 @@
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
       <c r="H245" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>20</v>
@@ -13820,10 +13898,10 @@
       <c r="F246" s="1"/>
       <c r="G246" s="1"/>
       <c r="H246" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>20</v>
@@ -13862,10 +13940,10 @@
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
       <c r="H247" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J247" s="1" t="s">
         <v>20</v>
@@ -13904,10 +13982,10 @@
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
       <c r="H248" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="J248" s="1" t="s">
         <v>20</v>
@@ -13946,10 +14024,10 @@
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
       <c r="H249" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>20</v>
@@ -13988,10 +14066,10 @@
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
       <c r="H250" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J250" s="1" t="s">
         <v>20</v>
@@ -14030,10 +14108,10 @@
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
       <c r="H251" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>20</v>
@@ -14072,10 +14150,10 @@
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
       <c r="H252" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>20</v>
@@ -14114,10 +14192,10 @@
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
       <c r="H253" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>20</v>
@@ -14156,10 +14234,10 @@
       <c r="F254" s="1"/>
       <c r="G254" s="1"/>
       <c r="H254" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>20</v>
@@ -14198,10 +14276,10 @@
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
       <c r="H255" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>20</v>
@@ -14240,10 +14318,10 @@
       <c r="F256" s="1"/>
       <c r="G256" s="1"/>
       <c r="H256" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>20</v>
@@ -14282,10 +14360,10 @@
       <c r="F257" s="1"/>
       <c r="G257" s="1"/>
       <c r="H257" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="J257" s="1" t="s">
         <v>20</v>
@@ -14324,10 +14402,10 @@
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
       <c r="H258" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>20</v>
@@ -14366,10 +14444,10 @@
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
       <c r="H259" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J259" s="1" t="s">
         <v>20</v>
@@ -14408,10 +14486,10 @@
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
       <c r="H260" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J260" s="1" t="s">
         <v>20</v>
@@ -14450,10 +14528,10 @@
       <c r="F261" s="1"/>
       <c r="G261" s="1"/>
       <c r="H261" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>20</v>
@@ -14492,10 +14570,10 @@
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
       <c r="H262" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>20</v>
@@ -14534,10 +14612,10 @@
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
       <c r="H263" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>20</v>
@@ -14576,10 +14654,10 @@
       <c r="F264" s="1"/>
       <c r="G264" s="1"/>
       <c r="H264" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>20</v>
@@ -14618,10 +14696,10 @@
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
       <c r="H265" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>20</v>
@@ -14714,10 +14792,10 @@
         <v>46094</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>20</v>
@@ -14814,10 +14892,10 @@
         <v>46094</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>20</v>
@@ -14864,10 +14942,10 @@
         <v>46094</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>20</v>
@@ -15060,10 +15138,10 @@
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
       <c r="H274" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>20</v>
@@ -15102,10 +15180,10 @@
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
       <c r="H275" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>20</v>
@@ -15144,10 +15222,10 @@
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
       <c r="H276" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>20</v>
@@ -15186,10 +15264,10 @@
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
       <c r="H277" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>20</v>
@@ -15282,10 +15360,10 @@
         <v>46094</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J279" s="1" t="s">
         <v>20</v>
@@ -15382,10 +15460,10 @@
         <v>46094</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>20</v>
@@ -15670,10 +15748,10 @@
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
       <c r="H287" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>20</v>
@@ -15838,10 +15916,10 @@
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>20</v>
@@ -15880,10 +15958,10 @@
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
       <c r="H292" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J292" s="1" t="s">
         <v>20</v>
@@ -15922,10 +16000,10 @@
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
       <c r="H293" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J293" s="1" t="s">
         <v>20</v>
@@ -15964,10 +16042,10 @@
       <c r="F294" s="1"/>
       <c r="G294" s="1"/>
       <c r="H294" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="I294" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J294" s="1" t="s">
         <v>20</v>
@@ -16006,10 +16084,10 @@
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
       <c r="H295" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J295" s="1" t="s">
         <v>20</v>
@@ -16048,10 +16126,10 @@
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
       <c r="H296" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J296" s="1" t="s">
         <v>20</v>
@@ -16090,10 +16168,10 @@
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
       <c r="H297" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>20</v>
@@ -16132,10 +16210,10 @@
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
       <c r="H298" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>20</v>
@@ -16174,10 +16252,10 @@
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
       <c r="H299" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>20</v>
@@ -16216,10 +16294,10 @@
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
       <c r="H300" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>20</v>
@@ -16258,10 +16336,10 @@
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
       <c r="H301" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>20</v>
@@ -16446,10 +16524,10 @@
         <v>46097</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>20</v>
@@ -16590,16 +16668,16 @@
         <v>46097.447005</v>
       </c>
       <c r="F308" s="2">
-        <v>82650</v>
+        <v>82669</v>
       </c>
       <c r="G308" s="3">
         <v>46097</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
@@ -16608,19 +16686,19 @@
         <v>21</v>
       </c>
       <c r="L308" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M308" s="4">
-        <v>17.3</v>
+        <v>44.9</v>
       </c>
       <c r="N308" s="4">
-        <v>17.3</v>
+        <v>449</v>
       </c>
       <c r="O308" s="1" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="P308" s="1" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="309">
@@ -16646,10 +16724,10 @@
         <v>46097</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>269</v>
+        <v>543</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>270</v>
+        <v>544</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>20</v>
@@ -16658,13 +16736,13 @@
         <v>21</v>
       </c>
       <c r="L309" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M309" s="4">
-        <v>3.5</v>
+        <v>17.3</v>
       </c>
       <c r="N309" s="4">
-        <v>35</v>
+        <v>17.3</v>
       </c>
       <c r="O309" s="1" t="s">
         <v>175</v>
@@ -16689,13 +16767,17 @@
       <c r="E310" s="3">
         <v>46097.447005</v>
       </c>
-      <c r="F310" s="1"/>
-      <c r="G310" s="1"/>
+      <c r="F310" s="2">
+        <v>82650</v>
+      </c>
+      <c r="G310" s="3">
+        <v>46097</v>
+      </c>
       <c r="H310" s="1" t="s">
-        <v>541</v>
+        <v>269</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>542</v>
+        <v>270</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>20</v>
@@ -16707,13 +16789,17 @@
         <v>10</v>
       </c>
       <c r="M310" s="4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N310" s="4">
-        <v>0</v>
-      </c>
-      <c r="O310" s="1"/>
-      <c r="P310" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="O310" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="P310" s="1" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="311">
       <c r="A311" s="2">
@@ -16731,13 +16817,17 @@
       <c r="E311" s="3">
         <v>46097.447005</v>
       </c>
-      <c r="F311" s="1"/>
-      <c r="G311" s="1"/>
+      <c r="F311" s="2">
+        <v>82663</v>
+      </c>
+      <c r="G311" s="3">
+        <v>46097</v>
+      </c>
       <c r="H311" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>20</v>
@@ -16749,13 +16839,17 @@
         <v>3</v>
       </c>
       <c r="M311" s="4">
-        <v>0</v>
+        <v>39.9</v>
       </c>
       <c r="N311" s="4">
-        <v>0</v>
-      </c>
-      <c r="O311" s="1"/>
-      <c r="P311" s="1"/>
+        <v>119.7</v>
+      </c>
+      <c r="O311" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="P311" s="1" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="312">
       <c r="A312" s="2">
@@ -16773,13 +16867,17 @@
       <c r="E312" s="3">
         <v>46097.447005</v>
       </c>
-      <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
+      <c r="F312" s="2">
+        <v>82663</v>
+      </c>
+      <c r="G312" s="3">
+        <v>46097</v>
+      </c>
       <c r="H312" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>20</v>
@@ -16791,13 +16889,17 @@
         <v>3</v>
       </c>
       <c r="M312" s="4">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="N312" s="4">
-        <v>0</v>
-      </c>
-      <c r="O312" s="1"/>
-      <c r="P312" s="1"/>
+        <v>89.7</v>
+      </c>
+      <c r="O312" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="P312" s="1" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="313">
       <c r="A313" s="2">
@@ -16815,13 +16917,17 @@
       <c r="E313" s="3">
         <v>46097.447005</v>
       </c>
-      <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
+      <c r="F313" s="2">
+        <v>82663</v>
+      </c>
+      <c r="G313" s="3">
+        <v>46097</v>
+      </c>
       <c r="H313" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>20</v>
@@ -16833,13 +16939,17 @@
         <v>3</v>
       </c>
       <c r="M313" s="4">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="N313" s="4">
-        <v>0</v>
-      </c>
-      <c r="O313" s="1"/>
-      <c r="P313" s="1"/>
+        <v>89.7</v>
+      </c>
+      <c r="O313" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="P313" s="1" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="314">
       <c r="A314" s="2">
@@ -16857,13 +16967,17 @@
       <c r="E314" s="3">
         <v>46097.447005</v>
       </c>
-      <c r="F314" s="1"/>
-      <c r="G314" s="1"/>
+      <c r="F314" s="2">
+        <v>82663</v>
+      </c>
+      <c r="G314" s="3">
+        <v>46097</v>
+      </c>
       <c r="H314" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>20</v>
@@ -16875,13 +16989,17 @@
         <v>7</v>
       </c>
       <c r="M314" s="4">
-        <v>0</v>
+        <v>39.9</v>
       </c>
       <c r="N314" s="4">
-        <v>0</v>
-      </c>
-      <c r="O314" s="1"/>
-      <c r="P314" s="1"/>
+        <v>279.3</v>
+      </c>
+      <c r="O314" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="P314" s="1" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="315">
       <c r="A315" s="2">
@@ -16899,31 +17017,39 @@
       <c r="E315" s="3">
         <v>46097.447005</v>
       </c>
-      <c r="F315" s="1"/>
-      <c r="G315" s="1"/>
+      <c r="F315" s="2">
+        <v>82652</v>
+      </c>
+      <c r="G315" s="3">
+        <v>46097</v>
+      </c>
       <c r="H315" s="1" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K315" s="1" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="L315" s="4">
         <v>10</v>
       </c>
       <c r="M315" s="4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N315" s="4">
-        <v>0</v>
-      </c>
-      <c r="O315" s="1"/>
-      <c r="P315" s="1"/>
+        <v>170</v>
+      </c>
+      <c r="O315" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="P315" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="316">
       <c r="A316" s="2">
@@ -16944,10 +17070,10 @@
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
       <c r="H316" s="1" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>20</v>
@@ -17033,13 +17159,17 @@
       <c r="E318" s="3">
         <v>46097.4499278356</v>
       </c>
-      <c r="F318" s="1"/>
-      <c r="G318" s="1"/>
+      <c r="F318" s="2">
+        <v>82668</v>
+      </c>
+      <c r="G318" s="3">
+        <v>46097</v>
+      </c>
       <c r="H318" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>20</v>
@@ -17051,13 +17181,17 @@
         <v>2</v>
       </c>
       <c r="M318" s="4">
-        <v>0</v>
+        <v>724.04</v>
       </c>
       <c r="N318" s="4">
-        <v>0</v>
-      </c>
-      <c r="O318" s="1"/>
-      <c r="P318" s="1"/>
+        <v>1448.08</v>
+      </c>
+      <c r="O318" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="P318" s="1" t="s">
+        <v>555</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="319">
       <c r="A319" s="2">
@@ -17075,13 +17209,17 @@
       <c r="E319" s="3">
         <v>46097.4499278356</v>
       </c>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
+      <c r="F319" s="2">
+        <v>82665</v>
+      </c>
+      <c r="G319" s="3">
+        <v>46097</v>
+      </c>
       <c r="H319" s="1" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="J319" s="1" t="s">
         <v>20</v>
@@ -17090,16 +17228,20 @@
         <v>21</v>
       </c>
       <c r="L319" s="4">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="M319" s="4">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="N319" s="4">
-        <v>0</v>
-      </c>
-      <c r="O319" s="1"/>
-      <c r="P319" s="1"/>
+        <v>1020.6</v>
+      </c>
+      <c r="O319" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="P319" s="1" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="320">
       <c r="A320" s="2">
@@ -17274,10 +17416,10 @@
         <v>46097</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>20</v>
@@ -17295,10 +17437,10 @@
         <v>9.5</v>
       </c>
       <c r="O323" s="1" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="P323" s="1" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="324">
@@ -17374,10 +17516,10 @@
         <v>46097</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="J325" s="1" t="s">
         <v>20</v>
@@ -17395,10 +17537,10 @@
         <v>140</v>
       </c>
       <c r="O325" s="1" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="P325" s="1" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="326">
@@ -17456,7 +17598,7 @@
         <v>2601</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>17</v>
@@ -17470,10 +17612,10 @@
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
       <c r="H327" s="1" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>20</v>
@@ -17498,7 +17640,7 @@
         <v>2601</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>17</v>
@@ -17512,10 +17654,10 @@
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
       <c r="H328" s="1" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="J328" s="1" t="s">
         <v>20</v>
@@ -17540,7 +17682,7 @@
         <v>2601</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>17</v>
@@ -17554,10 +17696,10 @@
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
       <c r="H329" s="1" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>20</v>
@@ -17582,7 +17724,7 @@
         <v>2601</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>17</v>
@@ -17596,10 +17738,10 @@
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
       <c r="H330" s="1" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>20</v>
@@ -17611,10 +17753,10 @@
         <v>1</v>
       </c>
       <c r="M330" s="4">
-        <v>0</v>
+        <v>251.9</v>
       </c>
       <c r="N330" s="4">
-        <v>0</v>
+        <v>251.9</v>
       </c>
       <c r="O330" s="1"/>
       <c r="P330" s="1"/>
@@ -17624,7 +17766,7 @@
         <v>2601</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>17</v>
@@ -17638,10 +17780,10 @@
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
       <c r="H331" s="1" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="J331" s="1" t="s">
         <v>20</v>
@@ -17666,7 +17808,7 @@
         <v>2601</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>17</v>
@@ -17680,10 +17822,10 @@
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
       <c r="H332" s="1" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="J332" s="1" t="s">
         <v>20</v>
@@ -17708,7 +17850,7 @@
         <v>2601</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>17</v>
@@ -17722,10 +17864,10 @@
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
       <c r="H333" s="1" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="J333" s="1" t="s">
         <v>20</v>
@@ -17750,7 +17892,7 @@
         <v>2601</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>17</v>
@@ -17764,10 +17906,10 @@
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
       <c r="H334" s="1" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="J334" s="1" t="s">
         <v>20</v>
@@ -17792,7 +17934,7 @@
         <v>2601</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>17</v>
@@ -17806,10 +17948,10 @@
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
       <c r="H335" s="1" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="J335" s="1" t="s">
         <v>20</v>
@@ -17834,7 +17976,7 @@
         <v>2601</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>17</v>
@@ -17848,10 +17990,10 @@
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
       <c r="H336" s="1" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="J336" s="1" t="s">
         <v>20</v>
@@ -17876,7 +18018,7 @@
         <v>2601</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>17</v>
@@ -17890,10 +18032,10 @@
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
       <c r="H337" s="1" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="J337" s="1" t="s">
         <v>20</v>
@@ -17918,7 +18060,7 @@
         <v>2601</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>17</v>
@@ -17932,10 +18074,10 @@
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
       <c r="H338" s="1" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="J338" s="1" t="s">
         <v>20</v>
@@ -17960,7 +18102,7 @@
         <v>2601</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>17</v>
@@ -17974,10 +18116,10 @@
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
       <c r="H339" s="1" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="J339" s="1" t="s">
         <v>20</v>
@@ -18002,7 +18144,7 @@
         <v>2601</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>17</v>
@@ -18016,10 +18158,10 @@
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
       <c r="H340" s="1" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="J340" s="1" t="s">
         <v>20</v>
@@ -18044,7 +18186,7 @@
         <v>2601</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>17</v>
@@ -18058,10 +18200,10 @@
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
       <c r="H341" s="1" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="J341" s="1" t="s">
         <v>20</v>
@@ -18086,7 +18228,7 @@
         <v>2601</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>17</v>
@@ -18100,10 +18242,10 @@
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
       <c r="H342" s="1" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="I342" s="1" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="J342" s="1" t="s">
         <v>20</v>
@@ -18128,7 +18270,7 @@
         <v>2601</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>17</v>
@@ -18142,10 +18284,10 @@
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
       <c r="H343" s="1" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="J343" s="1" t="s">
         <v>20</v>
@@ -18170,7 +18312,7 @@
         <v>2601</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>17</v>
@@ -18184,10 +18326,10 @@
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
       <c r="H344" s="1" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="J344" s="1" t="s">
         <v>20</v>
@@ -18212,7 +18354,7 @@
         <v>2601</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>17</v>
@@ -18226,10 +18368,10 @@
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
       <c r="H345" s="1" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="J345" s="1" t="s">
         <v>20</v>
@@ -18248,6 +18390,156 @@
       </c>
       <c r="O345" s="1"/>
       <c r="P345" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="346">
+      <c r="A346" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D346" s="2">
+        <v>75</v>
+      </c>
+      <c r="E346" s="3">
+        <v>46097.6179829282</v>
+      </c>
+      <c r="F346" s="2">
+        <v>82671</v>
+      </c>
+      <c r="G346" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H346" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="I346" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J346" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K346" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L346" s="4">
+        <v>1</v>
+      </c>
+      <c r="M346" s="4">
+        <v>305</v>
+      </c>
+      <c r="N346" s="4">
+        <v>305</v>
+      </c>
+      <c r="O346" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P346" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="347">
+      <c r="A347" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C347" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D347" s="2">
+        <v>75</v>
+      </c>
+      <c r="E347" s="3">
+        <v>46097.6179829282</v>
+      </c>
+      <c r="F347" s="2">
+        <v>82671</v>
+      </c>
+      <c r="G347" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H347" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I347" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="J347" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K347" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L347" s="4">
+        <v>1</v>
+      </c>
+      <c r="M347" s="4">
+        <v>92</v>
+      </c>
+      <c r="N347" s="4">
+        <v>92</v>
+      </c>
+      <c r="O347" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P347" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="348">
+      <c r="A348" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D348" s="2">
+        <v>75</v>
+      </c>
+      <c r="E348" s="3">
+        <v>46097.6179829282</v>
+      </c>
+      <c r="F348" s="2">
+        <v>82671</v>
+      </c>
+      <c r="G348" s="3">
+        <v>46097</v>
+      </c>
+      <c r="H348" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="I348" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="J348" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K348" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L348" s="4">
+        <v>25</v>
+      </c>
+      <c r="M348" s="4">
+        <v>59.9</v>
+      </c>
+      <c r="N348" s="4">
+        <v>1497.5</v>
+      </c>
+      <c r="O348" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P348" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -9342,37 +9342,37 @@
         <v>46093.4920058565</v>
       </c>
       <c r="F145" s="2">
-        <v>82672</v>
+        <v>82674</v>
       </c>
       <c r="G145" s="3">
         <v>46097</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>302</v>
+        <v>71</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>303</v>
+        <v>72</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="L145" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M145" s="4">
-        <v>150</v>
+        <v>23.43</v>
       </c>
       <c r="N145" s="4">
-        <v>300</v>
+        <v>468.6</v>
       </c>
       <c r="O145" s="1" t="s">
-        <v>305</v>
+        <v>73</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>306</v>
+        <v>74</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="146">
@@ -9392,37 +9392,37 @@
         <v>46093.4920058565</v>
       </c>
       <c r="F146" s="2">
-        <v>82581</v>
+        <v>82672</v>
       </c>
       <c r="G146" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="J146" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="L146" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="M146" s="4">
-        <v>1.5</v>
+        <v>150</v>
       </c>
       <c r="N146" s="4">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="O146" s="1" t="s">
-        <v>28</v>
+        <v>305</v>
       </c>
       <c r="P146" s="1" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="147">
@@ -9442,37 +9442,37 @@
         <v>46093.4920058565</v>
       </c>
       <c r="F147" s="2">
-        <v>82672</v>
+        <v>82581</v>
       </c>
       <c r="G147" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="J147" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="L147" s="4">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="M147" s="4">
-        <v>30</v>
+        <v>1.5</v>
       </c>
       <c r="N147" s="4">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="O147" s="1" t="s">
-        <v>305</v>
+        <v>28</v>
       </c>
       <c r="P147" s="1" t="s">
-        <v>306</v>
+        <v>29</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="148">
@@ -9498,10 +9498,10 @@
         <v>46097</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J148" s="1" t="s">
         <v>20</v>
@@ -9513,10 +9513,10 @@
         <v>2</v>
       </c>
       <c r="M148" s="4">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="N148" s="4">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>305</v>
@@ -9542,37 +9542,37 @@
         <v>46093.4920058565</v>
       </c>
       <c r="F149" s="2">
-        <v>82581</v>
+        <v>82672</v>
       </c>
       <c r="G149" s="3">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="J149" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="L149" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M149" s="4">
-        <v>4.2</v>
+        <v>90</v>
       </c>
       <c r="N149" s="4">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="O149" s="1" t="s">
-        <v>28</v>
+        <v>305</v>
       </c>
       <c r="P149" s="1" t="s">
-        <v>29</v>
+        <v>306</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="150">
@@ -9592,37 +9592,37 @@
         <v>46093.4920058565</v>
       </c>
       <c r="F150" s="2">
-        <v>82672</v>
+        <v>82581</v>
       </c>
       <c r="G150" s="3">
-        <v>46097</v>
+        <v>46093</v>
       </c>
       <c r="H150" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J150" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>304</v>
+        <v>21</v>
       </c>
       <c r="L150" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M150" s="4">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="N150" s="4">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="O150" s="1" t="s">
-        <v>305</v>
+        <v>28</v>
       </c>
       <c r="P150" s="1" t="s">
-        <v>306</v>
+        <v>29</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="151">
@@ -9648,10 +9648,10 @@
         <v>46097</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J151" s="1" t="s">
         <v>20</v>
@@ -9663,10 +9663,10 @@
         <v>2</v>
       </c>
       <c r="M151" s="4">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="N151" s="4">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>305</v>
@@ -9698,10 +9698,10 @@
         <v>46097</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="J152" s="1" t="s">
         <v>20</v>
@@ -9713,10 +9713,10 @@
         <v>2</v>
       </c>
       <c r="M152" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N152" s="4">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="O152" s="1" t="s">
         <v>305</v>
@@ -9741,31 +9741,39 @@
       <c r="E153" s="3">
         <v>46093.4920058565</v>
       </c>
-      <c r="F153" s="1"/>
-      <c r="G153" s="1"/>
+      <c r="F153" s="2">
+        <v>82672</v>
+      </c>
+      <c r="G153" s="3">
+        <v>46097</v>
+      </c>
       <c r="H153" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J153" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K153" s="1" t="s">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="L153" s="4">
+        <v>2</v>
+      </c>
+      <c r="M153" s="4">
         <v>1</v>
       </c>
-      <c r="M153" s="4">
-        <v>0</v>
-      </c>
       <c r="N153" s="4">
-        <v>0</v>
-      </c>
-      <c r="O153" s="1"/>
-      <c r="P153" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P153" s="1" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="154">
       <c r="A154" s="2">
@@ -9828,10 +9836,10 @@
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
       <c r="H155" s="1" t="s">
-        <v>71</v>
+        <v>321</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>72</v>
+        <v>322</v>
       </c>
       <c r="J155" s="1" t="s">
         <v>20</v>
@@ -9840,7 +9848,7 @@
         <v>21</v>
       </c>
       <c r="L155" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M155" s="4">
         <v>0</v>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="645">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1466,6 +1466,18 @@
     <t>METRO SHOPPING</t>
   </si>
   <si>
+    <t>K.08.0561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMADA PARA INFORMATICA CONECTOR RJ 45  BORNES DE PRESSÃO PRETA  LUMITEK - P/MOVEIS  67 X 43MM</t>
+  </si>
+  <si>
+    <t>00000000000587</t>
+  </si>
+  <si>
+    <t>PC 2000</t>
+  </si>
+  <si>
     <t>S.10.0062</t>
   </si>
   <si>
@@ -1520,12 +1532,6 @@
     <t>BONA SOAP LIMPADOR DE PISOS OLEADOS</t>
   </si>
   <si>
-    <t>K.08.0561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOMADA PARA INFORMATICA CONECTOR RJ 45  BORNES DE PRESSÃO PRETA  LUMITEK - P/MOVEIS  67 X 43MM</t>
-  </si>
-  <si>
     <t>K.08.1510</t>
   </si>
   <si>
@@ -1568,12 +1574,6 @@
     <t>TOMADA LUMITEK</t>
   </si>
   <si>
-    <t>00000000000587</t>
-  </si>
-  <si>
-    <t>PC 2000</t>
-  </si>
-  <si>
     <t>W.06.2001</t>
   </si>
   <si>
@@ -1628,6 +1628,90 @@
     <t>REGINA CAMPOS SALLES MORAES ABREU</t>
   </si>
   <si>
+    <t>E.04.0600</t>
+  </si>
+  <si>
+    <t>CARRINHO DE MÃO REFORÇADO PNEU CÂMARA TRAMONTINA</t>
+  </si>
+  <si>
+    <t>00000000008862</t>
+  </si>
+  <si>
+    <t>GUAIRA REAL</t>
+  </si>
+  <si>
+    <t>E.04.0122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRUMO METÁLICO PARA PEDREIRO  DE FACE- Nº5 - 900 G</t>
+  </si>
+  <si>
+    <t>E.04.0142</t>
+  </si>
+  <si>
+    <t>NÍVEL DE MADEIRA - 16''</t>
+  </si>
+  <si>
+    <t>E.04.0182</t>
+  </si>
+  <si>
+    <t>TRENA LONGA DE FIBRA- 30 M</t>
+  </si>
+  <si>
+    <t>E.04.0165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESQUADRO PROFISSIONAL DE ALUMÍNIO  SOLDADO - 1,20 X 0,8 M</t>
+  </si>
+  <si>
+    <t>E.04.0775</t>
+  </si>
+  <si>
+    <t>REGUA DE ALUMINIO 3 X 1'' C/ 3 M</t>
+  </si>
+  <si>
+    <t>E.04.0606</t>
+  </si>
+  <si>
+    <t>BOMBA PARA ENCHER PNEU DE CARRINHO DE MAO</t>
+  </si>
+  <si>
+    <t>E.04.0166</t>
+  </si>
+  <si>
+    <t>ESQUADRO PROFISSIONAL DE ALUMÍNIO SOLDADO - 0,80 X 0,60 M</t>
+  </si>
+  <si>
+    <t>E.04.0176</t>
+  </si>
+  <si>
+    <t>TRENA PROFISSIONAL DE AÇO 5 M</t>
+  </si>
+  <si>
+    <t>E.04.0776</t>
+  </si>
+  <si>
+    <t>REGUA DE ALUMINIO 3 X 1'' C/ 6 M</t>
+  </si>
+  <si>
+    <t>F.01.0011</t>
+  </si>
+  <si>
+    <t>ESCADA 6 DEGRAUS</t>
+  </si>
+  <si>
+    <t>F.01.0015</t>
+  </si>
+  <si>
+    <t>ESCADA DE FIBRA EXTENSÍVEL VAZADA C/ ALTURA</t>
+  </si>
+  <si>
+    <t>K.02.0752</t>
+  </si>
+  <si>
+    <t>MANGUEIRA</t>
+  </si>
+  <si>
     <t>C.05.0208</t>
   </si>
   <si>
@@ -1646,102 +1730,24 @@
     <t xml:space="preserve">PROMAPISO 2MM X 600MM X50M  PROMAFLEX</t>
   </si>
   <si>
-    <t>E.04.0600</t>
-  </si>
-  <si>
-    <t>CARRINHO DE MÃO REFORÇADO PNEU CÂMARA TRAMONTINA</t>
-  </si>
-  <si>
-    <t>E.04.0122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRUMO METÁLICO PARA PEDREIRO  DE FACE- Nº5 - 900 G</t>
-  </si>
-  <si>
-    <t>E.04.0142</t>
-  </si>
-  <si>
-    <t>NÍVEL DE MADEIRA - 16''</t>
-  </si>
-  <si>
-    <t>E.04.0182</t>
-  </si>
-  <si>
-    <t>TRENA LONGA DE FIBRA- 30 M</t>
-  </si>
-  <si>
     <t>E.04.0173</t>
   </si>
   <si>
     <t>NÍVEL A LASER</t>
   </si>
   <si>
-    <t>E.04.0165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESQUADRO PROFISSIONAL DE ALUMÍNIO  SOLDADO - 1,20 X 0,8 M</t>
-  </si>
-  <si>
-    <t>E.04.0775</t>
-  </si>
-  <si>
-    <t>REGUA DE ALUMINIO 3 X 1'' C/ 3 M</t>
-  </si>
-  <si>
-    <t>E.04.0606</t>
-  </si>
-  <si>
-    <t>BOMBA PARA ENCHER PNEU DE CARRINHO DE MAO</t>
-  </si>
-  <si>
-    <t>E.04.0166</t>
-  </si>
-  <si>
-    <t>ESQUADRO PROFISSIONAL DE ALUMÍNIO SOLDADO - 0,80 X 0,60 M</t>
-  </si>
-  <si>
-    <t>E.04.0176</t>
-  </si>
-  <si>
-    <t>TRENA PROFISSIONAL DE AÇO 5 M</t>
-  </si>
-  <si>
-    <t>E.04.0776</t>
-  </si>
-  <si>
-    <t>REGUA DE ALUMINIO 3 X 1'' C/ 6 M</t>
-  </si>
-  <si>
     <t>E.04.0177</t>
   </si>
   <si>
     <t>TRIPÉ PARA NIVEL A LASER</t>
   </si>
   <si>
-    <t>F.01.0011</t>
-  </si>
-  <si>
-    <t>ESCADA 6 DEGRAUS</t>
-  </si>
-  <si>
-    <t>F.01.0015</t>
-  </si>
-  <si>
-    <t>ESCADA DE FIBRA EXTENSÍVEL VAZADA C/ ALTURA</t>
-  </si>
-  <si>
     <t>G.03.0002</t>
   </si>
   <si>
     <t>CAÇAMBA - UNIDADE</t>
   </si>
   <si>
-    <t>K.02.0752</t>
-  </si>
-  <si>
-    <t>MANGUEIRA</t>
-  </si>
-  <si>
     <t>LUIZ ALBERTO HESS BORGES</t>
   </si>
   <si>
@@ -1763,6 +1769,36 @@
     <t>FELIPE HESS BORGES</t>
   </si>
   <si>
+    <t>H.11.0012</t>
+  </si>
+  <si>
+    <t>AÇO CA25 6,3 MM - VARA</t>
+  </si>
+  <si>
+    <t>00000000010253</t>
+  </si>
+  <si>
+    <t>DEPOSITO BRASIL</t>
+  </si>
+  <si>
+    <t>H.11.0013</t>
+  </si>
+  <si>
+    <t>AÇO CA25 8,0 MM - VARA</t>
+  </si>
+  <si>
+    <t>H.11.0034</t>
+  </si>
+  <si>
+    <t>AÇO CA50 10,0 MM - VARA</t>
+  </si>
+  <si>
+    <t>M.09.0022</t>
+  </si>
+  <si>
+    <t>ARAME RECOZIDO NØ 18</t>
+  </si>
+  <si>
     <t>E.03.0150</t>
   </si>
   <si>
@@ -1775,30 +1811,6 @@
     <t>COLHER DE PEDREIRO - 8''</t>
   </si>
   <si>
-    <t>H.11.0012</t>
-  </si>
-  <si>
-    <t>AÇO CA25 6,3 MM - VARA</t>
-  </si>
-  <si>
-    <t>H.11.0013</t>
-  </si>
-  <si>
-    <t>AÇO CA25 8,0 MM - VARA</t>
-  </si>
-  <si>
-    <t>H.11.0034</t>
-  </si>
-  <si>
-    <t>AÇO CA50 10,0 MM - VARA</t>
-  </si>
-  <si>
-    <t>M.09.0022</t>
-  </si>
-  <si>
-    <t>ARAME RECOZIDO NØ 18</t>
-  </si>
-  <si>
     <t>O.01.0101</t>
   </si>
   <si>
@@ -1857,6 +1869,84 @@
   </si>
   <si>
     <t>MÁSCARA DESCARTÁVEL RESPIRADOR COM VÁLVULA CLASSE PFF1</t>
+  </si>
+  <si>
+    <t>O.01.0102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABUA DE PINUS  1" X 6"</t>
+  </si>
+  <si>
+    <t>O.01.0116</t>
+  </si>
+  <si>
+    <t>CHAPA PLASTIFICADO 14 MM - 2,20 X 1,10 M</t>
+  </si>
+  <si>
+    <t>E.03.0055</t>
+  </si>
+  <si>
+    <t>REPELENTE CONTRA INSETOS</t>
+  </si>
+  <si>
+    <t>E.04.0870</t>
+  </si>
+  <si>
+    <t>PULVERIZADOR</t>
+  </si>
+  <si>
+    <t>E.04.0123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRUMO METÁLICO PARA PEDREIRO  DE CENTRO- Nº5 - 900 G</t>
+  </si>
+  <si>
+    <t>F.04.0201</t>
+  </si>
+  <si>
+    <t>MARTELETE ROMPEDOR 10KG COM FERRAMENTAS ( PONTEIRO OU TALHADEIRA )</t>
+  </si>
+  <si>
+    <t>K.01.0265</t>
+  </si>
+  <si>
+    <t>CABO FLEXÍVEL PP - 750 V - 2 X 1,5 MM²</t>
+  </si>
+  <si>
+    <t>K.07.0705</t>
+  </si>
+  <si>
+    <t>REFLETOR DE LED 200W A PROVA D'AGUA</t>
+  </si>
+  <si>
+    <t>K.01.1530</t>
+  </si>
+  <si>
+    <t>PROLONGADOR PROFISSIONAL PADRÃO BRASILEIRO 10A 2P (FEMEA) REF 615874</t>
+  </si>
+  <si>
+    <t>K.01.1480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLUG RESIDENCIAIS PADRÃO BRASILEIRO   10 A 2 P ( MACHO )</t>
+  </si>
+  <si>
+    <t>M.09.0006</t>
+  </si>
+  <si>
+    <t>ARAME GALVANIZADO NØ 20</t>
+  </si>
+  <si>
+    <t>O.01.0105</t>
+  </si>
+  <si>
+    <t>PONTALETE DE CEDRINHO - 3 X 3" - 1ª IND</t>
+  </si>
+  <si>
+    <t>O.01.0008</t>
+  </si>
+  <si>
+    <t>TÁBUA DE CEDRINHO - 1 X 12'' -</t>
   </si>
 </sst>
 </file>
@@ -2155,7 +2245,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P363"/>
+  <dimension ref="A1:P380"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -14916,10 +15006,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F268" s="2">
-        <v>82635</v>
+        <v>82698</v>
       </c>
       <c r="G268" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="H268" s="1" t="s">
         <v>484</v>
@@ -14937,16 +15027,16 @@
         <v>5</v>
       </c>
       <c r="M268" s="4">
-        <v>22</v>
+        <v>95.26</v>
       </c>
       <c r="N268" s="4">
-        <v>110</v>
+        <v>476.3</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>79</v>
+        <v>486</v>
       </c>
       <c r="P268" s="1" t="s">
-        <v>80</v>
+        <v>487</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="269">
@@ -14972,10 +15062,10 @@
         <v>46094</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>19</v>
@@ -14987,10 +15077,10 @@
         <v>5</v>
       </c>
       <c r="M269" s="4">
-        <v>25.9</v>
+        <v>22</v>
       </c>
       <c r="N269" s="4">
-        <v>129.5</v>
+        <v>110</v>
       </c>
       <c r="O269" s="1" t="s">
         <v>79</v>
@@ -15022,10 +15112,10 @@
         <v>46094</v>
       </c>
       <c r="H270" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>19</v>
@@ -15034,13 +15124,13 @@
         <v>33</v>
       </c>
       <c r="L270" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M270" s="4">
-        <v>55</v>
+        <v>25.9</v>
       </c>
       <c r="N270" s="4">
-        <v>330</v>
+        <v>129.5</v>
       </c>
       <c r="O270" s="1" t="s">
         <v>79</v>
@@ -15066,16 +15156,16 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F271" s="2">
-        <v>82681</v>
+        <v>82635</v>
       </c>
       <c r="G271" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>19</v>
@@ -15084,19 +15174,19 @@
         <v>33</v>
       </c>
       <c r="L271" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M271" s="4">
-        <v>3077</v>
+        <v>55</v>
       </c>
       <c r="N271" s="4">
-        <v>3077</v>
+        <v>330</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="P271" s="1" t="s">
-        <v>493</v>
+        <v>80</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="272">
@@ -15137,16 +15227,16 @@
         <v>1</v>
       </c>
       <c r="M272" s="4">
-        <v>5699</v>
+        <v>3077</v>
       </c>
       <c r="N272" s="4">
-        <v>5699</v>
+        <v>3077</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="P272" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="273">
@@ -15172,31 +15262,31 @@
         <v>46098</v>
       </c>
       <c r="H273" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="I273" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="J273" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K273" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L273" s="4">
+        <v>1</v>
+      </c>
+      <c r="M273" s="4">
+        <v>5699</v>
+      </c>
+      <c r="N273" s="4">
+        <v>5699</v>
+      </c>
+      <c r="O273" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="I273" s="1" t="s">
+      <c r="P273" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="J273" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K273" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L273" s="4">
-        <v>2</v>
-      </c>
-      <c r="M273" s="4">
-        <v>1273.99</v>
-      </c>
-      <c r="N273" s="4">
-        <v>2547.98</v>
-      </c>
-      <c r="O273" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="P273" s="1" t="s">
-        <v>493</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="274">
@@ -15222,10 +15312,10 @@
         <v>46098</v>
       </c>
       <c r="H274" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>19</v>
@@ -15234,19 +15324,19 @@
         <v>33</v>
       </c>
       <c r="L274" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M274" s="4">
-        <v>3424.61</v>
+        <v>1273.99</v>
       </c>
       <c r="N274" s="4">
-        <v>3424.61</v>
+        <v>2547.98</v>
       </c>
       <c r="O274" s="1" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="P274" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="275">
@@ -15266,37 +15356,37 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F275" s="2">
-        <v>82635</v>
+        <v>82681</v>
       </c>
       <c r="G275" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>154</v>
+        <v>502</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>155</v>
+        <v>503</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K275" s="1" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="L275" s="4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M275" s="4">
-        <v>14.3</v>
+        <v>3424.61</v>
       </c>
       <c r="N275" s="4">
-        <v>257.4</v>
+        <v>3424.61</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>79</v>
+        <v>496</v>
       </c>
       <c r="P275" s="1" t="s">
-        <v>80</v>
+        <v>497</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="276">
@@ -15315,31 +15405,39 @@
       <c r="E276" s="3">
         <v>46094.4767297338</v>
       </c>
-      <c r="F276" s="1"/>
-      <c r="G276" s="1"/>
+      <c r="F276" s="2">
+        <v>82635</v>
+      </c>
+      <c r="G276" s="3">
+        <v>46094</v>
+      </c>
       <c r="H276" s="1" t="s">
-        <v>500</v>
+        <v>154</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>501</v>
+        <v>155</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K276" s="1" t="s">
-        <v>164</v>
+        <v>59</v>
       </c>
       <c r="L276" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M276" s="4">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="N276" s="4">
-        <v>0</v>
-      </c>
-      <c r="O276" s="1"/>
-      <c r="P276" s="1"/>
+        <v>257.4</v>
+      </c>
+      <c r="O276" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P276" s="1" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="277">
       <c r="A277" s="2">
@@ -15360,19 +15458,19 @@
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
       <c r="H277" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K277" s="1" t="s">
-        <v>33</v>
+        <v>164</v>
       </c>
       <c r="L277" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M277" s="4">
         <v>0</v>
@@ -15402,10 +15500,10 @@
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
       <c r="H278" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J278" s="1" t="s">
         <v>19</v>
@@ -15444,10 +15542,10 @@
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
       <c r="H279" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J279" s="1" t="s">
         <v>19</v>
@@ -15486,10 +15584,10 @@
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
       <c r="H280" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>19</v>
@@ -15632,10 +15730,10 @@
         <v>46097</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>19</v>
@@ -15782,10 +15880,10 @@
         <v>46097</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J286" s="1" t="s">
         <v>19</v>
@@ -15832,10 +15930,10 @@
         <v>46097</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>19</v>
@@ -15932,10 +16030,10 @@
         <v>46097</v>
       </c>
       <c r="H289" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J289" s="1" t="s">
         <v>19</v>
@@ -15953,10 +16051,10 @@
         <v>119.7</v>
       </c>
       <c r="O289" s="1" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="P289" s="1" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="290">
@@ -15982,10 +16080,10 @@
         <v>46097</v>
       </c>
       <c r="H290" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J290" s="1" t="s">
         <v>19</v>
@@ -16003,10 +16101,10 @@
         <v>89.7</v>
       </c>
       <c r="O290" s="1" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="P290" s="1" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="291">
@@ -16032,10 +16130,10 @@
         <v>46097</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>19</v>
@@ -16053,10 +16151,10 @@
         <v>89.7</v>
       </c>
       <c r="O291" s="1" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="P291" s="1" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="292">
@@ -16082,10 +16180,10 @@
         <v>46097</v>
       </c>
       <c r="H292" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J292" s="1" t="s">
         <v>19</v>
@@ -16103,10 +16201,10 @@
         <v>279.3</v>
       </c>
       <c r="O292" s="1" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="P292" s="1" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="293">
@@ -16717,8 +16815,12 @@
       <c r="E305" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F305" s="1"/>
-      <c r="G305" s="1"/>
+      <c r="F305" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G305" s="3">
+        <v>46098</v>
+      </c>
       <c r="H305" s="1" t="s">
         <v>538</v>
       </c>
@@ -16732,16 +16834,20 @@
         <v>33</v>
       </c>
       <c r="L305" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M305" s="4">
-        <v>0</v>
+        <v>322</v>
       </c>
       <c r="N305" s="4">
-        <v>0</v>
-      </c>
-      <c r="O305" s="1"/>
-      <c r="P305" s="1"/>
+        <v>322</v>
+      </c>
+      <c r="O305" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P305" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="306">
       <c r="A306" s="2">
@@ -16759,13 +16865,17 @@
       <c r="E306" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F306" s="1"/>
-      <c r="G306" s="1"/>
+      <c r="F306" s="2">
+        <v>82691</v>
+      </c>
+      <c r="G306" s="3">
+        <v>46098</v>
+      </c>
       <c r="H306" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>19</v>
@@ -16774,16 +16884,20 @@
         <v>33</v>
       </c>
       <c r="L306" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M306" s="4">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="N306" s="4">
-        <v>0</v>
-      </c>
-      <c r="O306" s="1"/>
-      <c r="P306" s="1"/>
+        <v>58</v>
+      </c>
+      <c r="O306" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="P306" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="307">
       <c r="A307" s="2">
@@ -16801,31 +16915,39 @@
       <c r="E307" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F307" s="1"/>
-      <c r="G307" s="1"/>
+      <c r="F307" s="2">
+        <v>82691</v>
+      </c>
+      <c r="G307" s="3">
+        <v>46098</v>
+      </c>
       <c r="H307" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="L307" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M307" s="4">
-        <v>0</v>
+        <v>23.77</v>
       </c>
       <c r="N307" s="4">
-        <v>0</v>
-      </c>
-      <c r="O307" s="1"/>
-      <c r="P307" s="1"/>
+        <v>47.54</v>
+      </c>
+      <c r="O307" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="P307" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="308">
       <c r="A308" s="2">
@@ -16843,13 +16965,17 @@
       <c r="E308" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F308" s="1"/>
-      <c r="G308" s="1"/>
+      <c r="F308" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G308" s="3">
+        <v>46098</v>
+      </c>
       <c r="H308" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>19</v>
@@ -16861,13 +16987,17 @@
         <v>1</v>
       </c>
       <c r="M308" s="4">
-        <v>251.9</v>
+        <v>145</v>
       </c>
       <c r="N308" s="4">
-        <v>251.9</v>
-      </c>
-      <c r="O308" s="1"/>
-      <c r="P308" s="1"/>
+        <v>145</v>
+      </c>
+      <c r="O308" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P308" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="309">
       <c r="A309" s="2">
@@ -16885,13 +17015,17 @@
       <c r="E309" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F309" s="1"/>
-      <c r="G309" s="1"/>
+      <c r="F309" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G309" s="3">
+        <v>46098</v>
+      </c>
       <c r="H309" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>19</v>
@@ -16903,13 +17037,17 @@
         <v>2</v>
       </c>
       <c r="M309" s="4">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="N309" s="4">
-        <v>0</v>
-      </c>
-      <c r="O309" s="1"/>
-      <c r="P309" s="1"/>
+        <v>244</v>
+      </c>
+      <c r="O309" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P309" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="310">
       <c r="A310" s="2">
@@ -16927,13 +17065,17 @@
       <c r="E310" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F310" s="1"/>
-      <c r="G310" s="1"/>
+      <c r="F310" s="2">
+        <v>82691</v>
+      </c>
+      <c r="G310" s="3">
+        <v>46098</v>
+      </c>
       <c r="H310" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>19</v>
@@ -16945,13 +17087,17 @@
         <v>2</v>
       </c>
       <c r="M310" s="4">
-        <v>0</v>
+        <v>123.37</v>
       </c>
       <c r="N310" s="4">
-        <v>0</v>
-      </c>
-      <c r="O310" s="1"/>
-      <c r="P310" s="1"/>
+        <v>246.74</v>
+      </c>
+      <c r="O310" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="P310" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="311">
       <c r="A311" s="2">
@@ -16969,13 +17115,17 @@
       <c r="E311" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F311" s="1"/>
-      <c r="G311" s="1"/>
+      <c r="F311" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G311" s="3">
+        <v>46098</v>
+      </c>
       <c r="H311" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>19</v>
@@ -16987,13 +17137,17 @@
         <v>1</v>
       </c>
       <c r="M311" s="4">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N311" s="4">
-        <v>0</v>
-      </c>
-      <c r="O311" s="1"/>
-      <c r="P311" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="O311" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P311" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="312">
       <c r="A312" s="2">
@@ -17011,13 +17165,17 @@
       <c r="E312" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
+      <c r="F312" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G312" s="3">
+        <v>46098</v>
+      </c>
       <c r="H312" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>19</v>
@@ -17026,16 +17184,20 @@
         <v>33</v>
       </c>
       <c r="L312" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M312" s="4">
-        <v>0</v>
+        <v>92.8</v>
       </c>
       <c r="N312" s="4">
-        <v>0</v>
-      </c>
-      <c r="O312" s="1"/>
-      <c r="P312" s="1"/>
+        <v>185.6</v>
+      </c>
+      <c r="O312" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P312" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="313">
       <c r="A313" s="2">
@@ -17053,13 +17215,17 @@
       <c r="E313" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
+      <c r="F313" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G313" s="3">
+        <v>46098</v>
+      </c>
       <c r="H313" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>19</v>
@@ -17068,16 +17234,20 @@
         <v>33</v>
       </c>
       <c r="L313" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M313" s="4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N313" s="4">
-        <v>0</v>
-      </c>
-      <c r="O313" s="1"/>
-      <c r="P313" s="1"/>
+        <v>124</v>
+      </c>
+      <c r="O313" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P313" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="314">
       <c r="A314" s="2">
@@ -17095,13 +17265,17 @@
       <c r="E314" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F314" s="1"/>
-      <c r="G314" s="1"/>
+      <c r="F314" s="2">
+        <v>82691</v>
+      </c>
+      <c r="G314" s="3">
+        <v>46098</v>
+      </c>
       <c r="H314" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>19</v>
@@ -17113,13 +17287,17 @@
         <v>2</v>
       </c>
       <c r="M314" s="4">
-        <v>0</v>
+        <v>246.74</v>
       </c>
       <c r="N314" s="4">
-        <v>0</v>
-      </c>
-      <c r="O314" s="1"/>
-      <c r="P314" s="1"/>
+        <v>493.48</v>
+      </c>
+      <c r="O314" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="P314" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="315">
       <c r="A315" s="2">
@@ -17137,13 +17315,17 @@
       <c r="E315" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F315" s="1"/>
-      <c r="G315" s="1"/>
+      <c r="F315" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G315" s="3">
+        <v>46098</v>
+      </c>
       <c r="H315" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>19</v>
@@ -17155,13 +17337,17 @@
         <v>1</v>
       </c>
       <c r="M315" s="4">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="N315" s="4">
-        <v>0</v>
-      </c>
-      <c r="O315" s="1"/>
-      <c r="P315" s="1"/>
+        <v>253</v>
+      </c>
+      <c r="O315" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P315" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="316">
       <c r="A316" s="2">
@@ -17179,13 +17365,17 @@
       <c r="E316" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F316" s="1"/>
-      <c r="G316" s="1"/>
+      <c r="F316" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G316" s="3">
+        <v>46098</v>
+      </c>
       <c r="H316" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>19</v>
@@ -17194,16 +17384,20 @@
         <v>33</v>
       </c>
       <c r="L316" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M316" s="4">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="N316" s="4">
-        <v>0</v>
-      </c>
-      <c r="O316" s="1"/>
-      <c r="P316" s="1"/>
+        <v>625</v>
+      </c>
+      <c r="O316" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P316" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="317">
       <c r="A317" s="2">
@@ -17221,31 +17415,39 @@
       <c r="E317" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
+      <c r="F317" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G317" s="3">
+        <v>46098</v>
+      </c>
       <c r="H317" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="J317" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K317" s="1" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="L317" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="M317" s="4">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N317" s="4">
-        <v>0</v>
-      </c>
-      <c r="O317" s="1"/>
-      <c r="P317" s="1"/>
+        <v>283</v>
+      </c>
+      <c r="O317" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="P317" s="1" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="318">
       <c r="A318" s="2">
@@ -17266,10 +17468,10 @@
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
       <c r="H318" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>19</v>
@@ -17278,7 +17480,7 @@
         <v>33</v>
       </c>
       <c r="L318" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M318" s="4">
         <v>0</v>
@@ -17308,10 +17510,10 @@
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
       <c r="H319" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="J319" s="1" t="s">
         <v>19</v>
@@ -17350,19 +17552,19 @@
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
       <c r="H320" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="J320" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K320" s="1" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="L320" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M320" s="4">
         <v>0</v>
@@ -17392,10 +17594,10 @@
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
       <c r="H321" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="J321" s="1" t="s">
         <v>19</v>
@@ -17434,10 +17636,10 @@
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
       <c r="H322" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>19</v>
@@ -17446,7 +17648,7 @@
         <v>33</v>
       </c>
       <c r="L322" s="4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="M322" s="4">
         <v>0</v>
@@ -17476,19 +17678,19 @@
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
       <c r="H323" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K323" s="1" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="L323" s="4">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="M323" s="4">
         <v>0</v>
@@ -17504,7 +17706,7 @@
         <v>2317</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>24</v>
@@ -17554,7 +17756,7 @@
         <v>2317</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>24</v>
@@ -17604,7 +17806,7 @@
         <v>2317</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>24</v>
@@ -17622,10 +17824,10 @@
         <v>46097</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J326" s="1" t="s">
         <v>19</v>
@@ -17654,7 +17856,7 @@
         <v>2404</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>71</v>
@@ -17704,7 +17906,7 @@
         <v>2404</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>71</v>
@@ -17754,7 +17956,7 @@
         <v>2404</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>71</v>
@@ -17804,7 +18006,7 @@
         <v>2404</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>71</v>
@@ -17822,10 +18024,10 @@
         <v>46098</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>19</v>
@@ -17854,7 +18056,7 @@
         <v>2404</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>71</v>
@@ -17896,7 +18098,7 @@
         <v>2404</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>71</v>
@@ -17910,10 +18112,10 @@
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
       <c r="H332" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J332" s="1" t="s">
         <v>19</v>
@@ -17938,7 +18140,7 @@
         <v>2514</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>24</v>
@@ -17949,13 +18151,17 @@
       <c r="E333" s="3">
         <v>46098.4979333449</v>
       </c>
-      <c r="F333" s="1"/>
-      <c r="G333" s="1"/>
+      <c r="F333" s="2">
+        <v>82693</v>
+      </c>
+      <c r="G333" s="3">
+        <v>46098</v>
+      </c>
       <c r="H333" s="1" t="s">
-        <v>217</v>
+        <v>585</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>218</v>
+        <v>586</v>
       </c>
       <c r="J333" s="1" t="s">
         <v>19</v>
@@ -17964,23 +18170,27 @@
         <v>33</v>
       </c>
       <c r="L333" s="4">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="M333" s="4">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="N333" s="4">
-        <v>0</v>
-      </c>
-      <c r="O333" s="1"/>
-      <c r="P333" s="1"/>
+        <v>1011.5</v>
+      </c>
+      <c r="O333" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="P333" s="1" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="334">
       <c r="A334" s="2">
         <v>2514</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>24</v>
@@ -17991,13 +18201,17 @@
       <c r="E334" s="3">
         <v>46098.4979333449</v>
       </c>
-      <c r="F334" s="1"/>
-      <c r="G334" s="1"/>
+      <c r="F334" s="2">
+        <v>82693</v>
+      </c>
+      <c r="G334" s="3">
+        <v>46098</v>
+      </c>
       <c r="H334" s="1" t="s">
-        <v>510</v>
+        <v>589</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>511</v>
+        <v>590</v>
       </c>
       <c r="J334" s="1" t="s">
         <v>19</v>
@@ -18006,23 +18220,27 @@
         <v>33</v>
       </c>
       <c r="L334" s="4">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M334" s="4">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="N334" s="4">
-        <v>0</v>
-      </c>
-      <c r="O334" s="1"/>
-      <c r="P334" s="1"/>
+        <v>3290</v>
+      </c>
+      <c r="O334" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="P334" s="1" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="335">
       <c r="A335" s="2">
         <v>2514</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>24</v>
@@ -18033,38 +18251,46 @@
       <c r="E335" s="3">
         <v>46098.4979333449</v>
       </c>
-      <c r="F335" s="1"/>
-      <c r="G335" s="1"/>
+      <c r="F335" s="2">
+        <v>82693</v>
+      </c>
+      <c r="G335" s="3">
+        <v>46098</v>
+      </c>
       <c r="H335" s="1" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="I335" s="1" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="J335" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K335" s="1" t="s">
-        <v>188</v>
+        <v>33</v>
       </c>
       <c r="L335" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M335" s="4">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="N335" s="4">
-        <v>0</v>
-      </c>
-      <c r="O335" s="1"/>
-      <c r="P335" s="1"/>
+        <v>1240</v>
+      </c>
+      <c r="O335" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="P335" s="1" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="336">
       <c r="A336" s="2">
         <v>2514</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>24</v>
@@ -18075,38 +18301,46 @@
       <c r="E336" s="3">
         <v>46098.4979333449</v>
       </c>
-      <c r="F336" s="1"/>
-      <c r="G336" s="1"/>
+      <c r="F336" s="2">
+        <v>82693</v>
+      </c>
+      <c r="G336" s="3">
+        <v>46098</v>
+      </c>
       <c r="H336" s="1" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="J336" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K336" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="L336" s="4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M336" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N336" s="4">
-        <v>0</v>
-      </c>
-      <c r="O336" s="1"/>
-      <c r="P336" s="1"/>
+        <v>400</v>
+      </c>
+      <c r="O336" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="P336" s="1" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="337">
       <c r="A337" s="2">
         <v>2514</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>24</v>
@@ -18120,10 +18354,10 @@
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
       <c r="H337" s="1" t="s">
-        <v>587</v>
+        <v>217</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>588</v>
+        <v>218</v>
       </c>
       <c r="J337" s="1" t="s">
         <v>19</v>
@@ -18132,7 +18366,7 @@
         <v>33</v>
       </c>
       <c r="L337" s="4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="M337" s="4">
         <v>0</v>
@@ -18148,7 +18382,7 @@
         <v>2514</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>24</v>
@@ -18162,10 +18396,10 @@
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
       <c r="H338" s="1" t="s">
-        <v>589</v>
+        <v>512</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>590</v>
+        <v>513</v>
       </c>
       <c r="J338" s="1" t="s">
         <v>19</v>
@@ -18174,7 +18408,7 @@
         <v>33</v>
       </c>
       <c r="L338" s="4">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M338" s="4">
         <v>0</v>
@@ -18190,7 +18424,7 @@
         <v>2514</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>24</v>
@@ -18204,19 +18438,19 @@
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
       <c r="H339" s="1" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="J339" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K339" s="1" t="s">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="L339" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M339" s="4">
         <v>0</v>
@@ -18232,7 +18466,7 @@
         <v>2514</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>24</v>
@@ -18246,19 +18480,19 @@
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
       <c r="H340" s="1" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="I340" s="1" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="J340" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K340" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L340" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M340" s="4">
         <v>0</v>
@@ -18274,7 +18508,7 @@
         <v>2514</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>24</v>
@@ -18288,10 +18522,10 @@
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
       <c r="H341" s="1" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="I341" s="1" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="J341" s="1" t="s">
         <v>19</v>
@@ -18316,7 +18550,7 @@
         <v>2514</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>24</v>
@@ -18497,10 +18731,10 @@
         <v>1200</v>
       </c>
       <c r="O345" s="1" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="P345" s="1" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="346">
@@ -18547,10 +18781,10 @@
         <v>1081.5</v>
       </c>
       <c r="O346" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="P346" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="347">
@@ -18597,10 +18831,10 @@
         <v>570</v>
       </c>
       <c r="O347" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="P347" s="1" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="348">
@@ -18622,10 +18856,10 @@
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
       <c r="H348" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="J348" s="1" t="s">
         <v>19</v>
@@ -18664,10 +18898,10 @@
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
       <c r="H349" s="1" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="J349" s="1" t="s">
         <v>19</v>
@@ -18706,10 +18940,10 @@
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
       <c r="H350" s="1" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="J350" s="1" t="s">
         <v>19</v>
@@ -18748,10 +18982,10 @@
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
       <c r="H351" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="J351" s="1" t="s">
         <v>19</v>
@@ -18958,10 +19192,10 @@
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
       <c r="H356" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="I356" s="1" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="J356" s="1" t="s">
         <v>19</v>
@@ -19000,10 +19234,10 @@
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
       <c r="H357" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="I357" s="1" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="J357" s="1" t="s">
         <v>19</v>
@@ -19096,10 +19330,10 @@
         <v>46098</v>
       </c>
       <c r="H359" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I359" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J359" s="1" t="s">
         <v>19</v>
@@ -19290,6 +19524,736 @@
       </c>
       <c r="O363" s="1"/>
       <c r="P363" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="364">
+      <c r="A364" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C364" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D364" s="2">
+        <v>21</v>
+      </c>
+      <c r="E364" s="3">
+        <v>46098.6661386574</v>
+      </c>
+      <c r="F364" s="2">
+        <v>82696</v>
+      </c>
+      <c r="G364" s="3">
+        <v>46098</v>
+      </c>
+      <c r="H364" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I364" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J364" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K364" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L364" s="4">
+        <v>50</v>
+      </c>
+      <c r="M364" s="4">
+        <v>34.5</v>
+      </c>
+      <c r="N364" s="4">
+        <v>1725</v>
+      </c>
+      <c r="O364" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P364" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="365">
+      <c r="A365" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C365" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D365" s="2">
+        <v>21</v>
+      </c>
+      <c r="E365" s="3">
+        <v>46098.6661386574</v>
+      </c>
+      <c r="F365" s="1"/>
+      <c r="G365" s="1"/>
+      <c r="H365" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="I365" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="J365" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K365" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L365" s="4">
+        <v>21</v>
+      </c>
+      <c r="M365" s="4">
+        <v>0</v>
+      </c>
+      <c r="N365" s="4">
+        <v>0</v>
+      </c>
+      <c r="O365" s="1"/>
+      <c r="P365" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="366">
+      <c r="A366" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D366" s="2">
+        <v>21</v>
+      </c>
+      <c r="E366" s="3">
+        <v>46098.6661386574</v>
+      </c>
+      <c r="F366" s="1"/>
+      <c r="G366" s="1"/>
+      <c r="H366" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="I366" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="J366" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K366" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L366" s="4">
+        <v>10</v>
+      </c>
+      <c r="M366" s="4">
+        <v>0</v>
+      </c>
+      <c r="N366" s="4">
+        <v>0</v>
+      </c>
+      <c r="O366" s="1"/>
+      <c r="P366" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="367">
+      <c r="A367" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C367" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D367" s="2">
+        <v>32</v>
+      </c>
+      <c r="E367" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F367" s="2">
+        <v>82697</v>
+      </c>
+      <c r="G367" s="3">
+        <v>46098</v>
+      </c>
+      <c r="H367" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I367" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="J367" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K367" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L367" s="4">
+        <v>10000</v>
+      </c>
+      <c r="M367" s="4">
+        <v>0.0933</v>
+      </c>
+      <c r="N367" s="4">
+        <v>933</v>
+      </c>
+      <c r="O367" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P367" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="368">
+      <c r="A368" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D368" s="2">
+        <v>32</v>
+      </c>
+      <c r="E368" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F368" s="1"/>
+      <c r="G368" s="1"/>
+      <c r="H368" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I368" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J368" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K368" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L368" s="4">
+        <v>2</v>
+      </c>
+      <c r="M368" s="4">
+        <v>0</v>
+      </c>
+      <c r="N368" s="4">
+        <v>0</v>
+      </c>
+      <c r="O368" s="1"/>
+      <c r="P368" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="369">
+      <c r="A369" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D369" s="2">
+        <v>32</v>
+      </c>
+      <c r="E369" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F369" s="1"/>
+      <c r="G369" s="1"/>
+      <c r="H369" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="J369" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K369" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="L369" s="4">
+        <v>6</v>
+      </c>
+      <c r="M369" s="4">
+        <v>0</v>
+      </c>
+      <c r="N369" s="4">
+        <v>0</v>
+      </c>
+      <c r="O369" s="1"/>
+      <c r="P369" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="370">
+      <c r="A370" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D370" s="2">
+        <v>32</v>
+      </c>
+      <c r="E370" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F370" s="1"/>
+      <c r="G370" s="1"/>
+      <c r="H370" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="I370" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="J370" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K370" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L370" s="4">
+        <v>6</v>
+      </c>
+      <c r="M370" s="4">
+        <v>0</v>
+      </c>
+      <c r="N370" s="4">
+        <v>0</v>
+      </c>
+      <c r="O370" s="1"/>
+      <c r="P370" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="371">
+      <c r="A371" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D371" s="2">
+        <v>32</v>
+      </c>
+      <c r="E371" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F371" s="1"/>
+      <c r="G371" s="1"/>
+      <c r="H371" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="I371" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="J371" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K371" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L371" s="4">
+        <v>1</v>
+      </c>
+      <c r="M371" s="4">
+        <v>0</v>
+      </c>
+      <c r="N371" s="4">
+        <v>0</v>
+      </c>
+      <c r="O371" s="1"/>
+      <c r="P371" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="372">
+      <c r="A372" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D372" s="2">
+        <v>32</v>
+      </c>
+      <c r="E372" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F372" s="1"/>
+      <c r="G372" s="1"/>
+      <c r="H372" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="I372" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="J372" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K372" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L372" s="4">
+        <v>6</v>
+      </c>
+      <c r="M372" s="4">
+        <v>0</v>
+      </c>
+      <c r="N372" s="4">
+        <v>0</v>
+      </c>
+      <c r="O372" s="1"/>
+      <c r="P372" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="373">
+      <c r="A373" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D373" s="2">
+        <v>32</v>
+      </c>
+      <c r="E373" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F373" s="1"/>
+      <c r="G373" s="1"/>
+      <c r="H373" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I373" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J373" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K373" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L373" s="4">
+        <v>60</v>
+      </c>
+      <c r="M373" s="4">
+        <v>0</v>
+      </c>
+      <c r="N373" s="4">
+        <v>0</v>
+      </c>
+      <c r="O373" s="1"/>
+      <c r="P373" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="374">
+      <c r="A374" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D374" s="2">
+        <v>32</v>
+      </c>
+      <c r="E374" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F374" s="1"/>
+      <c r="G374" s="1"/>
+      <c r="H374" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="I374" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="J374" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K374" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L374" s="4">
+        <v>100</v>
+      </c>
+      <c r="M374" s="4">
+        <v>0</v>
+      </c>
+      <c r="N374" s="4">
+        <v>0</v>
+      </c>
+      <c r="O374" s="1"/>
+      <c r="P374" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="375">
+      <c r="A375" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D375" s="2">
+        <v>32</v>
+      </c>
+      <c r="E375" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F375" s="1"/>
+      <c r="G375" s="1"/>
+      <c r="H375" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="J375" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K375" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L375" s="4">
+        <v>6</v>
+      </c>
+      <c r="M375" s="4">
+        <v>0</v>
+      </c>
+      <c r="N375" s="4">
+        <v>0</v>
+      </c>
+      <c r="O375" s="1"/>
+      <c r="P375" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="376">
+      <c r="A376" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D376" s="2">
+        <v>32</v>
+      </c>
+      <c r="E376" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F376" s="1"/>
+      <c r="G376" s="1"/>
+      <c r="H376" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="J376" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K376" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L376" s="4">
+        <v>10</v>
+      </c>
+      <c r="M376" s="4">
+        <v>0</v>
+      </c>
+      <c r="N376" s="4">
+        <v>0</v>
+      </c>
+      <c r="O376" s="1"/>
+      <c r="P376" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="377">
+      <c r="A377" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D377" s="2">
+        <v>32</v>
+      </c>
+      <c r="E377" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F377" s="1"/>
+      <c r="G377" s="1"/>
+      <c r="H377" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="I377" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="J377" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K377" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="L377" s="4">
+        <v>10</v>
+      </c>
+      <c r="M377" s="4">
+        <v>0</v>
+      </c>
+      <c r="N377" s="4">
+        <v>0</v>
+      </c>
+      <c r="O377" s="1"/>
+      <c r="P377" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="378">
+      <c r="A378" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D378" s="2">
+        <v>32</v>
+      </c>
+      <c r="E378" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F378" s="1"/>
+      <c r="G378" s="1"/>
+      <c r="H378" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="I378" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="J378" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K378" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L378" s="4">
+        <v>10</v>
+      </c>
+      <c r="M378" s="4">
+        <v>0</v>
+      </c>
+      <c r="N378" s="4">
+        <v>0</v>
+      </c>
+      <c r="O378" s="1"/>
+      <c r="P378" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="379">
+      <c r="A379" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D379" s="2">
+        <v>32</v>
+      </c>
+      <c r="E379" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F379" s="1"/>
+      <c r="G379" s="1"/>
+      <c r="H379" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J379" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K379" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L379" s="4">
+        <v>100</v>
+      </c>
+      <c r="M379" s="4">
+        <v>0</v>
+      </c>
+      <c r="N379" s="4">
+        <v>0</v>
+      </c>
+      <c r="O379" s="1"/>
+      <c r="P379" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="380">
+      <c r="A380" s="2">
+        <v>2507</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D380" s="2">
+        <v>32</v>
+      </c>
+      <c r="E380" s="3">
+        <v>46098.6669450579</v>
+      </c>
+      <c r="F380" s="1"/>
+      <c r="G380" s="1"/>
+      <c r="H380" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="J380" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K380" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L380" s="4">
+        <v>100</v>
+      </c>
+      <c r="M380" s="4">
+        <v>0</v>
+      </c>
+      <c r="N380" s="4">
+        <v>0</v>
+      </c>
+      <c r="O380" s="1"/>
+      <c r="P380" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1295,6 +1295,30 @@
     <t>PC 2000</t>
   </si>
   <si>
+    <t>K.08.1510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAMPA PARA MODULO CEGO WHITE  REF KW00 LIVING NOW</t>
+  </si>
+  <si>
+    <t>00000000007369</t>
+  </si>
+  <si>
+    <t>LOGIPLAN</t>
+  </si>
+  <si>
+    <t>K.08.1540</t>
+  </si>
+  <si>
+    <t>PULSADOR 10 A 250V BTICINO LIVING NOW COD K4005</t>
+  </si>
+  <si>
+    <t>K.08.1534</t>
+  </si>
+  <si>
+    <t>CAMPAINHA CIGARRA 80DB</t>
+  </si>
+  <si>
     <t>S.10.0062</t>
   </si>
   <si>
@@ -1355,24 +1379,6 @@
     <t>BONA SOAP LIMPADOR DE PISOS OLEADOS</t>
   </si>
   <si>
-    <t>K.08.1510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAMPA PARA MODULO CEGO WHITE  REF KW00 LIVING NOW</t>
-  </si>
-  <si>
-    <t>K.08.1540</t>
-  </si>
-  <si>
-    <t>PULSADOR 10 A 250V BTICINO LIVING NOW COD K4005</t>
-  </si>
-  <si>
-    <t>K.08.1534</t>
-  </si>
-  <si>
-    <t>CAMPAINHA CIGARRA 80DB</t>
-  </si>
-  <si>
     <t>C.04.0022</t>
   </si>
   <si>
@@ -1418,6 +1424,12 @@
     <t>PRENDEDOR DE PORTA</t>
   </si>
   <si>
+    <t>00000000010264</t>
+  </si>
+  <si>
+    <t>WORKS PRENDEDOR</t>
+  </si>
+  <si>
     <t>00000000008792</t>
   </si>
   <si>
@@ -1466,6 +1478,30 @@
     <t>REGINA CAMPOS SALLES MORAES ABREU</t>
   </si>
   <si>
+    <t>D.04.0010</t>
+  </si>
+  <si>
+    <t>PLACA DE OBRA COM LOGO OSBORNE MEDINDO 2,00 X 1,00</t>
+  </si>
+  <si>
+    <t>00000000008050</t>
+  </si>
+  <si>
+    <t>VISUAL ARTES</t>
+  </si>
+  <si>
+    <t>E.02.0213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROMAPISO 2MM X 600MM X50M  PROMAFLEX</t>
+  </si>
+  <si>
+    <t>00000000006868</t>
+  </si>
+  <si>
+    <t>PROMAFLEX FILME PVC</t>
+  </si>
+  <si>
     <t>E.04.0600</t>
   </si>
   <si>
@@ -1568,18 +1604,6 @@
     <t>CADEIRA SECRETÁRIA FIXA</t>
   </si>
   <si>
-    <t>D.04.0010</t>
-  </si>
-  <si>
-    <t>PLACA DE OBRA COM LOGO OSBORNE MEDINDO 2,00 X 1,00</t>
-  </si>
-  <si>
-    <t>E.02.0213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROMAPISO 2MM X 600MM X50M  PROMAFLEX</t>
-  </si>
-  <si>
     <t>E.04.0173</t>
   </si>
   <si>
@@ -1673,24 +1697,48 @@
     <t>LIMPO SOLUÇÕES</t>
   </si>
   <si>
+    <t>E.02.0207</t>
+  </si>
+  <si>
+    <t>FITA ANTIDERRAPANTE TRANSPARENTE 50MMX5M</t>
+  </si>
+  <si>
     <t>00000000000762</t>
   </si>
   <si>
     <t>CASA DAS FECHADURAS</t>
   </si>
   <si>
+    <t>O.01.0110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABUA DE PINUS  1" X 4"</t>
+  </si>
+  <si>
+    <t>O.01.0121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABUA DE PINUS  3" X 3"</t>
+  </si>
+  <si>
+    <t>R.02.0153</t>
+  </si>
+  <si>
+    <t>THINNER - REDUTOR 5 L</t>
+  </si>
+  <si>
+    <t>P3.03.0192</t>
+  </si>
+  <si>
+    <t>SUPORTE PARA TV BI-ARTICULADO - PARA TV'S DE 10 A 60 POLEGADAS - COR PRETO</t>
+  </si>
+  <si>
     <t>C.04.0116</t>
   </si>
   <si>
     <t xml:space="preserve">COPO DESCARTAVEL  PARA AGUA 200 ML TIRA COM 100</t>
   </si>
   <si>
-    <t>E.02.0207</t>
-  </si>
-  <si>
-    <t>FITA ANTIDERRAPANTE TRANSPARENTE 50MMX5M</t>
-  </si>
-  <si>
     <t>F.04.0072</t>
   </si>
   <si>
@@ -1703,30 +1751,6 @@
     <t>BETONEIRA</t>
   </si>
   <si>
-    <t>O.01.0110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABUA DE PINUS  1" X 4"</t>
-  </si>
-  <si>
-    <t>O.01.0121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABUA DE PINUS  3" X 3"</t>
-  </si>
-  <si>
-    <t>R.02.0153</t>
-  </si>
-  <si>
-    <t>THINNER - REDUTOR 5 L</t>
-  </si>
-  <si>
-    <t>P3.03.0192</t>
-  </si>
-  <si>
-    <t>SUPORTE PARA TV BI-ARTICULADO - PARA TV'S DE 10 A 60 POLEGADAS - COR PRETO</t>
-  </si>
-  <si>
     <t>E.03.0101</t>
   </si>
   <si>
@@ -1742,6 +1766,12 @@
     <t xml:space="preserve">TABUA DE PINUS  1" X 6"</t>
   </si>
   <si>
+    <t>00000000008356</t>
+  </si>
+  <si>
+    <t>PALMAPLASTIC</t>
+  </si>
+  <si>
     <t>O.01.0116</t>
   </si>
   <si>
@@ -1775,6 +1805,12 @@
     <t>DIA</t>
   </si>
   <si>
+    <t>00000000008708</t>
+  </si>
+  <si>
+    <t>GADE</t>
+  </si>
+  <si>
     <t>K.01.0265</t>
   </si>
   <si>
@@ -1809,6 +1845,12 @@
   </si>
   <si>
     <t>PONTALETE DE CEDRINHO - 3 X 3" - 1ª IND</t>
+  </si>
+  <si>
+    <t>00000000009484</t>
+  </si>
+  <si>
+    <t>KALUTA</t>
   </si>
   <si>
     <t>O.01.0008</t>
@@ -12494,10 +12536,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F220" s="2">
-        <v>82635</v>
+        <v>82705</v>
       </c>
       <c r="G220" s="3">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>427</v>
@@ -12512,19 +12554,19 @@
         <v>21</v>
       </c>
       <c r="L220" s="4">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="M220" s="4">
-        <v>22</v>
+        <v>15.45</v>
       </c>
       <c r="N220" s="4">
-        <v>110</v>
+        <v>618</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>32</v>
+        <v>429</v>
       </c>
       <c r="P220" s="1" t="s">
-        <v>33</v>
+        <v>430</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="221">
@@ -12544,37 +12586,37 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F221" s="2">
-        <v>82635</v>
+        <v>82705</v>
       </c>
       <c r="G221" s="3">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="H221" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K221" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L221" s="4">
+        <v>2</v>
+      </c>
+      <c r="M221" s="4">
+        <v>53.24</v>
+      </c>
+      <c r="N221" s="4">
+        <v>106.48</v>
+      </c>
+      <c r="O221" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="I221" s="1" t="s">
+      <c r="P221" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="J221" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K221" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L221" s="4">
-        <v>5</v>
-      </c>
-      <c r="M221" s="4">
-        <v>25.9</v>
-      </c>
-      <c r="N221" s="4">
-        <v>129.5</v>
-      </c>
-      <c r="O221" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P221" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="222">
@@ -12594,16 +12636,16 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F222" s="2">
-        <v>82635</v>
+        <v>82705</v>
       </c>
       <c r="G222" s="3">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>20</v>
@@ -12612,19 +12654,19 @@
         <v>21</v>
       </c>
       <c r="L222" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M222" s="4">
-        <v>55</v>
+        <v>187.77</v>
       </c>
       <c r="N222" s="4">
-        <v>330</v>
+        <v>187.77</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>32</v>
+        <v>429</v>
       </c>
       <c r="P222" s="1" t="s">
-        <v>33</v>
+        <v>430</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="223">
@@ -12644,16 +12686,16 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F223" s="2">
-        <v>82681</v>
+        <v>82635</v>
       </c>
       <c r="G223" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>20</v>
@@ -12662,19 +12704,19 @@
         <v>21</v>
       </c>
       <c r="L223" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M223" s="4">
-        <v>3077</v>
+        <v>22</v>
       </c>
       <c r="N223" s="4">
-        <v>3077</v>
+        <v>110</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>435</v>
+        <v>32</v>
       </c>
       <c r="P223" s="1" t="s">
-        <v>436</v>
+        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="224">
@@ -12694,10 +12736,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F224" s="2">
-        <v>82681</v>
+        <v>82635</v>
       </c>
       <c r="G224" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="H224" s="1" t="s">
         <v>437</v>
@@ -12712,19 +12754,19 @@
         <v>21</v>
       </c>
       <c r="L224" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M224" s="4">
-        <v>5699</v>
+        <v>25.9</v>
       </c>
       <c r="N224" s="4">
-        <v>5699</v>
+        <v>129.5</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>435</v>
+        <v>32</v>
       </c>
       <c r="P224" s="1" t="s">
-        <v>436</v>
+        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="225">
@@ -12744,10 +12786,10 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F225" s="2">
-        <v>82681</v>
+        <v>82635</v>
       </c>
       <c r="G225" s="3">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>439</v>
@@ -12762,19 +12804,19 @@
         <v>21</v>
       </c>
       <c r="L225" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M225" s="4">
-        <v>1273.99</v>
+        <v>55</v>
       </c>
       <c r="N225" s="4">
-        <v>2547.98</v>
+        <v>330</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>435</v>
+        <v>32</v>
       </c>
       <c r="P225" s="1" t="s">
-        <v>436</v>
+        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="226">
@@ -12815,16 +12857,16 @@
         <v>1</v>
       </c>
       <c r="M226" s="4">
-        <v>3424.61</v>
+        <v>3077</v>
       </c>
       <c r="N226" s="4">
-        <v>3424.61</v>
+        <v>3077</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="P226" s="1" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="227">
@@ -12844,37 +12886,37 @@
         <v>46094.4767297338</v>
       </c>
       <c r="F227" s="2">
-        <v>82635</v>
+        <v>82681</v>
       </c>
       <c r="G227" s="3">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="H227" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K227" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L227" s="4">
+        <v>1</v>
+      </c>
+      <c r="M227" s="4">
+        <v>5699</v>
+      </c>
+      <c r="N227" s="4">
+        <v>5699</v>
+      </c>
+      <c r="O227" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="I227" s="1" t="s">
+      <c r="P227" s="1" t="s">
         <v>444</v>
-      </c>
-      <c r="J227" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K227" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="L227" s="4">
-        <v>18</v>
-      </c>
-      <c r="M227" s="4">
-        <v>14.3</v>
-      </c>
-      <c r="N227" s="4">
-        <v>257.4</v>
-      </c>
-      <c r="O227" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P227" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="228">
@@ -12893,31 +12935,39 @@
       <c r="E228" s="3">
         <v>46094.4767297338</v>
       </c>
-      <c r="F228" s="1"/>
-      <c r="G228" s="1"/>
+      <c r="F228" s="2">
+        <v>82681</v>
+      </c>
+      <c r="G228" s="3">
+        <v>46098</v>
+      </c>
       <c r="H228" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K228" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L228" s="4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M228" s="4">
-        <v>0</v>
+        <v>1273.99</v>
       </c>
       <c r="N228" s="4">
-        <v>0</v>
-      </c>
-      <c r="O228" s="1"/>
-      <c r="P228" s="1"/>
+        <v>2547.98</v>
+      </c>
+      <c r="O228" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="P228" s="1" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="229">
       <c r="A229" s="2">
@@ -12935,13 +12985,17 @@
       <c r="E229" s="3">
         <v>46094.4767297338</v>
       </c>
-      <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
+      <c r="F229" s="2">
+        <v>82681</v>
+      </c>
+      <c r="G229" s="3">
+        <v>46098</v>
+      </c>
       <c r="H229" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>20</v>
@@ -12950,16 +13004,20 @@
         <v>21</v>
       </c>
       <c r="L229" s="4">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="M229" s="4">
-        <v>0</v>
+        <v>3424.61</v>
       </c>
       <c r="N229" s="4">
-        <v>0</v>
-      </c>
-      <c r="O229" s="1"/>
-      <c r="P229" s="1"/>
+        <v>3424.61</v>
+      </c>
+      <c r="O229" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="P229" s="1" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="230">
       <c r="A230" s="2">
@@ -12977,31 +13035,39 @@
       <c r="E230" s="3">
         <v>46094.4767297338</v>
       </c>
-      <c r="F230" s="1"/>
-      <c r="G230" s="1"/>
+      <c r="F230" s="2">
+        <v>82635</v>
+      </c>
+      <c r="G230" s="3">
+        <v>46094</v>
+      </c>
       <c r="H230" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K230" s="1" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="L230" s="4">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="M230" s="4">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="N230" s="4">
-        <v>0</v>
-      </c>
-      <c r="O230" s="1"/>
-      <c r="P230" s="1"/>
+        <v>257.4</v>
+      </c>
+      <c r="O230" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P230" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="231">
       <c r="A231" s="2">
@@ -13022,19 +13088,19 @@
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
       <c r="H231" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>20</v>
+        <v>280</v>
       </c>
       <c r="K231" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L231" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M231" s="4">
         <v>0</v>
@@ -13133,10 +13199,10 @@
         <v>20</v>
       </c>
       <c r="M233" s="4">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="N233" s="4">
-        <v>90</v>
+        <v>90.6</v>
       </c>
       <c r="O233" s="1" t="s">
         <v>36</v>
@@ -13168,10 +13234,10 @@
         <v>46097</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J234" s="1" t="s">
         <v>20</v>
@@ -13218,10 +13284,10 @@
         <v>46097</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>20</v>
@@ -13318,10 +13384,10 @@
         <v>46097</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>20</v>
@@ -13368,10 +13434,10 @@
         <v>46097</v>
       </c>
       <c r="H238" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="J238" s="1" t="s">
         <v>20</v>
@@ -13468,10 +13534,10 @@
         <v>46097</v>
       </c>
       <c r="H240" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>20</v>
@@ -13518,10 +13584,10 @@
         <v>46097</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>20</v>
@@ -13568,10 +13634,10 @@
         <v>46097</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>20</v>
@@ -13618,10 +13684,10 @@
         <v>46097</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J243" s="1" t="s">
         <v>20</v>
@@ -13668,16 +13734,16 @@
         <v>46097</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K244" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="L244" s="4">
         <v>10</v>
@@ -13711,13 +13777,17 @@
       <c r="E245" s="3">
         <v>46097.447005</v>
       </c>
-      <c r="F245" s="1"/>
-      <c r="G245" s="1"/>
+      <c r="F245" s="2">
+        <v>82721</v>
+      </c>
+      <c r="G245" s="3">
+        <v>46099</v>
+      </c>
       <c r="H245" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>20</v>
@@ -13729,13 +13799,17 @@
         <v>14</v>
       </c>
       <c r="M245" s="4">
-        <v>0</v>
+        <v>150.16</v>
       </c>
       <c r="N245" s="4">
-        <v>0</v>
-      </c>
-      <c r="O245" s="1"/>
-      <c r="P245" s="1"/>
+        <v>2102.24</v>
+      </c>
+      <c r="O245" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="P245" s="1" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="246">
       <c r="A246" s="2">
@@ -13831,10 +13905,10 @@
         <v>1448.08</v>
       </c>
       <c r="O247" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="P247" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="248">
@@ -13860,10 +13934,10 @@
         <v>46097</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="J248" s="1" t="s">
         <v>20</v>
@@ -13881,10 +13955,10 @@
         <v>1020.6</v>
       </c>
       <c r="O248" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="P248" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="249">
@@ -13892,7 +13966,7 @@
         <v>2504</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>17</v>
@@ -13910,10 +13984,10 @@
         <v>46097</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>20</v>
@@ -13942,7 +14016,7 @@
         <v>2504</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>17</v>
@@ -13992,7 +14066,7 @@
         <v>2504</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>17</v>
@@ -14010,10 +14084,10 @@
         <v>46097</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>20</v>
@@ -14042,7 +14116,7 @@
         <v>2504</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>17</v>
@@ -14060,10 +14134,10 @@
         <v>46097</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>20</v>
@@ -14081,10 +14155,10 @@
         <v>9.5</v>
       </c>
       <c r="O252" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="P252" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="253">
@@ -14092,7 +14166,7 @@
         <v>2504</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>17</v>
@@ -14142,7 +14216,7 @@
         <v>2504</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>17</v>
@@ -14160,10 +14234,10 @@
         <v>46097</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>20</v>
@@ -14181,10 +14255,10 @@
         <v>140</v>
       </c>
       <c r="O254" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="P254" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="255">
@@ -14192,7 +14266,7 @@
         <v>2504</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>17</v>
@@ -14210,10 +14284,10 @@
         <v>46097</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>20</v>
@@ -14242,7 +14316,7 @@
         <v>2601</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>94</v>
@@ -14254,16 +14328,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F256" s="2">
-        <v>82692</v>
+        <v>82717</v>
       </c>
       <c r="G256" s="3">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>20</v>
@@ -14275,16 +14349,16 @@
         <v>1</v>
       </c>
       <c r="M256" s="4">
-        <v>322</v>
+        <v>860</v>
       </c>
       <c r="N256" s="4">
-        <v>322</v>
+        <v>860</v>
       </c>
       <c r="O256" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="P256" s="1" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="257">
@@ -14292,7 +14366,7 @@
         <v>2601</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>94</v>
@@ -14304,37 +14378,37 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F257" s="2">
-        <v>82691</v>
+        <v>82716</v>
       </c>
       <c r="G257" s="3">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J257" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="L257" s="4">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M257" s="4">
-        <v>29</v>
+        <v>300</v>
       </c>
       <c r="N257" s="4">
-        <v>58</v>
+        <v>2400</v>
       </c>
       <c r="O257" s="1" t="s">
-        <v>126</v>
+        <v>494</v>
       </c>
       <c r="P257" s="1" t="s">
-        <v>127</v>
+        <v>495</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="258">
@@ -14342,7 +14416,7 @@
         <v>2601</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>94</v>
@@ -14354,16 +14428,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F258" s="2">
-        <v>82691</v>
+        <v>82692</v>
       </c>
       <c r="G258" s="3">
         <v>46098</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>20</v>
@@ -14372,19 +14446,19 @@
         <v>21</v>
       </c>
       <c r="L258" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M258" s="4">
-        <v>23.77</v>
+        <v>322</v>
       </c>
       <c r="N258" s="4">
-        <v>47.54</v>
+        <v>322</v>
       </c>
       <c r="O258" s="1" t="s">
-        <v>126</v>
+        <v>498</v>
       </c>
       <c r="P258" s="1" t="s">
-        <v>127</v>
+        <v>499</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="259">
@@ -14392,7 +14466,7 @@
         <v>2601</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>94</v>
@@ -14404,16 +14478,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F259" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="G259" s="3">
         <v>46098</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="J259" s="1" t="s">
         <v>20</v>
@@ -14422,19 +14496,19 @@
         <v>21</v>
       </c>
       <c r="L259" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M259" s="4">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="N259" s="4">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="O259" s="1" t="s">
-        <v>486</v>
+        <v>126</v>
       </c>
       <c r="P259" s="1" t="s">
-        <v>487</v>
+        <v>127</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="260">
@@ -14442,7 +14516,7 @@
         <v>2601</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>94</v>
@@ -14454,16 +14528,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F260" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="G260" s="3">
         <v>46098</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="J260" s="1" t="s">
         <v>20</v>
@@ -14475,16 +14549,16 @@
         <v>2</v>
       </c>
       <c r="M260" s="4">
-        <v>122</v>
+        <v>23.77</v>
       </c>
       <c r="N260" s="4">
-        <v>244</v>
+        <v>47.54</v>
       </c>
       <c r="O260" s="1" t="s">
-        <v>486</v>
+        <v>126</v>
       </c>
       <c r="P260" s="1" t="s">
-        <v>487</v>
+        <v>127</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="261">
@@ -14492,7 +14566,7 @@
         <v>2601</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>94</v>
@@ -14504,16 +14578,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F261" s="2">
-        <v>82691</v>
+        <v>82692</v>
       </c>
       <c r="G261" s="3">
         <v>46098</v>
       </c>
       <c r="H261" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="I261" s="1" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="J261" s="1" t="s">
         <v>20</v>
@@ -14522,19 +14596,19 @@
         <v>21</v>
       </c>
       <c r="L261" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M261" s="4">
-        <v>123.37</v>
+        <v>145</v>
       </c>
       <c r="N261" s="4">
-        <v>246.74</v>
+        <v>145</v>
       </c>
       <c r="O261" s="1" t="s">
-        <v>126</v>
+        <v>498</v>
       </c>
       <c r="P261" s="1" t="s">
-        <v>127</v>
+        <v>499</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="262">
@@ -14542,7 +14616,7 @@
         <v>2601</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>94</v>
@@ -14560,31 +14634,31 @@
         <v>46098</v>
       </c>
       <c r="H262" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="I262" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="J262" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K262" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L262" s="4">
+        <v>2</v>
+      </c>
+      <c r="M262" s="4">
+        <v>122</v>
+      </c>
+      <c r="N262" s="4">
+        <v>244</v>
+      </c>
+      <c r="O262" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="I262" s="1" t="s">
+      <c r="P262" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="J262" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K262" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L262" s="4">
-        <v>1</v>
-      </c>
-      <c r="M262" s="4">
-        <v>61</v>
-      </c>
-      <c r="N262" s="4">
-        <v>61</v>
-      </c>
-      <c r="O262" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="P262" s="1" t="s">
-        <v>487</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="263">
@@ -14592,7 +14666,7 @@
         <v>2601</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>94</v>
@@ -14604,16 +14678,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F263" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="G263" s="3">
         <v>46098</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>20</v>
@@ -14625,16 +14699,16 @@
         <v>2</v>
       </c>
       <c r="M263" s="4">
-        <v>92.8</v>
+        <v>123.37</v>
       </c>
       <c r="N263" s="4">
-        <v>185.6</v>
+        <v>246.74</v>
       </c>
       <c r="O263" s="1" t="s">
-        <v>486</v>
+        <v>126</v>
       </c>
       <c r="P263" s="1" t="s">
-        <v>487</v>
+        <v>127</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="264">
@@ -14642,7 +14716,7 @@
         <v>2601</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>94</v>
@@ -14660,10 +14734,10 @@
         <v>46098</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>20</v>
@@ -14672,19 +14746,19 @@
         <v>21</v>
       </c>
       <c r="L264" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M264" s="4">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N264" s="4">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="O264" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="P264" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="265">
@@ -14692,7 +14766,7 @@
         <v>2601</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>94</v>
@@ -14704,16 +14778,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F265" s="2">
-        <v>82691</v>
+        <v>82692</v>
       </c>
       <c r="G265" s="3">
         <v>46098</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>20</v>
@@ -14725,16 +14799,16 @@
         <v>2</v>
       </c>
       <c r="M265" s="4">
-        <v>246.74</v>
+        <v>92.8</v>
       </c>
       <c r="N265" s="4">
-        <v>493.48</v>
+        <v>185.6</v>
       </c>
       <c r="O265" s="1" t="s">
-        <v>126</v>
+        <v>498</v>
       </c>
       <c r="P265" s="1" t="s">
-        <v>127</v>
+        <v>499</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="266">
@@ -14742,7 +14816,7 @@
         <v>2601</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>94</v>
@@ -14760,10 +14834,10 @@
         <v>46098</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>20</v>
@@ -14772,19 +14846,19 @@
         <v>21</v>
       </c>
       <c r="L266" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M266" s="4">
-        <v>253</v>
+        <v>31</v>
       </c>
       <c r="N266" s="4">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="O266" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="P266" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="267">
@@ -14792,7 +14866,7 @@
         <v>2601</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>94</v>
@@ -14804,16 +14878,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F267" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="G267" s="3">
         <v>46098</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>20</v>
@@ -14822,19 +14896,19 @@
         <v>21</v>
       </c>
       <c r="L267" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M267" s="4">
-        <v>625</v>
+        <v>246.74</v>
       </c>
       <c r="N267" s="4">
-        <v>625</v>
+        <v>493.48</v>
       </c>
       <c r="O267" s="1" t="s">
-        <v>486</v>
+        <v>126</v>
       </c>
       <c r="P267" s="1" t="s">
-        <v>487</v>
+        <v>127</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="268">
@@ -14842,7 +14916,7 @@
         <v>2601</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>94</v>
@@ -14854,16 +14928,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F268" s="2">
-        <v>82699</v>
+        <v>82692</v>
       </c>
       <c r="G268" s="3">
         <v>46098</v>
       </c>
       <c r="H268" s="1" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>20</v>
@@ -14872,19 +14946,19 @@
         <v>21</v>
       </c>
       <c r="L268" s="4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="M268" s="4">
-        <v>390</v>
+        <v>253</v>
       </c>
       <c r="N268" s="4">
-        <v>13650</v>
+        <v>253</v>
       </c>
       <c r="O268" s="1" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
       <c r="P268" s="1" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="269">
@@ -14892,7 +14966,7 @@
         <v>2601</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>94</v>
@@ -14910,31 +14984,31 @@
         <v>46098</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K269" s="1" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="L269" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M269" s="4">
-        <v>5.66</v>
+        <v>625</v>
       </c>
       <c r="N269" s="4">
-        <v>283</v>
+        <v>625</v>
       </c>
       <c r="O269" s="1" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="P269" s="1" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="270">
@@ -14942,7 +15016,7 @@
         <v>2601</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>94</v>
@@ -14953,13 +15027,17 @@
       <c r="E270" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F270" s="1"/>
-      <c r="G270" s="1"/>
+      <c r="F270" s="2">
+        <v>82699</v>
+      </c>
+      <c r="G270" s="3">
+        <v>46098</v>
+      </c>
       <c r="H270" s="1" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>20</v>
@@ -14968,23 +15046,27 @@
         <v>21</v>
       </c>
       <c r="L270" s="4">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="M270" s="4">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N270" s="4">
-        <v>0</v>
-      </c>
-      <c r="O270" s="1"/>
-      <c r="P270" s="1"/>
+        <v>13650</v>
+      </c>
+      <c r="O270" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="P270" s="1" t="s">
+        <v>525</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="271">
       <c r="A271" s="2">
         <v>2601</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>94</v>
@@ -14995,38 +15077,46 @@
       <c r="E271" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F271" s="1"/>
-      <c r="G271" s="1"/>
+      <c r="F271" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G271" s="3">
+        <v>46098</v>
+      </c>
       <c r="H271" s="1" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K271" s="1" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="L271" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M271" s="4">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N271" s="4">
-        <v>0</v>
-      </c>
-      <c r="O271" s="1"/>
-      <c r="P271" s="1"/>
+        <v>283</v>
+      </c>
+      <c r="O271" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="P271" s="1" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="272">
       <c r="A272" s="2">
         <v>2601</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>94</v>
@@ -15040,19 +15130,19 @@
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K272" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L272" s="4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M272" s="4">
         <v>0</v>
@@ -15068,7 +15158,7 @@
         <v>2601</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>94</v>
@@ -15082,10 +15172,10 @@
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>20</v>
@@ -15110,7 +15200,7 @@
         <v>2601</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>94</v>
@@ -15124,10 +15214,10 @@
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
       <c r="H274" s="1" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>20</v>
@@ -15152,7 +15242,7 @@
         <v>2317</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>94</v>
@@ -15202,7 +15292,7 @@
         <v>2317</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>94</v>
@@ -15252,7 +15342,7 @@
         <v>2317</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>94</v>
@@ -15270,10 +15360,10 @@
         <v>46097</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>20</v>
@@ -15302,7 +15392,7 @@
         <v>2404</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>17</v>
@@ -15314,7 +15404,7 @@
         <v>46098.4966723148</v>
       </c>
       <c r="F278" s="2">
-        <v>82683</v>
+        <v>82685</v>
       </c>
       <c r="G278" s="3">
         <v>46098</v>
@@ -15341,10 +15431,10 @@
         <v>39</v>
       </c>
       <c r="O278" s="1" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="P278" s="1" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="279">
@@ -15352,7 +15442,7 @@
         <v>2404</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>17</v>
@@ -15364,7 +15454,7 @@
         <v>46098.4966723148</v>
       </c>
       <c r="F279" s="2">
-        <v>82683</v>
+        <v>82685</v>
       </c>
       <c r="G279" s="3">
         <v>46098</v>
@@ -15385,16 +15475,16 @@
         <v>1</v>
       </c>
       <c r="M279" s="4">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="N279" s="4">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="P279" s="1" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="280">
@@ -15402,7 +15492,7 @@
         <v>2404</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>17</v>
@@ -15420,10 +15510,10 @@
         <v>46098</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>20</v>
@@ -15432,13 +15522,13 @@
         <v>21</v>
       </c>
       <c r="L280" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M280" s="4">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="N280" s="4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O280" s="1" t="s">
         <v>32</v>
@@ -15452,7 +15542,7 @@
         <v>2404</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>17</v>
@@ -15464,16 +15554,16 @@
         <v>46098.4966723148</v>
       </c>
       <c r="F281" s="2">
-        <v>82683</v>
+        <v>82685</v>
       </c>
       <c r="G281" s="3">
         <v>46098</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>459</v>
+        <v>43</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>460</v>
+        <v>44</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>20</v>
@@ -15482,19 +15572,19 @@
         <v>21</v>
       </c>
       <c r="L281" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M281" s="4">
-        <v>17.3</v>
+        <v>16</v>
       </c>
       <c r="N281" s="4">
-        <v>17.3</v>
+        <v>80</v>
       </c>
       <c r="O281" s="1" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="P281" s="1" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="282">
@@ -15502,7 +15592,7 @@
         <v>2404</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>17</v>
@@ -15513,13 +15603,17 @@
       <c r="E282" s="3">
         <v>46098.4966723148</v>
       </c>
-      <c r="F282" s="1"/>
-      <c r="G282" s="1"/>
+      <c r="F282" s="2">
+        <v>82685</v>
+      </c>
+      <c r="G282" s="3">
+        <v>46098</v>
+      </c>
       <c r="H282" s="1" t="s">
-        <v>117</v>
+        <v>538</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>118</v>
+        <v>539</v>
       </c>
       <c r="J282" s="1" t="s">
         <v>20</v>
@@ -15528,23 +15622,27 @@
         <v>21</v>
       </c>
       <c r="L282" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M282" s="4">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="N282" s="4">
-        <v>0</v>
-      </c>
-      <c r="O282" s="1"/>
-      <c r="P282" s="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="O282" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P282" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="283">
       <c r="A283" s="2">
         <v>2404</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>17</v>
@@ -15555,13 +15653,17 @@
       <c r="E283" s="3">
         <v>46098.4966723148</v>
       </c>
-      <c r="F283" s="1"/>
-      <c r="G283" s="1"/>
+      <c r="F283" s="2">
+        <v>82685</v>
+      </c>
+      <c r="G283" s="3">
+        <v>46098</v>
+      </c>
       <c r="H283" s="1" t="s">
-        <v>530</v>
+        <v>461</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>531</v>
+        <v>462</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>20</v>
@@ -15570,23 +15672,27 @@
         <v>21</v>
       </c>
       <c r="L283" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M283" s="4">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="N283" s="4">
-        <v>0</v>
-      </c>
-      <c r="O283" s="1"/>
-      <c r="P283" s="1"/>
+        <v>17.3</v>
+      </c>
+      <c r="O283" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P283" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="284">
       <c r="A284" s="2">
         <v>2514</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>94</v>
@@ -15604,10 +15710,10 @@
         <v>46098</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>20</v>
@@ -15625,10 +15731,10 @@
         <v>1011.5</v>
       </c>
       <c r="O284" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="P284" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="285">
@@ -15636,7 +15742,7 @@
         <v>2514</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>94</v>
@@ -15654,10 +15760,10 @@
         <v>46098</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>20</v>
@@ -15675,10 +15781,10 @@
         <v>3290</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="P285" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="286">
@@ -15686,7 +15792,7 @@
         <v>2514</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>94</v>
@@ -15704,10 +15810,10 @@
         <v>46098</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="J286" s="1" t="s">
         <v>20</v>
@@ -15725,10 +15831,10 @@
         <v>1240</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="P286" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="287">
@@ -15736,7 +15842,7 @@
         <v>2514</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>94</v>
@@ -15754,10 +15860,10 @@
         <v>46098</v>
       </c>
       <c r="H287" s="1" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="I287" s="1" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="J287" s="1" t="s">
         <v>20</v>
@@ -15775,10 +15881,10 @@
         <v>400</v>
       </c>
       <c r="O287" s="1" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="P287" s="1" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="288">
@@ -15786,7 +15892,7 @@
         <v>2514</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>94</v>
@@ -15828,7 +15934,7 @@
         <v>2514</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>94</v>
@@ -15842,10 +15948,10 @@
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
       <c r="H289" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I289" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J289" s="1" t="s">
         <v>20</v>
@@ -15870,7 +15976,7 @@
         <v>2514</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>94</v>
@@ -15884,10 +15990,10 @@
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
       <c r="H290" s="1" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="I290" s="1" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="J290" s="1" t="s">
         <v>20</v>
@@ -15912,7 +16018,7 @@
         <v>2514</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>94</v>
@@ -15926,10 +16032,10 @@
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
       <c r="H291" s="1" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>20</v>
@@ -15954,7 +16060,7 @@
         <v>2514</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>94</v>
@@ -15968,10 +16074,10 @@
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
       <c r="H292" s="1" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="I292" s="1" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="J292" s="1" t="s">
         <v>20</v>
@@ -15996,7 +16102,7 @@
         <v>2514</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>94</v>
@@ -16010,10 +16116,10 @@
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
       <c r="H293" s="1" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="I293" s="1" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="J293" s="1" t="s">
         <v>20</v>
@@ -16077,10 +16183,10 @@
         <v>44</v>
       </c>
       <c r="O294" s="1" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="P294" s="1" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="295">
@@ -16127,10 +16233,10 @@
         <v>17.9</v>
       </c>
       <c r="O295" s="1" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="P295" s="1" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="296">
@@ -16150,37 +16256,37 @@
         <v>46098.5034667708</v>
       </c>
       <c r="F296" s="2">
-        <v>82687</v>
+        <v>82722</v>
       </c>
       <c r="G296" s="3">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="H296" s="1" t="s">
-        <v>216</v>
+        <v>561</v>
       </c>
       <c r="I296" s="1" t="s">
-        <v>217</v>
+        <v>562</v>
       </c>
       <c r="J296" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K296" s="1" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="L296" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M296" s="4">
-        <v>38.5</v>
+        <v>63.6</v>
       </c>
       <c r="N296" s="4">
-        <v>577.5</v>
+        <v>318</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>553</v>
+        <v>250</v>
       </c>
       <c r="P296" s="1" t="s">
-        <v>554</v>
+        <v>251</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="297">
@@ -16199,31 +16305,39 @@
       <c r="E297" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F297" s="1"/>
-      <c r="G297" s="1"/>
+      <c r="F297" s="2">
+        <v>82722</v>
+      </c>
+      <c r="G297" s="3">
+        <v>46099</v>
+      </c>
       <c r="H297" s="1" t="s">
-        <v>555</v>
+        <v>256</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>556</v>
+        <v>257</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K297" s="1" t="s">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="L297" s="4">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="M297" s="4">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="N297" s="4">
-        <v>0</v>
-      </c>
-      <c r="O297" s="1"/>
-      <c r="P297" s="1"/>
+        <v>1912.5</v>
+      </c>
+      <c r="O297" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P297" s="1" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="298">
       <c r="A298" s="2">
@@ -16241,31 +16355,39 @@
       <c r="E298" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F298" s="1"/>
-      <c r="G298" s="1"/>
+      <c r="F298" s="2">
+        <v>82722</v>
+      </c>
+      <c r="G298" s="3">
+        <v>46099</v>
+      </c>
       <c r="H298" s="1" t="s">
-        <v>557</v>
+        <v>214</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>558</v>
+        <v>215</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K298" s="1" t="s">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="L298" s="4">
-        <v>5</v>
+        <v>150</v>
       </c>
       <c r="M298" s="4">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="N298" s="4">
-        <v>0</v>
-      </c>
-      <c r="O298" s="1"/>
-      <c r="P298" s="1"/>
+        <v>1335</v>
+      </c>
+      <c r="O298" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P298" s="1" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="299">
       <c r="A299" s="2">
@@ -16283,31 +16405,39 @@
       <c r="E299" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F299" s="1"/>
-      <c r="G299" s="1"/>
+      <c r="F299" s="2">
+        <v>82687</v>
+      </c>
+      <c r="G299" s="3">
+        <v>46098</v>
+      </c>
       <c r="H299" s="1" t="s">
-        <v>559</v>
+        <v>216</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>560</v>
+        <v>217</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K299" s="1" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="L299" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M299" s="4">
-        <v>0</v>
+        <v>38.5</v>
       </c>
       <c r="N299" s="4">
-        <v>0</v>
-      </c>
-      <c r="O299" s="1"/>
-      <c r="P299" s="1"/>
+        <v>577.5</v>
+      </c>
+      <c r="O299" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="P299" s="1" t="s">
+        <v>564</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="300">
       <c r="A300" s="2">
@@ -16325,31 +16455,39 @@
       <c r="E300" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F300" s="1"/>
-      <c r="G300" s="1"/>
+      <c r="F300" s="2">
+        <v>82723</v>
+      </c>
+      <c r="G300" s="3">
+        <v>46099</v>
+      </c>
       <c r="H300" s="1" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K300" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="L300" s="4">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="M300" s="4">
-        <v>0</v>
+        <v>3.333333</v>
       </c>
       <c r="N300" s="4">
-        <v>0</v>
-      </c>
-      <c r="O300" s="1"/>
-      <c r="P300" s="1"/>
+        <v>399.99996</v>
+      </c>
+      <c r="O300" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="P300" s="1" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="301">
       <c r="A301" s="2">
@@ -16367,31 +16505,39 @@
       <c r="E301" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F301" s="1"/>
-      <c r="G301" s="1"/>
+      <c r="F301" s="2">
+        <v>82723</v>
+      </c>
+      <c r="G301" s="3">
+        <v>46099</v>
+      </c>
       <c r="H301" s="1" t="s">
-        <v>256</v>
+        <v>567</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>257</v>
+        <v>568</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K301" s="1" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="L301" s="4">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="M301" s="4">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="N301" s="4">
-        <v>1200</v>
-      </c>
-      <c r="O301" s="1"/>
-      <c r="P301" s="1"/>
+        <v>1152</v>
+      </c>
+      <c r="O301" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="P301" s="1" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="302">
       <c r="A302" s="2">
@@ -16409,31 +16555,39 @@
       <c r="E302" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F302" s="1"/>
-      <c r="G302" s="1"/>
+      <c r="F302" s="2">
+        <v>82723</v>
+      </c>
+      <c r="G302" s="3">
+        <v>46099</v>
+      </c>
       <c r="H302" s="1" t="s">
-        <v>214</v>
+        <v>557</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>215</v>
+        <v>558</v>
       </c>
       <c r="J302" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K302" s="1" t="s">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="L302" s="4">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="M302" s="4">
-        <v>7.21</v>
+        <v>14</v>
       </c>
       <c r="N302" s="4">
-        <v>1081.5</v>
-      </c>
-      <c r="O302" s="1"/>
-      <c r="P302" s="1"/>
+        <v>1260</v>
+      </c>
+      <c r="O302" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="P302" s="1" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="303">
       <c r="A303" s="2">
@@ -16451,31 +16605,39 @@
       <c r="E303" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F303" s="1"/>
-      <c r="G303" s="1"/>
+      <c r="F303" s="2">
+        <v>82723</v>
+      </c>
+      <c r="G303" s="3">
+        <v>46099</v>
+      </c>
       <c r="H303" s="1" t="s">
-        <v>563</v>
+        <v>260</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>564</v>
+        <v>261</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K303" s="1" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="L303" s="4">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="M303" s="4">
-        <v>0</v>
+        <v>172.9</v>
       </c>
       <c r="N303" s="4">
-        <v>0</v>
-      </c>
-      <c r="O303" s="1"/>
-      <c r="P303" s="1"/>
+        <v>1729</v>
+      </c>
+      <c r="O303" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="P303" s="1" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="304">
       <c r="A304" s="2">
@@ -16493,31 +16655,39 @@
       <c r="E304" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F304" s="1"/>
-      <c r="G304" s="1"/>
+      <c r="F304" s="2">
+        <v>82722</v>
+      </c>
+      <c r="G304" s="3">
+        <v>46099</v>
+      </c>
       <c r="H304" s="1" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="J304" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K304" s="1" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="L304" s="4">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M304" s="4">
-        <v>0</v>
+        <v>89.52</v>
       </c>
       <c r="N304" s="4">
-        <v>0</v>
-      </c>
-      <c r="O304" s="1"/>
-      <c r="P304" s="1"/>
+        <v>89.52</v>
+      </c>
+      <c r="O304" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P304" s="1" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="305">
       <c r="A305" s="2">
@@ -16535,31 +16705,39 @@
       <c r="E305" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F305" s="1"/>
-      <c r="G305" s="1"/>
+      <c r="F305" s="2">
+        <v>82722</v>
+      </c>
+      <c r="G305" s="3">
+        <v>46099</v>
+      </c>
       <c r="H305" s="1" t="s">
-        <v>549</v>
+        <v>571</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K305" s="1" t="s">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="L305" s="4">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="M305" s="4">
-        <v>0</v>
+        <v>76.83</v>
       </c>
       <c r="N305" s="4">
-        <v>0</v>
-      </c>
-      <c r="O305" s="1"/>
-      <c r="P305" s="1"/>
+        <v>76.83</v>
+      </c>
+      <c r="O305" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P305" s="1" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="306">
       <c r="A306" s="2">
@@ -16580,10 +16758,10 @@
       <c r="F306" s="1"/>
       <c r="G306" s="1"/>
       <c r="H306" s="1" t="s">
-        <v>260</v>
+        <v>573</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>261</v>
+        <v>574</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>20</v>
@@ -16592,7 +16770,7 @@
         <v>21</v>
       </c>
       <c r="L306" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M306" s="4">
         <v>0</v>
@@ -16622,16 +16800,16 @@
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
       <c r="H307" s="1" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="L307" s="4">
         <v>1</v>
@@ -16664,16 +16842,16 @@
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
       <c r="H308" s="1" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="L308" s="4">
         <v>1</v>
@@ -16692,7 +16870,7 @@
         <v>2504</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>17</v>
@@ -16704,10 +16882,10 @@
         <v>46098.5062577778</v>
       </c>
       <c r="F309" s="2">
-        <v>82689</v>
+        <v>82714</v>
       </c>
       <c r="G309" s="3">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="H309" s="1" t="s">
         <v>38</v>
@@ -16725,16 +16903,16 @@
         <v>1</v>
       </c>
       <c r="M309" s="4">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="N309" s="4">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="O309" s="1" t="s">
-        <v>142</v>
+        <v>32</v>
       </c>
       <c r="P309" s="1" t="s">
-        <v>143</v>
+        <v>33</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="310">
@@ -16742,7 +16920,7 @@
         <v>2504</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>17</v>
@@ -16760,16 +16938,16 @@
         <v>46098</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K310" s="1" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="L310" s="4">
         <v>15</v>
@@ -16792,7 +16970,7 @@
         <v>2504</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>17</v>
@@ -16834,7 +17012,7 @@
         <v>2504</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>17</v>
@@ -16876,7 +17054,7 @@
         <v>2504</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>17</v>
@@ -16918,7 +17096,7 @@
         <v>2504</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>17</v>
@@ -16993,10 +17171,10 @@
         <v>50</v>
       </c>
       <c r="M315" s="4">
-        <v>34.5</v>
+        <v>36.5</v>
       </c>
       <c r="N315" s="4">
-        <v>1725</v>
+        <v>1825</v>
       </c>
       <c r="O315" s="1" t="s">
         <v>97</v>
@@ -17021,13 +17199,17 @@
       <c r="E316" s="3">
         <v>46098.6661386574</v>
       </c>
-      <c r="F316" s="1"/>
-      <c r="G316" s="1"/>
+      <c r="F316" s="2">
+        <v>82704</v>
+      </c>
+      <c r="G316" s="3">
+        <v>46099</v>
+      </c>
       <c r="H316" s="1" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>20</v>
@@ -17039,13 +17221,17 @@
         <v>21</v>
       </c>
       <c r="M316" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N316" s="4">
-        <v>0</v>
-      </c>
-      <c r="O316" s="1"/>
-      <c r="P316" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="O316" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="P316" s="1" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="317">
       <c r="A317" s="2">
@@ -17063,13 +17249,17 @@
       <c r="E317" s="3">
         <v>46098.6661386574</v>
       </c>
-      <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
+      <c r="F317" s="2">
+        <v>82704</v>
+      </c>
+      <c r="G317" s="3">
+        <v>46099</v>
+      </c>
       <c r="H317" s="1" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="J317" s="1" t="s">
         <v>20</v>
@@ -17081,13 +17271,17 @@
         <v>10</v>
       </c>
       <c r="M317" s="4">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="N317" s="4">
-        <v>0</v>
-      </c>
-      <c r="O317" s="1"/>
-      <c r="P317" s="1"/>
+        <v>1490</v>
+      </c>
+      <c r="O317" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="P317" s="1" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="318">
       <c r="A318" s="2">
@@ -17155,8 +17349,12 @@
       <c r="E319" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
+      <c r="F319" s="2">
+        <v>82708</v>
+      </c>
+      <c r="G319" s="3">
+        <v>46099</v>
+      </c>
       <c r="H319" s="1" t="s">
         <v>113</v>
       </c>
@@ -17173,13 +17371,17 @@
         <v>2</v>
       </c>
       <c r="M319" s="4">
-        <v>0</v>
+        <v>65.6</v>
       </c>
       <c r="N319" s="4">
-        <v>0</v>
-      </c>
-      <c r="O319" s="1"/>
-      <c r="P319" s="1"/>
+        <v>131.2</v>
+      </c>
+      <c r="O319" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P319" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="320">
       <c r="A320" s="2">
@@ -17197,8 +17399,12 @@
       <c r="E320" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F320" s="1"/>
-      <c r="G320" s="1"/>
+      <c r="F320" s="2">
+        <v>82708</v>
+      </c>
+      <c r="G320" s="3">
+        <v>46099</v>
+      </c>
       <c r="H320" s="1" t="s">
         <v>401</v>
       </c>
@@ -17215,13 +17421,17 @@
         <v>6</v>
       </c>
       <c r="M320" s="4">
-        <v>0</v>
+        <v>22.24</v>
       </c>
       <c r="N320" s="4">
-        <v>0</v>
-      </c>
-      <c r="O320" s="1"/>
-      <c r="P320" s="1"/>
+        <v>133.44</v>
+      </c>
+      <c r="O320" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P320" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="321">
       <c r="A321" s="2">
@@ -17239,13 +17449,17 @@
       <c r="E321" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F321" s="1"/>
-      <c r="G321" s="1"/>
+      <c r="F321" s="2">
+        <v>82712</v>
+      </c>
+      <c r="G321" s="3">
+        <v>46099</v>
+      </c>
       <c r="H321" s="1" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="J321" s="1" t="s">
         <v>20</v>
@@ -17254,16 +17468,20 @@
         <v>21</v>
       </c>
       <c r="L321" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M321" s="4">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N321" s="4">
-        <v>0</v>
-      </c>
-      <c r="O321" s="1"/>
-      <c r="P321" s="1"/>
+        <v>390</v>
+      </c>
+      <c r="O321" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P321" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="322">
       <c r="A322" s="2">
@@ -17281,13 +17499,17 @@
       <c r="E322" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F322" s="1"/>
-      <c r="G322" s="1"/>
+      <c r="F322" s="2">
+        <v>82712</v>
+      </c>
+      <c r="G322" s="3">
+        <v>46099</v>
+      </c>
       <c r="H322" s="1" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>20</v>
@@ -17299,13 +17521,17 @@
         <v>1</v>
       </c>
       <c r="M322" s="4">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="N322" s="4">
-        <v>0</v>
-      </c>
-      <c r="O322" s="1"/>
-      <c r="P322" s="1"/>
+        <v>320</v>
+      </c>
+      <c r="O322" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="P322" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="323">
       <c r="A323" s="2">
@@ -17323,13 +17549,17 @@
       <c r="E323" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F323" s="1"/>
-      <c r="G323" s="1"/>
+      <c r="F323" s="2">
+        <v>82709</v>
+      </c>
+      <c r="G323" s="3">
+        <v>46099</v>
+      </c>
       <c r="H323" s="1" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>20</v>
@@ -17341,13 +17571,17 @@
         <v>6</v>
       </c>
       <c r="M323" s="4">
-        <v>0</v>
+        <v>47.7</v>
       </c>
       <c r="N323" s="4">
-        <v>0</v>
-      </c>
-      <c r="O323" s="1"/>
-      <c r="P323" s="1"/>
+        <v>286.2</v>
+      </c>
+      <c r="O323" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="P323" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="324">
       <c r="A324" s="2">
@@ -17365,31 +17599,39 @@
       <c r="E324" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F324" s="1"/>
-      <c r="G324" s="1"/>
+      <c r="F324" s="2">
+        <v>82706</v>
+      </c>
+      <c r="G324" s="3">
+        <v>46099</v>
+      </c>
       <c r="H324" s="1" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="J324" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K324" s="1" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="L324" s="4">
         <v>60</v>
       </c>
       <c r="M324" s="4">
-        <v>0</v>
+        <v>18.33</v>
       </c>
       <c r="N324" s="4">
-        <v>0</v>
-      </c>
-      <c r="O324" s="1"/>
-      <c r="P324" s="1"/>
+        <v>1099.8</v>
+      </c>
+      <c r="O324" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="P324" s="1" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="325">
       <c r="A325" s="2">
@@ -17407,13 +17649,17 @@
       <c r="E325" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F325" s="1"/>
-      <c r="G325" s="1"/>
+      <c r="F325" s="2">
+        <v>82707</v>
+      </c>
+      <c r="G325" s="3">
+        <v>46099</v>
+      </c>
       <c r="H325" s="1" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="J325" s="1" t="s">
         <v>20</v>
@@ -17425,13 +17671,17 @@
         <v>100</v>
       </c>
       <c r="M325" s="4">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="N325" s="4">
-        <v>0</v>
-      </c>
-      <c r="O325" s="1"/>
-      <c r="P325" s="1"/>
+        <v>647</v>
+      </c>
+      <c r="O325" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="P325" s="1" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="326">
       <c r="A326" s="2">
@@ -17449,13 +17699,17 @@
       <c r="E326" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F326" s="1"/>
-      <c r="G326" s="1"/>
+      <c r="F326" s="2">
+        <v>82707</v>
+      </c>
+      <c r="G326" s="3">
+        <v>46099</v>
+      </c>
       <c r="H326" s="1" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="J326" s="1" t="s">
         <v>20</v>
@@ -17467,13 +17721,17 @@
         <v>6</v>
       </c>
       <c r="M326" s="4">
-        <v>0</v>
+        <v>136.91</v>
       </c>
       <c r="N326" s="4">
-        <v>0</v>
-      </c>
-      <c r="O326" s="1"/>
-      <c r="P326" s="1"/>
+        <v>821.46</v>
+      </c>
+      <c r="O326" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="P326" s="1" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="327">
       <c r="A327" s="2">
@@ -17491,13 +17749,17 @@
       <c r="E327" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F327" s="1"/>
-      <c r="G327" s="1"/>
+      <c r="F327" s="2">
+        <v>82707</v>
+      </c>
+      <c r="G327" s="3">
+        <v>46099</v>
+      </c>
       <c r="H327" s="1" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>20</v>
@@ -17509,13 +17771,17 @@
         <v>10</v>
       </c>
       <c r="M327" s="4">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="N327" s="4">
-        <v>0</v>
-      </c>
-      <c r="O327" s="1"/>
-      <c r="P327" s="1"/>
+        <v>229</v>
+      </c>
+      <c r="O327" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="P327" s="1" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="328">
       <c r="A328" s="2">
@@ -17533,13 +17799,17 @@
       <c r="E328" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F328" s="1"/>
-      <c r="G328" s="1"/>
+      <c r="F328" s="2">
+        <v>82707</v>
+      </c>
+      <c r="G328" s="3">
+        <v>46099</v>
+      </c>
       <c r="H328" s="1" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="J328" s="1" t="s">
         <v>20</v>
@@ -17551,13 +17821,17 @@
         <v>10</v>
       </c>
       <c r="M328" s="4">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="N328" s="4">
-        <v>0</v>
-      </c>
-      <c r="O328" s="1"/>
-      <c r="P328" s="1"/>
+        <v>249</v>
+      </c>
+      <c r="O328" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="P328" s="1" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="329">
       <c r="A329" s="2">
@@ -17575,13 +17849,17 @@
       <c r="E329" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F329" s="1"/>
-      <c r="G329" s="1"/>
+      <c r="F329" s="2">
+        <v>82709</v>
+      </c>
+      <c r="G329" s="3">
+        <v>46099</v>
+      </c>
       <c r="H329" s="1" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>20</v>
@@ -17593,13 +17871,17 @@
         <v>10</v>
       </c>
       <c r="M329" s="4">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="N329" s="4">
-        <v>0</v>
-      </c>
-      <c r="O329" s="1"/>
-      <c r="P329" s="1"/>
+        <v>460</v>
+      </c>
+      <c r="O329" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="P329" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="330">
       <c r="A330" s="2">
@@ -17617,13 +17899,17 @@
       <c r="E330" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F330" s="1"/>
-      <c r="G330" s="1"/>
+      <c r="F330" s="2">
+        <v>82713</v>
+      </c>
+      <c r="G330" s="3">
+        <v>46099</v>
+      </c>
       <c r="H330" s="1" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>20</v>
@@ -17635,13 +17921,17 @@
         <v>100</v>
       </c>
       <c r="M330" s="4">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="N330" s="4">
-        <v>0</v>
-      </c>
-      <c r="O330" s="1"/>
-      <c r="P330" s="1"/>
+        <v>1440</v>
+      </c>
+      <c r="O330" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="P330" s="1" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="331">
       <c r="A331" s="2">
@@ -17659,13 +17949,17 @@
       <c r="E331" s="3">
         <v>46098.6669450579</v>
       </c>
-      <c r="F331" s="1"/>
-      <c r="G331" s="1"/>
+      <c r="F331" s="2">
+        <v>82713</v>
+      </c>
+      <c r="G331" s="3">
+        <v>46099</v>
+      </c>
       <c r="H331" s="1" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="J331" s="1" t="s">
         <v>20</v>
@@ -17677,13 +17971,17 @@
         <v>100</v>
       </c>
       <c r="M331" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N331" s="4">
-        <v>0</v>
-      </c>
-      <c r="O331" s="1"/>
-      <c r="P331" s="1"/>
+        <v>3000</v>
+      </c>
+      <c r="O331" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="P331" s="1" t="s">
+        <v>612</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="619">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1697,18 +1697,18 @@
     <t>LIMPO SOLUÇÕES</t>
   </si>
   <si>
+    <t>C.04.0116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPO DESCARTAVEL  PARA AGUA 200 ML TIRA COM 100</t>
+  </si>
+  <si>
     <t>E.02.0207</t>
   </si>
   <si>
     <t>FITA ANTIDERRAPANTE TRANSPARENTE 50MMX5M</t>
   </si>
   <si>
-    <t>00000000000762</t>
-  </si>
-  <si>
-    <t>CASA DAS FECHADURAS</t>
-  </si>
-  <si>
     <t>O.01.0110</t>
   </si>
   <si>
@@ -1733,12 +1733,6 @@
     <t>SUPORTE PARA TV BI-ARTICULADO - PARA TV'S DE 10 A 60 POLEGADAS - COR PRETO</t>
   </si>
   <si>
-    <t>C.04.0116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPO DESCARTAVEL  PARA AGUA 200 ML TIRA COM 100</t>
-  </si>
-  <si>
     <t>F.04.0072</t>
   </si>
   <si>
@@ -1857,6 +1851,24 @@
   </si>
   <si>
     <t>TÁBUA DE CEDRINHO - 1 X 12'' -</t>
+  </si>
+  <si>
+    <t>E.03.0132</t>
+  </si>
+  <si>
+    <t>PROTETOR AURICULAR DE SILICONE C/ CORDÃO 16 DECIBÉIS</t>
+  </si>
+  <si>
+    <t>E.03.0125</t>
+  </si>
+  <si>
+    <t>OCULOS DE SEGURANÇA DE SOBREPOR PARA USO COM OCULOS CORRETIVOS.</t>
+  </si>
+  <si>
+    <t>W.06.1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADESIVO ESTRUTURAL BASE EPÓXI MÉDIA FLUIDEZ  COMPOUND ADESIVO  1KG   ( A+B)</t>
   </si>
 </sst>
 </file>
@@ -2155,7 +2167,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P331"/>
+  <dimension ref="A1:P342"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -16177,10 +16189,10 @@
         <v>1</v>
       </c>
       <c r="M294" s="4">
-        <v>44</v>
+        <v>59.9</v>
       </c>
       <c r="N294" s="4">
-        <v>44</v>
+        <v>59.9</v>
       </c>
       <c r="O294" s="1" t="s">
         <v>559</v>
@@ -16227,10 +16239,10 @@
         <v>1</v>
       </c>
       <c r="M295" s="4">
-        <v>17.9</v>
+        <v>89.9</v>
       </c>
       <c r="N295" s="4">
-        <v>17.9</v>
+        <v>89.9</v>
       </c>
       <c r="O295" s="1" t="s">
         <v>559</v>
@@ -16256,10 +16268,10 @@
         <v>46098.5034667708</v>
       </c>
       <c r="F296" s="2">
-        <v>82722</v>
+        <v>82686</v>
       </c>
       <c r="G296" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="H296" s="1" t="s">
         <v>561</v>
@@ -16271,22 +16283,22 @@
         <v>20</v>
       </c>
       <c r="K296" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L296" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M296" s="4">
-        <v>63.6</v>
+        <v>99.9</v>
       </c>
       <c r="N296" s="4">
-        <v>318</v>
+        <v>199.8</v>
       </c>
       <c r="O296" s="1" t="s">
-        <v>250</v>
+        <v>559</v>
       </c>
       <c r="P296" s="1" t="s">
-        <v>251</v>
+        <v>560</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="297">
@@ -16312,25 +16324,25 @@
         <v>46099</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>256</v>
+        <v>563</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>257</v>
+        <v>564</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K297" s="1" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="L297" s="4">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="M297" s="4">
-        <v>12.75</v>
+        <v>63.6</v>
       </c>
       <c r="N297" s="4">
-        <v>1912.5</v>
+        <v>318</v>
       </c>
       <c r="O297" s="1" t="s">
         <v>250</v>
@@ -16362,10 +16374,10 @@
         <v>46099</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>20</v>
@@ -16377,10 +16389,10 @@
         <v>150</v>
       </c>
       <c r="M298" s="4">
-        <v>8.9</v>
+        <v>12.75</v>
       </c>
       <c r="N298" s="4">
-        <v>1335</v>
+        <v>1912.5</v>
       </c>
       <c r="O298" s="1" t="s">
         <v>250</v>
@@ -16406,16 +16418,16 @@
         <v>46098.5034667708</v>
       </c>
       <c r="F299" s="2">
-        <v>82687</v>
+        <v>82722</v>
       </c>
       <c r="G299" s="3">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>20</v>
@@ -16424,19 +16436,19 @@
         <v>83</v>
       </c>
       <c r="L299" s="4">
-        <v>15</v>
+        <v>150</v>
       </c>
       <c r="M299" s="4">
-        <v>38.5</v>
+        <v>8.9</v>
       </c>
       <c r="N299" s="4">
-        <v>577.5</v>
+        <v>1335</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>563</v>
+        <v>250</v>
       </c>
       <c r="P299" s="1" t="s">
-        <v>564</v>
+        <v>251</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="300">
@@ -16456,37 +16468,37 @@
         <v>46098.5034667708</v>
       </c>
       <c r="F300" s="2">
-        <v>82723</v>
+        <v>82687</v>
       </c>
       <c r="G300" s="3">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>565</v>
+        <v>216</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>566</v>
+        <v>217</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K300" s="1" t="s">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="L300" s="4">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="M300" s="4">
-        <v>3.333333</v>
+        <v>38.5</v>
       </c>
       <c r="N300" s="4">
-        <v>399.99996</v>
+        <v>577.5</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="P300" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="301">
@@ -16512,10 +16524,10 @@
         <v>46099</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>20</v>
@@ -16527,10 +16539,10 @@
         <v>120</v>
       </c>
       <c r="M301" s="4">
-        <v>9.6</v>
+        <v>3.333333</v>
       </c>
       <c r="N301" s="4">
-        <v>1152</v>
+        <v>399.99996</v>
       </c>
       <c r="O301" s="1" t="s">
         <v>262</v>
@@ -16562,10 +16574,10 @@
         <v>46099</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="J302" s="1" t="s">
         <v>20</v>
@@ -16574,13 +16586,13 @@
         <v>203</v>
       </c>
       <c r="L302" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="M302" s="4">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="N302" s="4">
-        <v>1260</v>
+        <v>1152</v>
       </c>
       <c r="O302" s="1" t="s">
         <v>262</v>
@@ -16612,25 +16624,25 @@
         <v>46099</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>260</v>
+        <v>557</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>261</v>
+        <v>558</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K303" s="1" t="s">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="L303" s="4">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="M303" s="4">
-        <v>172.9</v>
+        <v>14</v>
       </c>
       <c r="N303" s="4">
-        <v>1729</v>
+        <v>1260</v>
       </c>
       <c r="O303" s="1" t="s">
         <v>262</v>
@@ -16656,37 +16668,37 @@
         <v>46098.5034667708</v>
       </c>
       <c r="F304" s="2">
-        <v>82722</v>
+        <v>82723</v>
       </c>
       <c r="G304" s="3">
         <v>46099</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>569</v>
+        <v>260</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>570</v>
+        <v>261</v>
       </c>
       <c r="J304" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K304" s="1" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="L304" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M304" s="4">
-        <v>89.52</v>
+        <v>172.9</v>
       </c>
       <c r="N304" s="4">
-        <v>89.52</v>
+        <v>1729</v>
       </c>
       <c r="O304" s="1" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="P304" s="1" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="305">
@@ -16712,25 +16724,25 @@
         <v>46099</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K305" s="1" t="s">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="L305" s="4">
         <v>1</v>
       </c>
       <c r="M305" s="4">
-        <v>76.83</v>
+        <v>89.52</v>
       </c>
       <c r="N305" s="4">
-        <v>76.83</v>
+        <v>89.52</v>
       </c>
       <c r="O305" s="1" t="s">
         <v>250</v>
@@ -16755,13 +16767,17 @@
       <c r="E306" s="3">
         <v>46098.5034667708</v>
       </c>
-      <c r="F306" s="1"/>
-      <c r="G306" s="1"/>
+      <c r="F306" s="2">
+        <v>82722</v>
+      </c>
+      <c r="G306" s="3">
+        <v>46099</v>
+      </c>
       <c r="H306" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>20</v>
@@ -16770,16 +16786,20 @@
         <v>21</v>
       </c>
       <c r="L306" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M306" s="4">
-        <v>0</v>
+        <v>76.83</v>
       </c>
       <c r="N306" s="4">
-        <v>0</v>
-      </c>
-      <c r="O306" s="1"/>
-      <c r="P306" s="1"/>
+        <v>76.83</v>
+      </c>
+      <c r="O306" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="P306" s="1" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="307">
       <c r="A307" s="2">
@@ -16800,10 +16820,10 @@
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
       <c r="H307" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>20</v>
@@ -16842,10 +16862,10 @@
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
       <c r="H308" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
@@ -16938,16 +16958,16 @@
         <v>46098</v>
       </c>
       <c r="H310" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="I310" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="J310" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K310" s="1" t="s">
         <v>579</v>
-      </c>
-      <c r="I310" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="J310" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K310" s="1" t="s">
-        <v>581</v>
       </c>
       <c r="L310" s="4">
         <v>15</v>
@@ -17206,10 +17226,10 @@
         <v>46099</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>20</v>
@@ -17227,10 +17247,10 @@
         <v>126</v>
       </c>
       <c r="O316" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="P316" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="317">
@@ -17256,10 +17276,10 @@
         <v>46099</v>
       </c>
       <c r="H317" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="I317" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J317" s="1" t="s">
         <v>20</v>
@@ -17277,10 +17297,10 @@
         <v>1490</v>
       </c>
       <c r="O317" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="P317" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="318">
@@ -17456,10 +17476,10 @@
         <v>46099</v>
       </c>
       <c r="H321" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J321" s="1" t="s">
         <v>20</v>
@@ -17506,10 +17526,10 @@
         <v>46099</v>
       </c>
       <c r="H322" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>20</v>
@@ -17556,10 +17576,10 @@
         <v>46099</v>
       </c>
       <c r="H323" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>20</v>
@@ -17606,16 +17626,16 @@
         <v>46099</v>
       </c>
       <c r="H324" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="I324" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="J324" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K324" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="I324" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="J324" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K324" s="1" t="s">
-        <v>596</v>
       </c>
       <c r="L324" s="4">
         <v>60</v>
@@ -17627,10 +17647,10 @@
         <v>1099.8</v>
       </c>
       <c r="O324" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="P324" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="325">
@@ -17656,10 +17676,10 @@
         <v>46099</v>
       </c>
       <c r="H325" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="J325" s="1" t="s">
         <v>20</v>
@@ -17706,10 +17726,10 @@
         <v>46099</v>
       </c>
       <c r="H326" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J326" s="1" t="s">
         <v>20</v>
@@ -17756,10 +17776,10 @@
         <v>46099</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>20</v>
@@ -17806,10 +17826,10 @@
         <v>46099</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J328" s="1" t="s">
         <v>20</v>
@@ -17856,10 +17876,10 @@
         <v>46099</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>20</v>
@@ -17906,10 +17926,10 @@
         <v>46099</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>20</v>
@@ -17927,10 +17947,10 @@
         <v>1440</v>
       </c>
       <c r="O330" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="P330" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="331">
@@ -17956,10 +17976,10 @@
         <v>46099</v>
       </c>
       <c r="H331" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="J331" s="1" t="s">
         <v>20</v>
@@ -17977,11 +17997,489 @@
         <v>3000</v>
       </c>
       <c r="O331" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="P331" s="1" t="s">
-        <v>612</v>
-      </c>
+        <v>610</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="332">
+      <c r="A332" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D332" s="2">
+        <v>28</v>
+      </c>
+      <c r="E332" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F332" s="2">
+        <v>82725</v>
+      </c>
+      <c r="G332" s="3">
+        <v>46099</v>
+      </c>
+      <c r="H332" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I332" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J332" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K332" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L332" s="4">
+        <v>10</v>
+      </c>
+      <c r="M332" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="N332" s="4">
+        <v>42</v>
+      </c>
+      <c r="O332" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="P332" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="333">
+      <c r="A333" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D333" s="2">
+        <v>28</v>
+      </c>
+      <c r="E333" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F333" s="2">
+        <v>82724</v>
+      </c>
+      <c r="G333" s="3">
+        <v>46099</v>
+      </c>
+      <c r="H333" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="I333" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J333" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K333" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="L333" s="4">
+        <v>50</v>
+      </c>
+      <c r="M333" s="4">
+        <v>5.8</v>
+      </c>
+      <c r="N333" s="4">
+        <v>290</v>
+      </c>
+      <c r="O333" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P333" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="334">
+      <c r="A334" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C334" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D334" s="2">
+        <v>28</v>
+      </c>
+      <c r="E334" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F334" s="1"/>
+      <c r="G334" s="1"/>
+      <c r="H334" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I334" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J334" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K334" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L334" s="4">
+        <v>12</v>
+      </c>
+      <c r="M334" s="4">
+        <v>0</v>
+      </c>
+      <c r="N334" s="4">
+        <v>0</v>
+      </c>
+      <c r="O334" s="1"/>
+      <c r="P334" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="335">
+      <c r="A335" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C335" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D335" s="2">
+        <v>28</v>
+      </c>
+      <c r="E335" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F335" s="1"/>
+      <c r="G335" s="1"/>
+      <c r="H335" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="I335" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="J335" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K335" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L335" s="4">
+        <v>15</v>
+      </c>
+      <c r="M335" s="4">
+        <v>0</v>
+      </c>
+      <c r="N335" s="4">
+        <v>0</v>
+      </c>
+      <c r="O335" s="1"/>
+      <c r="P335" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="336">
+      <c r="A336" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C336" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D336" s="2">
+        <v>28</v>
+      </c>
+      <c r="E336" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F336" s="1"/>
+      <c r="G336" s="1"/>
+      <c r="H336" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="I336" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="J336" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K336" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L336" s="4">
+        <v>30</v>
+      </c>
+      <c r="M336" s="4">
+        <v>0</v>
+      </c>
+      <c r="N336" s="4">
+        <v>0</v>
+      </c>
+      <c r="O336" s="1"/>
+      <c r="P336" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="337">
+      <c r="A337" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C337" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D337" s="2">
+        <v>28</v>
+      </c>
+      <c r="E337" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F337" s="1"/>
+      <c r="G337" s="1"/>
+      <c r="H337" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="I337" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J337" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K337" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L337" s="4">
+        <v>1</v>
+      </c>
+      <c r="M337" s="4">
+        <v>0</v>
+      </c>
+      <c r="N337" s="4">
+        <v>0</v>
+      </c>
+      <c r="O337" s="1"/>
+      <c r="P337" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="338">
+      <c r="A338" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D338" s="2">
+        <v>28</v>
+      </c>
+      <c r="E338" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="I338" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="J338" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K338" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L338" s="4">
+        <v>10</v>
+      </c>
+      <c r="M338" s="4">
+        <v>0</v>
+      </c>
+      <c r="N338" s="4">
+        <v>0</v>
+      </c>
+      <c r="O338" s="1"/>
+      <c r="P338" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="339">
+      <c r="A339" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C339" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D339" s="2">
+        <v>28</v>
+      </c>
+      <c r="E339" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F339" s="1"/>
+      <c r="G339" s="1"/>
+      <c r="H339" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I339" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J339" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K339" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L339" s="4">
+        <v>1</v>
+      </c>
+      <c r="M339" s="4">
+        <v>0</v>
+      </c>
+      <c r="N339" s="4">
+        <v>0</v>
+      </c>
+      <c r="O339" s="1"/>
+      <c r="P339" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="340">
+      <c r="A340" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D340" s="2">
+        <v>28</v>
+      </c>
+      <c r="E340" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F340" s="1"/>
+      <c r="G340" s="1"/>
+      <c r="H340" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I340" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J340" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K340" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="L340" s="4">
+        <v>1</v>
+      </c>
+      <c r="M340" s="4">
+        <v>0</v>
+      </c>
+      <c r="N340" s="4">
+        <v>0</v>
+      </c>
+      <c r="O340" s="1"/>
+      <c r="P340" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="341">
+      <c r="A341" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D341" s="2">
+        <v>28</v>
+      </c>
+      <c r="E341" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F341" s="1"/>
+      <c r="G341" s="1"/>
+      <c r="H341" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I341" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J341" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K341" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L341" s="4">
+        <v>30</v>
+      </c>
+      <c r="M341" s="4">
+        <v>0</v>
+      </c>
+      <c r="N341" s="4">
+        <v>0</v>
+      </c>
+      <c r="O341" s="1"/>
+      <c r="P341" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="342">
+      <c r="A342" s="2">
+        <v>2511</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D342" s="2">
+        <v>28</v>
+      </c>
+      <c r="E342" s="3">
+        <v>46099.6523956944</v>
+      </c>
+      <c r="F342" s="1"/>
+      <c r="G342" s="1"/>
+      <c r="H342" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="I342" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="J342" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K342" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L342" s="4">
+        <v>10</v>
+      </c>
+      <c r="M342" s="4">
+        <v>0</v>
+      </c>
+      <c r="N342" s="4">
+        <v>0</v>
+      </c>
+      <c r="O342" s="1"/>
+      <c r="P342" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -16574,37 +16574,37 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F305" s="2">
-        <v>82725</v>
+        <v>82730</v>
       </c>
       <c r="G305" s="3">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K305" s="1" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="L305" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M305" s="4">
-        <v>4.2</v>
+        <v>180</v>
       </c>
       <c r="N305" s="4">
-        <v>42</v>
+        <v>540</v>
       </c>
       <c r="O305" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="P305" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="306">
@@ -16624,16 +16624,16 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F306" s="2">
-        <v>82724</v>
+        <v>82725</v>
       </c>
       <c r="G306" s="3">
         <v>46099</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>577</v>
+        <v>140</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>578</v>
+        <v>141</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>20</v>
@@ -16642,19 +16642,19 @@
         <v>36</v>
       </c>
       <c r="L306" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M306" s="4">
-        <v>55</v>
+        <v>4.2</v>
       </c>
       <c r="N306" s="4">
-        <v>1650</v>
+        <v>42</v>
       </c>
       <c r="O306" s="1" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="P306" s="1" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="307">
@@ -16674,37 +16674,37 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F307" s="2">
-        <v>82724</v>
+        <v>82730</v>
       </c>
       <c r="G307" s="3">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="L307" s="4">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="M307" s="4">
-        <v>5.8</v>
+        <v>200</v>
       </c>
       <c r="N307" s="4">
-        <v>290</v>
+        <v>600</v>
       </c>
       <c r="O307" s="1" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="P307" s="1" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="308">
@@ -16724,37 +16724,37 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F308" s="2">
-        <v>82727</v>
+        <v>82730</v>
       </c>
       <c r="G308" s="3">
         <v>46100</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>579</v>
+        <v>144</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>580</v>
+        <v>145</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="L308" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M308" s="4">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="N308" s="4">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="O308" s="1" t="s">
-        <v>581</v>
+        <v>132</v>
       </c>
       <c r="P308" s="1" t="s">
-        <v>582</v>
+        <v>133</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="309">
@@ -16773,13 +16773,17 @@
       <c r="E309" s="3">
         <v>46099.6523956944</v>
       </c>
-      <c r="F309" s="1"/>
-      <c r="G309" s="1"/>
+      <c r="F309" s="2">
+        <v>82724</v>
+      </c>
+      <c r="G309" s="3">
+        <v>46099</v>
+      </c>
       <c r="H309" s="1" t="s">
-        <v>61</v>
+        <v>577</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>62</v>
+        <v>578</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>20</v>
@@ -16788,16 +16792,20 @@
         <v>36</v>
       </c>
       <c r="L309" s="4">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M309" s="4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N309" s="4">
-        <v>0</v>
-      </c>
-      <c r="O309" s="1"/>
-      <c r="P309" s="1"/>
+        <v>1650</v>
+      </c>
+      <c r="O309" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P309" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="310">
       <c r="A310" s="2">
@@ -16815,31 +16823,39 @@
       <c r="E310" s="3">
         <v>46099.6523956944</v>
       </c>
-      <c r="F310" s="1"/>
-      <c r="G310" s="1"/>
+      <c r="F310" s="2">
+        <v>82724</v>
+      </c>
+      <c r="G310" s="3">
+        <v>46099</v>
+      </c>
       <c r="H310" s="1" t="s">
-        <v>583</v>
+        <v>169</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>584</v>
+        <v>170</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K310" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="L310" s="4">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="M310" s="4">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N310" s="4">
-        <v>0</v>
-      </c>
-      <c r="O310" s="1"/>
-      <c r="P310" s="1"/>
+        <v>290</v>
+      </c>
+      <c r="O310" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P310" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="311">
       <c r="A311" s="2">
@@ -16857,13 +16873,17 @@
       <c r="E311" s="3">
         <v>46099.6523956944</v>
       </c>
-      <c r="F311" s="1"/>
-      <c r="G311" s="1"/>
+      <c r="F311" s="2">
+        <v>82727</v>
+      </c>
+      <c r="G311" s="3">
+        <v>46100</v>
+      </c>
       <c r="H311" s="1" t="s">
-        <v>364</v>
+        <v>579</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>365</v>
+        <v>580</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>20</v>
@@ -16872,16 +16892,20 @@
         <v>36</v>
       </c>
       <c r="L311" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M311" s="4">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N311" s="4">
-        <v>0</v>
-      </c>
-      <c r="O311" s="1"/>
-      <c r="P311" s="1"/>
+        <v>540</v>
+      </c>
+      <c r="O311" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="P311" s="1" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="312">
       <c r="A312" s="2">
@@ -16902,19 +16926,19 @@
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
       <c r="H312" s="1" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="L312" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M312" s="4">
         <v>0</v>
@@ -16944,10 +16968,10 @@
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
       <c r="H313" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>20</v>
@@ -16956,7 +16980,7 @@
         <v>36</v>
       </c>
       <c r="L313" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M313" s="4">
         <v>0</v>
@@ -16986,19 +17010,19 @@
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
       <c r="H314" s="1" t="s">
-        <v>142</v>
+        <v>364</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>143</v>
+        <v>365</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K314" s="1" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="L314" s="4">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M314" s="4">
         <v>0</v>
@@ -17028,19 +17052,19 @@
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
       <c r="H315" s="1" t="s">
-        <v>144</v>
+        <v>585</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>145</v>
+        <v>586</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K315" s="1" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="L315" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M315" s="4">
         <v>0</v>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1745,6 +1745,18 @@
     <t>1807 PARTICIPAÇÕES LTDA</t>
   </si>
   <si>
+    <t>E.03.0132</t>
+  </si>
+  <si>
+    <t>PROTETOR AURICULAR DE SILICONE C/ CORDÃO 16 DECIBÉIS</t>
+  </si>
+  <si>
+    <t>E.03.0125</t>
+  </si>
+  <si>
+    <t>OCULOS DE SEGURANÇA DE SOBREPOR PARA USO COM OCULOS CORRETIVOS.</t>
+  </si>
+  <si>
     <t>J.02.0905</t>
   </si>
   <si>
@@ -1761,18 +1773,6 @@
   </si>
   <si>
     <t>VEDAZ</t>
-  </si>
-  <si>
-    <t>E.03.0132</t>
-  </si>
-  <si>
-    <t>PROTETOR AURICULAR DE SILICONE C/ CORDÃO 16 DECIBÉIS</t>
-  </si>
-  <si>
-    <t>E.03.0125</t>
-  </si>
-  <si>
-    <t>OCULOS DE SEGURANÇA DE SOBREPOR PARA USO COM OCULOS CORRETIVOS.</t>
   </si>
 </sst>
 </file>
@@ -16574,37 +16574,37 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F305" s="2">
-        <v>82730</v>
+        <v>82725</v>
       </c>
       <c r="G305" s="3">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>138</v>
+        <v>61</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K305" s="1" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="L305" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M305" s="4">
-        <v>180</v>
+        <v>23.43</v>
       </c>
       <c r="N305" s="4">
-        <v>540</v>
+        <v>281.16</v>
       </c>
       <c r="O305" s="1" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="P305" s="1" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="306">
@@ -16630,10 +16630,10 @@
         <v>46099</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>140</v>
+        <v>577</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>141</v>
+        <v>578</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>20</v>
@@ -16642,19 +16642,19 @@
         <v>36</v>
       </c>
       <c r="L306" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M306" s="4">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="N306" s="4">
-        <v>42</v>
+        <v>21.75</v>
       </c>
       <c r="O306" s="1" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="P306" s="1" t="s">
-        <v>128</v>
+        <v>64</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="307">
@@ -16674,37 +16674,37 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F307" s="2">
-        <v>82730</v>
+        <v>82725</v>
       </c>
       <c r="G307" s="3">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>142</v>
+        <v>364</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>143</v>
+        <v>365</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="L307" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="M307" s="4">
-        <v>200</v>
+        <v>4.77</v>
       </c>
       <c r="N307" s="4">
-        <v>600</v>
+        <v>143.1</v>
       </c>
       <c r="O307" s="1" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="P307" s="1" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="308">
@@ -16730,10 +16730,10 @@
         <v>46100</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
@@ -16745,10 +16745,10 @@
         <v>3</v>
       </c>
       <c r="M308" s="4">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="N308" s="4">
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="O308" s="1" t="s">
         <v>132</v>
@@ -16774,16 +16774,16 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F309" s="2">
-        <v>82724</v>
+        <v>82725</v>
       </c>
       <c r="G309" s="3">
         <v>46099</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>20</v>
@@ -16792,19 +16792,19 @@
         <v>36</v>
       </c>
       <c r="L309" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="M309" s="4">
-        <v>55</v>
+        <v>10.35</v>
       </c>
       <c r="N309" s="4">
-        <v>1650</v>
+        <v>103.5</v>
       </c>
       <c r="O309" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P309" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="310">
@@ -16824,37 +16824,37 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F310" s="2">
-        <v>82724</v>
+        <v>82725</v>
       </c>
       <c r="G310" s="3">
         <v>46099</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K310" s="1" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L310" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="M310" s="4">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="N310" s="4">
-        <v>290</v>
+        <v>42</v>
       </c>
       <c r="O310" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P310" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="311">
@@ -16874,37 +16874,37 @@
         <v>46099.6523956944</v>
       </c>
       <c r="F311" s="2">
-        <v>82727</v>
+        <v>82730</v>
       </c>
       <c r="G311" s="3">
         <v>46100</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>579</v>
+        <v>142</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>580</v>
+        <v>143</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K311" s="1" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="L311" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M311" s="4">
-        <v>54</v>
+        <v>200</v>
       </c>
       <c r="N311" s="4">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="O311" s="1" t="s">
-        <v>581</v>
+        <v>132</v>
       </c>
       <c r="P311" s="1" t="s">
-        <v>582</v>
+        <v>133</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="312">
@@ -16923,31 +16923,39 @@
       <c r="E312" s="3">
         <v>46099.6523956944</v>
       </c>
-      <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
+      <c r="F312" s="2">
+        <v>82730</v>
+      </c>
+      <c r="G312" s="3">
+        <v>46100</v>
+      </c>
       <c r="H312" s="1" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="I312" s="1" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="J312" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="L312" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M312" s="4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N312" s="4">
-        <v>0</v>
-      </c>
-      <c r="O312" s="1"/>
-      <c r="P312" s="1"/>
+        <v>600</v>
+      </c>
+      <c r="O312" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P312" s="1" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="313">
       <c r="A313" s="2">
@@ -16965,13 +16973,17 @@
       <c r="E313" s="3">
         <v>46099.6523956944</v>
       </c>
-      <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
+      <c r="F313" s="2">
+        <v>82724</v>
+      </c>
+      <c r="G313" s="3">
+        <v>46099</v>
+      </c>
       <c r="H313" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>20</v>
@@ -16980,16 +16992,20 @@
         <v>36</v>
       </c>
       <c r="L313" s="4">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M313" s="4">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="N313" s="4">
-        <v>0</v>
-      </c>
-      <c r="O313" s="1"/>
-      <c r="P313" s="1"/>
+        <v>1650</v>
+      </c>
+      <c r="O313" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P313" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="314">
       <c r="A314" s="2">
@@ -17007,31 +17023,39 @@
       <c r="E314" s="3">
         <v>46099.6523956944</v>
       </c>
-      <c r="F314" s="1"/>
-      <c r="G314" s="1"/>
+      <c r="F314" s="2">
+        <v>82724</v>
+      </c>
+      <c r="G314" s="3">
+        <v>46099</v>
+      </c>
       <c r="H314" s="1" t="s">
-        <v>364</v>
+        <v>169</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>365</v>
+        <v>170</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K314" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="L314" s="4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M314" s="4">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N314" s="4">
-        <v>0</v>
-      </c>
-      <c r="O314" s="1"/>
-      <c r="P314" s="1"/>
+        <v>290</v>
+      </c>
+      <c r="O314" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P314" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="315">
       <c r="A315" s="2">
@@ -17049,13 +17073,17 @@
       <c r="E315" s="3">
         <v>46099.6523956944</v>
       </c>
-      <c r="F315" s="1"/>
-      <c r="G315" s="1"/>
+      <c r="F315" s="2">
+        <v>82727</v>
+      </c>
+      <c r="G315" s="3">
+        <v>46100</v>
+      </c>
       <c r="H315" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>20</v>
@@ -17067,13 +17095,17 @@
         <v>10</v>
       </c>
       <c r="M315" s="4">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="N315" s="4">
-        <v>0</v>
-      </c>
-      <c r="O315" s="1"/>
-      <c r="P315" s="1"/>
+        <v>540</v>
+      </c>
+      <c r="O315" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="P315" s="1" t="s">
+        <v>586</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1472,6 +1472,60 @@
     <t>LOJA MIX</t>
   </si>
   <si>
+    <t>E.04.0113</t>
+  </si>
+  <si>
+    <t>COLHER DE PEDREIRO - 8''</t>
+  </si>
+  <si>
+    <t>H.11.0012</t>
+  </si>
+  <si>
+    <t>AÇO CA25 6,3 MM - VARA</t>
+  </si>
+  <si>
+    <t>00000000010253</t>
+  </si>
+  <si>
+    <t>DEPOSITO BRASIL</t>
+  </si>
+  <si>
+    <t>H.11.0013</t>
+  </si>
+  <si>
+    <t>AÇO CA25 8,0 MM - VARA</t>
+  </si>
+  <si>
+    <t>H.11.0034</t>
+  </si>
+  <si>
+    <t>AÇO CA50 10,0 MM - VARA</t>
+  </si>
+  <si>
+    <t>M.09.0022</t>
+  </si>
+  <si>
+    <t>ARAME RECOZIDO NØ 18</t>
+  </si>
+  <si>
+    <t>O.01.0101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABUA DE PINUS  1" X 8"</t>
+  </si>
+  <si>
+    <t>00000000008356</t>
+  </si>
+  <si>
+    <t>PALMAPLASTIC</t>
+  </si>
+  <si>
+    <t>O.01.0142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABUA DE PINUS  1" X 12"</t>
+  </si>
+  <si>
     <t>E.03.0150</t>
   </si>
   <si>
@@ -1481,54 +1535,6 @@
     <t>PAR</t>
   </si>
   <si>
-    <t>E.04.0113</t>
-  </si>
-  <si>
-    <t>COLHER DE PEDREIRO - 8''</t>
-  </si>
-  <si>
-    <t>H.11.0012</t>
-  </si>
-  <si>
-    <t>AÇO CA25 6,3 MM - VARA</t>
-  </si>
-  <si>
-    <t>00000000010253</t>
-  </si>
-  <si>
-    <t>DEPOSITO BRASIL</t>
-  </si>
-  <si>
-    <t>H.11.0013</t>
-  </si>
-  <si>
-    <t>AÇO CA25 8,0 MM - VARA</t>
-  </si>
-  <si>
-    <t>H.11.0034</t>
-  </si>
-  <si>
-    <t>AÇO CA50 10,0 MM - VARA</t>
-  </si>
-  <si>
-    <t>M.09.0022</t>
-  </si>
-  <si>
-    <t>ARAME RECOZIDO NØ 18</t>
-  </si>
-  <si>
-    <t>O.01.0101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABUA DE PINUS  1" X 8"</t>
-  </si>
-  <si>
-    <t>O.01.0142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TABUA DE PINUS  1" X 12"</t>
-  </si>
-  <si>
     <t>00000000009969</t>
   </si>
   <si>
@@ -1610,12 +1616,6 @@
     <t xml:space="preserve">TABUA DE PINUS  1" X 6"</t>
   </si>
   <si>
-    <t>00000000008356</t>
-  </si>
-  <si>
-    <t>PALMAPLASTIC</t>
-  </si>
-  <si>
     <t>O.01.0116</t>
   </si>
   <si>
@@ -1760,6 +1760,12 @@
     <t>MODULO DE TOMAD 2P+T 10A PIAL PLUS + REF. 615040BC</t>
   </si>
   <si>
+    <t>C.04.0039</t>
+  </si>
+  <si>
+    <t>VASSOURA DE PIAÇAVA Nº 2 CHAPA</t>
+  </si>
+  <si>
     <t>E.02.0072</t>
   </si>
   <si>
@@ -1772,40 +1778,34 @@
     <t>PROTETOR AURICULAR DE SILICONE C/ CORDÃO 17 DECIBÉIS</t>
   </si>
   <si>
+    <t>E.04.0170</t>
+  </si>
+  <si>
+    <t>TRENA PROFISSIONAL DE AÇO 8 M X 26 MM</t>
+  </si>
+  <si>
+    <t>E.04.0003</t>
+  </si>
+  <si>
+    <t>BALDE PVC PARA OBRA</t>
+  </si>
+  <si>
+    <t>J.02.0029</t>
+  </si>
+  <si>
+    <t>ARGAMASSA PARA CHAPISCO DE CAMADA FINA- 20KG - MARRON-CLARO(ROLADO)</t>
+  </si>
+  <si>
     <t>E.04.0720</t>
   </si>
   <si>
     <t>BROXA RETANGULAR</t>
   </si>
   <si>
-    <t>E.04.0170</t>
-  </si>
-  <si>
-    <t>TRENA PROFISSIONAL DE AÇO 8 M X 26 MM</t>
-  </si>
-  <si>
-    <t>E.04.0003</t>
-  </si>
-  <si>
-    <t>BALDE PVC PARA OBRA</t>
-  </si>
-  <si>
     <t>E.04.0269</t>
   </si>
   <si>
     <t>BLOCO DE ESPUMA OU CAMURÇA</t>
-  </si>
-  <si>
-    <t>J.02.0029</t>
-  </si>
-  <si>
-    <t>ARGAMASSA PARA CHAPISCO DE CAMADA FINA- 20KG - MARRON-CLARO(ROLADO)</t>
-  </si>
-  <si>
-    <t>C.04.0039</t>
-  </si>
-  <si>
-    <t>VASSOURA DE PIAÇAVA Nº 2 CHAPA</t>
   </si>
   <si>
     <t>H.11.0123</t>
@@ -3041,10 +3041,10 @@
         <v>2</v>
       </c>
       <c r="M18" s="4">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="N18" s="4">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>71</v>
@@ -11075,10 +11075,10 @@
         <v>2</v>
       </c>
       <c r="M191" s="4">
-        <v>9.06</v>
+        <v>10.66</v>
       </c>
       <c r="N191" s="4">
-        <v>18.12</v>
+        <v>21.32</v>
       </c>
       <c r="O191" s="1" t="s">
         <v>58</v>
@@ -13745,16 +13745,16 @@
         <v>20</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>488</v>
+        <v>26</v>
       </c>
       <c r="L245" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M245" s="4">
-        <v>189.9</v>
+        <v>34.5</v>
       </c>
       <c r="N245" s="4">
-        <v>189.9</v>
+        <v>69</v>
       </c>
       <c r="O245" s="1" t="s">
         <v>484</v>
@@ -13780,37 +13780,37 @@
         <v>46098.4979333449</v>
       </c>
       <c r="F246" s="2">
-        <v>82760</v>
+        <v>82693</v>
       </c>
       <c r="G246" s="3">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="H246" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="I246" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="I246" s="1" t="s">
+      <c r="J246" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K246" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L246" s="4">
+        <v>35</v>
+      </c>
+      <c r="M246" s="4">
+        <v>28.9</v>
+      </c>
+      <c r="N246" s="4">
+        <v>1011.5</v>
+      </c>
+      <c r="O246" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="J246" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K246" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L246" s="4">
-        <v>2</v>
-      </c>
-      <c r="M246" s="4">
-        <v>34.5</v>
-      </c>
-      <c r="N246" s="4">
-        <v>69</v>
-      </c>
-      <c r="O246" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="P246" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="247">
@@ -13836,31 +13836,31 @@
         <v>46098</v>
       </c>
       <c r="H247" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K247" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L247" s="4">
+        <v>70</v>
+      </c>
+      <c r="M247" s="4">
+        <v>47</v>
+      </c>
+      <c r="N247" s="4">
+        <v>3290</v>
+      </c>
+      <c r="O247" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="P247" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="I247" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="J247" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K247" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="L247" s="4">
-        <v>35</v>
-      </c>
-      <c r="M247" s="4">
-        <v>28.9</v>
-      </c>
-      <c r="N247" s="4">
-        <v>1011.5</v>
-      </c>
-      <c r="O247" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="P247" s="1" t="s">
-        <v>494</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="248">
@@ -13886,11 +13886,11 @@
         <v>46098</v>
       </c>
       <c r="H248" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="I248" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="I248" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="J248" s="1" t="s">
         <v>20</v>
       </c>
@@ -13898,19 +13898,19 @@
         <v>26</v>
       </c>
       <c r="L248" s="4">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="M248" s="4">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="N248" s="4">
-        <v>3290</v>
+        <v>1240</v>
       </c>
       <c r="O248" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="P248" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="249">
@@ -13936,31 +13936,31 @@
         <v>46098</v>
       </c>
       <c r="H249" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="I249" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="I249" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="J249" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="L249" s="4">
         <v>20</v>
       </c>
       <c r="M249" s="4">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="N249" s="4">
-        <v>1240</v>
+        <v>400</v>
       </c>
       <c r="O249" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="P249" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="250">
@@ -13980,37 +13980,37 @@
         <v>46098.4979333449</v>
       </c>
       <c r="F250" s="2">
-        <v>82693</v>
+        <v>82763</v>
       </c>
       <c r="G250" s="3">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="H250" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="I250" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="I250" s="1" t="s">
+      <c r="J250" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K250" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L250" s="4">
+        <v>120</v>
+      </c>
+      <c r="M250" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="N250" s="4">
+        <v>828</v>
+      </c>
+      <c r="O250" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="J250" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K250" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L250" s="4">
-        <v>20</v>
-      </c>
-      <c r="M250" s="4">
-        <v>20</v>
-      </c>
-      <c r="N250" s="4">
-        <v>400</v>
-      </c>
-      <c r="O250" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="P250" s="1" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="251">
@@ -14029,13 +14029,17 @@
       <c r="E251" s="3">
         <v>46098.4979333449</v>
       </c>
-      <c r="F251" s="1"/>
-      <c r="G251" s="1"/>
+      <c r="F251" s="2">
+        <v>82763</v>
+      </c>
+      <c r="G251" s="3">
+        <v>46101</v>
+      </c>
       <c r="H251" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>20</v>
@@ -14044,16 +14048,20 @@
         <v>132</v>
       </c>
       <c r="L251" s="4">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="M251" s="4">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="N251" s="4">
-        <v>0</v>
-      </c>
-      <c r="O251" s="1"/>
-      <c r="P251" s="1"/>
+        <v>2682</v>
+      </c>
+      <c r="O251" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="P251" s="1" t="s">
+        <v>501</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="252">
       <c r="A252" s="2">
@@ -14074,25 +14082,25 @@
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
       <c r="H252" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>132</v>
+        <v>506</v>
       </c>
       <c r="L252" s="4">
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="M252" s="4">
-        <v>0</v>
+        <v>189.9</v>
       </c>
       <c r="N252" s="4">
-        <v>0</v>
+        <v>189.9</v>
       </c>
       <c r="O252" s="1"/>
       <c r="P252" s="1"/>
@@ -14141,10 +14149,10 @@
         <v>59.9</v>
       </c>
       <c r="O253" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P253" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="254">
@@ -14191,10 +14199,10 @@
         <v>89.9</v>
       </c>
       <c r="O254" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P254" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="255">
@@ -14220,10 +14228,10 @@
         <v>46098</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>20</v>
@@ -14241,10 +14249,10 @@
         <v>199.8</v>
       </c>
       <c r="O255" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P255" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="256">
@@ -14270,10 +14278,10 @@
         <v>46099</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>20</v>
@@ -14320,10 +14328,10 @@
         <v>46101</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J257" s="1" t="s">
         <v>20</v>
@@ -14341,10 +14349,10 @@
         <v>950</v>
       </c>
       <c r="O257" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P257" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="258">
@@ -14370,10 +14378,10 @@
         <v>46101</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>20</v>
@@ -14391,10 +14399,10 @@
         <v>390</v>
       </c>
       <c r="O258" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="P258" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="259">
@@ -14570,10 +14578,10 @@
         <v>46099</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>20</v>
@@ -14620,10 +14628,10 @@
         <v>46099</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>20</v>
@@ -14670,10 +14678,10 @@
         <v>46099</v>
       </c>
       <c r="H264" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="I264" s="1" t="s">
         <v>503</v>
-      </c>
-      <c r="I264" s="1" t="s">
-        <v>504</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>20</v>
@@ -14770,10 +14778,10 @@
         <v>46099</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>20</v>
@@ -14820,10 +14828,10 @@
         <v>46099</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>20</v>
@@ -14920,16 +14928,16 @@
         <v>46098</v>
       </c>
       <c r="H269" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K269" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L269" s="4">
         <v>15</v>
@@ -14966,10 +14974,10 @@
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
       <c r="H270" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>20</v>
@@ -15008,10 +15016,10 @@
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
       <c r="H271" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>20</v>
@@ -15050,10 +15058,10 @@
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>20</v>
@@ -15092,10 +15100,10 @@
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>20</v>
@@ -15188,10 +15196,10 @@
         <v>46099</v>
       </c>
       <c r="H275" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>20</v>
@@ -15209,10 +15217,10 @@
         <v>126</v>
       </c>
       <c r="O275" s="1" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="P275" s="1" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="276">
@@ -15259,10 +15267,10 @@
         <v>1490</v>
       </c>
       <c r="O276" s="1" t="s">
-        <v>532</v>
+        <v>500</v>
       </c>
       <c r="P276" s="1" t="s">
-        <v>533</v>
+        <v>501</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="277">
@@ -16531,8 +16539,12 @@
       <c r="E302" s="3">
         <v>46100.6514887616</v>
       </c>
-      <c r="F302" s="1"/>
-      <c r="G302" s="1"/>
+      <c r="F302" s="2">
+        <v>82771</v>
+      </c>
+      <c r="G302" s="3">
+        <v>46101</v>
+      </c>
       <c r="H302" s="1" t="s">
         <v>578</v>
       </c>
@@ -16549,13 +16561,17 @@
         <v>1</v>
       </c>
       <c r="M302" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N302" s="4">
-        <v>0</v>
-      </c>
-      <c r="O302" s="1"/>
-      <c r="P302" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="O302" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="P302" s="1" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="303">
       <c r="A303" s="2">
@@ -16573,8 +16589,12 @@
       <c r="E303" s="3">
         <v>46100.6514887616</v>
       </c>
-      <c r="F303" s="1"/>
-      <c r="G303" s="1"/>
+      <c r="F303" s="2">
+        <v>82771</v>
+      </c>
+      <c r="G303" s="3">
+        <v>46101</v>
+      </c>
       <c r="H303" s="1" t="s">
         <v>578</v>
       </c>
@@ -16591,13 +16611,17 @@
         <v>1</v>
       </c>
       <c r="M303" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N303" s="4">
-        <v>0</v>
-      </c>
-      <c r="O303" s="1"/>
-      <c r="P303" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="O303" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="P303" s="1" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="304">
       <c r="A304" s="2">
@@ -16615,8 +16639,12 @@
       <c r="E304" s="3">
         <v>46100.6514887616</v>
       </c>
-      <c r="F304" s="1"/>
-      <c r="G304" s="1"/>
+      <c r="F304" s="2">
+        <v>82771</v>
+      </c>
+      <c r="G304" s="3">
+        <v>46101</v>
+      </c>
       <c r="H304" s="1" t="s">
         <v>578</v>
       </c>
@@ -16633,13 +16661,17 @@
         <v>1</v>
       </c>
       <c r="M304" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N304" s="4">
-        <v>0</v>
-      </c>
-      <c r="O304" s="1"/>
-      <c r="P304" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="O304" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="P304" s="1" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="305">
       <c r="A305" s="2">
@@ -16657,8 +16689,12 @@
       <c r="E305" s="3">
         <v>46100.6514887616</v>
       </c>
-      <c r="F305" s="1"/>
-      <c r="G305" s="1"/>
+      <c r="F305" s="2">
+        <v>82771</v>
+      </c>
+      <c r="G305" s="3">
+        <v>46101</v>
+      </c>
       <c r="H305" s="1" t="s">
         <v>578</v>
       </c>
@@ -16675,13 +16711,17 @@
         <v>2</v>
       </c>
       <c r="M305" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N305" s="4">
-        <v>0</v>
-      </c>
-      <c r="O305" s="1"/>
-      <c r="P305" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="O305" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="P305" s="1" t="s">
+        <v>550</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="306">
       <c r="A306" s="2">
@@ -16699,8 +16739,12 @@
       <c r="E306" s="3">
         <v>46100.6514887616</v>
       </c>
-      <c r="F306" s="1"/>
-      <c r="G306" s="1"/>
+      <c r="F306" s="2">
+        <v>82770</v>
+      </c>
+      <c r="G306" s="3">
+        <v>46101</v>
+      </c>
       <c r="H306" s="1" t="s">
         <v>580</v>
       </c>
@@ -16717,13 +16761,17 @@
         <v>20</v>
       </c>
       <c r="M306" s="4">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="N306" s="4">
-        <v>0</v>
-      </c>
-      <c r="O306" s="1"/>
-      <c r="P306" s="1"/>
+        <v>394</v>
+      </c>
+      <c r="O306" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="P306" s="1" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="307">
       <c r="A307" s="2">
@@ -16742,7 +16790,7 @@
         <v>46100.6528700694</v>
       </c>
       <c r="F307" s="2">
-        <v>82748</v>
+        <v>82746</v>
       </c>
       <c r="G307" s="3">
         <v>46100</v>
@@ -16757,22 +16805,22 @@
         <v>20</v>
       </c>
       <c r="K307" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L307" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M307" s="4">
-        <v>149</v>
+        <v>16.15</v>
       </c>
       <c r="N307" s="4">
-        <v>298</v>
+        <v>80.75</v>
       </c>
       <c r="O307" s="1" t="s">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="P307" s="1" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="308">
@@ -16807,16 +16855,16 @@
         <v>20</v>
       </c>
       <c r="K308" s="1" t="s">
-        <v>527</v>
+        <v>21</v>
       </c>
       <c r="L308" s="4">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="M308" s="4">
-        <v>2</v>
+        <v>149</v>
       </c>
       <c r="N308" s="4">
-        <v>60</v>
+        <v>298</v>
       </c>
       <c r="O308" s="1" t="s">
         <v>160</v>
@@ -16842,7 +16890,7 @@
         <v>46100.6528700694</v>
       </c>
       <c r="F309" s="2">
-        <v>82746</v>
+        <v>82748</v>
       </c>
       <c r="G309" s="3">
         <v>46100</v>
@@ -16857,22 +16905,22 @@
         <v>20</v>
       </c>
       <c r="K309" s="1" t="s">
-        <v>26</v>
+        <v>529</v>
       </c>
       <c r="L309" s="4">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M309" s="4">
-        <v>5.01</v>
+        <v>2</v>
       </c>
       <c r="N309" s="4">
-        <v>30.06</v>
+        <v>60</v>
       </c>
       <c r="O309" s="1" t="s">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="P309" s="1" t="s">
-        <v>65</v>
+        <v>161</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="310">
@@ -16913,10 +16961,10 @@
         <v>3</v>
       </c>
       <c r="M310" s="4">
-        <v>47.93</v>
+        <v>57.54</v>
       </c>
       <c r="N310" s="4">
-        <v>143.79</v>
+        <v>172.62</v>
       </c>
       <c r="O310" s="1" t="s">
         <v>64</v>
@@ -16963,10 +17011,10 @@
         <v>3</v>
       </c>
       <c r="M311" s="4">
-        <v>7.11</v>
+        <v>8.75</v>
       </c>
       <c r="N311" s="4">
-        <v>21.33</v>
+        <v>26.25</v>
       </c>
       <c r="O311" s="1" t="s">
         <v>64</v>
@@ -16992,7 +17040,7 @@
         <v>46100.6528700694</v>
       </c>
       <c r="F312" s="2">
-        <v>82746</v>
+        <v>82747</v>
       </c>
       <c r="G312" s="3">
         <v>46100</v>
@@ -17007,22 +17055,22 @@
         <v>20</v>
       </c>
       <c r="K312" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L312" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M312" s="4">
-        <v>6</v>
+        <v>49.2</v>
       </c>
       <c r="N312" s="4">
-        <v>60</v>
+        <v>984</v>
       </c>
       <c r="O312" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="P312" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="313">
@@ -17042,37 +17090,37 @@
         <v>46100.6528700694</v>
       </c>
       <c r="F313" s="2">
-        <v>82747</v>
+        <v>82745</v>
       </c>
       <c r="G313" s="3">
         <v>46100</v>
       </c>
       <c r="H313" s="1" t="s">
-        <v>594</v>
+        <v>182</v>
       </c>
       <c r="I313" s="1" t="s">
-        <v>595</v>
+        <v>183</v>
       </c>
       <c r="J313" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K313" s="1" t="s">
-        <v>33</v>
+        <v>184</v>
       </c>
       <c r="L313" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="M313" s="4">
-        <v>49.2</v>
+        <v>15</v>
       </c>
       <c r="N313" s="4">
-        <v>984</v>
+        <v>75</v>
       </c>
       <c r="O313" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="P313" s="1" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="314">
@@ -17091,39 +17139,31 @@
       <c r="E314" s="3">
         <v>46100.6528700694</v>
       </c>
-      <c r="F314" s="2">
-        <v>82745</v>
-      </c>
-      <c r="G314" s="3">
-        <v>46100</v>
-      </c>
+      <c r="F314" s="1"/>
+      <c r="G314" s="1"/>
       <c r="H314" s="1" t="s">
-        <v>182</v>
+        <v>594</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>183</v>
+        <v>595</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K314" s="1" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
       <c r="L314" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M314" s="4">
-        <v>15</v>
+        <v>5.01</v>
       </c>
       <c r="N314" s="4">
-        <v>75</v>
-      </c>
-      <c r="O314" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="P314" s="1" t="s">
-        <v>50</v>
-      </c>
+        <v>30.06</v>
+      </c>
+      <c r="O314" s="1"/>
+      <c r="P314" s="1"/>
     </row>
     <row ht="12.75" customHeight="1" r="315">
       <c r="A315" s="2">
@@ -17156,13 +17196,13 @@
         <v>26</v>
       </c>
       <c r="L315" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M315" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N315" s="4">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O315" s="1"/>
       <c r="P315" s="1"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1832,6 +1832,12 @@
     <t>BORRIFADOR MANUAL</t>
   </si>
   <si>
+    <t>D.01.0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMÁRIO DE AÇO - ROUPEIRO 8 VÃOS  PEQUENOS  EM CHAPA 24</t>
+  </si>
+  <si>
     <t>C.05.0264</t>
   </si>
   <si>
@@ -1842,12 +1848,6 @@
   </si>
   <si>
     <t>PORTA CADEADO</t>
-  </si>
-  <si>
-    <t>D.01.0001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARMÁRIO DE AÇO - ROUPEIRO 8 VÃOS  PEQUENOS  EM CHAPA 24</t>
   </si>
   <si>
     <t>E.01.0009</t>
@@ -17509,8 +17509,12 @@
       <c r="E319" s="3">
         <v>46104.452366169</v>
       </c>
-      <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
+      <c r="F319" s="2">
+        <v>82784</v>
+      </c>
+      <c r="G319" s="3">
+        <v>46104</v>
+      </c>
       <c r="H319" s="1" t="s">
         <v>606</v>
       </c>
@@ -17527,13 +17531,17 @@
         <v>1</v>
       </c>
       <c r="M319" s="4">
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="N319" s="4">
-        <v>0</v>
-      </c>
-      <c r="O319" s="1"/>
-      <c r="P319" s="1"/>
+        <v>1092</v>
+      </c>
+      <c r="O319" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="P319" s="1" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="320">
       <c r="A320" s="2">

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1832,16 +1832,16 @@
     <t>BORRIFADOR MANUAL</t>
   </si>
   <si>
+    <t>C.05.0264</t>
+  </si>
+  <si>
+    <t>LIXEIRA -</t>
+  </si>
+  <si>
     <t>D.01.0001</t>
   </si>
   <si>
     <t xml:space="preserve">ARMÁRIO DE AÇO - ROUPEIRO 8 VÃOS  PEQUENOS  EM CHAPA 24</t>
-  </si>
-  <si>
-    <t>C.05.0264</t>
-  </si>
-  <si>
-    <t>LIXEIRA -</t>
   </si>
   <si>
     <t>C.05.0306</t>
@@ -17481,10 +17481,10 @@
         <v>1</v>
       </c>
       <c r="M318" s="4">
-        <v>9.3</v>
+        <v>12.9</v>
       </c>
       <c r="N318" s="4">
-        <v>9.3</v>
+        <v>12.9</v>
       </c>
       <c r="O318" s="1" t="s">
         <v>78</v>
@@ -17510,7 +17510,7 @@
         <v>46104.452366169</v>
       </c>
       <c r="F319" s="2">
-        <v>82784</v>
+        <v>82780</v>
       </c>
       <c r="G319" s="3">
         <v>46104</v>
@@ -17531,16 +17531,16 @@
         <v>1</v>
       </c>
       <c r="M319" s="4">
-        <v>1092</v>
+        <v>35</v>
       </c>
       <c r="N319" s="4">
-        <v>1092</v>
+        <v>35</v>
       </c>
       <c r="O319" s="1" t="s">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="P319" s="1" t="s">
-        <v>435</v>
+        <v>79</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="320">
@@ -17559,8 +17559,12 @@
       <c r="E320" s="3">
         <v>46104.452366169</v>
       </c>
-      <c r="F320" s="1"/>
-      <c r="G320" s="1"/>
+      <c r="F320" s="2">
+        <v>82784</v>
+      </c>
+      <c r="G320" s="3">
+        <v>46104</v>
+      </c>
       <c r="H320" s="1" t="s">
         <v>608</v>
       </c>
@@ -17577,13 +17581,17 @@
         <v>1</v>
       </c>
       <c r="M320" s="4">
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="N320" s="4">
-        <v>0</v>
-      </c>
-      <c r="O320" s="1"/>
-      <c r="P320" s="1"/>
+        <v>1092</v>
+      </c>
+      <c r="O320" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="P320" s="1" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="321">
       <c r="A321" s="2">
@@ -17601,13 +17609,17 @@
       <c r="E321" s="3">
         <v>46104.452366169</v>
       </c>
-      <c r="F321" s="1"/>
-      <c r="G321" s="1"/>
+      <c r="F321" s="2">
+        <v>82785</v>
+      </c>
+      <c r="G321" s="3">
+        <v>46104</v>
+      </c>
       <c r="H321" s="1" t="s">
-        <v>610</v>
+        <v>354</v>
       </c>
       <c r="I321" s="1" t="s">
-        <v>611</v>
+        <v>355</v>
       </c>
       <c r="J321" s="1" t="s">
         <v>20</v>
@@ -17616,16 +17628,20 @@
         <v>28</v>
       </c>
       <c r="L321" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M321" s="4">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N321" s="4">
-        <v>0</v>
-      </c>
-      <c r="O321" s="1"/>
-      <c r="P321" s="1"/>
+        <v>920</v>
+      </c>
+      <c r="O321" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P321" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="322">
       <c r="A322" s="2">
@@ -17646,10 +17662,10 @@
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
       <c r="H322" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>20</v>
@@ -17688,10 +17704,10 @@
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
       <c r="H323" s="1" t="s">
-        <v>354</v>
+        <v>612</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>355</v>
+        <v>613</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>20</v>
@@ -17700,7 +17716,7 @@
         <v>28</v>
       </c>
       <c r="L323" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M323" s="4">
         <v>0</v>
@@ -18421,10 +18437,10 @@
         <v>2</v>
       </c>
       <c r="M340" s="4">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="N340" s="4">
-        <v>27</v>
+        <v>29.8</v>
       </c>
       <c r="O340" s="1" t="s">
         <v>78</v>
@@ -18506,10 +18522,10 @@
         <v>46104</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>87</v>
+        <v>639</v>
       </c>
       <c r="I342" s="1" t="s">
-        <v>88</v>
+        <v>640</v>
       </c>
       <c r="J342" s="1" t="s">
         <v>20</v>
@@ -18518,13 +18534,13 @@
         <v>28</v>
       </c>
       <c r="L342" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M342" s="4">
-        <v>24.9</v>
+        <v>3.38</v>
       </c>
       <c r="N342" s="4">
-        <v>49.8</v>
+        <v>16.9</v>
       </c>
       <c r="O342" s="1" t="s">
         <v>78</v>
@@ -18550,37 +18566,37 @@
         <v>46104.4566862384</v>
       </c>
       <c r="F343" s="2">
-        <v>82781</v>
+        <v>82782</v>
       </c>
       <c r="G343" s="3">
         <v>46104</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>18</v>
+        <v>641</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>19</v>
+        <v>642</v>
       </c>
       <c r="J343" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K343" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L343" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M343" s="4">
-        <v>305</v>
+        <v>50</v>
       </c>
       <c r="N343" s="4">
-        <v>305</v>
+        <v>200</v>
       </c>
       <c r="O343" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="P343" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="344">
@@ -18600,37 +18616,37 @@
         <v>46104.4566862384</v>
       </c>
       <c r="F344" s="2">
-        <v>82781</v>
+        <v>82782</v>
       </c>
       <c r="G344" s="3">
         <v>46104</v>
       </c>
       <c r="H344" s="1" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="I344" s="1" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="J344" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K344" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L344" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M344" s="4">
-        <v>89.9</v>
+        <v>25.9</v>
       </c>
       <c r="N344" s="4">
-        <v>359.6</v>
+        <v>51.8</v>
       </c>
       <c r="O344" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="P344" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="345">
@@ -18649,31 +18665,39 @@
       <c r="E345" s="3">
         <v>46104.4566862384</v>
       </c>
-      <c r="F345" s="1"/>
-      <c r="G345" s="1"/>
+      <c r="F345" s="2">
+        <v>82781</v>
+      </c>
+      <c r="G345" s="3">
+        <v>46104</v>
+      </c>
       <c r="H345" s="1" t="s">
-        <v>639</v>
+        <v>18</v>
       </c>
       <c r="I345" s="1" t="s">
-        <v>640</v>
+        <v>19</v>
       </c>
       <c r="J345" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K345" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L345" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M345" s="4">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="N345" s="4">
-        <v>0</v>
-      </c>
-      <c r="O345" s="1"/>
-      <c r="P345" s="1"/>
+        <v>305</v>
+      </c>
+      <c r="O345" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P345" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="346">
       <c r="A346" s="2">
@@ -18691,31 +18715,39 @@
       <c r="E346" s="3">
         <v>46104.4566862384</v>
       </c>
-      <c r="F346" s="1"/>
-      <c r="G346" s="1"/>
+      <c r="F346" s="2">
+        <v>82781</v>
+      </c>
+      <c r="G346" s="3">
+        <v>46104</v>
+      </c>
       <c r="H346" s="1" t="s">
-        <v>641</v>
+        <v>24</v>
       </c>
       <c r="I346" s="1" t="s">
-        <v>642</v>
+        <v>25</v>
       </c>
       <c r="J346" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K346" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L346" s="4">
         <v>4</v>
       </c>
       <c r="M346" s="4">
-        <v>0</v>
+        <v>89.9</v>
       </c>
       <c r="N346" s="4">
-        <v>0</v>
-      </c>
-      <c r="O346" s="1"/>
-      <c r="P346" s="1"/>
+        <v>359.6</v>
+      </c>
+      <c r="O346" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P346" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="347">
       <c r="A347" s="2">
@@ -18733,8 +18765,12 @@
       <c r="E347" s="3">
         <v>46104.4566862384</v>
       </c>
-      <c r="F347" s="1"/>
-      <c r="G347" s="1"/>
+      <c r="F347" s="2">
+        <v>82781</v>
+      </c>
+      <c r="G347" s="3">
+        <v>46104</v>
+      </c>
       <c r="H347" s="1" t="s">
         <v>356</v>
       </c>
@@ -18751,13 +18787,17 @@
         <v>3</v>
       </c>
       <c r="M347" s="4">
-        <v>4.93</v>
+        <v>13.9</v>
       </c>
       <c r="N347" s="4">
-        <v>14.79</v>
-      </c>
-      <c r="O347" s="1"/>
-      <c r="P347" s="1"/>
+        <v>41.7</v>
+      </c>
+      <c r="O347" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P347" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="348">
       <c r="A348" s="2">
@@ -18775,8 +18815,12 @@
       <c r="E348" s="3">
         <v>46104.4566862384</v>
       </c>
-      <c r="F348" s="1"/>
-      <c r="G348" s="1"/>
+      <c r="F348" s="2">
+        <v>82781</v>
+      </c>
+      <c r="G348" s="3">
+        <v>46104</v>
+      </c>
       <c r="H348" s="1" t="s">
         <v>643</v>
       </c>
@@ -18793,13 +18837,17 @@
         <v>2</v>
       </c>
       <c r="M348" s="4">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N348" s="4">
-        <v>0</v>
-      </c>
-      <c r="O348" s="1"/>
-      <c r="P348" s="1"/>
+        <v>278</v>
+      </c>
+      <c r="O348" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P348" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="349">
       <c r="A349" s="2">
@@ -18817,8 +18865,12 @@
       <c r="E349" s="3">
         <v>46104.4566862384</v>
       </c>
-      <c r="F349" s="1"/>
-      <c r="G349" s="1"/>
+      <c r="F349" s="2">
+        <v>82782</v>
+      </c>
+      <c r="G349" s="3">
+        <v>46104</v>
+      </c>
       <c r="H349" s="1" t="s">
         <v>645</v>
       </c>
@@ -18835,13 +18887,17 @@
         <v>2</v>
       </c>
       <c r="M349" s="4">
-        <v>0</v>
+        <v>19.9</v>
       </c>
       <c r="N349" s="4">
-        <v>0</v>
-      </c>
-      <c r="O349" s="1"/>
-      <c r="P349" s="1"/>
+        <v>39.8</v>
+      </c>
+      <c r="O349" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="P349" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="350">
       <c r="A350" s="2">
@@ -18859,8 +18915,12 @@
       <c r="E350" s="3">
         <v>46104.4566862384</v>
       </c>
-      <c r="F350" s="1"/>
-      <c r="G350" s="1"/>
+      <c r="F350" s="2">
+        <v>82781</v>
+      </c>
+      <c r="G350" s="3">
+        <v>46104</v>
+      </c>
       <c r="H350" s="1" t="s">
         <v>370</v>
       </c>
@@ -18877,13 +18937,17 @@
         <v>6</v>
       </c>
       <c r="M350" s="4">
-        <v>10.31</v>
+        <v>25.9</v>
       </c>
       <c r="N350" s="4">
-        <v>61.86</v>
-      </c>
-      <c r="O350" s="1"/>
-      <c r="P350" s="1"/>
+        <v>155.4</v>
+      </c>
+      <c r="O350" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P350" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="649">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1286,6 +1286,18 @@
     <t>REGINA CAMPOS SALLES MORAES ABREU</t>
   </si>
   <si>
+    <t>C.05.0208</t>
+  </si>
+  <si>
+    <t>CADEIRA SECRETÁRIA FIXA</t>
+  </si>
+  <si>
+    <t>00000000010368</t>
+  </si>
+  <si>
+    <t>DOMINIO FERRAMENTAS</t>
+  </si>
+  <si>
     <t>D.04.0010</t>
   </si>
   <si>
@@ -1340,6 +1352,12 @@
     <t>TRENA LONGA DE FIBRA- 30 M</t>
   </si>
   <si>
+    <t>E.04.0173</t>
+  </si>
+  <si>
+    <t>NÍVEL A LASER</t>
+  </si>
+  <si>
     <t>E.04.0165</t>
   </si>
   <si>
@@ -1376,6 +1394,12 @@
     <t>REGUA DE ALUMINIO 3 X 1'' C/ 6 M</t>
   </si>
   <si>
+    <t>E.04.0177</t>
+  </si>
+  <si>
+    <t>TRIPÉ PARA NIVEL A LASER</t>
+  </si>
+  <si>
     <t>F.01.0011</t>
   </si>
   <si>
@@ -1404,24 +1428,6 @@
   </si>
   <si>
     <t>MANGUEIRA</t>
-  </si>
-  <si>
-    <t>C.05.0208</t>
-  </si>
-  <si>
-    <t>CADEIRA SECRETÁRIA FIXA</t>
-  </si>
-  <si>
-    <t>E.04.0173</t>
-  </si>
-  <si>
-    <t>NÍVEL A LASER</t>
-  </si>
-  <si>
-    <t>E.04.0177</t>
-  </si>
-  <si>
-    <t>TRIPÉ PARA NIVEL A LASER</t>
   </si>
   <si>
     <t>LUIZ ALBERTO HESS BORGES</t>
@@ -12174,10 +12180,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F211" s="2">
-        <v>82717</v>
+        <v>82786</v>
       </c>
       <c r="G211" s="3">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>424</v>
@@ -12192,13 +12198,13 @@
         <v>28</v>
       </c>
       <c r="L211" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M211" s="4">
-        <v>860</v>
+        <v>216</v>
       </c>
       <c r="N211" s="4">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="O211" s="1" t="s">
         <v>426</v>
@@ -12224,7 +12230,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F212" s="2">
-        <v>82716</v>
+        <v>82717</v>
       </c>
       <c r="G212" s="3">
         <v>46099</v>
@@ -12239,16 +12245,16 @@
         <v>20</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="L212" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M212" s="4">
-        <v>300</v>
+        <v>860</v>
       </c>
       <c r="N212" s="4">
-        <v>2400</v>
+        <v>860</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>430</v>
@@ -12274,10 +12280,10 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F213" s="2">
-        <v>82692</v>
+        <v>82716</v>
       </c>
       <c r="G213" s="3">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="H213" s="1" t="s">
         <v>432</v>
@@ -12289,16 +12295,16 @@
         <v>20</v>
       </c>
       <c r="K213" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L213" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M213" s="4">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="N213" s="4">
-        <v>322</v>
+        <v>2400</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>434</v>
@@ -12324,7 +12330,7 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F214" s="2">
-        <v>82691</v>
+        <v>82692</v>
       </c>
       <c r="G214" s="3">
         <v>46098</v>
@@ -12342,19 +12348,19 @@
         <v>28</v>
       </c>
       <c r="L214" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M214" s="4">
-        <v>29</v>
+        <v>322</v>
       </c>
       <c r="N214" s="4">
-        <v>58</v>
+        <v>322</v>
       </c>
       <c r="O214" s="1" t="s">
-        <v>97</v>
+        <v>438</v>
       </c>
       <c r="P214" s="1" t="s">
-        <v>98</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="215">
@@ -12380,10 +12386,10 @@
         <v>46098</v>
       </c>
       <c r="H215" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I215" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="J215" s="1" t="s">
         <v>20</v>
@@ -12395,10 +12401,10 @@
         <v>2</v>
       </c>
       <c r="M215" s="4">
-        <v>23.77</v>
+        <v>29</v>
       </c>
       <c r="N215" s="4">
-        <v>47.54</v>
+        <v>58</v>
       </c>
       <c r="O215" s="1" t="s">
         <v>97</v>
@@ -12424,16 +12430,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F216" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="G216" s="3">
         <v>46098</v>
       </c>
       <c r="H216" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I216" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J216" s="1" t="s">
         <v>20</v>
@@ -12442,19 +12448,19 @@
         <v>28</v>
       </c>
       <c r="L216" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M216" s="4">
-        <v>145</v>
+        <v>23.77</v>
       </c>
       <c r="N216" s="4">
-        <v>145</v>
+        <v>47.54</v>
       </c>
       <c r="O216" s="1" t="s">
-        <v>434</v>
+        <v>97</v>
       </c>
       <c r="P216" s="1" t="s">
-        <v>435</v>
+        <v>98</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="217">
@@ -12480,10 +12486,10 @@
         <v>46098</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>20</v>
@@ -12492,19 +12498,19 @@
         <v>28</v>
       </c>
       <c r="L217" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M217" s="4">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="N217" s="4">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="O217" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="P217" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="218">
@@ -12524,16 +12530,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F218" s="2">
-        <v>82691</v>
+        <v>82786</v>
       </c>
       <c r="G218" s="3">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="H218" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I218" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="J218" s="1" t="s">
         <v>20</v>
@@ -12542,19 +12548,19 @@
         <v>28</v>
       </c>
       <c r="L218" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M218" s="4">
-        <v>123.37</v>
+        <v>918</v>
       </c>
       <c r="N218" s="4">
-        <v>246.74</v>
+        <v>918</v>
       </c>
       <c r="O218" s="1" t="s">
-        <v>97</v>
+        <v>426</v>
       </c>
       <c r="P218" s="1" t="s">
-        <v>98</v>
+        <v>427</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="219">
@@ -12580,10 +12586,10 @@
         <v>46098</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I219" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J219" s="1" t="s">
         <v>20</v>
@@ -12592,19 +12598,19 @@
         <v>28</v>
       </c>
       <c r="L219" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M219" s="4">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="N219" s="4">
-        <v>61</v>
+        <v>244</v>
       </c>
       <c r="O219" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="P219" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="220">
@@ -12624,16 +12630,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F220" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="G220" s="3">
         <v>46098</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J220" s="1" t="s">
         <v>20</v>
@@ -12645,16 +12651,16 @@
         <v>2</v>
       </c>
       <c r="M220" s="4">
-        <v>92.8</v>
+        <v>123.37</v>
       </c>
       <c r="N220" s="4">
-        <v>185.6</v>
+        <v>246.74</v>
       </c>
       <c r="O220" s="1" t="s">
-        <v>434</v>
+        <v>97</v>
       </c>
       <c r="P220" s="1" t="s">
-        <v>435</v>
+        <v>98</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="221">
@@ -12680,10 +12686,10 @@
         <v>46098</v>
       </c>
       <c r="H221" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="J221" s="1" t="s">
         <v>20</v>
@@ -12692,19 +12698,19 @@
         <v>28</v>
       </c>
       <c r="L221" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M221" s="4">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="N221" s="4">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="O221" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="P221" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="222">
@@ -12724,16 +12730,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F222" s="2">
-        <v>82691</v>
+        <v>82692</v>
       </c>
       <c r="G222" s="3">
         <v>46098</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J222" s="1" t="s">
         <v>20</v>
@@ -12745,16 +12751,16 @@
         <v>2</v>
       </c>
       <c r="M222" s="4">
-        <v>246.74</v>
+        <v>92.8</v>
       </c>
       <c r="N222" s="4">
-        <v>493.48</v>
+        <v>185.6</v>
       </c>
       <c r="O222" s="1" t="s">
-        <v>97</v>
+        <v>438</v>
       </c>
       <c r="P222" s="1" t="s">
-        <v>98</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="223">
@@ -12780,10 +12786,10 @@
         <v>46098</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>20</v>
@@ -12792,19 +12798,19 @@
         <v>28</v>
       </c>
       <c r="L223" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M223" s="4">
-        <v>253</v>
+        <v>31</v>
       </c>
       <c r="N223" s="4">
-        <v>253</v>
+        <v>124</v>
       </c>
       <c r="O223" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="P223" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="224">
@@ -12824,16 +12830,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F224" s="2">
-        <v>82692</v>
+        <v>82691</v>
       </c>
       <c r="G224" s="3">
         <v>46098</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="J224" s="1" t="s">
         <v>20</v>
@@ -12842,19 +12848,19 @@
         <v>28</v>
       </c>
       <c r="L224" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M224" s="4">
-        <v>625</v>
+        <v>246.74</v>
       </c>
       <c r="N224" s="4">
-        <v>625</v>
+        <v>493.48</v>
       </c>
       <c r="O224" s="1" t="s">
-        <v>434</v>
+        <v>97</v>
       </c>
       <c r="P224" s="1" t="s">
-        <v>435</v>
+        <v>98</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="225">
@@ -12874,16 +12880,16 @@
         <v>46097.4682502893</v>
       </c>
       <c r="F225" s="2">
-        <v>82699</v>
+        <v>82786</v>
       </c>
       <c r="G225" s="3">
-        <v>46098</v>
+        <v>46104</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>20</v>
@@ -12892,19 +12898,19 @@
         <v>28</v>
       </c>
       <c r="L225" s="4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="M225" s="4">
-        <v>390</v>
+        <v>394.8</v>
       </c>
       <c r="N225" s="4">
-        <v>13650</v>
+        <v>394.8</v>
       </c>
       <c r="O225" s="1" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
       <c r="P225" s="1" t="s">
-        <v>461</v>
+        <v>427</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="226">
@@ -12939,22 +12945,22 @@
         <v>20</v>
       </c>
       <c r="K226" s="1" t="s">
-        <v>125</v>
+        <v>28</v>
       </c>
       <c r="L226" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M226" s="4">
-        <v>5.66</v>
+        <v>253</v>
       </c>
       <c r="N226" s="4">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="O226" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="P226" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="227">
@@ -12973,8 +12979,12 @@
       <c r="E227" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F227" s="1"/>
-      <c r="G227" s="1"/>
+      <c r="F227" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G227" s="3">
+        <v>46098</v>
+      </c>
       <c r="H227" s="1" t="s">
         <v>464</v>
       </c>
@@ -12988,16 +12998,20 @@
         <v>28</v>
       </c>
       <c r="L227" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M227" s="4">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="N227" s="4">
-        <v>0</v>
-      </c>
-      <c r="O227" s="1"/>
-      <c r="P227" s="1"/>
+        <v>625</v>
+      </c>
+      <c r="O227" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="P227" s="1" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="228">
       <c r="A228" s="2">
@@ -13015,8 +13029,12 @@
       <c r="E228" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F228" s="1"/>
-      <c r="G228" s="1"/>
+      <c r="F228" s="2">
+        <v>82699</v>
+      </c>
+      <c r="G228" s="3">
+        <v>46098</v>
+      </c>
       <c r="H228" s="1" t="s">
         <v>466</v>
       </c>
@@ -13030,16 +13048,20 @@
         <v>28</v>
       </c>
       <c r="L228" s="4">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="M228" s="4">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N228" s="4">
-        <v>0</v>
-      </c>
-      <c r="O228" s="1"/>
-      <c r="P228" s="1"/>
+        <v>13650</v>
+      </c>
+      <c r="O228" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="P228" s="1" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="229">
       <c r="A229" s="2">
@@ -13057,38 +13079,46 @@
       <c r="E229" s="3">
         <v>46097.4682502893</v>
       </c>
-      <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
+      <c r="F229" s="2">
+        <v>82692</v>
+      </c>
+      <c r="G229" s="3">
+        <v>46098</v>
+      </c>
       <c r="H229" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J229" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K229" s="1" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="L229" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="M229" s="4">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="N229" s="4">
-        <v>0</v>
-      </c>
-      <c r="O229" s="1"/>
-      <c r="P229" s="1"/>
+        <v>283</v>
+      </c>
+      <c r="O229" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="P229" s="1" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="230">
       <c r="A230" s="2">
         <v>2317</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>75</v>
@@ -13138,7 +13168,7 @@
         <v>2317</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>75</v>
@@ -13188,7 +13218,7 @@
         <v>2317</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>75</v>
@@ -13206,10 +13236,10 @@
         <v>46097</v>
       </c>
       <c r="H232" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>20</v>
@@ -13238,7 +13268,7 @@
         <v>2404</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>17</v>
@@ -13288,7 +13318,7 @@
         <v>2404</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>17</v>
@@ -13338,7 +13368,7 @@
         <v>2404</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>17</v>
@@ -13388,7 +13418,7 @@
         <v>2404</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>17</v>
@@ -13438,7 +13468,7 @@
         <v>2404</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>17</v>
@@ -13456,10 +13486,10 @@
         <v>46098</v>
       </c>
       <c r="H237" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="J237" s="1" t="s">
         <v>20</v>
@@ -13488,7 +13518,7 @@
         <v>2404</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>17</v>
@@ -13538,7 +13568,7 @@
         <v>2514</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>75</v>
@@ -13577,10 +13607,10 @@
         <v>115.6</v>
       </c>
       <c r="O239" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P239" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="240">
@@ -13588,7 +13618,7 @@
         <v>2514</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>75</v>
@@ -13627,10 +13657,10 @@
         <v>85.9</v>
       </c>
       <c r="O240" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P240" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="241">
@@ -13638,7 +13668,7 @@
         <v>2514</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>75</v>
@@ -13656,10 +13686,10 @@
         <v>46101</v>
       </c>
       <c r="H241" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J241" s="1" t="s">
         <v>20</v>
@@ -13677,10 +13707,10 @@
         <v>69</v>
       </c>
       <c r="O241" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="P241" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="242">
@@ -13688,7 +13718,7 @@
         <v>2514</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>75</v>
@@ -13706,10 +13736,10 @@
         <v>46098</v>
       </c>
       <c r="H242" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J242" s="1" t="s">
         <v>20</v>
@@ -13727,10 +13757,10 @@
         <v>1011.5</v>
       </c>
       <c r="O242" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P242" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="243">
@@ -13738,7 +13768,7 @@
         <v>2514</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>75</v>
@@ -13756,10 +13786,10 @@
         <v>46098</v>
       </c>
       <c r="H243" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J243" s="1" t="s">
         <v>20</v>
@@ -13777,10 +13807,10 @@
         <v>3290</v>
       </c>
       <c r="O243" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P243" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="244">
@@ -13788,7 +13818,7 @@
         <v>2514</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>75</v>
@@ -13806,10 +13836,10 @@
         <v>46098</v>
       </c>
       <c r="H244" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J244" s="1" t="s">
         <v>20</v>
@@ -13827,10 +13857,10 @@
         <v>1240</v>
       </c>
       <c r="O244" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P244" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="245">
@@ -13838,7 +13868,7 @@
         <v>2514</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>75</v>
@@ -13856,10 +13886,10 @@
         <v>46098</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>20</v>
@@ -13877,10 +13907,10 @@
         <v>400</v>
       </c>
       <c r="O245" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P245" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="246">
@@ -13888,7 +13918,7 @@
         <v>2514</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>75</v>
@@ -13906,10 +13936,10 @@
         <v>46101</v>
       </c>
       <c r="H246" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J246" s="1" t="s">
         <v>20</v>
@@ -13927,10 +13957,10 @@
         <v>828</v>
       </c>
       <c r="O246" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P246" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="247">
@@ -13938,7 +13968,7 @@
         <v>2514</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>75</v>
@@ -13956,10 +13986,10 @@
         <v>46101</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J247" s="1" t="s">
         <v>20</v>
@@ -13977,10 +14007,10 @@
         <v>2682</v>
       </c>
       <c r="O247" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P247" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="248">
@@ -13988,7 +14018,7 @@
         <v>2514</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>75</v>
@@ -14002,16 +14032,16 @@
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
       <c r="H248" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J248" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L248" s="4">
         <v>1</v>
@@ -14069,10 +14099,10 @@
         <v>59.9</v>
       </c>
       <c r="O249" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="P249" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="250">
@@ -14119,10 +14149,10 @@
         <v>89.9</v>
       </c>
       <c r="O250" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="P250" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="251">
@@ -14148,10 +14178,10 @@
         <v>46098</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>20</v>
@@ -14169,10 +14199,10 @@
         <v>199.8</v>
       </c>
       <c r="O251" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="P251" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="252">
@@ -14198,10 +14228,10 @@
         <v>46099</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>20</v>
@@ -14248,10 +14278,10 @@
         <v>46101</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>20</v>
@@ -14269,10 +14299,10 @@
         <v>950</v>
       </c>
       <c r="O253" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P253" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="254">
@@ -14298,10 +14328,10 @@
         <v>46101</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>20</v>
@@ -14319,10 +14349,10 @@
         <v>390</v>
       </c>
       <c r="O254" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P254" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="255">
@@ -14498,10 +14528,10 @@
         <v>46099</v>
       </c>
       <c r="H258" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>20</v>
@@ -14548,10 +14578,10 @@
         <v>46099</v>
       </c>
       <c r="H259" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I259" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J259" s="1" t="s">
         <v>20</v>
@@ -14598,10 +14628,10 @@
         <v>46099</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="J260" s="1" t="s">
         <v>20</v>
@@ -14698,10 +14728,10 @@
         <v>46099</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>20</v>
@@ -14748,10 +14778,10 @@
         <v>46099</v>
       </c>
       <c r="H263" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="J263" s="1" t="s">
         <v>20</v>
@@ -14848,16 +14878,16 @@
         <v>46098</v>
       </c>
       <c r="H265" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K265" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L265" s="4">
         <v>15</v>
@@ -14894,10 +14924,10 @@
       <c r="F266" s="1"/>
       <c r="G266" s="1"/>
       <c r="H266" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>20</v>
@@ -14936,10 +14966,10 @@
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
       <c r="H267" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>20</v>
@@ -14978,10 +15008,10 @@
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
       <c r="H268" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>20</v>
@@ -15020,10 +15050,10 @@
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
       <c r="H269" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J269" s="1" t="s">
         <v>20</v>
@@ -15116,10 +15146,10 @@
         <v>46099</v>
       </c>
       <c r="H271" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>20</v>
@@ -15137,10 +15167,10 @@
         <v>126</v>
       </c>
       <c r="O271" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P271" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="272">
@@ -15166,10 +15196,10 @@
         <v>46099</v>
       </c>
       <c r="H272" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>20</v>
@@ -15187,10 +15217,10 @@
         <v>1490</v>
       </c>
       <c r="O272" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="P272" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="273">
@@ -15216,10 +15246,10 @@
         <v>46098</v>
       </c>
       <c r="H273" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>20</v>
@@ -15237,10 +15267,10 @@
         <v>933</v>
       </c>
       <c r="O273" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P273" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="274">
@@ -15366,10 +15396,10 @@
         <v>46099</v>
       </c>
       <c r="H276" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>20</v>
@@ -15416,10 +15446,10 @@
         <v>46099</v>
       </c>
       <c r="H277" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="I277" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="J277" s="1" t="s">
         <v>20</v>
@@ -15466,10 +15496,10 @@
         <v>46099</v>
       </c>
       <c r="H278" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="J278" s="1" t="s">
         <v>20</v>
@@ -15516,16 +15546,16 @@
         <v>46099</v>
       </c>
       <c r="H279" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J279" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K279" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="L279" s="4">
         <v>60</v>
@@ -15537,10 +15567,10 @@
         <v>1099.8</v>
       </c>
       <c r="O279" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P279" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="280">
@@ -15566,10 +15596,10 @@
         <v>46099</v>
       </c>
       <c r="H280" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="J280" s="1" t="s">
         <v>20</v>
@@ -15616,10 +15646,10 @@
         <v>46099</v>
       </c>
       <c r="H281" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J281" s="1" t="s">
         <v>20</v>
@@ -15666,10 +15696,10 @@
         <v>46099</v>
       </c>
       <c r="H282" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J282" s="1" t="s">
         <v>20</v>
@@ -15716,10 +15746,10 @@
         <v>46099</v>
       </c>
       <c r="H283" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="J283" s="1" t="s">
         <v>20</v>
@@ -15766,10 +15796,10 @@
         <v>46099</v>
       </c>
       <c r="H284" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="J284" s="1" t="s">
         <v>20</v>
@@ -15816,10 +15846,10 @@
         <v>46099</v>
       </c>
       <c r="H285" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="I285" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J285" s="1" t="s">
         <v>20</v>
@@ -15837,10 +15867,10 @@
         <v>1440</v>
       </c>
       <c r="O285" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="P285" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="286">
@@ -15866,10 +15896,10 @@
         <v>46099</v>
       </c>
       <c r="H286" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="I286" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J286" s="1" t="s">
         <v>20</v>
@@ -15887,10 +15917,10 @@
         <v>3000</v>
       </c>
       <c r="O286" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="P286" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="287">
@@ -15898,7 +15928,7 @@
         <v>2511</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>75</v>
@@ -15948,7 +15978,7 @@
         <v>2511</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>75</v>
@@ -15966,10 +15996,10 @@
         <v>46099</v>
       </c>
       <c r="H288" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="I288" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="J288" s="1" t="s">
         <v>20</v>
@@ -15998,7 +16028,7 @@
         <v>2511</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>75</v>
@@ -16048,7 +16078,7 @@
         <v>2511</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>75</v>
@@ -16098,7 +16128,7 @@
         <v>2511</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>75</v>
@@ -16116,10 +16146,10 @@
         <v>46099</v>
       </c>
       <c r="H291" s="1" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I291" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J291" s="1" t="s">
         <v>20</v>
@@ -16148,7 +16178,7 @@
         <v>2511</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>75</v>
@@ -16198,7 +16228,7 @@
         <v>2511</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>75</v>
@@ -16248,7 +16278,7 @@
         <v>2511</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>75</v>
@@ -16298,7 +16328,7 @@
         <v>2511</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>75</v>
@@ -16316,10 +16346,10 @@
         <v>46099</v>
       </c>
       <c r="H295" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="I295" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="J295" s="1" t="s">
         <v>20</v>
@@ -16348,7 +16378,7 @@
         <v>2511</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>75</v>
@@ -16398,7 +16428,7 @@
         <v>2511</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>75</v>
@@ -16416,10 +16446,10 @@
         <v>46100</v>
       </c>
       <c r="H297" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="I297" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="J297" s="1" t="s">
         <v>20</v>
@@ -16437,10 +16467,10 @@
         <v>540</v>
       </c>
       <c r="O297" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P297" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="298">
@@ -16466,10 +16496,10 @@
         <v>46101</v>
       </c>
       <c r="H298" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I298" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J298" s="1" t="s">
         <v>20</v>
@@ -16487,10 +16517,10 @@
         <v>1</v>
       </c>
       <c r="O298" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P298" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="299">
@@ -16516,10 +16546,10 @@
         <v>46101</v>
       </c>
       <c r="H299" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I299" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J299" s="1" t="s">
         <v>20</v>
@@ -16537,10 +16567,10 @@
         <v>1</v>
       </c>
       <c r="O299" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P299" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="300">
@@ -16566,10 +16596,10 @@
         <v>46101</v>
       </c>
       <c r="H300" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I300" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J300" s="1" t="s">
         <v>20</v>
@@ -16587,10 +16617,10 @@
         <v>1</v>
       </c>
       <c r="O300" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P300" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="301">
@@ -16616,10 +16646,10 @@
         <v>46101</v>
       </c>
       <c r="H301" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I301" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J301" s="1" t="s">
         <v>20</v>
@@ -16637,10 +16667,10 @@
         <v>2</v>
       </c>
       <c r="O301" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P301" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="302">
@@ -16666,10 +16696,10 @@
         <v>46101</v>
       </c>
       <c r="H302" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="I302" s="1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="J302" s="1" t="s">
         <v>20</v>
@@ -16716,10 +16746,10 @@
         <v>46100</v>
       </c>
       <c r="H303" s="1" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="I303" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="J303" s="1" t="s">
         <v>20</v>
@@ -16766,10 +16796,10 @@
         <v>46100</v>
       </c>
       <c r="H304" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="I304" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="J304" s="1" t="s">
         <v>20</v>
@@ -16816,16 +16846,16 @@
         <v>46100</v>
       </c>
       <c r="H305" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="I305" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="J305" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K305" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L305" s="4">
         <v>30</v>
@@ -16866,10 +16896,10 @@
         <v>46100</v>
       </c>
       <c r="H306" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I306" s="1" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J306" s="1" t="s">
         <v>20</v>
@@ -16916,10 +16946,10 @@
         <v>46100</v>
       </c>
       <c r="H307" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="I307" s="1" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="J307" s="1" t="s">
         <v>20</v>
@@ -16966,10 +16996,10 @@
         <v>46100</v>
       </c>
       <c r="H308" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I308" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J308" s="1" t="s">
         <v>20</v>
@@ -17016,10 +17046,10 @@
         <v>46100</v>
       </c>
       <c r="H309" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="I309" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="J309" s="1" t="s">
         <v>20</v>
@@ -17066,10 +17096,10 @@
         <v>46100</v>
       </c>
       <c r="H310" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>20</v>
@@ -17116,10 +17146,10 @@
         <v>46100</v>
       </c>
       <c r="H311" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="I311" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="J311" s="1" t="s">
         <v>20</v>
@@ -17266,10 +17296,10 @@
         <v>46100</v>
       </c>
       <c r="H314" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I314" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="J314" s="1" t="s">
         <v>20</v>
@@ -17316,16 +17346,16 @@
         <v>46101</v>
       </c>
       <c r="H315" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K315" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L315" s="4">
         <v>1</v>
@@ -17337,10 +17367,10 @@
         <v>189189.98</v>
       </c>
       <c r="O315" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P315" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="316">
@@ -17366,10 +17396,10 @@
         <v>46104</v>
       </c>
       <c r="H316" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="I316" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="J316" s="1" t="s">
         <v>20</v>
@@ -17387,10 +17417,10 @@
         <v>120000</v>
       </c>
       <c r="O316" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="P316" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="317">
@@ -17466,10 +17496,10 @@
         <v>46104</v>
       </c>
       <c r="H318" s="1" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="I318" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J318" s="1" t="s">
         <v>20</v>
@@ -17516,10 +17546,10 @@
         <v>46104</v>
       </c>
       <c r="H319" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I319" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J319" s="1" t="s">
         <v>20</v>
@@ -17566,10 +17596,10 @@
         <v>46104</v>
       </c>
       <c r="H320" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="I320" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="J320" s="1" t="s">
         <v>20</v>
@@ -17587,10 +17617,10 @@
         <v>1092</v>
       </c>
       <c r="O320" s="1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="P320" s="1" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="321">
@@ -17662,10 +17692,10 @@
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
       <c r="H322" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="I322" s="1" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="J322" s="1" t="s">
         <v>20</v>
@@ -17704,10 +17734,10 @@
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
       <c r="H323" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I323" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J323" s="1" t="s">
         <v>20</v>
@@ -17746,10 +17776,10 @@
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
       <c r="H324" s="1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="I324" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="J324" s="1" t="s">
         <v>20</v>
@@ -17788,10 +17818,10 @@
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
       <c r="H325" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="I325" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="J325" s="1" t="s">
         <v>20</v>
@@ -17830,10 +17860,10 @@
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
       <c r="H326" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="I326" s="1" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="J326" s="1" t="s">
         <v>20</v>
@@ -17872,10 +17902,10 @@
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
       <c r="H327" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="I327" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="J327" s="1" t="s">
         <v>20</v>
@@ -17914,10 +17944,10 @@
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
       <c r="H328" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="I328" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="J328" s="1" t="s">
         <v>20</v>
@@ -17956,10 +17986,10 @@
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
       <c r="H329" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="I329" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="J329" s="1" t="s">
         <v>20</v>
@@ -17998,10 +18028,10 @@
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
       <c r="H330" s="1" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="I330" s="1" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="J330" s="1" t="s">
         <v>20</v>
@@ -18082,10 +18112,10 @@
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
       <c r="H332" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I332" s="1" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="J332" s="1" t="s">
         <v>20</v>
@@ -18124,10 +18154,10 @@
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
       <c r="H333" s="1" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="I333" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="J333" s="1" t="s">
         <v>20</v>
@@ -18166,10 +18196,10 @@
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
       <c r="H334" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="I334" s="1" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="J334" s="1" t="s">
         <v>20</v>
@@ -18250,10 +18280,10 @@
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
       <c r="H336" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="I336" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J336" s="1" t="s">
         <v>20</v>
@@ -18292,10 +18322,10 @@
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
       <c r="H337" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="I337" s="1" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="J337" s="1" t="s">
         <v>20</v>
@@ -18334,10 +18364,10 @@
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
       <c r="H338" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="I338" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="J338" s="1" t="s">
         <v>20</v>
@@ -18376,10 +18406,10 @@
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
       <c r="H339" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="I339" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="J339" s="1" t="s">
         <v>20</v>
@@ -18404,7 +18434,7 @@
         <v>2407</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>75</v>
@@ -18454,7 +18484,7 @@
         <v>2407</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>75</v>
@@ -18504,7 +18534,7 @@
         <v>2407</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>75</v>
@@ -18522,10 +18552,10 @@
         <v>46104</v>
       </c>
       <c r="H342" s="1" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="I342" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="J342" s="1" t="s">
         <v>20</v>
@@ -18554,7 +18584,7 @@
         <v>2407</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>75</v>
@@ -18572,10 +18602,10 @@
         <v>46104</v>
       </c>
       <c r="H343" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I343" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J343" s="1" t="s">
         <v>20</v>
@@ -18604,7 +18634,7 @@
         <v>2407</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>75</v>
@@ -18654,7 +18684,7 @@
         <v>2407</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>75</v>
@@ -18704,7 +18734,7 @@
         <v>2407</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>75</v>
@@ -18754,7 +18784,7 @@
         <v>2407</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>75</v>
@@ -18804,7 +18834,7 @@
         <v>2407</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>75</v>
@@ -18822,10 +18852,10 @@
         <v>46104</v>
       </c>
       <c r="H348" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="I348" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="J348" s="1" t="s">
         <v>20</v>
@@ -18854,7 +18884,7 @@
         <v>2407</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>75</v>
@@ -18872,10 +18902,10 @@
         <v>46104</v>
       </c>
       <c r="H349" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="I349" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="J349" s="1" t="s">
         <v>20</v>
@@ -18904,7 +18934,7 @@
         <v>2407</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>75</v>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1895,18 +1895,18 @@
     <t>BROCA DE AÇO RÁPIDO - DIAM: 6 MM - COMP: 95 MM</t>
   </si>
   <si>
+    <t>O.01.0120</t>
+  </si>
+  <si>
+    <t>CHAPA PLASTIFICADO 20 MM - 2,20 X 1,10 M</t>
+  </si>
+  <si>
     <t>P1.02.0004</t>
   </si>
   <si>
     <t>DOBRADIÇA METAL 3 X 2 1/2"</t>
   </si>
   <si>
-    <t>O.01.0120</t>
-  </si>
-  <si>
-    <t>CHAPA PLASTIFICADO 20 MM - 2,20 X 1,10 M</t>
-  </si>
-  <si>
     <t>SUN MORITZ ADMINISTRADORA</t>
   </si>
   <si>
@@ -1944,6 +1944,12 @@
   </si>
   <si>
     <t>TINTA IMPERMEABILIZANTE ICOPER 10KG LAJES E TELHADOS</t>
+  </si>
+  <si>
+    <t>00000000000552</t>
+  </si>
+  <si>
+    <t>ISOCOM</t>
   </si>
   <si>
     <t>U.01.0400</t>
@@ -18261,10 +18267,10 @@
         <v>46104.452366169</v>
       </c>
       <c r="F330" s="2">
-        <v>82792</v>
+        <v>82810</v>
       </c>
       <c r="G330" s="3">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="H330" s="1" t="s">
         <v>627</v>
@@ -18279,19 +18285,19 @@
         <v>21</v>
       </c>
       <c r="L330" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M330" s="4">
-        <v>8.3</v>
+        <v>160</v>
       </c>
       <c r="N330" s="4">
-        <v>24.9</v>
+        <v>960</v>
       </c>
       <c r="O330" s="1" t="s">
-        <v>72</v>
+        <v>486</v>
       </c>
       <c r="P330" s="1" t="s">
-        <v>73</v>
+        <v>487</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="331">
@@ -18310,8 +18316,12 @@
       <c r="E331" s="3">
         <v>46104.452366169</v>
       </c>
-      <c r="F331" s="1"/>
-      <c r="G331" s="1"/>
+      <c r="F331" s="2">
+        <v>82792</v>
+      </c>
+      <c r="G331" s="3">
+        <v>46105</v>
+      </c>
       <c r="H331" s="1" t="s">
         <v>629</v>
       </c>
@@ -18325,16 +18335,20 @@
         <v>21</v>
       </c>
       <c r="L331" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M331" s="4">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="N331" s="4">
-        <v>0</v>
-      </c>
-      <c r="O331" s="1"/>
-      <c r="P331" s="1"/>
+        <v>24.9</v>
+      </c>
+      <c r="O331" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P331" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="332">
       <c r="A332" s="2">
@@ -19202,8 +19216,12 @@
       <c r="E349" s="3">
         <v>46105.7312393519</v>
       </c>
-      <c r="F349" s="1"/>
-      <c r="G349" s="1"/>
+      <c r="F349" s="2">
+        <v>82812</v>
+      </c>
+      <c r="G349" s="3">
+        <v>46106</v>
+      </c>
       <c r="H349" s="1" t="s">
         <v>642</v>
       </c>
@@ -19220,13 +19238,17 @@
         <v>1</v>
       </c>
       <c r="M349" s="4">
-        <v>0</v>
+        <v>1464.7</v>
       </c>
       <c r="N349" s="4">
-        <v>0</v>
-      </c>
-      <c r="O349" s="1"/>
-      <c r="P349" s="1"/>
+        <v>1464.7</v>
+      </c>
+      <c r="O349" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="P349" s="1" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="350">
       <c r="A350" s="2">
@@ -19247,10 +19269,10 @@
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
       <c r="H350" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="I350" s="1" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J350" s="1" t="s">
         <v>20</v>
@@ -19289,10 +19311,10 @@
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
       <c r="H351" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="I351" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="J351" s="1" t="s">
         <v>20</v>
@@ -19331,10 +19353,10 @@
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
       <c r="H352" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="I352" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="J352" s="1" t="s">
         <v>20</v>
@@ -19373,10 +19395,10 @@
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
       <c r="H353" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="I353" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="J353" s="1" t="s">
         <v>20</v>
@@ -19415,10 +19437,10 @@
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
       <c r="H354" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="I354" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="J354" s="1" t="s">
         <v>20</v>
@@ -19499,10 +19521,10 @@
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
       <c r="H356" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="I356" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="J356" s="1" t="s">
         <v>20</v>
@@ -19541,10 +19563,10 @@
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
       <c r="H357" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="I357" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="J357" s="1" t="s">
         <v>20</v>
@@ -19583,10 +19605,10 @@
       <c r="F358" s="1"/>
       <c r="G358" s="1"/>
       <c r="H358" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="I358" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="J358" s="1" t="s">
         <v>20</v>
@@ -19667,10 +19689,10 @@
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
       <c r="H360" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I360" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="J360" s="1" t="s">
         <v>20</v>
@@ -19751,10 +19773,10 @@
       <c r="F362" s="1"/>
       <c r="G362" s="1"/>
       <c r="H362" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="I362" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="J362" s="1" t="s">
         <v>20</v>
@@ -19835,10 +19857,10 @@
       <c r="F364" s="1"/>
       <c r="G364" s="1"/>
       <c r="H364" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="I364" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="J364" s="1" t="s">
         <v>20</v>
@@ -19961,10 +19983,10 @@
       <c r="F367" s="1"/>
       <c r="G367" s="1"/>
       <c r="H367" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="I367" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="J367" s="1" t="s">
         <v>20</v>
@@ -20003,10 +20025,10 @@
       <c r="F368" s="1"/>
       <c r="G368" s="1"/>
       <c r="H368" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="I368" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="J368" s="1" t="s">
         <v>20</v>
@@ -20045,10 +20067,10 @@
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
       <c r="H369" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="I369" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="J369" s="1" t="s">
         <v>20</v>
@@ -20087,10 +20109,10 @@
       <c r="F370" s="1"/>
       <c r="G370" s="1"/>
       <c r="H370" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="I370" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="J370" s="1" t="s">
         <v>20</v>
@@ -20129,10 +20151,10 @@
       <c r="F371" s="1"/>
       <c r="G371" s="1"/>
       <c r="H371" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I371" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J371" s="1" t="s">
         <v>20</v>
@@ -20171,10 +20193,10 @@
       <c r="F372" s="1"/>
       <c r="G372" s="1"/>
       <c r="H372" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="I372" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="J372" s="1" t="s">
         <v>20</v>
@@ -20213,10 +20235,10 @@
       <c r="F373" s="1"/>
       <c r="G373" s="1"/>
       <c r="H373" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="I373" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="J373" s="1" t="s">
         <v>20</v>
@@ -20255,10 +20277,10 @@
       <c r="F374" s="1"/>
       <c r="G374" s="1"/>
       <c r="H374" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="I374" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="J374" s="1" t="s">
         <v>20</v>
@@ -20297,10 +20319,10 @@
       <c r="F375" s="1"/>
       <c r="G375" s="1"/>
       <c r="H375" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="I375" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="J375" s="1" t="s">
         <v>20</v>
@@ -20339,10 +20361,10 @@
       <c r="F376" s="1"/>
       <c r="G376" s="1"/>
       <c r="H376" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I376" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J376" s="1" t="s">
         <v>20</v>
@@ -20381,10 +20403,10 @@
       <c r="F377" s="1"/>
       <c r="G377" s="1"/>
       <c r="H377" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="I377" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="J377" s="1" t="s">
         <v>20</v>
@@ -20423,10 +20445,10 @@
       <c r="F378" s="1"/>
       <c r="G378" s="1"/>
       <c r="H378" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="I378" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="J378" s="1" t="s">
         <v>20</v>
@@ -20465,10 +20487,10 @@
       <c r="F379" s="1"/>
       <c r="G379" s="1"/>
       <c r="H379" s="1" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="I379" s="1" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="J379" s="1" t="s">
         <v>20</v>
@@ -20507,10 +20529,10 @@
       <c r="F380" s="1"/>
       <c r="G380" s="1"/>
       <c r="H380" s="1" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="I380" s="1" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="J380" s="1" t="s">
         <v>20</v>
@@ -20549,10 +20571,10 @@
       <c r="F381" s="1"/>
       <c r="G381" s="1"/>
       <c r="H381" s="1" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I381" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="J381" s="1" t="s">
         <v>20</v>
@@ -20633,10 +20655,10 @@
       <c r="F383" s="1"/>
       <c r="G383" s="1"/>
       <c r="H383" s="1" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I383" s="1" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="J383" s="1" t="s">
         <v>20</v>
@@ -20675,10 +20697,10 @@
       <c r="F384" s="1"/>
       <c r="G384" s="1"/>
       <c r="H384" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="I384" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="J384" s="1" t="s">
         <v>20</v>
@@ -20813,10 +20835,10 @@
         <v>46106</v>
       </c>
       <c r="H387" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I387" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J387" s="1" t="s">
         <v>20</v>
@@ -20863,10 +20885,10 @@
         <v>46106</v>
       </c>
       <c r="H388" s="1" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I388" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J388" s="1" t="s">
         <v>20</v>
@@ -20913,10 +20935,10 @@
         <v>46106</v>
       </c>
       <c r="H389" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I389" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="J389" s="1" t="s">
         <v>20</v>
@@ -21013,10 +21035,10 @@
         <v>46105</v>
       </c>
       <c r="H391" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="I391" s="1" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="J391" s="1" t="s">
         <v>20</v>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="741">
   <si>
     <t>EMPRD</t>
   </si>
@@ -2136,6 +2136,105 @@
   </si>
   <si>
     <t>CANTONEIRA DE ALUMINIO</t>
+  </si>
+  <si>
+    <t>U.02.0586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TANQUE MEKAL  CT 40</t>
+  </si>
+  <si>
+    <t>U.02.2806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACABAMENTO PARA CAIXA DE DESCARGA EMBUTIDA  MECÂNICA H SLIM DUO COD 4900 C.HSL</t>
+  </si>
+  <si>
+    <t>E.03.0001</t>
+  </si>
+  <si>
+    <t>LUVA DE MALHA PIGMENTADA</t>
+  </si>
+  <si>
+    <t>E.03.0151</t>
+  </si>
+  <si>
+    <t>BOTA DE SEGURANÇA EM COURO COM SOLADO EM PU VULCAFLEX</t>
+  </si>
+  <si>
+    <t>E.03.0045</t>
+  </si>
+  <si>
+    <t>LUVA DE LÁTEX NATURAL CORRUGADA SS 1009</t>
+  </si>
+  <si>
+    <t>E.03.0340</t>
+  </si>
+  <si>
+    <t>JUGULAR SINTÉTICA</t>
+  </si>
+  <si>
+    <t>E.03.0153</t>
+  </si>
+  <si>
+    <t>BOTA DE PVC - CANO LONGO</t>
+  </si>
+  <si>
+    <t>E.03.0104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MASCARA DESCARTAVEL  SEM VALVULA</t>
+  </si>
+  <si>
+    <t>E.03.0257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACETE MSA  MODELO  V-GARD  COM CANEIRA CATRACA CINZA</t>
+  </si>
+  <si>
+    <t>E.03.0289</t>
+  </si>
+  <si>
+    <t>CARNEIRA PARA CAPACETE MSA</t>
+  </si>
+  <si>
+    <t>E.04.1242</t>
+  </si>
+  <si>
+    <t>MAÇARICO PORTÁTIL PROFISSIONAL COM GÁS (REFIL)</t>
+  </si>
+  <si>
+    <t>E.04.1243</t>
+  </si>
+  <si>
+    <t>REFIL DE GÁS PARA MAÇARICO PORTÁTIL</t>
+  </si>
+  <si>
+    <t>E.04.1804</t>
+  </si>
+  <si>
+    <t>PONTEIRO 20 X 250MM SDS PLUS</t>
+  </si>
+  <si>
+    <t>E.04.1854</t>
+  </si>
+  <si>
+    <t>TALHADEIRA 20 X 250MM SDS PLUS</t>
+  </si>
+  <si>
+    <t>J.03.0003</t>
+  </si>
+  <si>
+    <t>AREIA GROSSA</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>S.08.0200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIAPLUS 1000/TOP IMPER. BI-COMPONENTE(A+B)  - EMB. 18KG</t>
   </si>
 </sst>
 </file>
@@ -2434,7 +2533,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P392"/>
+  <dimension ref="A1:P420"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="7.71428571428571" customWidth="1" style="1"/>
@@ -21078,8 +21177,12 @@
       <c r="E392" s="3">
         <v>46106.4928109606</v>
       </c>
-      <c r="F392" s="1"/>
-      <c r="G392" s="1"/>
+      <c r="F392" s="2">
+        <v>82814</v>
+      </c>
+      <c r="G392" s="3">
+        <v>46106</v>
+      </c>
       <c r="H392" s="1" t="s">
         <v>125</v>
       </c>
@@ -21096,13 +21199,1265 @@
         <v>18</v>
       </c>
       <c r="M392" s="4">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N392" s="4">
-        <v>0</v>
-      </c>
-      <c r="O392" s="1"/>
-      <c r="P392" s="1"/>
+        <v>104.4</v>
+      </c>
+      <c r="O392" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P392" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="393">
+      <c r="A393" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B393" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D393" s="2">
+        <v>22</v>
+      </c>
+      <c r="E393" s="3">
+        <v>46106.7264048495</v>
+      </c>
+      <c r="F393" s="1"/>
+      <c r="G393" s="1"/>
+      <c r="H393" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I393" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J393" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K393" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L393" s="4">
+        <v>5</v>
+      </c>
+      <c r="M393" s="4">
+        <v>0</v>
+      </c>
+      <c r="N393" s="4">
+        <v>0</v>
+      </c>
+      <c r="O393" s="1"/>
+      <c r="P393" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="394">
+      <c r="A394" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D394" s="2">
+        <v>22</v>
+      </c>
+      <c r="E394" s="3">
+        <v>46106.7264048495</v>
+      </c>
+      <c r="F394" s="1"/>
+      <c r="G394" s="1"/>
+      <c r="H394" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I394" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J394" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K394" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L394" s="4">
+        <v>2</v>
+      </c>
+      <c r="M394" s="4">
+        <v>0</v>
+      </c>
+      <c r="N394" s="4">
+        <v>0</v>
+      </c>
+      <c r="O394" s="1"/>
+      <c r="P394" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="395">
+      <c r="A395" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D395" s="2">
+        <v>22</v>
+      </c>
+      <c r="E395" s="3">
+        <v>46106.7264048495</v>
+      </c>
+      <c r="F395" s="1"/>
+      <c r="G395" s="1"/>
+      <c r="H395" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="I395" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="J395" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K395" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L395" s="4">
+        <v>2</v>
+      </c>
+      <c r="M395" s="4">
+        <v>0</v>
+      </c>
+      <c r="N395" s="4">
+        <v>0</v>
+      </c>
+      <c r="O395" s="1"/>
+      <c r="P395" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="396">
+      <c r="A396" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D396" s="2">
+        <v>22</v>
+      </c>
+      <c r="E396" s="3">
+        <v>46106.7264048495</v>
+      </c>
+      <c r="F396" s="1"/>
+      <c r="G396" s="1"/>
+      <c r="H396" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="I396" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="J396" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K396" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L396" s="4">
+        <v>4</v>
+      </c>
+      <c r="M396" s="4">
+        <v>0</v>
+      </c>
+      <c r="N396" s="4">
+        <v>0</v>
+      </c>
+      <c r="O396" s="1"/>
+      <c r="P396" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="397">
+      <c r="A397" s="2">
+        <v>2516</v>
+      </c>
+      <c r="B397" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D397" s="2">
+        <v>22</v>
+      </c>
+      <c r="E397" s="3">
+        <v>46106.7264048495</v>
+      </c>
+      <c r="F397" s="1"/>
+      <c r="G397" s="1"/>
+      <c r="H397" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="I397" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="J397" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K397" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L397" s="4">
+        <v>3</v>
+      </c>
+      <c r="M397" s="4">
+        <v>0</v>
+      </c>
+      <c r="N397" s="4">
+        <v>0</v>
+      </c>
+      <c r="O397" s="1"/>
+      <c r="P397" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="398">
+      <c r="A398" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D398" s="2">
+        <v>33</v>
+      </c>
+      <c r="E398" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F398" s="2">
+        <v>82819</v>
+      </c>
+      <c r="G398" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H398" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I398" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J398" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K398" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L398" s="4">
+        <v>1</v>
+      </c>
+      <c r="M398" s="4">
+        <v>189</v>
+      </c>
+      <c r="N398" s="4">
+        <v>189</v>
+      </c>
+      <c r="O398" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="P398" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="399">
+      <c r="A399" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B399" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D399" s="2">
+        <v>33</v>
+      </c>
+      <c r="E399" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F399" s="2">
+        <v>82819</v>
+      </c>
+      <c r="G399" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H399" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I399" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J399" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K399" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L399" s="4">
+        <v>1</v>
+      </c>
+      <c r="M399" s="4">
+        <v>189</v>
+      </c>
+      <c r="N399" s="4">
+        <v>189</v>
+      </c>
+      <c r="O399" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="P399" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="400">
+      <c r="A400" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B400" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D400" s="2">
+        <v>33</v>
+      </c>
+      <c r="E400" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F400" s="2">
+        <v>82819</v>
+      </c>
+      <c r="G400" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H400" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I400" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J400" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K400" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L400" s="4">
+        <v>1</v>
+      </c>
+      <c r="M400" s="4">
+        <v>189</v>
+      </c>
+      <c r="N400" s="4">
+        <v>189</v>
+      </c>
+      <c r="O400" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="P400" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="401">
+      <c r="A401" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B401" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D401" s="2">
+        <v>33</v>
+      </c>
+      <c r="E401" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F401" s="2">
+        <v>82819</v>
+      </c>
+      <c r="G401" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H401" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="I401" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="J401" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K401" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L401" s="4">
+        <v>50</v>
+      </c>
+      <c r="M401" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="N401" s="4">
+        <v>195</v>
+      </c>
+      <c r="O401" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="P401" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="402">
+      <c r="A402" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B402" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D402" s="2">
+        <v>33</v>
+      </c>
+      <c r="E402" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F402" s="2">
+        <v>82820</v>
+      </c>
+      <c r="G402" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H402" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="I402" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="J402" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K402" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L402" s="4">
+        <v>2</v>
+      </c>
+      <c r="M402" s="4">
+        <v>75</v>
+      </c>
+      <c r="N402" s="4">
+        <v>150</v>
+      </c>
+      <c r="O402" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P402" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="403">
+      <c r="A403" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B403" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D403" s="2">
+        <v>33</v>
+      </c>
+      <c r="E403" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F403" s="2">
+        <v>82819</v>
+      </c>
+      <c r="G403" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H403" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="I403" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="J403" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K403" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L403" s="4">
+        <v>30</v>
+      </c>
+      <c r="M403" s="4">
+        <v>13.9</v>
+      </c>
+      <c r="N403" s="4">
+        <v>417</v>
+      </c>
+      <c r="O403" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="P403" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="404">
+      <c r="A404" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B404" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D404" s="2">
+        <v>33</v>
+      </c>
+      <c r="E404" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F404" s="2">
+        <v>82820</v>
+      </c>
+      <c r="G404" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H404" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I404" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J404" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K404" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L404" s="4">
+        <v>20</v>
+      </c>
+      <c r="M404" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="N404" s="4">
+        <v>90</v>
+      </c>
+      <c r="O404" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P404" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="405">
+      <c r="A405" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B405" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D405" s="2">
+        <v>33</v>
+      </c>
+      <c r="E405" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F405" s="2">
+        <v>82821</v>
+      </c>
+      <c r="G405" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H405" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="I405" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J405" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K405" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L405" s="4">
+        <v>6</v>
+      </c>
+      <c r="M405" s="4">
+        <v>5.9</v>
+      </c>
+      <c r="N405" s="4">
+        <v>35.4</v>
+      </c>
+      <c r="O405" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P405" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="406">
+      <c r="A406" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B406" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D406" s="2">
+        <v>33</v>
+      </c>
+      <c r="E406" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F406" s="2">
+        <v>82821</v>
+      </c>
+      <c r="G406" s="3">
+        <v>46106</v>
+      </c>
+      <c r="H406" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="I406" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J406" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K406" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L406" s="4">
+        <v>10</v>
+      </c>
+      <c r="M406" s="4">
+        <v>17.3</v>
+      </c>
+      <c r="N406" s="4">
+        <v>173</v>
+      </c>
+      <c r="O406" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P406" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row ht="12.75" customHeight="1" r="407">
+      <c r="A407" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B407" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D407" s="2">
+        <v>33</v>
+      </c>
+      <c r="E407" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F407" s="1"/>
+      <c r="G407" s="1"/>
+      <c r="H407" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I407" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="J407" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K407" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L407" s="4">
+        <v>10</v>
+      </c>
+      <c r="M407" s="4">
+        <v>0</v>
+      </c>
+      <c r="N407" s="4">
+        <v>0</v>
+      </c>
+      <c r="O407" s="1"/>
+      <c r="P407" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="408">
+      <c r="A408" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D408" s="2">
+        <v>33</v>
+      </c>
+      <c r="E408" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F408" s="1"/>
+      <c r="G408" s="1"/>
+      <c r="H408" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="I408" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="J408" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K408" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L408" s="4">
+        <v>1</v>
+      </c>
+      <c r="M408" s="4">
+        <v>0</v>
+      </c>
+      <c r="N408" s="4">
+        <v>0</v>
+      </c>
+      <c r="O408" s="1"/>
+      <c r="P408" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="409">
+      <c r="A409" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B409" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D409" s="2">
+        <v>33</v>
+      </c>
+      <c r="E409" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F409" s="1"/>
+      <c r="G409" s="1"/>
+      <c r="H409" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="I409" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="J409" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K409" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L409" s="4">
+        <v>1</v>
+      </c>
+      <c r="M409" s="4">
+        <v>0</v>
+      </c>
+      <c r="N409" s="4">
+        <v>0</v>
+      </c>
+      <c r="O409" s="1"/>
+      <c r="P409" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="410">
+      <c r="A410" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B410" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D410" s="2">
+        <v>33</v>
+      </c>
+      <c r="E410" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F410" s="1"/>
+      <c r="G410" s="1"/>
+      <c r="H410" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="I410" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="J410" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K410" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L410" s="4">
+        <v>2</v>
+      </c>
+      <c r="M410" s="4">
+        <v>0</v>
+      </c>
+      <c r="N410" s="4">
+        <v>0</v>
+      </c>
+      <c r="O410" s="1"/>
+      <c r="P410" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="411">
+      <c r="A411" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D411" s="2">
+        <v>33</v>
+      </c>
+      <c r="E411" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F411" s="1"/>
+      <c r="G411" s="1"/>
+      <c r="H411" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="I411" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="J411" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K411" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L411" s="4">
+        <v>50</v>
+      </c>
+      <c r="M411" s="4">
+        <v>0</v>
+      </c>
+      <c r="N411" s="4">
+        <v>0</v>
+      </c>
+      <c r="O411" s="1"/>
+      <c r="P411" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="412">
+      <c r="A412" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D412" s="2">
+        <v>33</v>
+      </c>
+      <c r="E412" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F412" s="1"/>
+      <c r="G412" s="1"/>
+      <c r="H412" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="I412" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="J412" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K412" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L412" s="4">
+        <v>6</v>
+      </c>
+      <c r="M412" s="4">
+        <v>0</v>
+      </c>
+      <c r="N412" s="4">
+        <v>0</v>
+      </c>
+      <c r="O412" s="1"/>
+      <c r="P412" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="413">
+      <c r="A413" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B413" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D413" s="2">
+        <v>33</v>
+      </c>
+      <c r="E413" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F413" s="1"/>
+      <c r="G413" s="1"/>
+      <c r="H413" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="I413" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="J413" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K413" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L413" s="4">
+        <v>10</v>
+      </c>
+      <c r="M413" s="4">
+        <v>0</v>
+      </c>
+      <c r="N413" s="4">
+        <v>0</v>
+      </c>
+      <c r="O413" s="1"/>
+      <c r="P413" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="414">
+      <c r="A414" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B414" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D414" s="2">
+        <v>33</v>
+      </c>
+      <c r="E414" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F414" s="1"/>
+      <c r="G414" s="1"/>
+      <c r="H414" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="I414" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="J414" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K414" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L414" s="4">
+        <v>10</v>
+      </c>
+      <c r="M414" s="4">
+        <v>0</v>
+      </c>
+      <c r="N414" s="4">
+        <v>0</v>
+      </c>
+      <c r="O414" s="1"/>
+      <c r="P414" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="415">
+      <c r="A415" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D415" s="2">
+        <v>33</v>
+      </c>
+      <c r="E415" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F415" s="1"/>
+      <c r="G415" s="1"/>
+      <c r="H415" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="I415" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="J415" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K415" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L415" s="4">
+        <v>1</v>
+      </c>
+      <c r="M415" s="4">
+        <v>0</v>
+      </c>
+      <c r="N415" s="4">
+        <v>0</v>
+      </c>
+      <c r="O415" s="1"/>
+      <c r="P415" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="416">
+      <c r="A416" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B416" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D416" s="2">
+        <v>33</v>
+      </c>
+      <c r="E416" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F416" s="1"/>
+      <c r="G416" s="1"/>
+      <c r="H416" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="I416" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="J416" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K416" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L416" s="4">
+        <v>2</v>
+      </c>
+      <c r="M416" s="4">
+        <v>0</v>
+      </c>
+      <c r="N416" s="4">
+        <v>0</v>
+      </c>
+      <c r="O416" s="1"/>
+      <c r="P416" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="417">
+      <c r="A417" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B417" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D417" s="2">
+        <v>33</v>
+      </c>
+      <c r="E417" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F417" s="1"/>
+      <c r="G417" s="1"/>
+      <c r="H417" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="I417" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="J417" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K417" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L417" s="4">
+        <v>6</v>
+      </c>
+      <c r="M417" s="4">
+        <v>0</v>
+      </c>
+      <c r="N417" s="4">
+        <v>0</v>
+      </c>
+      <c r="O417" s="1"/>
+      <c r="P417" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="418">
+      <c r="A418" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D418" s="2">
+        <v>33</v>
+      </c>
+      <c r="E418" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F418" s="1"/>
+      <c r="G418" s="1"/>
+      <c r="H418" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I418" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="J418" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K418" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L418" s="4">
+        <v>6</v>
+      </c>
+      <c r="M418" s="4">
+        <v>0</v>
+      </c>
+      <c r="N418" s="4">
+        <v>0</v>
+      </c>
+      <c r="O418" s="1"/>
+      <c r="P418" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="419">
+      <c r="A419" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D419" s="2">
+        <v>33</v>
+      </c>
+      <c r="E419" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F419" s="1"/>
+      <c r="G419" s="1"/>
+      <c r="H419" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="I419" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="J419" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K419" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="L419" s="4">
+        <v>60</v>
+      </c>
+      <c r="M419" s="4">
+        <v>0</v>
+      </c>
+      <c r="N419" s="4">
+        <v>0</v>
+      </c>
+      <c r="O419" s="1"/>
+      <c r="P419" s="1"/>
+    </row>
+    <row ht="12.75" customHeight="1" r="420">
+      <c r="A420" s="2">
+        <v>2506</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D420" s="2">
+        <v>33</v>
+      </c>
+      <c r="E420" s="3">
+        <v>46106.7275206944</v>
+      </c>
+      <c r="F420" s="1"/>
+      <c r="G420" s="1"/>
+      <c r="H420" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="I420" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="J420" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K420" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L420" s="4">
+        <v>10</v>
+      </c>
+      <c r="M420" s="4">
+        <v>0</v>
+      </c>
+      <c r="N420" s="4">
+        <v>0</v>
+      </c>
+      <c r="O420" s="1"/>
+      <c r="P420" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -1547,6 +1547,12 @@
     <t>PÁ PARA LIXO PEQUENA</t>
   </si>
   <si>
+    <t>C.04.0047</t>
+  </si>
+  <si>
+    <t>VASSOURA DE PÊLO ANIMAL 60 CM</t>
+  </si>
+  <si>
     <t>E.04.0716</t>
   </si>
   <si>
@@ -1569,12 +1575,6 @@
   </si>
   <si>
     <t>PREGO DE AÇO COM CABEÇA 17 X 21</t>
-  </si>
-  <si>
-    <t>C.04.0047</t>
-  </si>
-  <si>
-    <t>VASSOURA DE PÊLO ANIMAL 60 CM</t>
   </si>
   <si>
     <t>E.02.0001</t>
@@ -14002,10 +14002,10 @@
         <v>46108</v>
       </c>
       <c r="H248" s="1" t="s">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>31</v>
+        <v>366</v>
       </c>
       <c r="J248" s="1" t="s">
         <v>20</v>
@@ -14014,13 +14014,13 @@
         <v>21</v>
       </c>
       <c r="L248" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M248" s="4">
-        <v>68</v>
+        <v>3.5</v>
       </c>
       <c r="N248" s="4">
-        <v>272</v>
+        <v>70</v>
       </c>
       <c r="O248" s="1" t="s">
         <v>324</v>
@@ -14052,10 +14052,10 @@
         <v>46108</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>509</v>
+        <v>30</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>510</v>
+        <v>31</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>20</v>
@@ -14064,13 +14064,13 @@
         <v>21</v>
       </c>
       <c r="L249" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M249" s="4">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="N249" s="4">
-        <v>60</v>
+        <v>276</v>
       </c>
       <c r="O249" s="1" t="s">
         <v>324</v>
@@ -14096,16 +14096,16 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F250" s="2">
-        <v>82845</v>
+        <v>82843</v>
       </c>
       <c r="G250" s="3">
         <v>46108</v>
       </c>
       <c r="H250" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="J250" s="1" t="s">
         <v>20</v>
@@ -14114,19 +14114,19 @@
         <v>21</v>
       </c>
       <c r="L250" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M250" s="4">
-        <v>37.05</v>
+        <v>10</v>
       </c>
       <c r="N250" s="4">
-        <v>148.2</v>
+        <v>60</v>
       </c>
       <c r="O250" s="1" t="s">
-        <v>60</v>
+        <v>324</v>
       </c>
       <c r="P250" s="1" t="s">
-        <v>61</v>
+        <v>325</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="251">
@@ -14146,37 +14146,37 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F251" s="2">
-        <v>82845</v>
+        <v>82843</v>
       </c>
       <c r="G251" s="3">
         <v>46108</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>57</v>
+        <v>511</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>58</v>
+        <v>512</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K251" s="1" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="L251" s="4">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="M251" s="4">
-        <v>34.5</v>
+        <v>69.9</v>
       </c>
       <c r="N251" s="4">
-        <v>1035</v>
+        <v>209.7</v>
       </c>
       <c r="O251" s="1" t="s">
-        <v>60</v>
+        <v>324</v>
       </c>
       <c r="P251" s="1" t="s">
-        <v>61</v>
+        <v>325</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="252">
@@ -14196,37 +14196,37 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F252" s="2">
-        <v>82844</v>
+        <v>82843</v>
       </c>
       <c r="G252" s="3">
         <v>46108</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>513</v>
+        <v>147</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>514</v>
+        <v>148</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="L252" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M252" s="4">
-        <v>13.51</v>
+        <v>16.9</v>
       </c>
       <c r="N252" s="4">
-        <v>27.02</v>
+        <v>67.6</v>
       </c>
       <c r="O252" s="1" t="s">
-        <v>515</v>
+        <v>324</v>
       </c>
       <c r="P252" s="1" t="s">
-        <v>516</v>
+        <v>325</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="253">
@@ -14246,16 +14246,16 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F253" s="2">
-        <v>82844</v>
+        <v>82845</v>
       </c>
       <c r="G253" s="3">
         <v>46108</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>377</v>
+        <v>513</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>378</v>
+        <v>514</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>20</v>
@@ -14264,19 +14264,19 @@
         <v>21</v>
       </c>
       <c r="L253" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M253" s="4">
-        <v>10.31</v>
+        <v>37.05</v>
       </c>
       <c r="N253" s="4">
-        <v>61.86</v>
+        <v>148.2</v>
       </c>
       <c r="O253" s="1" t="s">
-        <v>515</v>
+        <v>60</v>
       </c>
       <c r="P253" s="1" t="s">
-        <v>516</v>
+        <v>61</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="254">
@@ -14296,37 +14296,37 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F254" s="2">
-        <v>82844</v>
+        <v>82845</v>
       </c>
       <c r="G254" s="3">
         <v>46108</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>517</v>
+        <v>57</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>518</v>
+        <v>58</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K254" s="1" t="s">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="L254" s="4">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="M254" s="4">
-        <v>49.16</v>
+        <v>34.5</v>
       </c>
       <c r="N254" s="4">
-        <v>49.16</v>
+        <v>1035</v>
       </c>
       <c r="O254" s="1" t="s">
-        <v>515</v>
+        <v>60</v>
       </c>
       <c r="P254" s="1" t="s">
-        <v>516</v>
+        <v>61</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="255">
@@ -14345,31 +14345,39 @@
       <c r="E255" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F255" s="1"/>
-      <c r="G255" s="1"/>
+      <c r="F255" s="2">
+        <v>82844</v>
+      </c>
+      <c r="G255" s="3">
+        <v>46108</v>
+      </c>
       <c r="H255" s="1" t="s">
-        <v>365</v>
+        <v>515</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>366</v>
+        <v>516</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K255" s="1" t="s">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="L255" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="M255" s="4">
-        <v>0</v>
+        <v>13.51</v>
       </c>
       <c r="N255" s="4">
-        <v>0</v>
-      </c>
-      <c r="O255" s="1"/>
-      <c r="P255" s="1"/>
+        <v>27.02</v>
+      </c>
+      <c r="O255" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="P255" s="1" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="256">
       <c r="A256" s="2">
@@ -14387,13 +14395,17 @@
       <c r="E256" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F256" s="1"/>
-      <c r="G256" s="1"/>
+      <c r="F256" s="2">
+        <v>82844</v>
+      </c>
+      <c r="G256" s="3">
+        <v>46108</v>
+      </c>
       <c r="H256" s="1" t="s">
-        <v>519</v>
+        <v>377</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>520</v>
+        <v>378</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>20</v>
@@ -14402,16 +14414,20 @@
         <v>21</v>
       </c>
       <c r="L256" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M256" s="4">
-        <v>0</v>
+        <v>10.31</v>
       </c>
       <c r="N256" s="4">
-        <v>0</v>
-      </c>
-      <c r="O256" s="1"/>
-      <c r="P256" s="1"/>
+        <v>61.86</v>
+      </c>
+      <c r="O256" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="P256" s="1" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="257">
       <c r="A257" s="2">
@@ -14429,31 +14445,39 @@
       <c r="E257" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F257" s="1"/>
-      <c r="G257" s="1"/>
+      <c r="F257" s="2">
+        <v>82844</v>
+      </c>
+      <c r="G257" s="3">
+        <v>46108</v>
+      </c>
       <c r="H257" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J257" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="L257" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="M257" s="4">
-        <v>0</v>
+        <v>49.16</v>
       </c>
       <c r="N257" s="4">
-        <v>0</v>
-      </c>
-      <c r="O257" s="1"/>
-      <c r="P257" s="1"/>
+        <v>49.16</v>
+      </c>
+      <c r="O257" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="P257" s="1" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="258">
       <c r="A258" s="2">
@@ -14474,19 +14498,19 @@
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
       <c r="H258" s="1" t="s">
-        <v>147</v>
+        <v>521</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>148</v>
+        <v>522</v>
       </c>
       <c r="J258" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="L258" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="M258" s="4">
         <v>0</v>

--- a/AcompReq.xlsx
+++ b/AcompReq.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="553">
   <si>
     <t>EMPRD</t>
   </si>
@@ -1553,22 +1553,73 @@
     <t>VASSOURA DE PÊLO ANIMAL 60 CM</t>
   </si>
   <si>
+    <t>E.02.0001</t>
+  </si>
+  <si>
+    <t>CORDA DE 100% POLIAMIDA DE SEGURANÇA COM MARCA D'ÁGUA 1/2''</t>
+  </si>
+  <si>
+    <t>E.04.0281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPÁTULA DE AÇO LISA  - 6 CM</t>
+  </si>
+  <si>
+    <t>E.04.0614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNEU  PARA CARRINHO DE MÃO</t>
+  </si>
+  <si>
+    <t>E.04.0284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPÁTULA DE AÇO LISA  - 12 CM</t>
+  </si>
+  <si>
     <t>E.04.0716</t>
   </si>
   <si>
     <t>DISCO DE CORTE DIAMANTADO PARA PORCELANATO CONTINUO 4 1/2''</t>
   </si>
   <si>
+    <t>E.04.0737</t>
+  </si>
+  <si>
+    <t>DISCO PARA CORTE DE FERRO DE 7''</t>
+  </si>
+  <si>
+    <t>E.04.1800</t>
+  </si>
+  <si>
+    <t>PONTEIRO 14 X 250MM SDS PLUS</t>
+  </si>
+  <si>
+    <t>E.04.1850</t>
+  </si>
+  <si>
+    <t>TALHADEIRA 14 X 250MM SDS PLUS</t>
+  </si>
+  <si>
+    <t>R.02.0022</t>
+  </si>
+  <si>
+    <t>TINTA ACRILICA LATA DE 18L</t>
+  </si>
+  <si>
+    <t>LAT</t>
+  </si>
+  <si>
     <t>R.02.0152</t>
   </si>
   <si>
     <t>THINNER - REDUTOR LITRO</t>
   </si>
   <si>
-    <t>00000000006858</t>
-  </si>
-  <si>
-    <t>WADY</t>
+    <t>R.02.0187</t>
+  </si>
+  <si>
+    <t>TRINCHA 1/2"</t>
   </si>
   <si>
     <t>W.01.0044</t>
@@ -1577,67 +1628,10 @@
     <t>PREGO DE AÇO COM CABEÇA 17 X 21</t>
   </si>
   <si>
-    <t>E.02.0001</t>
-  </si>
-  <si>
-    <t>CORDA DE 100% POLIAMIDA DE SEGURANÇA COM MARCA D'ÁGUA 1/2''</t>
-  </si>
-  <si>
-    <t>E.04.0281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPÁTULA DE AÇO LISA  - 6 CM</t>
-  </si>
-  <si>
-    <t>E.04.0614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNEU  PARA CARRINHO DE MÃO</t>
-  </si>
-  <si>
-    <t>E.04.0284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESPÁTULA DE AÇO LISA  - 12 CM</t>
-  </si>
-  <si>
-    <t>E.04.0737</t>
-  </si>
-  <si>
-    <t>DISCO PARA CORTE DE FERRO DE 7''</t>
-  </si>
-  <si>
-    <t>E.04.1800</t>
-  </si>
-  <si>
-    <t>PONTEIRO 14 X 250MM SDS PLUS</t>
-  </si>
-  <si>
-    <t>E.04.1850</t>
-  </si>
-  <si>
-    <t>TALHADEIRA 14 X 250MM SDS PLUS</t>
-  </si>
-  <si>
     <t>F.04.0200</t>
   </si>
   <si>
     <t xml:space="preserve">MARTELETE ROMPEDOR 5KG COM  FERRAMENTAS ( PONTEIRO OU TALHADEIRA )</t>
-  </si>
-  <si>
-    <t>R.02.0022</t>
-  </si>
-  <si>
-    <t>TINTA ACRILICA LATA DE 18L</t>
-  </si>
-  <si>
-    <t>LAT</t>
-  </si>
-  <si>
-    <t>R.02.0187</t>
-  </si>
-  <si>
-    <t>TRINCHA 1/2"</t>
   </si>
   <si>
     <t>ROBERTO KLABIN MARTINS XAVIER</t>
@@ -14196,37 +14190,37 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F252" s="2">
-        <v>82843</v>
+        <v>82845</v>
       </c>
       <c r="G252" s="3">
         <v>46108</v>
       </c>
       <c r="H252" s="1" t="s">
-        <v>147</v>
+        <v>513</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>148</v>
+        <v>514</v>
       </c>
       <c r="J252" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="L252" s="4">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="M252" s="4">
-        <v>16.9</v>
+        <v>4.96</v>
       </c>
       <c r="N252" s="4">
-        <v>67.6</v>
+        <v>248</v>
       </c>
       <c r="O252" s="1" t="s">
-        <v>324</v>
+        <v>60</v>
       </c>
       <c r="P252" s="1" t="s">
-        <v>325</v>
+        <v>61</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="253">
@@ -14246,16 +14240,16 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F253" s="2">
-        <v>82845</v>
+        <v>82843</v>
       </c>
       <c r="G253" s="3">
         <v>46108</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>513</v>
+        <v>147</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>514</v>
+        <v>148</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>20</v>
@@ -14267,16 +14261,16 @@
         <v>4</v>
       </c>
       <c r="M253" s="4">
-        <v>37.05</v>
+        <v>16.9</v>
       </c>
       <c r="N253" s="4">
-        <v>148.2</v>
+        <v>67.6</v>
       </c>
       <c r="O253" s="1" t="s">
-        <v>60</v>
+        <v>324</v>
       </c>
       <c r="P253" s="1" t="s">
-        <v>61</v>
+        <v>325</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="254">
@@ -14302,25 +14296,25 @@
         <v>46108</v>
       </c>
       <c r="H254" s="1" t="s">
-        <v>57</v>
+        <v>515</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>58</v>
+        <v>516</v>
       </c>
       <c r="J254" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K254" s="1" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="L254" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M254" s="4">
-        <v>34.5</v>
+        <v>9.89</v>
       </c>
       <c r="N254" s="4">
-        <v>1035</v>
+        <v>49.45</v>
       </c>
       <c r="O254" s="1" t="s">
         <v>60</v>
@@ -14346,37 +14340,37 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F255" s="2">
-        <v>82844</v>
+        <v>82845</v>
       </c>
       <c r="G255" s="3">
         <v>46108</v>
       </c>
       <c r="H255" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="J255" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K255" s="1" t="s">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="L255" s="4">
         <v>2</v>
       </c>
       <c r="M255" s="4">
-        <v>13.51</v>
+        <v>39.63</v>
       </c>
       <c r="N255" s="4">
-        <v>27.02</v>
+        <v>79.26</v>
       </c>
       <c r="O255" s="1" t="s">
-        <v>517</v>
+        <v>60</v>
       </c>
       <c r="P255" s="1" t="s">
-        <v>518</v>
+        <v>61</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="256">
@@ -14396,16 +14390,16 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F256" s="2">
-        <v>82844</v>
+        <v>82845</v>
       </c>
       <c r="G256" s="3">
         <v>46108</v>
       </c>
       <c r="H256" s="1" t="s">
-        <v>377</v>
+        <v>519</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>378</v>
+        <v>520</v>
       </c>
       <c r="J256" s="1" t="s">
         <v>20</v>
@@ -14414,19 +14408,19 @@
         <v>21</v>
       </c>
       <c r="L256" s="4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M256" s="4">
-        <v>10.31</v>
+        <v>12.62</v>
       </c>
       <c r="N256" s="4">
-        <v>61.86</v>
+        <v>63.1</v>
       </c>
       <c r="O256" s="1" t="s">
-        <v>517</v>
+        <v>60</v>
       </c>
       <c r="P256" s="1" t="s">
-        <v>518</v>
+        <v>61</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="257">
@@ -14446,37 +14440,37 @@
         <v>46108.4131517361</v>
       </c>
       <c r="F257" s="2">
-        <v>82844</v>
+        <v>82845</v>
       </c>
       <c r="G257" s="3">
         <v>46108</v>
       </c>
       <c r="H257" s="1" t="s">
-        <v>519</v>
+        <v>117</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>520</v>
+        <v>118</v>
       </c>
       <c r="J257" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="L257" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M257" s="4">
-        <v>49.16</v>
+        <v>188.8</v>
       </c>
       <c r="N257" s="4">
-        <v>49.16</v>
+        <v>566.4</v>
       </c>
       <c r="O257" s="1" t="s">
-        <v>517</v>
+        <v>60</v>
       </c>
       <c r="P257" s="1" t="s">
-        <v>518</v>
+        <v>61</v>
       </c>
     </row>
     <row ht="12.75" customHeight="1" r="258">
@@ -14495,8 +14489,12 @@
       <c r="E258" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F258" s="1"/>
-      <c r="G258" s="1"/>
+      <c r="F258" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G258" s="3">
+        <v>46108</v>
+      </c>
       <c r="H258" s="1" t="s">
         <v>521</v>
       </c>
@@ -14507,19 +14505,23 @@
         <v>20</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="L258" s="4">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="M258" s="4">
-        <v>0</v>
+        <v>92.06</v>
       </c>
       <c r="N258" s="4">
-        <v>0</v>
-      </c>
-      <c r="O258" s="1"/>
-      <c r="P258" s="1"/>
+        <v>368.24</v>
+      </c>
+      <c r="O258" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P258" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="259">
       <c r="A259" s="2">
@@ -14537,8 +14539,12 @@
       <c r="E259" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F259" s="1"/>
-      <c r="G259" s="1"/>
+      <c r="F259" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G259" s="3">
+        <v>46108</v>
+      </c>
       <c r="H259" s="1" t="s">
         <v>523</v>
       </c>
@@ -14552,16 +14558,20 @@
         <v>21</v>
       </c>
       <c r="L259" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M259" s="4">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="N259" s="4">
-        <v>0</v>
-      </c>
-      <c r="O259" s="1"/>
-      <c r="P259" s="1"/>
+        <v>128.4</v>
+      </c>
+      <c r="O259" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P259" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="260">
       <c r="A260" s="2">
@@ -14579,8 +14589,12 @@
       <c r="E260" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F260" s="1"/>
-      <c r="G260" s="1"/>
+      <c r="F260" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G260" s="3">
+        <v>46108</v>
+      </c>
       <c r="H260" s="1" t="s">
         <v>525</v>
       </c>
@@ -14594,16 +14608,20 @@
         <v>21</v>
       </c>
       <c r="L260" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M260" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N260" s="4">
-        <v>0</v>
-      </c>
-      <c r="O260" s="1"/>
-      <c r="P260" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="O260" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P260" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="261">
       <c r="A261" s="2">
@@ -14621,8 +14639,12 @@
       <c r="E261" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F261" s="1"/>
-      <c r="G261" s="1"/>
+      <c r="F261" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G261" s="3">
+        <v>46108</v>
+      </c>
       <c r="H261" s="1" t="s">
         <v>527</v>
       </c>
@@ -14636,16 +14658,20 @@
         <v>21</v>
       </c>
       <c r="L261" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M261" s="4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N261" s="4">
-        <v>0</v>
-      </c>
-      <c r="O261" s="1"/>
-      <c r="P261" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="O261" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P261" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="262">
       <c r="A262" s="2">
@@ -14663,31 +14689,39 @@
       <c r="E262" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F262" s="1"/>
-      <c r="G262" s="1"/>
+      <c r="F262" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G262" s="3">
+        <v>46108</v>
+      </c>
       <c r="H262" s="1" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K262" s="1" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="L262" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="M262" s="4">
-        <v>0</v>
+        <v>32.82</v>
       </c>
       <c r="N262" s="4">
-        <v>0</v>
-      </c>
-      <c r="O262" s="1"/>
-      <c r="P262" s="1"/>
+        <v>984.6</v>
+      </c>
+      <c r="O262" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P262" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="263">
       <c r="A263" s="2">
@@ -14705,8 +14739,12 @@
       <c r="E263" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F263" s="1"/>
-      <c r="G263" s="1"/>
+      <c r="F263" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G263" s="3">
+        <v>46108</v>
+      </c>
       <c r="H263" s="1" t="s">
         <v>529</v>
       </c>
@@ -14717,19 +14755,23 @@
         <v>20</v>
       </c>
       <c r="K263" s="1" t="s">
-        <v>21</v>
+        <v>531</v>
       </c>
       <c r="L263" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M263" s="4">
-        <v>0</v>
+        <v>422.31</v>
       </c>
       <c r="N263" s="4">
-        <v>0</v>
-      </c>
-      <c r="O263" s="1"/>
-      <c r="P263" s="1"/>
+        <v>422.31</v>
+      </c>
+      <c r="O263" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P263" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="264">
       <c r="A264" s="2">
@@ -14747,31 +14789,39 @@
       <c r="E264" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F264" s="1"/>
-      <c r="G264" s="1"/>
+      <c r="F264" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G264" s="3">
+        <v>46108</v>
+      </c>
       <c r="H264" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K264" s="1" t="s">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="L264" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M264" s="4">
-        <v>0</v>
+        <v>24.37</v>
       </c>
       <c r="N264" s="4">
-        <v>0</v>
-      </c>
-      <c r="O264" s="1"/>
-      <c r="P264" s="1"/>
+        <v>48.74</v>
+      </c>
+      <c r="O264" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P264" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="265">
       <c r="A265" s="2">
@@ -14789,13 +14839,17 @@
       <c r="E265" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F265" s="1"/>
-      <c r="G265" s="1"/>
+      <c r="F265" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G265" s="3">
+        <v>46108</v>
+      </c>
       <c r="H265" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I265" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J265" s="1" t="s">
         <v>20</v>
@@ -14804,7 +14858,7 @@
         <v>21</v>
       </c>
       <c r="L265" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M265" s="4">
         <v>0</v>
@@ -14812,8 +14866,12 @@
       <c r="N265" s="4">
         <v>0</v>
       </c>
-      <c r="O265" s="1"/>
-      <c r="P265" s="1"/>
+      <c r="O265" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P265" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="266">
       <c r="A266" s="2">
@@ -14831,31 +14889,39 @@
       <c r="E266" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F266" s="1"/>
-      <c r="G266" s="1"/>
+      <c r="F266" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G266" s="3">
+        <v>46108</v>
+      </c>
       <c r="H266" s="1" t="s">
-        <v>535</v>
+        <v>377</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>536</v>
+        <v>378</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K266" s="1" t="s">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="L266" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M266" s="4">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="N266" s="4">
-        <v>0</v>
-      </c>
-      <c r="O266" s="1"/>
-      <c r="P266" s="1"/>
+        <v>106.8</v>
+      </c>
+      <c r="O266" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P266" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="267">
       <c r="A267" s="2">
@@ -14873,31 +14939,39 @@
       <c r="E267" s="3">
         <v>46108.4131517361</v>
       </c>
-      <c r="F267" s="1"/>
-      <c r="G267" s="1"/>
+      <c r="F267" s="2">
+        <v>82845</v>
+      </c>
+      <c r="G267" s="3">
+        <v>46108</v>
+      </c>
       <c r="H267" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="I267" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="I267" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="J267" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K267" s="1" t="s">
-        <v>539</v>
+        <v>166</v>
       </c>
       <c r="L267" s="4">
         <v>1</v>
       </c>
       <c r="M267" s="4">
-        <v>0</v>
+        <v>54.45</v>
       </c>
       <c r="N267" s="4">
-        <v>0</v>
-      </c>
-      <c r="O267" s="1"/>
-      <c r="P267" s="1"/>
+        <v>54.45</v>
+      </c>
+      <c r="O267" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P267" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="268">
       <c r="A268" s="2">
@@ -14918,19 +14992,19 @@
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
       <c r="H268" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K268" s="1" t="s">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="L268" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M268" s="4">
         <v>0</v>
@@ -14946,7 +15020,7 @@
         <v>2512</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>56</v>
@@ -14996,7 +15070,7 @@
         <v>2512</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>56</v>
@@ -15046,7 +15120,7 @@
         <v>2512</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>56</v>
@@ -15096,7 +15170,7 @@
         <v>2512</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>56</v>
@@ -15110,10 +15184,10 @@
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
       <c r="H272" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>20</v>
@@ -15138,7 +15212,7 @@
         <v>2512</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>56</v>
@@ -15152,10 +15226,10 @@
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
       <c r="H273" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>20</v>
@@ -15180,7 +15254,7 @@
         <v>2512</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>56</v>
@@ -15194,10 +15268,10 @@
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
       <c r="H274" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>20</v>
@@ -15222,7 +15296,7 @@
         <v>2512</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>56</v>
@@ -15236,16 +15310,16 @@
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
       <c r="H275" s="1" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K275" s="1" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L275" s="4">
         <v>3</v>
@@ -15264,7 +15338,7 @@
         <v>2512</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>56</v>
@@ -15278,16 +15352,16 @@
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
       <c r="H276" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="I276" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="J276" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K276" s="1" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L276" s="4">
         <v>2</v>
@@ -15306,7 +15380,7 @@
         <v>2512</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>56</v>
@@ -15348,7 +15422,7 @@
         <v>2512</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>56</v>
@@ -15362,16 +15436,16 @@
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
       <c r="H278" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="I278" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="J278" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K278" s="1" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L278" s="4">
         <v>10</v>
@@ -15404,10 +15478,10 @@
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
       <c r="H279" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="J279" s="1" t="s">
         <v>20</v>
